--- a/database/event/2541/event_2541_evp_summary.xlsx
+++ b/database/event/2541/event_2541_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.317</v>
+        <v>8.615600000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>4.3504</v>
+        <v>5.1225</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5345</v>
+        <v>2.9885</v>
       </c>
       <c r="E2" t="n">
-        <v>7.317</v>
+        <v>8.615600000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6875</v>
+        <v>2.9862</v>
       </c>
       <c r="G2" t="n">
         <v>5.6294</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6875</v>
+        <v>2.9862</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6875</v>
+        <v>2.9862</v>
       </c>
       <c r="J2" t="n">
         <v>5.6294</v>
@@ -529,7 +529,7 @@
         <v>205</v>
       </c>
       <c r="M2" t="n">
-        <v>7.3169</v>
+        <v>8.615600000000001</v>
       </c>
       <c r="N2" t="n">
         <v>248</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.0762</v>
+        <v>7.6307</v>
       </c>
       <c r="C3" t="n">
-        <v>4.2072</v>
+        <v>4.5369</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4373</v>
+        <v>2.5962</v>
       </c>
       <c r="E3" t="n">
-        <v>7.0762</v>
+        <v>7.6307</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5125</v>
+        <v>2.067</v>
       </c>
       <c r="G3" t="n">
         <v>5.5637</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5125</v>
+        <v>2.067</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5125</v>
+        <v>2.067</v>
       </c>
       <c r="J3" t="n">
         <v>5.5637</v>
@@ -575,7 +575,7 @@
         <v>205</v>
       </c>
       <c r="M3" t="n">
-        <v>7.0762</v>
+        <v>7.6307</v>
       </c>
       <c r="N3" t="n">
         <v>248</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.4727</v>
+        <v>6.8812</v>
       </c>
       <c r="C4" t="n">
-        <v>3.8484</v>
+        <v>4.0913</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1935</v>
+        <v>2.2976</v>
       </c>
       <c r="E4" t="n">
-        <v>6.4727</v>
+        <v>6.8812</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8295</v>
+        <v>3.238</v>
       </c>
       <c r="G4" t="n">
         <v>3.6432</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8295</v>
+        <v>3.238</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8427</v>
+        <v>3.2652</v>
       </c>
       <c r="J4" t="n">
         <v>3.6432</v>
@@ -621,7 +621,7 @@
         <v>198</v>
       </c>
       <c r="M4" t="n">
-        <v>6.4859</v>
+        <v>6.9084</v>
       </c>
       <c r="N4" t="n">
         <v>295</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.0702</v>
+        <v>5.069</v>
       </c>
       <c r="C5" t="n">
-        <v>3.0145</v>
+        <v>3.0138</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6269</v>
+        <v>1.5756</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0702</v>
+        <v>5.069</v>
       </c>
       <c r="F5" t="n">
-        <v>0.32</v>
+        <v>0.3188</v>
       </c>
       <c r="G5" t="n">
         <v>4.7501</v>
       </c>
       <c r="H5" t="n">
-        <v>0.32</v>
+        <v>0.3188</v>
       </c>
       <c r="I5" t="n">
         <v>0.3215</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.7613</v>
+        <v>4.758</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8309</v>
+        <v>2.8289</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5021</v>
+        <v>1.4517</v>
       </c>
       <c r="E6" t="n">
-        <v>4.7613</v>
+        <v>4.758</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8878</v>
+        <v>0.8845</v>
       </c>
       <c r="G6" t="n">
         <v>3.8735</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8878</v>
+        <v>0.8845</v>
       </c>
       <c r="I6" t="n">
         <v>0.8919</v>
@@ -722,173 +722,173 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.4527</v>
+        <v>4.6016</v>
       </c>
       <c r="C7" t="n">
-        <v>2.0528</v>
+        <v>2.7359</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9735</v>
+        <v>1.3894</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4527</v>
+        <v>4.6016</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1765</v>
+        <v>2.9508</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2762</v>
+        <v>1.6508</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1765</v>
+        <v>2.9508</v>
       </c>
       <c r="I7" t="n">
-        <v>1.182</v>
+        <v>2.9508</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2762</v>
+        <v>1.6508</v>
       </c>
       <c r="K7" t="n">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="L7" t="n">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4582</v>
+        <v>4.6016</v>
       </c>
       <c r="N7" t="n">
-        <v>212</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.3287</v>
+        <v>3.8533</v>
       </c>
       <c r="C8" t="n">
-        <v>1.9791</v>
+        <v>2.291</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9234</v>
+        <v>1.0912</v>
       </c>
       <c r="E8" t="n">
-        <v>3.3287</v>
+        <v>3.8533</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6779</v>
+        <v>3.3237</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6508</v>
+        <v>0.5296</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6779</v>
+        <v>3.3237</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6779</v>
+        <v>3.3517</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6508</v>
+        <v>0.5296</v>
       </c>
       <c r="K8" t="n">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="L8" t="n">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3287</v>
+        <v>3.8813</v>
       </c>
       <c r="N8" t="n">
-        <v>155</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2036</v>
+        <v>3.7992</v>
       </c>
       <c r="C9" t="n">
-        <v>1.9047</v>
+        <v>2.2588</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8728</v>
+        <v>1.0697</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2036</v>
+        <v>3.7992</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2243</v>
+        <v>2.6519</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9793</v>
+        <v>1.1473</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2243</v>
+        <v>2.6519</v>
       </c>
       <c r="I9" t="n">
-        <v>1.23</v>
+        <v>2.6519</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9793</v>
+        <v>1.1473</v>
       </c>
       <c r="K9" t="n">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="L9" t="n">
-        <v>198</v>
+        <v>54</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2093</v>
+        <v>3.7992</v>
       </c>
       <c r="N9" t="n">
-        <v>295</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.1874</v>
+        <v>3.4483</v>
       </c>
       <c r="C10" t="n">
-        <v>1.8951</v>
+        <v>2.0502</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8663</v>
+        <v>0.9298999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>3.1874</v>
+        <v>3.4483</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6578</v>
+        <v>1.1721</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5296</v>
+        <v>2.2762</v>
       </c>
       <c r="H10" t="n">
-        <v>2.6578</v>
+        <v>1.1721</v>
       </c>
       <c r="I10" t="n">
-        <v>2.6702</v>
+        <v>1.182</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5296</v>
+        <v>2.2762</v>
       </c>
       <c r="K10" t="n">
         <v>88</v>
@@ -897,7 +897,7 @@
         <v>124</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1998</v>
+        <v>3.4582</v>
       </c>
       <c r="N10" t="n">
         <v>212</v>
@@ -906,139 +906,139 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1591</v>
+        <v>3.3045</v>
       </c>
       <c r="C11" t="n">
-        <v>1.8783</v>
+        <v>1.9647</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8548</v>
+        <v>0.8726</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1591</v>
+        <v>3.3045</v>
       </c>
       <c r="F11" t="n">
-        <v>1.318</v>
+        <v>1.8973</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8411</v>
+        <v>1.4072</v>
       </c>
       <c r="H11" t="n">
-        <v>1.318</v>
+        <v>1.8973</v>
       </c>
       <c r="I11" t="n">
-        <v>1.318</v>
+        <v>1.8973</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8411</v>
+        <v>1.4072</v>
       </c>
       <c r="K11" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L11" t="n">
-        <v>205</v>
+        <v>109</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1591</v>
+        <v>3.3045</v>
       </c>
       <c r="N11" t="n">
-        <v>248</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9198</v>
+        <v>3.2097</v>
       </c>
       <c r="C12" t="n">
-        <v>1.736</v>
+        <v>1.9083</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7582</v>
+        <v>0.8348</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9198</v>
+        <v>3.2097</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5126</v>
+        <v>1.3686</v>
       </c>
       <c r="G12" t="n">
-        <v>1.4072</v>
+        <v>1.8411</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5126</v>
+        <v>1.3686</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5126</v>
+        <v>1.3686</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4072</v>
+        <v>1.8411</v>
       </c>
       <c r="K12" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="L12" t="n">
-        <v>109</v>
+        <v>205</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9198</v>
+        <v>3.2097</v>
       </c>
       <c r="N12" t="n">
-        <v>155</v>
+        <v>248</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.767</v>
+        <v>3.1991</v>
       </c>
       <c r="C13" t="n">
-        <v>1.6451</v>
+        <v>1.902</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6964</v>
+        <v>0.8306</v>
       </c>
       <c r="E13" t="n">
-        <v>2.767</v>
+        <v>3.1991</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6197</v>
+        <v>1.2198</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1473</v>
+        <v>1.9793</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6197</v>
+        <v>1.2198</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6197</v>
+        <v>1.23</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1473</v>
+        <v>1.9793</v>
       </c>
       <c r="K13" t="n">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="L13" t="n">
-        <v>54</v>
+        <v>198</v>
       </c>
       <c r="M13" t="n">
-        <v>2.767</v>
+        <v>3.2093</v>
       </c>
       <c r="N13" t="n">
-        <v>108</v>
+        <v>295</v>
       </c>
     </row>
     <row r="14">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3533</v>
+        <v>2.3451</v>
       </c>
       <c r="C14" t="n">
-        <v>1.3992</v>
+        <v>1.3943</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5293</v>
+        <v>0.4904</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3533</v>
+        <v>2.3451</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3598</v>
+        <v>2.3516</v>
       </c>
       <c r="G14" t="n">
         <v>-0.0065</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3598</v>
+        <v>2.3516</v>
       </c>
       <c r="I14" t="n">
-        <v>2.3708</v>
+        <v>2.3714</v>
       </c>
       <c r="J14" t="n">
         <v>-0.0065</v>
@@ -1081,7 +1081,7 @@
         <v>124</v>
       </c>
       <c r="M14" t="n">
-        <v>2.3643</v>
+        <v>2.3649</v>
       </c>
       <c r="N14" t="n">
         <v>212</v>
@@ -1090,35 +1090,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2075</v>
+        <v>2.2474</v>
       </c>
       <c r="C15" t="n">
-        <v>1.3125</v>
+        <v>1.3362</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4704</v>
+        <v>0.4515</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2075</v>
+        <v>2.2474</v>
       </c>
       <c r="F15" t="n">
-        <v>2.506</v>
+        <v>1.8424</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2985</v>
+        <v>0.405</v>
       </c>
       <c r="H15" t="n">
-        <v>2.506</v>
+        <v>1.8424</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5177</v>
+        <v>1.8579</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2985</v>
+        <v>0.405</v>
       </c>
       <c r="K15" t="n">
         <v>128</v>
@@ -1127,7 +1127,7 @@
         <v>70</v>
       </c>
       <c r="M15" t="n">
-        <v>2.2192</v>
+        <v>2.2629</v>
       </c>
       <c r="N15" t="n">
         <v>198</v>
@@ -1136,311 +1136,311 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1301</v>
+        <v>2.2357</v>
       </c>
       <c r="C16" t="n">
-        <v>1.2665</v>
+        <v>1.3292</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4392</v>
+        <v>0.4468</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1301</v>
+        <v>2.2357</v>
       </c>
       <c r="F16" t="n">
-        <v>0.606</v>
+        <v>2.5342</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5241</v>
+        <v>-0.2985</v>
       </c>
       <c r="H16" t="n">
-        <v>0.606</v>
+        <v>2.5342</v>
       </c>
       <c r="I16" t="n">
-        <v>0.606</v>
+        <v>2.5555</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5241</v>
+        <v>-0.2985</v>
       </c>
       <c r="K16" t="n">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="L16" t="n">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1301</v>
+        <v>2.257</v>
       </c>
       <c r="N16" t="n">
-        <v>155</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.0827</v>
+        <v>2.1509</v>
       </c>
       <c r="C17" t="n">
-        <v>1.2383</v>
+        <v>1.2788</v>
       </c>
       <c r="D17" t="n">
-        <v>0.42</v>
+        <v>0.413</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0827</v>
+        <v>2.1509</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7771</v>
+        <v>2.3624</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3056</v>
+        <v>-0.2115</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7771</v>
+        <v>2.3624</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7854</v>
+        <v>2.3624</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3056</v>
+        <v>-0.2115</v>
       </c>
       <c r="K17" t="n">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="L17" t="n">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="M17" t="n">
-        <v>2.091</v>
+        <v>2.1509</v>
       </c>
       <c r="N17" t="n">
-        <v>212</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9788</v>
+        <v>2.1301</v>
       </c>
       <c r="C18" t="n">
-        <v>1.1765</v>
+        <v>1.2665</v>
       </c>
       <c r="D18" t="n">
-        <v>0.378</v>
+        <v>0.4047</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9788</v>
+        <v>2.1301</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5738</v>
+        <v>0.606</v>
       </c>
       <c r="G18" t="n">
-        <v>0.405</v>
+        <v>1.5241</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5738</v>
+        <v>0.606</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5811</v>
+        <v>0.606</v>
       </c>
       <c r="J18" t="n">
-        <v>0.405</v>
+        <v>1.5241</v>
       </c>
       <c r="K18" t="n">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="L18" t="n">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="M18" t="n">
-        <v>1.9861</v>
+        <v>2.1301</v>
       </c>
       <c r="N18" t="n">
-        <v>198</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.9075</v>
+        <v>2.1054</v>
       </c>
       <c r="C19" t="n">
-        <v>1.1341</v>
+        <v>1.2518</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3492</v>
+        <v>0.3949</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9075</v>
+        <v>2.1054</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9075</v>
+        <v>1.719</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.3864</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9075</v>
+        <v>1.719</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9075</v>
+        <v>1.719</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.3864</v>
       </c>
       <c r="K19" t="n">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M19" t="n">
-        <v>1.9075</v>
+        <v>2.1054</v>
       </c>
       <c r="N19" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.682</v>
+        <v>2.1037</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>1.2508</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2581</v>
+        <v>0.3942</v>
       </c>
       <c r="E20" t="n">
-        <v>1.682</v>
+        <v>2.1037</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8759</v>
+        <v>2.1037</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1939</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8759</v>
+        <v>2.1037</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8847</v>
+        <v>2.1037</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1939</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="L20" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.6908</v>
+        <v>2.1037</v>
       </c>
       <c r="N20" t="n">
-        <v>198</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.5453</v>
+        <v>2.0761</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9188</v>
+        <v>1.2344</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2029</v>
+        <v>0.3832</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5453</v>
+        <v>2.0761</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3277</v>
+        <v>1.7705</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7824</v>
+        <v>0.3056</v>
       </c>
       <c r="H21" t="n">
-        <v>2.3277</v>
+        <v>1.7705</v>
       </c>
       <c r="I21" t="n">
-        <v>2.3386</v>
+        <v>1.7854</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7824</v>
+        <v>0.3056</v>
       </c>
       <c r="K21" t="n">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="L21" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="M21" t="n">
-        <v>1.5562</v>
+        <v>2.091</v>
       </c>
       <c r="N21" t="n">
-        <v>198</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.3547</v>
+        <v>1.9796</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8054</v>
+        <v>1.177</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1259</v>
+        <v>0.3448</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3547</v>
+        <v>1.9796</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0474</v>
+        <v>1.5659</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3073</v>
+        <v>0.4137</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0474</v>
+        <v>1.5659</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0474</v>
+        <v>1.5659</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3073</v>
+        <v>0.4137</v>
       </c>
       <c r="K22" t="n">
         <v>50</v>
@@ -1449,7 +1449,7 @@
         <v>69</v>
       </c>
       <c r="M22" t="n">
-        <v>1.3547</v>
+        <v>1.9796</v>
       </c>
       <c r="N22" t="n">
         <v>119</v>
@@ -1458,415 +1458,415 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.3236</v>
+        <v>1.8951</v>
       </c>
       <c r="C23" t="n">
-        <v>0.787</v>
+        <v>1.1267</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1133</v>
+        <v>0.3111</v>
       </c>
       <c r="E23" t="n">
-        <v>1.3236</v>
+        <v>1.8951</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9099</v>
+        <v>2.6775</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4137</v>
+        <v>-0.7824</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9099</v>
+        <v>2.6775</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9099</v>
+        <v>2.7</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4137</v>
+        <v>-0.7824</v>
       </c>
       <c r="K23" t="n">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="L23" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M23" t="n">
-        <v>1.3236</v>
+        <v>1.9176</v>
       </c>
       <c r="N23" t="n">
-        <v>119</v>
+        <v>198</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.3231</v>
+        <v>1.8804</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7867</v>
+        <v>1.118</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1131</v>
+        <v>0.3052</v>
       </c>
       <c r="E24" t="n">
-        <v>1.3231</v>
+        <v>1.8804</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5346</v>
+        <v>1.8804</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2115</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.5346</v>
+        <v>1.8804</v>
       </c>
       <c r="I24" t="n">
-        <v>1.5346</v>
+        <v>1.8804</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2115</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="L24" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.3231</v>
+        <v>1.8804</v>
       </c>
       <c r="N24" t="n">
-        <v>108</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.3129</v>
+        <v>1.675</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7806</v>
+        <v>0.9959</v>
       </c>
       <c r="D25" t="n">
-        <v>0.109</v>
+        <v>0.2234</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3129</v>
+        <v>1.675</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5858</v>
+        <v>1.8689</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7271</v>
+        <v>-0.1939</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5858</v>
+        <v>1.8689</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5858</v>
+        <v>1.8847</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7271</v>
+        <v>-0.1939</v>
       </c>
       <c r="K25" t="n">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="L25" t="n">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="M25" t="n">
-        <v>1.3129</v>
+        <v>1.6908</v>
       </c>
       <c r="N25" t="n">
-        <v>155</v>
+        <v>198</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.2589</v>
+        <v>1.6221</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7485000000000001</v>
+        <v>0.9644</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0872</v>
+        <v>0.2023</v>
       </c>
       <c r="E26" t="n">
-        <v>1.2589</v>
+        <v>1.6221</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.895</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3864</v>
+        <v>0.7271</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.895</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.895</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3864</v>
+        <v>0.7271</v>
       </c>
       <c r="K26" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L26" t="n">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="M26" t="n">
-        <v>1.2589</v>
+        <v>1.6221</v>
       </c>
       <c r="N26" t="n">
-        <v>119</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.1952</v>
+        <v>1.4397</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7106</v>
+        <v>0.856</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0615</v>
+        <v>0.1297</v>
       </c>
       <c r="E27" t="n">
-        <v>1.1952</v>
+        <v>1.4397</v>
       </c>
       <c r="F27" t="n">
-        <v>1.1862</v>
+        <v>1.1324</v>
       </c>
       <c r="G27" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.3073</v>
       </c>
       <c r="H27" t="n">
-        <v>1.1862</v>
+        <v>1.1324</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1862</v>
+        <v>1.1324</v>
       </c>
       <c r="J27" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.3073</v>
       </c>
       <c r="K27" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L27" t="n">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="M27" t="n">
-        <v>1.1952</v>
+        <v>1.4397</v>
       </c>
       <c r="N27" t="n">
-        <v>155</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.0046</v>
+        <v>1.3468</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.8007</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0155</v>
+        <v>0.0927</v>
       </c>
       <c r="E28" t="n">
-        <v>1.0046</v>
+        <v>1.3468</v>
       </c>
       <c r="F28" t="n">
-        <v>1.0046</v>
+        <v>1.3378</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>1.0046</v>
+        <v>1.3378</v>
       </c>
       <c r="I28" t="n">
-        <v>1.0046</v>
+        <v>1.3378</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="M28" t="n">
-        <v>1.0046</v>
+        <v>1.3468</v>
       </c>
       <c r="N28" t="n">
-        <v>121</v>
+        <v>155</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9674</v>
+        <v>1.3306</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5752</v>
+        <v>0.7911</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0306</v>
+        <v>0.0862</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9674</v>
+        <v>1.3306</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9674</v>
+        <v>1.8378</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.5072</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9674</v>
+        <v>1.8378</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9674</v>
+        <v>1.8378</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.5072</v>
       </c>
       <c r="K29" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9674</v>
+        <v>1.3306</v>
       </c>
       <c r="N29" t="n">
-        <v>53</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9604</v>
+        <v>1.0394</v>
       </c>
       <c r="C30" t="n">
-        <v>0.571</v>
+        <v>0.618</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0334</v>
+        <v>-0.0298</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9604</v>
+        <v>1.0394</v>
       </c>
       <c r="F30" t="n">
-        <v>1.5417</v>
+        <v>1.9102</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.5813</v>
+        <v>-0.8708</v>
       </c>
       <c r="H30" t="n">
-        <v>1.5417</v>
+        <v>1.9102</v>
       </c>
       <c r="I30" t="n">
-        <v>1.5489</v>
+        <v>1.9102</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.5813</v>
+        <v>-0.8708</v>
       </c>
       <c r="K30" t="n">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="L30" t="n">
-        <v>45</v>
+        <v>205</v>
       </c>
       <c r="M30" t="n">
-        <v>0.9675999999999999</v>
+        <v>1.0394</v>
       </c>
       <c r="N30" t="n">
-        <v>165</v>
+        <v>248</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9198</v>
+        <v>0.9841</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.5851</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0498</v>
+        <v>-0.0518</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9198</v>
+        <v>0.9841</v>
       </c>
       <c r="F31" t="n">
-        <v>1.427</v>
+        <v>0.9841</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.5072</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.427</v>
+        <v>0.9841</v>
       </c>
       <c r="I31" t="n">
-        <v>1.427</v>
+        <v>0.9841</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.5072</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="L31" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.9198000000000001</v>
+        <v>0.9841</v>
       </c>
       <c r="N31" t="n">
-        <v>119</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8823</v>
+        <v>0.9776</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5246</v>
+        <v>0.5812</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0649</v>
+        <v>-0.0544</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8823</v>
+        <v>0.9776</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7044</v>
+        <v>0.7997</v>
       </c>
       <c r="G32" t="n">
         <v>0.1779</v>
       </c>
       <c r="H32" t="n">
-        <v>0.7044</v>
+        <v>0.7997</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7044</v>
+        <v>0.7997</v>
       </c>
       <c r="J32" t="n">
         <v>0.1779</v>
@@ -1909,7 +1909,7 @@
         <v>54</v>
       </c>
       <c r="M32" t="n">
-        <v>0.8823000000000001</v>
+        <v>0.9776</v>
       </c>
       <c r="N32" t="n">
         <v>108</v>
@@ -1918,81 +1918,81 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.865</v>
+        <v>0.9674</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5143</v>
+        <v>0.5752</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.0585</v>
       </c>
       <c r="E33" t="n">
-        <v>0.865</v>
+        <v>0.9674</v>
       </c>
       <c r="F33" t="n">
-        <v>0.865</v>
+        <v>0.9674</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.865</v>
+        <v>0.9674</v>
       </c>
       <c r="I33" t="n">
-        <v>0.865</v>
+        <v>0.9674</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.865</v>
+        <v>0.9674</v>
       </c>
       <c r="N33" t="n">
-        <v>92</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8417</v>
+        <v>0.9547</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5004</v>
+        <v>0.5676</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0813</v>
+        <v>-0.0636</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8417</v>
+        <v>0.9547</v>
       </c>
       <c r="F34" t="n">
-        <v>1.6214</v>
+        <v>1.536</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.7796999999999999</v>
+        <v>-0.5813</v>
       </c>
       <c r="H34" t="n">
-        <v>1.6214</v>
+        <v>1.536</v>
       </c>
       <c r="I34" t="n">
-        <v>1.6289</v>
+        <v>1.5489</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.7796999999999999</v>
+        <v>-0.5813</v>
       </c>
       <c r="K34" t="n">
         <v>120</v>
@@ -2001,7 +2001,7 @@
         <v>45</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8492000000000001</v>
+        <v>0.9675999999999999</v>
       </c>
       <c r="N34" t="n">
         <v>165</v>
@@ -2010,47 +2010,47 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SicK</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7736</v>
+        <v>0.8986</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4599</v>
+        <v>0.5343</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1088</v>
+        <v>-0.0859</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7736</v>
+        <v>0.8986</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7736</v>
+        <v>1.6783</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.7796999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7736</v>
+        <v>1.6783</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7736</v>
+        <v>1.6924</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.7796999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>53</v>
+        <v>120</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7736</v>
+        <v>0.9127</v>
       </c>
       <c r="N35" t="n">
-        <v>53</v>
+        <v>165</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7684</v>
+        <v>0.8912</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4569</v>
+        <v>0.5299</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1109</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7684</v>
+        <v>0.8912</v>
       </c>
       <c r="F36" t="n">
-        <v>1.0952</v>
+        <v>1.218</v>
       </c>
       <c r="G36" t="n">
         <v>-0.3268</v>
       </c>
       <c r="H36" t="n">
-        <v>1.0952</v>
+        <v>1.218</v>
       </c>
       <c r="I36" t="n">
-        <v>1.0952</v>
+        <v>1.218</v>
       </c>
       <c r="J36" t="n">
         <v>-0.3268</v>
@@ -2093,7 +2093,7 @@
         <v>205</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7684</v>
+        <v>0.8912</v>
       </c>
       <c r="N36" t="n">
         <v>248</v>
@@ -2102,415 +2102,415 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>SicK</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7167</v>
+        <v>0.7736</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4261</v>
+        <v>0.4599</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1318</v>
+        <v>-0.1357</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7167</v>
+        <v>0.7736</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.1763</v>
+        <v>0.7736</v>
       </c>
       <c r="G37" t="n">
-        <v>0.893</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.1763</v>
+        <v>0.7736</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1771</v>
+        <v>0.7736</v>
       </c>
       <c r="J37" t="n">
-        <v>0.893</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="L37" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7159</v>
+        <v>0.7736</v>
       </c>
       <c r="N37" t="n">
-        <v>295</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4085</v>
+        <v>0.7174</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2429</v>
+        <v>0.4265</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2563</v>
+        <v>-0.1581</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4085</v>
+        <v>0.7174</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4085</v>
+        <v>-0.1756</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>0.893</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4085</v>
+        <v>-0.1756</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4085</v>
+        <v>-0.1771</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>0.893</v>
       </c>
       <c r="K38" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="M38" t="n">
-        <v>0.4085</v>
+        <v>0.7159</v>
       </c>
       <c r="N38" t="n">
-        <v>42</v>
+        <v>295</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>pyth</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.3693</v>
+        <v>0.5099</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2196</v>
+        <v>0.3032</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2722</v>
+        <v>-0.2408</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3693</v>
+        <v>0.5099</v>
       </c>
       <c r="F39" t="n">
-        <v>1.2401</v>
+        <v>1.5099</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.8708</v>
+        <v>-1</v>
       </c>
       <c r="H39" t="n">
-        <v>1.2401</v>
+        <v>1.5099</v>
       </c>
       <c r="I39" t="n">
-        <v>1.2401</v>
+        <v>1.5226</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.8708</v>
+        <v>-1</v>
       </c>
       <c r="K39" t="n">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="L39" t="n">
-        <v>205</v>
+        <v>45</v>
       </c>
       <c r="M39" t="n">
-        <v>0.3693</v>
+        <v>0.5226</v>
       </c>
       <c r="N39" t="n">
-        <v>248</v>
+        <v>165</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>USTILO</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.3646</v>
+        <v>0.4085</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2168</v>
+        <v>0.2429</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2741</v>
+        <v>-0.2812</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3646</v>
+        <v>0.4085</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3646</v>
+        <v>0.4085</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3646</v>
+        <v>0.4085</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3646</v>
+        <v>0.4085</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.3646</v>
+        <v>0.4085</v>
       </c>
       <c r="N40" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>USTILO</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.2737</v>
+        <v>0.3646</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1627</v>
+        <v>0.2168</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3108</v>
+        <v>-0.2987</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2737</v>
+        <v>0.3646</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2737</v>
+        <v>0.3646</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2737</v>
+        <v>0.3646</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2737</v>
+        <v>0.3646</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.2737</v>
+        <v>0.3646</v>
       </c>
       <c r="N41" t="n">
-        <v>134</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.1355</v>
+        <v>0.3219</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0806</v>
+        <v>0.1914</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3666</v>
+        <v>-0.3157</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1355</v>
+        <v>0.3219</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4852</v>
+        <v>0.3219</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.3497</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4852</v>
+        <v>0.3219</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4875</v>
+        <v>0.3219</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.3497</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="L42" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1378</v>
+        <v>0.3219</v>
       </c>
       <c r="N42" t="n">
-        <v>212</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>pyth</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.2737</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0586</v>
+        <v>0.1627</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3815</v>
+        <v>-0.3349</v>
       </c>
       <c r="E43" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.2737</v>
       </c>
       <c r="F43" t="n">
-        <v>1.0986</v>
+        <v>0.2737</v>
       </c>
       <c r="G43" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.0986</v>
+        <v>0.2737</v>
       </c>
       <c r="I43" t="n">
-        <v>1.1038</v>
+        <v>0.2737</v>
       </c>
       <c r="J43" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="L43" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.1037999999999999</v>
+        <v>0.2737</v>
       </c>
       <c r="N43" t="n">
-        <v>165</v>
+        <v>134</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.0522</v>
+        <v>0.2378</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.031</v>
+        <v>0.1414</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4424</v>
+        <v>-0.3492</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.0522</v>
+        <v>0.2378</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.0522</v>
+        <v>0.9184</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>-0.6806</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.0522</v>
+        <v>0.9184</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0522</v>
+        <v>0.9262</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>-0.6806</v>
       </c>
       <c r="K44" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.0522</v>
+        <v>0.2456</v>
       </c>
       <c r="N44" t="n">
-        <v>121</v>
+        <v>165</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yam</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.0781</v>
+        <v>0.1337</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.0464</v>
+        <v>0.0795</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4529</v>
+        <v>-0.3906</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.0781</v>
+        <v>0.1337</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.0781</v>
+        <v>0.4834</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>-0.3497</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.0781</v>
+        <v>0.4834</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0781</v>
+        <v>0.4875</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>-0.3497</v>
       </c>
       <c r="K45" t="n">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.0781</v>
+        <v>0.1378</v>
       </c>
       <c r="N45" t="n">
-        <v>52</v>
+        <v>212</v>
       </c>
     </row>
     <row r="46">
@@ -2520,28 +2520,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.1219</v>
+        <v>0.0993</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.0725</v>
+        <v>0.059</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4706</v>
+        <v>-0.4043</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.1219</v>
+        <v>0.0993</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.1219</v>
+        <v>0.0993</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.1219</v>
+        <v>0.0993</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1219</v>
+        <v>0.0993</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.1219</v>
+        <v>0.0993</v>
       </c>
       <c r="N46" t="n">
         <v>93</v>
@@ -2562,262 +2562,262 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.1417</v>
+        <v>-0.0522</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.0842</v>
+        <v>-0.031</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4786</v>
+        <v>-0.4647</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.1417</v>
+        <v>-0.0522</v>
       </c>
       <c r="F47" t="n">
-        <v>0.5389</v>
+        <v>-0.0522</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.6806</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.5389</v>
+        <v>-0.0522</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5414</v>
+        <v>-0.0522</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.6806</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L47" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.1392</v>
+        <v>-0.0522</v>
       </c>
       <c r="N47" t="n">
-        <v>165</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>yam</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.2536</v>
+        <v>-0.0781</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.1508</v>
+        <v>-0.0464</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.5238</v>
+        <v>-0.475</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.2536</v>
+        <v>-0.0781</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7464</v>
+        <v>-0.0781</v>
       </c>
       <c r="G48" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.7464</v>
+        <v>-0.0781</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7464</v>
+        <v>-0.0781</v>
       </c>
       <c r="J48" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L48" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.2536</v>
+        <v>-0.0781</v>
       </c>
       <c r="N48" t="n">
-        <v>119</v>
+        <v>52</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>atter</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.2561</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.1523</v>
+        <v>-0.048</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.5248</v>
+        <v>-0.4761</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.2561</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.2561</v>
+        <v>0.5999</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>-0.6806</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.2561</v>
+        <v>0.5999</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2561</v>
+        <v>0.6049</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>-0.6806</v>
       </c>
       <c r="K49" t="n">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.2561</v>
+        <v>-0.07569999999999999</v>
       </c>
       <c r="N49" t="n">
-        <v>52</v>
+        <v>165</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.2573</v>
+        <v>-0.2536</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.153</v>
+        <v>-0.1508</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5253</v>
+        <v>-0.5449000000000001</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.2573</v>
+        <v>-0.2536</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.2573</v>
+        <v>0.7464</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.2573</v>
+        <v>0.7464</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2573</v>
+        <v>0.7464</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K50" t="n">
-        <v>134</v>
+        <v>50</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.2573</v>
+        <v>-0.2536</v>
       </c>
       <c r="N50" t="n">
-        <v>134</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HZ</t>
+          <t>atter</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.3135</v>
+        <v>-0.2561</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.1864</v>
+        <v>-0.1523</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.548</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.3135</v>
+        <v>-0.2561</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.3135</v>
+        <v>-0.2561</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.3135</v>
+        <v>-0.2561</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3135</v>
+        <v>-0.2561</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.3135</v>
+        <v>-0.2561</v>
       </c>
       <c r="N51" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.3413</v>
+        <v>-0.2573</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.2029</v>
+        <v>-0.153</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5592</v>
+        <v>-0.5464</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.3413</v>
+        <v>-0.2573</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.3413</v>
+        <v>-0.2573</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.3413</v>
+        <v>-0.2573</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.3413</v>
+        <v>-0.2573</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.3413</v>
+        <v>-0.2573</v>
       </c>
       <c r="N52" t="n">
         <v>134</v>
@@ -2838,262 +2838,262 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>HZ</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.3456</v>
+        <v>-0.3135</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.2055</v>
+        <v>-0.1864</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.5688</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.3456</v>
+        <v>-0.3135</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.3456</v>
+        <v>-0.3135</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.3456</v>
+        <v>-0.3135</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.3456</v>
+        <v>-0.3135</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>134</v>
+        <v>42</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.3456</v>
+        <v>-0.3135</v>
       </c>
       <c r="N53" t="n">
-        <v>134</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ANDROID</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.3803</v>
+        <v>-0.3413</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.2261</v>
+        <v>-0.2029</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.575</v>
+        <v>-0.5799</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.3803</v>
+        <v>-0.3413</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.3803</v>
+        <v>-0.3413</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.3803</v>
+        <v>-0.3413</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3803</v>
+        <v>-0.3413</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.3803</v>
+        <v>-0.3413</v>
       </c>
       <c r="N54" t="n">
-        <v>41</v>
+        <v>134</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.4678</v>
+        <v>-0.3456</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.2781</v>
+        <v>-0.2055</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6103</v>
+        <v>-0.5816</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.4678</v>
+        <v>-0.3456</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.4678</v>
+        <v>-0.3456</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.4678</v>
+        <v>-0.3456</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4678</v>
+        <v>-0.3456</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>92</v>
+        <v>134</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.4678</v>
+        <v>-0.3456</v>
       </c>
       <c r="N55" t="n">
-        <v>92</v>
+        <v>134</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>ANDROID</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.4888</v>
+        <v>-0.3803</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.2906</v>
+        <v>-0.2261</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6188</v>
+        <v>-0.5954</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.4888</v>
+        <v>-0.3803</v>
       </c>
       <c r="F56" t="n">
-        <v>0.5112</v>
+        <v>-0.3803</v>
       </c>
       <c r="G56" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.5112</v>
+        <v>-0.3803</v>
       </c>
       <c r="I56" t="n">
-        <v>0.5135999999999999</v>
+        <v>-0.3803</v>
       </c>
       <c r="J56" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>128</v>
+        <v>41</v>
       </c>
       <c r="L56" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.4864000000000001</v>
+        <v>-0.3803</v>
       </c>
       <c r="N56" t="n">
-        <v>198</v>
+        <v>41</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.543</v>
+        <v>-0.4907</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.3228</v>
+        <v>-0.2917</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6407</v>
+        <v>-0.6394</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.543</v>
+        <v>-0.4907</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.543</v>
+        <v>0.5093</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.543</v>
+        <v>0.5093</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.543</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K57" t="n">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.543</v>
+        <v>-0.4864000000000001</v>
       </c>
       <c r="N57" t="n">
-        <v>93</v>
+        <v>198</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.5593</v>
+        <v>-0.543</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.3325</v>
+        <v>-0.3228</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6473</v>
+        <v>-0.6602</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.5593</v>
+        <v>-0.543</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.5593</v>
+        <v>-0.543</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.5593</v>
+        <v>-0.543</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.5593</v>
+        <v>-0.543</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.5593</v>
+        <v>-0.543</v>
       </c>
       <c r="N58" t="n">
         <v>93</v>
@@ -3114,231 +3114,231 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.5666</v>
+        <v>-0.5593</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.3369</v>
+        <v>-0.3325</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6503</v>
+        <v>-0.6667</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.5666</v>
+        <v>-0.5593</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.5666</v>
+        <v>-0.5593</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.5666</v>
+        <v>-0.5593</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.5666</v>
+        <v>-0.5593</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.5666</v>
+        <v>-0.5593</v>
       </c>
       <c r="N59" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ShahZaM</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.5774</v>
+        <v>-0.5666</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.3433</v>
+        <v>-0.3369</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6546</v>
+        <v>-0.6696</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.5774</v>
+        <v>-0.5666</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.5774</v>
+        <v>-0.5666</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.5774</v>
+        <v>-0.5666</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5774</v>
+        <v>-0.5666</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.5774</v>
+        <v>-0.5666</v>
       </c>
       <c r="N60" t="n">
-        <v>53</v>
+        <v>92</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>ShahZaM</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.5774</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.3557</v>
+        <v>-0.3433</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6631</v>
+        <v>-0.6739000000000001</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.5774</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.5774</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.5774</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.5774</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.5774</v>
       </c>
       <c r="N61" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>dephh</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.5991</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.3562</v>
+        <v>-0.3557</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6634</v>
+        <v>-0.6823</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.5991</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.5991</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.5991</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.5991</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.5991</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="N62" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>dephh</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.6129</v>
+        <v>-0.5991</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.3644</v>
+        <v>-0.3562</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.669</v>
+        <v>-0.6826</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.6129</v>
+        <v>-0.5991</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0677</v>
+        <v>-0.5991</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.6806</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0677</v>
+        <v>-0.5991</v>
       </c>
       <c r="I63" t="n">
-        <v>0.068</v>
+        <v>-0.5991</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.6806</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>120</v>
+        <v>41</v>
       </c>
       <c r="L63" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.6126</v>
+        <v>-0.5991</v>
       </c>
       <c r="N63" t="n">
-        <v>165</v>
+        <v>41</v>
       </c>
     </row>
     <row r="64">
@@ -3354,7 +3354,7 @@
         <v>-0.3739</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6754</v>
+        <v>-0.6944</v>
       </c>
       <c r="E64" t="n">
         <v>-0.6288</v>
@@ -3400,7 +3400,7 @@
         <v>-0.4383</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7192</v>
+        <v>-0.7376</v>
       </c>
       <c r="E65" t="n">
         <v>-0.7372</v>
@@ -3446,7 +3446,7 @@
         <v>-0.4584</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7328</v>
+        <v>-0.7511</v>
       </c>
       <c r="E66" t="n">
         <v>-0.771</v>
@@ -3482,170 +3482,170 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>desi</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.8469</v>
+        <v>-0.7986</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.5034999999999999</v>
+        <v>-0.4748</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7635</v>
+        <v>-0.7621</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.8469</v>
+        <v>-0.7986</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.8469</v>
+        <v>-0.7986</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.8469</v>
+        <v>-0.7986</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.8469</v>
+        <v>-0.7986</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.8469</v>
+        <v>-0.7986</v>
       </c>
       <c r="N67" t="n">
-        <v>41</v>
+        <v>93</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>desi</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.8786</v>
+        <v>-0.8469</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.5224</v>
+        <v>-0.5034999999999999</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7763</v>
+        <v>-0.7813</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.8786</v>
+        <v>-0.8469</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.8786</v>
+        <v>-0.8469</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.8786</v>
+        <v>-0.8469</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.8786</v>
+        <v>-0.8469</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.8786</v>
+        <v>-0.8469</v>
       </c>
       <c r="N68" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.8786</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.5541</v>
+        <v>-0.5224</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.7939000000000001</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.8786</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.8786</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.8786</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.8786</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>121</v>
+        <v>42</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.8786</v>
       </c>
       <c r="N69" t="n">
-        <v>121</v>
+        <v>42</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.9637</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.573</v>
+        <v>-0.5541</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8107</v>
+        <v>-0.8152</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.9637</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.9637</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.9637</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.9637</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.9637</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="N70" t="n">
         <v>121</v>
@@ -3666,93 +3666,93 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.9675</v>
+        <v>-0.9637</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.5752</v>
+        <v>-0.573</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8122</v>
+        <v>-0.8278</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.9675</v>
+        <v>-0.9637</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.9675</v>
+        <v>-0.9637</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.9675</v>
+        <v>-0.9637</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.9675</v>
+        <v>-0.9637</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.9675</v>
+        <v>-0.9637</v>
       </c>
       <c r="N71" t="n">
-        <v>92</v>
+        <v>121</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.9886</v>
+        <v>-0.9675</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.5878</v>
+        <v>-0.5752</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8207</v>
+        <v>-0.8294</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.9886</v>
+        <v>-0.9675</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.9886</v>
+        <v>-0.9675</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.9886</v>
+        <v>-0.9675</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.9886</v>
+        <v>-0.9675</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.9886</v>
+        <v>-0.9675</v>
       </c>
       <c r="N72" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="73">
@@ -3768,7 +3768,7 @@
         <v>-0.5986</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.8280999999999999</v>
+        <v>-0.845</v>
       </c>
       <c r="E73" t="n">
         <v>-1.0068</v>
@@ -3814,7 +3814,7 @@
         <v>-0.6122</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.8373</v>
+        <v>-0.8541</v>
       </c>
       <c r="E74" t="n">
         <v>-1.0296</v>
@@ -3860,7 +3860,7 @@
         <v>-0.632</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.8508</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="E75" t="n">
         <v>-1.0629</v>
@@ -3906,7 +3906,7 @@
         <v>-0.6624</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.8714</v>
+        <v>-0.8878</v>
       </c>
       <c r="E76" t="n">
         <v>-1.1141</v>
@@ -3952,7 +3952,7 @@
         <v>-0.8036</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.9674</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="E77" t="n">
         <v>-1.3516</v>
@@ -3998,7 +3998,7 @@
         <v>-0.8371</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.9901</v>
+        <v>-1.0048</v>
       </c>
       <c r="E78" t="n">
         <v>-1.4079</v>
@@ -4044,7 +4044,7 @@
         <v>-0.8388</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.9913</v>
+        <v>-1.006</v>
       </c>
       <c r="E79" t="n">
         <v>-1.4108</v>
@@ -4090,7 +4090,7 @@
         <v>-0.9367</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.0578</v>
+        <v>-1.0716</v>
       </c>
       <c r="E80" t="n">
         <v>-1.5755</v>
@@ -4136,7 +4136,7 @@
         <v>-1.1731</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.2185</v>
+        <v>-1.23</v>
       </c>
       <c r="E81" t="n">
         <v>-1.9731</v>

--- a/database/event/2541/event_2541_evp_summary.xlsx
+++ b/database/event/2541/event_2541_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.615600000000001</v>
+        <v>7.6007</v>
       </c>
       <c r="C2" t="n">
-        <v>5.1225</v>
+        <v>4.519</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9885</v>
+        <v>2.7933</v>
       </c>
       <c r="E2" t="n">
-        <v>8.615600000000001</v>
+        <v>7.6007</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9862</v>
+        <v>2.6903</v>
       </c>
       <c r="G2" t="n">
-        <v>5.6294</v>
+        <v>4.9105</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9862</v>
+        <v>2.6903</v>
       </c>
       <c r="I2" t="n">
-        <v>2.9862</v>
+        <v>2.6903</v>
       </c>
       <c r="J2" t="n">
-        <v>5.6294</v>
+        <v>4.9105</v>
       </c>
       <c r="K2" t="n">
         <v>43</v>
@@ -529,7 +529,7 @@
         <v>205</v>
       </c>
       <c r="M2" t="n">
-        <v>8.615600000000001</v>
+        <v>7.6008</v>
       </c>
       <c r="N2" t="n">
         <v>248</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.6307</v>
+        <v>6.5446</v>
       </c>
       <c r="C3" t="n">
-        <v>4.5369</v>
+        <v>3.8911</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5962</v>
+        <v>2.3165</v>
       </c>
       <c r="E3" t="n">
-        <v>7.6307</v>
+        <v>6.5446</v>
       </c>
       <c r="F3" t="n">
-        <v>2.067</v>
+        <v>2.0653</v>
       </c>
       <c r="G3" t="n">
-        <v>5.5637</v>
+        <v>4.4793</v>
       </c>
       <c r="H3" t="n">
-        <v>2.067</v>
+        <v>2.0653</v>
       </c>
       <c r="I3" t="n">
-        <v>2.067</v>
+        <v>2.0653</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5637</v>
+        <v>4.4793</v>
       </c>
       <c r="K3" t="n">
         <v>43</v>
@@ -575,7 +575,7 @@
         <v>205</v>
       </c>
       <c r="M3" t="n">
-        <v>7.6307</v>
+        <v>6.544600000000001</v>
       </c>
       <c r="N3" t="n">
         <v>248</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.8812</v>
+        <v>6.1762</v>
       </c>
       <c r="C4" t="n">
-        <v>4.0913</v>
+        <v>3.6721</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2976</v>
+        <v>2.1502</v>
       </c>
       <c r="E4" t="n">
-        <v>6.8812</v>
+        <v>6.1762</v>
       </c>
       <c r="F4" t="n">
-        <v>3.238</v>
+        <v>3.1621</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6432</v>
+        <v>3.0141</v>
       </c>
       <c r="H4" t="n">
-        <v>3.238</v>
+        <v>3.5836</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2652</v>
+        <v>3.731</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6432</v>
+        <v>3.0141</v>
       </c>
       <c r="K4" t="n">
         <v>97</v>
@@ -621,7 +621,7 @@
         <v>198</v>
       </c>
       <c r="M4" t="n">
-        <v>6.9084</v>
+        <v>6.7451</v>
       </c>
       <c r="N4" t="n">
         <v>295</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.069</v>
+        <v>4.795</v>
       </c>
       <c r="C5" t="n">
-        <v>3.0138</v>
+        <v>2.8509</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5756</v>
+        <v>1.5267</v>
       </c>
       <c r="E5" t="n">
-        <v>5.069</v>
+        <v>4.795</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3188</v>
+        <v>0.6228</v>
       </c>
       <c r="G5" t="n">
-        <v>4.7501</v>
+        <v>4.1722</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3188</v>
+        <v>0.6228</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3215</v>
+        <v>0.6484</v>
       </c>
       <c r="J5" t="n">
-        <v>4.7501</v>
+        <v>4.1722</v>
       </c>
       <c r="K5" t="n">
         <v>97</v>
@@ -667,7 +667,7 @@
         <v>198</v>
       </c>
       <c r="M5" t="n">
-        <v>5.0716</v>
+        <v>4.8206</v>
       </c>
       <c r="N5" t="n">
         <v>295</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.758</v>
+        <v>4.6488</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8289</v>
+        <v>2.764</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4517</v>
+        <v>1.4607</v>
       </c>
       <c r="E6" t="n">
-        <v>4.758</v>
+        <v>4.6488</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8845</v>
+        <v>1.2003</v>
       </c>
       <c r="G6" t="n">
-        <v>3.8735</v>
+        <v>3.4485</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8845</v>
+        <v>1.2003</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8919</v>
+        <v>1.2497</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8735</v>
+        <v>3.4485</v>
       </c>
       <c r="K6" t="n">
         <v>97</v>
@@ -713,7 +713,7 @@
         <v>198</v>
       </c>
       <c r="M6" t="n">
-        <v>4.7654</v>
+        <v>4.6982</v>
       </c>
       <c r="N6" t="n">
         <v>295</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.6016</v>
+        <v>4.0824</v>
       </c>
       <c r="C7" t="n">
-        <v>2.7359</v>
+        <v>2.4272</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3894</v>
+        <v>1.205</v>
       </c>
       <c r="E7" t="n">
-        <v>4.6016</v>
+        <v>4.0824</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9508</v>
+        <v>2.7343</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6508</v>
+        <v>1.3481</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9508</v>
+        <v>2.7343</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9508</v>
+        <v>2.7343</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6508</v>
+        <v>1.3481</v>
       </c>
       <c r="K7" t="n">
         <v>46</v>
@@ -759,7 +759,7 @@
         <v>109</v>
       </c>
       <c r="M7" t="n">
-        <v>4.6016</v>
+        <v>4.0824</v>
       </c>
       <c r="N7" t="n">
         <v>155</v>
@@ -768,47 +768,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8533</v>
+        <v>3.9983</v>
       </c>
       <c r="C8" t="n">
-        <v>2.291</v>
+        <v>2.3772</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0912</v>
+        <v>1.167</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8533</v>
+        <v>3.9983</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3237</v>
+        <v>2.0633</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5296</v>
+        <v>1.935</v>
       </c>
       <c r="H8" t="n">
-        <v>3.3237</v>
+        <v>2.0633</v>
       </c>
       <c r="I8" t="n">
-        <v>3.3517</v>
+        <v>2.1482</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5296</v>
+        <v>1.935</v>
       </c>
       <c r="K8" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="L8" t="n">
-        <v>124</v>
+        <v>198</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8813</v>
+        <v>4.0832</v>
       </c>
       <c r="N8" t="n">
-        <v>212</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7992</v>
+        <v>3.5009</v>
       </c>
       <c r="C9" t="n">
-        <v>2.2588</v>
+        <v>2.0815</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0697</v>
+        <v>0.9425</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7992</v>
+        <v>3.5009</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6519</v>
+        <v>2.439</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1473</v>
+        <v>1.0619</v>
       </c>
       <c r="H9" t="n">
-        <v>2.6519</v>
+        <v>2.439</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6519</v>
+        <v>2.439</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1473</v>
+        <v>1.0619</v>
       </c>
       <c r="K9" t="n">
         <v>54</v>
@@ -851,7 +851,7 @@
         <v>54</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7992</v>
+        <v>3.5009</v>
       </c>
       <c r="N9" t="n">
         <v>108</v>
@@ -860,185 +860,185 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4483</v>
+        <v>3.4103</v>
       </c>
       <c r="C10" t="n">
-        <v>2.0502</v>
+        <v>2.0276</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9298999999999999</v>
+        <v>0.9016</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4483</v>
+        <v>3.4103</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1721</v>
+        <v>1.9666</v>
       </c>
       <c r="G10" t="n">
-        <v>2.2762</v>
+        <v>1.4437</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1721</v>
+        <v>1.9666</v>
       </c>
       <c r="I10" t="n">
-        <v>1.182</v>
+        <v>1.9666</v>
       </c>
       <c r="J10" t="n">
-        <v>2.2762</v>
+        <v>1.4437</v>
       </c>
       <c r="K10" t="n">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="L10" t="n">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4582</v>
+        <v>3.4103</v>
       </c>
       <c r="N10" t="n">
-        <v>212</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.3045</v>
+        <v>3.3928</v>
       </c>
       <c r="C11" t="n">
-        <v>1.9647</v>
+        <v>2.0172</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8726</v>
+        <v>0.8937</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3045</v>
+        <v>3.3928</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8973</v>
+        <v>1.5353</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4072</v>
+        <v>1.8575</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8973</v>
+        <v>1.5353</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8973</v>
+        <v>1.5984</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4072</v>
+        <v>1.8575</v>
       </c>
       <c r="K11" t="n">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="L11" t="n">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3045</v>
+        <v>3.4559</v>
       </c>
       <c r="N11" t="n">
-        <v>155</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.2097</v>
+        <v>3.3605</v>
       </c>
       <c r="C12" t="n">
-        <v>1.9083</v>
+        <v>1.998</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8348</v>
+        <v>0.8791</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2097</v>
+        <v>3.3605</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3686</v>
+        <v>3.0228</v>
       </c>
       <c r="G12" t="n">
-        <v>1.8411</v>
+        <v>0.3377</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3686</v>
+        <v>3.2779</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3686</v>
+        <v>3.4127</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8411</v>
+        <v>0.3377</v>
       </c>
       <c r="K12" t="n">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="L12" t="n">
-        <v>205</v>
+        <v>124</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2097</v>
+        <v>3.7504</v>
       </c>
       <c r="N12" t="n">
-        <v>248</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.1991</v>
+        <v>3.3048</v>
       </c>
       <c r="C13" t="n">
-        <v>1.902</v>
+        <v>1.9649</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8306</v>
+        <v>0.8539</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1991</v>
+        <v>3.3048</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2198</v>
+        <v>1.6012</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9793</v>
+        <v>1.7036</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2198</v>
+        <v>1.6012</v>
       </c>
       <c r="I13" t="n">
-        <v>1.23</v>
+        <v>1.6012</v>
       </c>
       <c r="J13" t="n">
-        <v>1.9793</v>
+        <v>1.7036</v>
       </c>
       <c r="K13" t="n">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="L13" t="n">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2093</v>
+        <v>3.3048</v>
       </c>
       <c r="N13" t="n">
-        <v>295</v>
+        <v>248</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3451</v>
+        <v>3.2291</v>
       </c>
       <c r="C14" t="n">
-        <v>1.3943</v>
+        <v>1.9199</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4904</v>
+        <v>0.8198</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3451</v>
+        <v>3.2291</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3516</v>
+        <v>3.015</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0065</v>
+        <v>0.2141</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3516</v>
+        <v>3.2606</v>
       </c>
       <c r="I14" t="n">
-        <v>2.3714</v>
+        <v>3.3947</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0065</v>
+        <v>0.2141</v>
       </c>
       <c r="K14" t="n">
         <v>88</v>
@@ -1081,7 +1081,7 @@
         <v>124</v>
       </c>
       <c r="M14" t="n">
-        <v>2.3649</v>
+        <v>3.6088</v>
       </c>
       <c r="N14" t="n">
         <v>212</v>
@@ -1090,47 +1090,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2474</v>
+        <v>3.007</v>
       </c>
       <c r="C15" t="n">
-        <v>1.3362</v>
+        <v>1.7878</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4515</v>
+        <v>0.7195</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2474</v>
+        <v>3.007</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8424</v>
+        <v>2.6078</v>
       </c>
       <c r="G15" t="n">
-        <v>0.405</v>
+        <v>0.3992</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8424</v>
+        <v>2.6078</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8579</v>
+        <v>2.7151</v>
       </c>
       <c r="J15" t="n">
-        <v>0.405</v>
+        <v>0.3992</v>
       </c>
       <c r="K15" t="n">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="L15" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="M15" t="n">
-        <v>2.2629</v>
+        <v>3.1143</v>
       </c>
       <c r="N15" t="n">
-        <v>198</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2357</v>
+        <v>2.3373</v>
       </c>
       <c r="C16" t="n">
-        <v>1.3292</v>
+        <v>1.3897</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4468</v>
+        <v>0.4172</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2357</v>
+        <v>2.3373</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5342</v>
+        <v>2.5567</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2985</v>
+        <v>-0.2194</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5342</v>
+        <v>2.5567</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5555</v>
+        <v>2.6618</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2985</v>
+        <v>-0.2194</v>
       </c>
       <c r="K16" t="n">
         <v>128</v>
@@ -1173,7 +1173,7 @@
         <v>70</v>
       </c>
       <c r="M16" t="n">
-        <v>2.257</v>
+        <v>2.4424</v>
       </c>
       <c r="N16" t="n">
         <v>198</v>
@@ -1182,461 +1182,461 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1509</v>
+        <v>2.285</v>
       </c>
       <c r="C17" t="n">
-        <v>1.2788</v>
+        <v>1.3586</v>
       </c>
       <c r="D17" t="n">
-        <v>0.413</v>
+        <v>0.3935</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1509</v>
+        <v>2.285</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3624</v>
+        <v>1.8943</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2115</v>
+        <v>0.3907</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3624</v>
+        <v>1.8943</v>
       </c>
       <c r="I17" t="n">
-        <v>2.3624</v>
+        <v>1.9722</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2115</v>
+        <v>0.3907</v>
       </c>
       <c r="K17" t="n">
-        <v>54</v>
+        <v>128</v>
       </c>
       <c r="L17" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="M17" t="n">
-        <v>2.1509</v>
+        <v>2.3629</v>
       </c>
       <c r="N17" t="n">
-        <v>108</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.1301</v>
+        <v>2.2758</v>
       </c>
       <c r="C18" t="n">
-        <v>1.2665</v>
+        <v>1.3531</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4047</v>
+        <v>0.3894</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1301</v>
+        <v>2.2758</v>
       </c>
       <c r="F18" t="n">
-        <v>0.606</v>
+        <v>2.7912</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5241</v>
+        <v>-0.5154</v>
       </c>
       <c r="H18" t="n">
-        <v>0.606</v>
+        <v>2.7912</v>
       </c>
       <c r="I18" t="n">
-        <v>0.606</v>
+        <v>2.906</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5241</v>
+        <v>-0.5154</v>
       </c>
       <c r="K18" t="n">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="L18" t="n">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="M18" t="n">
-        <v>2.1301</v>
+        <v>2.3906</v>
       </c>
       <c r="N18" t="n">
-        <v>155</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.1054</v>
+        <v>2.2521</v>
       </c>
       <c r="C19" t="n">
-        <v>1.2518</v>
+        <v>1.339</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3949</v>
+        <v>0.3787</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1054</v>
+        <v>2.2521</v>
       </c>
       <c r="F19" t="n">
-        <v>1.719</v>
+        <v>2.2521</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3864</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.719</v>
+        <v>2.2521</v>
       </c>
       <c r="I19" t="n">
-        <v>1.719</v>
+        <v>2.2521</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3864</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>50</v>
+        <v>121</v>
       </c>
       <c r="L19" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.1054</v>
+        <v>2.2521</v>
       </c>
       <c r="N19" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.1037</v>
+        <v>2.0769</v>
       </c>
       <c r="C20" t="n">
-        <v>1.2508</v>
+        <v>1.2348</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3942</v>
+        <v>0.2996</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1037</v>
+        <v>2.0769</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1037</v>
+        <v>2.1601</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.0832</v>
       </c>
       <c r="H20" t="n">
-        <v>2.1037</v>
+        <v>2.1601</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1037</v>
+        <v>2.1601</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.0832</v>
       </c>
       <c r="K20" t="n">
-        <v>121</v>
+        <v>54</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M20" t="n">
-        <v>2.1037</v>
+        <v>2.0769</v>
       </c>
       <c r="N20" t="n">
-        <v>121</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.0761</v>
+        <v>2.0212</v>
       </c>
       <c r="C21" t="n">
-        <v>1.2344</v>
+        <v>1.2017</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3832</v>
+        <v>0.2745</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0761</v>
+        <v>2.0212</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7705</v>
+        <v>2.0212</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3056</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.7705</v>
+        <v>2.0212</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7854</v>
+        <v>2.0212</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3056</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="L21" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.091</v>
+        <v>2.0212</v>
       </c>
       <c r="N21" t="n">
-        <v>212</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.9796</v>
+        <v>1.9916</v>
       </c>
       <c r="C22" t="n">
-        <v>1.177</v>
+        <v>1.1841</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3448</v>
+        <v>0.2611</v>
       </c>
       <c r="E22" t="n">
-        <v>1.9796</v>
+        <v>1.9916</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5659</v>
+        <v>2.1112</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4137</v>
+        <v>-0.1196</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5659</v>
+        <v>2.1112</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5659</v>
+        <v>2.198</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4137</v>
+        <v>-0.1196</v>
       </c>
       <c r="K22" t="n">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="L22" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M22" t="n">
-        <v>1.9796</v>
+        <v>2.0784</v>
       </c>
       <c r="N22" t="n">
-        <v>119</v>
+        <v>198</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.8951</v>
+        <v>1.9818</v>
       </c>
       <c r="C23" t="n">
-        <v>1.1267</v>
+        <v>1.1783</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3111</v>
+        <v>0.2567</v>
       </c>
       <c r="E23" t="n">
-        <v>1.8951</v>
+        <v>1.9818</v>
       </c>
       <c r="F23" t="n">
-        <v>2.6775</v>
+        <v>1.5838</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7824</v>
+        <v>0.398</v>
       </c>
       <c r="H23" t="n">
-        <v>2.6775</v>
+        <v>1.5838</v>
       </c>
       <c r="I23" t="n">
-        <v>2.7</v>
+        <v>1.5838</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7824</v>
+        <v>0.398</v>
       </c>
       <c r="K23" t="n">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="L23" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M23" t="n">
-        <v>1.9176</v>
+        <v>1.9818</v>
       </c>
       <c r="N23" t="n">
-        <v>198</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.8804</v>
+        <v>1.9561</v>
       </c>
       <c r="C24" t="n">
-        <v>1.118</v>
+        <v>1.163</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3052</v>
+        <v>0.2451</v>
       </c>
       <c r="E24" t="n">
-        <v>1.8804</v>
+        <v>1.9561</v>
       </c>
       <c r="F24" t="n">
-        <v>1.8804</v>
+        <v>0.7816</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1.1745</v>
       </c>
       <c r="H24" t="n">
-        <v>1.8804</v>
+        <v>0.7816</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8804</v>
+        <v>0.7816</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1.1745</v>
       </c>
       <c r="K24" t="n">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="M24" t="n">
-        <v>1.8804</v>
+        <v>1.9561</v>
       </c>
       <c r="N24" t="n">
-        <v>121</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.675</v>
+        <v>1.9384</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9959</v>
+        <v>1.1525</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2234</v>
+        <v>0.2371</v>
       </c>
       <c r="E25" t="n">
-        <v>1.675</v>
+        <v>1.9384</v>
       </c>
       <c r="F25" t="n">
-        <v>1.8689</v>
+        <v>1.4777</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.1939</v>
+        <v>0.4607</v>
       </c>
       <c r="H25" t="n">
-        <v>1.8689</v>
+        <v>1.4777</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8847</v>
+        <v>1.4777</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1939</v>
+        <v>0.4607</v>
       </c>
       <c r="K25" t="n">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="L25" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M25" t="n">
-        <v>1.6908</v>
+        <v>1.9384</v>
       </c>
       <c r="N25" t="n">
-        <v>198</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.6221</v>
+        <v>1.6878</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9644</v>
+        <v>1.0035</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2023</v>
+        <v>0.1239</v>
       </c>
       <c r="E26" t="n">
-        <v>1.6221</v>
+        <v>1.6878</v>
       </c>
       <c r="F26" t="n">
-        <v>0.895</v>
+        <v>1.4374</v>
       </c>
       <c r="G26" t="n">
-        <v>0.7271</v>
+        <v>0.2504</v>
       </c>
       <c r="H26" t="n">
-        <v>0.895</v>
+        <v>1.4374</v>
       </c>
       <c r="I26" t="n">
-        <v>0.895</v>
+        <v>1.4374</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7271</v>
+        <v>0.2504</v>
       </c>
       <c r="K26" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="L26" t="n">
-        <v>109</v>
+        <v>205</v>
       </c>
       <c r="M26" t="n">
-        <v>1.6221</v>
+        <v>1.6878</v>
       </c>
       <c r="N26" t="n">
-        <v>155</v>
+        <v>248</v>
       </c>
     </row>
     <row r="27">
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.4397</v>
+        <v>1.6676</v>
       </c>
       <c r="C27" t="n">
-        <v>0.856</v>
+        <v>0.9915</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1297</v>
+        <v>0.1148</v>
       </c>
       <c r="E27" t="n">
-        <v>1.4397</v>
+        <v>1.6676</v>
       </c>
       <c r="F27" t="n">
-        <v>1.1324</v>
+        <v>1.2894</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3073</v>
+        <v>0.3782</v>
       </c>
       <c r="H27" t="n">
-        <v>1.1324</v>
+        <v>1.2894</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1324</v>
+        <v>1.2894</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3073</v>
+        <v>0.3782</v>
       </c>
       <c r="K27" t="n">
         <v>50</v>
@@ -1679,7 +1679,7 @@
         <v>69</v>
       </c>
       <c r="M27" t="n">
-        <v>1.4397</v>
+        <v>1.6676</v>
       </c>
       <c r="N27" t="n">
         <v>119</v>
@@ -1688,35 +1688,35 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.3468</v>
+        <v>1.5877</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8007</v>
+        <v>0.944</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0927</v>
+        <v>0.0788</v>
       </c>
       <c r="E28" t="n">
-        <v>1.3468</v>
+        <v>1.5877</v>
       </c>
       <c r="F28" t="n">
-        <v>1.3378</v>
+        <v>0.9683</v>
       </c>
       <c r="G28" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.6194</v>
       </c>
       <c r="H28" t="n">
-        <v>1.3378</v>
+        <v>0.9683</v>
       </c>
       <c r="I28" t="n">
-        <v>1.3378</v>
+        <v>0.9683</v>
       </c>
       <c r="J28" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.6194</v>
       </c>
       <c r="K28" t="n">
         <v>46</v>
@@ -1725,7 +1725,7 @@
         <v>109</v>
       </c>
       <c r="M28" t="n">
-        <v>1.3468</v>
+        <v>1.5877</v>
       </c>
       <c r="N28" t="n">
         <v>155</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.3306</v>
+        <v>1.5445</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7911</v>
+        <v>0.9183</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0862</v>
+        <v>0.0593</v>
       </c>
       <c r="E29" t="n">
-        <v>1.3306</v>
+        <v>1.5445</v>
       </c>
       <c r="F29" t="n">
-        <v>1.8378</v>
+        <v>1.8552</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.5072</v>
+        <v>-0.3107</v>
       </c>
       <c r="H29" t="n">
-        <v>1.8378</v>
+        <v>1.8552</v>
       </c>
       <c r="I29" t="n">
-        <v>1.8378</v>
+        <v>1.8552</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.5072</v>
+        <v>-0.3107</v>
       </c>
       <c r="K29" t="n">
         <v>50</v>
@@ -1771,7 +1771,7 @@
         <v>69</v>
       </c>
       <c r="M29" t="n">
-        <v>1.3306</v>
+        <v>1.5445</v>
       </c>
       <c r="N29" t="n">
         <v>119</v>
@@ -1780,415 +1780,415 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.0394</v>
+        <v>1.3854</v>
       </c>
       <c r="C30" t="n">
-        <v>0.618</v>
+        <v>0.8237</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0298</v>
+        <v>-0.0126</v>
       </c>
       <c r="E30" t="n">
-        <v>1.0394</v>
+        <v>1.3854</v>
       </c>
       <c r="F30" t="n">
-        <v>1.9102</v>
+        <v>1.4802</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.8708</v>
+        <v>-0.0948</v>
       </c>
       <c r="H30" t="n">
-        <v>1.9102</v>
+        <v>1.4802</v>
       </c>
       <c r="I30" t="n">
-        <v>1.9102</v>
+        <v>1.4802</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.8708</v>
+        <v>-0.0948</v>
       </c>
       <c r="K30" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L30" t="n">
-        <v>205</v>
+        <v>109</v>
       </c>
       <c r="M30" t="n">
-        <v>1.0394</v>
+        <v>1.3854</v>
       </c>
       <c r="N30" t="n">
-        <v>248</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9841</v>
+        <v>1.2682</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5851</v>
+        <v>0.754</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0518</v>
+        <v>-0.0655</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9841</v>
+        <v>1.2682</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9841</v>
+        <v>1.8304</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.5622</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9841</v>
+        <v>1.8304</v>
       </c>
       <c r="I31" t="n">
-        <v>0.9841</v>
+        <v>1.9057</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.5622</v>
       </c>
       <c r="K31" t="n">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M31" t="n">
-        <v>0.9841</v>
+        <v>1.3435</v>
       </c>
       <c r="N31" t="n">
-        <v>92</v>
+        <v>165</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>loWel</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9776</v>
+        <v>1.2494</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5812</v>
+        <v>0.7428</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0544</v>
+        <v>-0.074</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9776</v>
+        <v>1.2494</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7997</v>
+        <v>0.2099</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1779</v>
+        <v>1.0395</v>
       </c>
       <c r="H32" t="n">
-        <v>0.7997</v>
+        <v>0.2099</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7997</v>
+        <v>0.2185</v>
       </c>
       <c r="J32" t="n">
-        <v>0.1779</v>
+        <v>1.0395</v>
       </c>
       <c r="K32" t="n">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="L32" t="n">
-        <v>54</v>
+        <v>198</v>
       </c>
       <c r="M32" t="n">
-        <v>0.9776</v>
+        <v>1.258</v>
       </c>
       <c r="N32" t="n">
-        <v>108</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9674</v>
+        <v>1.2069</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5752</v>
+        <v>0.7176</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0585</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9674</v>
+        <v>1.2069</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9674</v>
+        <v>1.6643</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.4574</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9674</v>
+        <v>1.6643</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9674</v>
+        <v>1.7327</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.4574</v>
       </c>
       <c r="K33" t="n">
-        <v>53</v>
+        <v>120</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M33" t="n">
-        <v>0.9674</v>
+        <v>1.2753</v>
       </c>
       <c r="N33" t="n">
-        <v>53</v>
+        <v>165</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>loWel</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9547</v>
+        <v>1.1687</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5676</v>
+        <v>0.6949</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0636</v>
+        <v>-0.1104</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9547</v>
+        <v>1.1687</v>
       </c>
       <c r="F34" t="n">
-        <v>1.536</v>
+        <v>0.88</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.5813</v>
+        <v>0.2887</v>
       </c>
       <c r="H34" t="n">
-        <v>1.536</v>
+        <v>0.88</v>
       </c>
       <c r="I34" t="n">
-        <v>1.5489</v>
+        <v>0.88</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.5813</v>
+        <v>0.2887</v>
       </c>
       <c r="K34" t="n">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="L34" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="M34" t="n">
-        <v>0.9675999999999999</v>
+        <v>1.1687</v>
       </c>
       <c r="N34" t="n">
-        <v>165</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8986</v>
+        <v>1.1299</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5343</v>
+        <v>0.6718</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0859</v>
+        <v>-0.1279</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8986</v>
+        <v>1.1299</v>
       </c>
       <c r="F35" t="n">
-        <v>1.6783</v>
+        <v>1.1299</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.7796999999999999</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.6783</v>
+        <v>1.1299</v>
       </c>
       <c r="I35" t="n">
-        <v>1.6924</v>
+        <v>1.1299</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.7796999999999999</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>120</v>
+        <v>53</v>
       </c>
       <c r="L35" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.9127</v>
+        <v>1.1299</v>
       </c>
       <c r="N35" t="n">
-        <v>165</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8912</v>
+        <v>1.1021</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5299</v>
+        <v>0.6553</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.1405</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8912</v>
+        <v>1.1021</v>
       </c>
       <c r="F36" t="n">
-        <v>1.218</v>
+        <v>1.1021</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.3268</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.218</v>
+        <v>1.1021</v>
       </c>
       <c r="I36" t="n">
-        <v>1.218</v>
+        <v>1.1021</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.3268</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="L36" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8912</v>
+        <v>1.1021</v>
       </c>
       <c r="N36" t="n">
-        <v>248</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SicK</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7736</v>
+        <v>1.0224</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4599</v>
+        <v>0.6079</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1357</v>
+        <v>-0.1765</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7736</v>
+        <v>1.0224</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7736</v>
+        <v>1.8517</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.8293</v>
       </c>
       <c r="H37" t="n">
-        <v>0.7736</v>
+        <v>1.8517</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7736</v>
+        <v>1.8517</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.8293</v>
       </c>
       <c r="K37" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7736</v>
+        <v>1.0224</v>
       </c>
       <c r="N37" t="n">
-        <v>53</v>
+        <v>248</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>SicK</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7174</v>
+        <v>0.8786</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4265</v>
+        <v>0.5224</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1581</v>
+        <v>-0.2414</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7174</v>
+        <v>0.8786</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.1756</v>
+        <v>0.8786</v>
       </c>
       <c r="G38" t="n">
-        <v>0.893</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.1756</v>
+        <v>0.8786</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1771</v>
+        <v>0.8786</v>
       </c>
       <c r="J38" t="n">
-        <v>0.893</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="L38" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.7159</v>
+        <v>0.8786</v>
       </c>
       <c r="N38" t="n">
-        <v>295</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39">
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5099</v>
+        <v>0.8542999999999999</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3032</v>
+        <v>0.5079</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2408</v>
+        <v>-0.2523</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5099</v>
+        <v>0.8542999999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>1.5099</v>
+        <v>1.6314</v>
       </c>
       <c r="G39" t="n">
-        <v>-1</v>
+        <v>-0.7771</v>
       </c>
       <c r="H39" t="n">
-        <v>1.5099</v>
+        <v>1.6314</v>
       </c>
       <c r="I39" t="n">
-        <v>1.5226</v>
+        <v>1.6985</v>
       </c>
       <c r="J39" t="n">
-        <v>-1</v>
+        <v>-0.7771</v>
       </c>
       <c r="K39" t="n">
         <v>120</v>
@@ -2231,7 +2231,7 @@
         <v>45</v>
       </c>
       <c r="M39" t="n">
-        <v>0.5226</v>
+        <v>0.9213999999999999</v>
       </c>
       <c r="N39" t="n">
         <v>165</v>
@@ -2240,461 +2240,461 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4085</v>
+        <v>0.7314000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2429</v>
+        <v>0.4349</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2812</v>
+        <v>-0.3078</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4085</v>
+        <v>0.7314000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4085</v>
+        <v>0.8695000000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-0.1381</v>
       </c>
       <c r="H40" t="n">
-        <v>0.4085</v>
+        <v>0.8695000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4085</v>
+        <v>0.9053</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-0.1381</v>
       </c>
       <c r="K40" t="n">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4085</v>
+        <v>0.7672</v>
       </c>
       <c r="N40" t="n">
-        <v>42</v>
+        <v>212</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>USTILO</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.3646</v>
+        <v>0.5426</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2168</v>
+        <v>0.3226</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2987</v>
+        <v>-0.3931</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3646</v>
+        <v>0.5426</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3646</v>
+        <v>0.5426</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3646</v>
+        <v>0.5426</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3646</v>
+        <v>0.5426</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>52</v>
+        <v>121</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.3646</v>
+        <v>0.5426</v>
       </c>
       <c r="N41" t="n">
-        <v>52</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.3219</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1914</v>
+        <v>0.303</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3157</v>
+        <v>-0.408</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3219</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3219</v>
+        <v>1.0092</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>-0.4996</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3219</v>
+        <v>1.0092</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3219</v>
+        <v>1.0507</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>-0.4996</v>
       </c>
       <c r="K42" t="n">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3219</v>
+        <v>0.5510999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>92</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>USTILO</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.2737</v>
+        <v>0.5095</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1627</v>
+        <v>0.3029</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3349</v>
+        <v>-0.408</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2737</v>
+        <v>0.5095</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2737</v>
+        <v>0.5095</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2737</v>
+        <v>0.5095</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2737</v>
+        <v>0.5095</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.2737</v>
+        <v>0.5095</v>
       </c>
       <c r="N43" t="n">
-        <v>134</v>
+        <v>52</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2378</v>
+        <v>0.4895</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1414</v>
+        <v>0.291</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3492</v>
+        <v>-0.417</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2378</v>
+        <v>0.4895</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9184</v>
+        <v>0.4895</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.6806</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9184</v>
+        <v>0.4895</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9262</v>
+        <v>0.4895</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.6806</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="L44" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2456</v>
+        <v>0.4895</v>
       </c>
       <c r="N44" t="n">
-        <v>165</v>
+        <v>134</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.1337</v>
+        <v>0.3782</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0795</v>
+        <v>0.2249</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3906</v>
+        <v>-0.4673</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1337</v>
+        <v>0.3782</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4834</v>
+        <v>0.3782</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.3497</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.4834</v>
+        <v>0.3782</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4875</v>
+        <v>0.3782</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.3497</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="L45" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.1378</v>
+        <v>0.3782</v>
       </c>
       <c r="N45" t="n">
-        <v>212</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.0993</v>
+        <v>0.3563</v>
       </c>
       <c r="C46" t="n">
-        <v>0.059</v>
+        <v>0.2118</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4043</v>
+        <v>-0.4772</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0993</v>
+        <v>0.3563</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0993</v>
+        <v>0.8559</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>-0.4996</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0993</v>
+        <v>0.8559</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0993</v>
+        <v>0.8911</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>-0.4996</v>
       </c>
       <c r="K46" t="n">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M46" t="n">
-        <v>0.0993</v>
+        <v>0.3915</v>
       </c>
       <c r="N46" t="n">
-        <v>93</v>
+        <v>165</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.0522</v>
+        <v>0.3381</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.031</v>
+        <v>0.201</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4647</v>
+        <v>-0.4854</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.0522</v>
+        <v>0.3381</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.0522</v>
+        <v>0.3381</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.0522</v>
+        <v>0.3381</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0522</v>
+        <v>0.3381</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.0522</v>
+        <v>0.3381</v>
       </c>
       <c r="N47" t="n">
-        <v>121</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yam</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.0781</v>
+        <v>0.2882</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0464</v>
+        <v>0.1714</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.475</v>
+        <v>-0.5079</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.0781</v>
+        <v>0.2882</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.0781</v>
+        <v>0.2882</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.0781</v>
+        <v>0.2882</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0781</v>
+        <v>0.2882</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.0781</v>
+        <v>0.2882</v>
       </c>
       <c r="N48" t="n">
-        <v>52</v>
+        <v>93</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.08069999999999999</v>
+        <v>0.2147</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.048</v>
+        <v>0.1277</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4761</v>
+        <v>-0.5411</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.08069999999999999</v>
+        <v>0.2147</v>
       </c>
       <c r="F49" t="n">
-        <v>0.5999</v>
+        <v>0.9191</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.6806</v>
+        <v>-0.7044</v>
       </c>
       <c r="H49" t="n">
-        <v>0.5999</v>
+        <v>0.9191</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6049</v>
+        <v>0.9569</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.6806</v>
+        <v>-0.7044</v>
       </c>
       <c r="K49" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="L49" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.07569999999999999</v>
+        <v>0.2524999999999999</v>
       </c>
       <c r="N49" t="n">
-        <v>165</v>
+        <v>198</v>
       </c>
     </row>
     <row r="50">
@@ -2704,31 +2704,31 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.2536</v>
+        <v>0.1869</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.1508</v>
+        <v>0.1111</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5449000000000001</v>
+        <v>-0.5536</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.2536</v>
+        <v>0.1869</v>
       </c>
       <c r="F50" t="n">
-        <v>0.7464</v>
+        <v>0.9252</v>
       </c>
       <c r="G50" t="n">
-        <v>-1</v>
+        <v>-0.7383</v>
       </c>
       <c r="H50" t="n">
-        <v>0.7464</v>
+        <v>0.9252</v>
       </c>
       <c r="I50" t="n">
-        <v>0.7464</v>
+        <v>0.9252</v>
       </c>
       <c r="J50" t="n">
-        <v>-1</v>
+        <v>-0.7383</v>
       </c>
       <c r="K50" t="n">
         <v>50</v>
@@ -2737,7 +2737,7 @@
         <v>69</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.2536</v>
+        <v>0.1869000000000001</v>
       </c>
       <c r="N50" t="n">
         <v>119</v>
@@ -2746,32 +2746,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>atter</t>
+          <t>yam</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.2561</v>
+        <v>0.1207</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.1523</v>
+        <v>0.0718</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5459000000000001</v>
+        <v>-0.5835</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.2561</v>
+        <v>0.1207</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.2561</v>
+        <v>0.1207</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.2561</v>
+        <v>0.1207</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2561</v>
+        <v>0.1207</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.2561</v>
+        <v>0.1207</v>
       </c>
       <c r="N51" t="n">
         <v>52</v>
@@ -2792,93 +2792,93 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>atter</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.2573</v>
+        <v>0.0246</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.153</v>
+        <v>0.0146</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5464</v>
+        <v>-0.6269</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.2573</v>
+        <v>0.0246</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.2573</v>
+        <v>0.0246</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.2573</v>
+        <v>0.0246</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.2573</v>
+        <v>0.0246</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.2573</v>
+        <v>0.0246</v>
       </c>
       <c r="N52" t="n">
-        <v>134</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HZ</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.3135</v>
+        <v>-0.0353</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1864</v>
+        <v>-0.021</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5688</v>
+        <v>-0.654</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.3135</v>
+        <v>-0.0353</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.3135</v>
+        <v>-0.0353</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.3135</v>
+        <v>-0.0353</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.3135</v>
+        <v>-0.0353</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>42</v>
+        <v>134</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.3135</v>
+        <v>-0.0353</v>
       </c>
       <c r="N53" t="n">
-        <v>42</v>
+        <v>134</v>
       </c>
     </row>
     <row r="54">
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.3413</v>
+        <v>-0.0584</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.2029</v>
+        <v>-0.0347</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5799</v>
+        <v>-0.6644</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.3413</v>
+        <v>-0.0584</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.3413</v>
+        <v>-0.0584</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.3413</v>
+        <v>-0.0584</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3413</v>
+        <v>-0.0584</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.3413</v>
+        <v>-0.0584</v>
       </c>
       <c r="N54" t="n">
         <v>134</v>
@@ -2930,216 +2930,216 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>HZ</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.3456</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.2055</v>
+        <v>-0.0529</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5816</v>
+        <v>-0.6781</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.3456</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.3456</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.3456</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3456</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>134</v>
+        <v>42</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.3456</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="N55" t="n">
-        <v>134</v>
+        <v>42</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ANDROID</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.3803</v>
+        <v>-0.2723</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.2261</v>
+        <v>-0.1619</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5954</v>
+        <v>-0.7609</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.3803</v>
+        <v>-0.2723</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.3803</v>
+        <v>-0.2723</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.3803</v>
+        <v>-0.2723</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3803</v>
+        <v>-0.2723</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.3803</v>
+        <v>-0.2723</v>
       </c>
       <c r="N56" t="n">
-        <v>41</v>
+        <v>92</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.4907</v>
+        <v>-0.2741</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.2917</v>
+        <v>-0.163</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6394</v>
+        <v>-0.7618</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.4907</v>
+        <v>-0.2741</v>
       </c>
       <c r="F57" t="n">
-        <v>0.5093</v>
+        <v>-0.2741</v>
       </c>
       <c r="G57" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.5093</v>
+        <v>-0.2741</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5135999999999999</v>
+        <v>-0.2741</v>
       </c>
       <c r="J57" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="L57" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.4864000000000001</v>
+        <v>-0.2741</v>
       </c>
       <c r="N57" t="n">
-        <v>198</v>
+        <v>93</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.543</v>
+        <v>-0.2912</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.3228</v>
+        <v>-0.1731</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6602</v>
+        <v>-0.7695</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.543</v>
+        <v>-0.2912</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.543</v>
+        <v>-0.2912</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.543</v>
+        <v>-0.2912</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.543</v>
+        <v>-0.2912</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.543</v>
+        <v>-0.2912</v>
       </c>
       <c r="N58" t="n">
-        <v>93</v>
+        <v>134</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.5593</v>
+        <v>-0.295</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.3325</v>
+        <v>-0.1754</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6667</v>
+        <v>-0.7712</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.5593</v>
+        <v>-0.295</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.5593</v>
+        <v>-0.295</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.5593</v>
+        <v>-0.295</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.5593</v>
+        <v>-0.295</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.5593</v>
+        <v>-0.295</v>
       </c>
       <c r="N59" t="n">
         <v>93</v>
@@ -3160,185 +3160,185 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>ANDROID</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.5666</v>
+        <v>-0.3226</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.3369</v>
+        <v>-0.1918</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6696</v>
+        <v>-0.7837</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.5666</v>
+        <v>-0.3226</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.5666</v>
+        <v>-0.3226</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.5666</v>
+        <v>-0.3226</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5666</v>
+        <v>-0.3226</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.5666</v>
+        <v>-0.3226</v>
       </c>
       <c r="N60" t="n">
-        <v>92</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ShahZaM</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.5774</v>
+        <v>-0.3739</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.3433</v>
+        <v>-0.2223</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6739000000000001</v>
+        <v>-0.8068</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.5774</v>
+        <v>-0.3739</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.5774</v>
+        <v>-0.3739</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.5774</v>
+        <v>-0.3739</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5774</v>
+        <v>-0.3739</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.5774</v>
+        <v>-0.3739</v>
       </c>
       <c r="N61" t="n">
-        <v>53</v>
+        <v>93</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>ShahZaM</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.3763</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.3557</v>
+        <v>-0.2237</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6823</v>
+        <v>-0.8079</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.3763</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.3763</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.3763</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.3763</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.3763</v>
       </c>
       <c r="N62" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>dephh</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.5991</v>
+        <v>-0.3788</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.3562</v>
+        <v>-0.2252</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6826</v>
+        <v>-0.8090000000000001</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.5991</v>
+        <v>-0.3788</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.5991</v>
+        <v>-0.3788</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.5991</v>
+        <v>-0.3788</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.5991</v>
+        <v>-0.3788</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.5991</v>
+        <v>-0.3788</v>
       </c>
       <c r="N63" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
     </row>
     <row r="64">
@@ -3348,28 +3348,28 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.6288</v>
+        <v>-0.3959</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.3739</v>
+        <v>-0.2354</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6944</v>
+        <v>-0.8167</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.6288</v>
+        <v>-0.3959</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.6288</v>
+        <v>-0.3959</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.6288</v>
+        <v>-0.3959</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.6288</v>
+        <v>-0.3959</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.6288</v>
+        <v>-0.3959</v>
       </c>
       <c r="N64" t="n">
         <v>134</v>
@@ -3390,415 +3390,415 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>dephh</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.7372</v>
+        <v>-0.458</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.4383</v>
+        <v>-0.2723</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7376</v>
+        <v>-0.8448</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.7372</v>
+        <v>-0.458</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.7372</v>
+        <v>-0.458</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.7372</v>
+        <v>-0.458</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.7372</v>
+        <v>-0.458</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.7372</v>
+        <v>-0.458</v>
       </c>
       <c r="N65" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Relyks</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.771</v>
+        <v>-0.4731</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.4584</v>
+        <v>-0.2813</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7511</v>
+        <v>-0.8516</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.771</v>
+        <v>-0.4731</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.771</v>
+        <v>-0.4731</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.771</v>
+        <v>-0.4731</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.771</v>
+        <v>-0.4731</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.771</v>
+        <v>-0.4731</v>
       </c>
       <c r="N66" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>Relyks</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.7986</v>
+        <v>-0.5046</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.4748</v>
+        <v>-0.3</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7621</v>
+        <v>-0.8658</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.7986</v>
+        <v>-0.5046</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.7986</v>
+        <v>-0.5046</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.7986</v>
+        <v>-0.5046</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.7986</v>
+        <v>-0.5046</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.7986</v>
+        <v>-0.5046</v>
       </c>
       <c r="N67" t="n">
-        <v>93</v>
+        <v>53</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>desi</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.8469</v>
+        <v>-0.5646</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.5034999999999999</v>
+        <v>-0.3357</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7813</v>
+        <v>-0.8929</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.8469</v>
+        <v>-0.5646</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.8469</v>
+        <v>-0.5646</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.8469</v>
+        <v>-0.5646</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.8469</v>
+        <v>-0.5646</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>41</v>
+        <v>121</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.8469</v>
+        <v>-0.5646</v>
       </c>
       <c r="N68" t="n">
-        <v>41</v>
+        <v>121</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.8786</v>
+        <v>-0.5744</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.5224</v>
+        <v>-0.3415</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.7939000000000001</v>
+        <v>-0.8973</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.8786</v>
+        <v>-0.5744</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.8786</v>
+        <v>-0.5744</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.8786</v>
+        <v>-0.5744</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.8786</v>
+        <v>-0.5744</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>42</v>
+        <v>121</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.8786</v>
+        <v>-0.5744</v>
       </c>
       <c r="N69" t="n">
-        <v>42</v>
+        <v>121</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.5541</v>
+        <v>-0.3677</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8152</v>
+        <v>-0.9172</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="N70" t="n">
-        <v>121</v>
+        <v>93</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>desi</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.9637</v>
+        <v>-0.6224</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.573</v>
+        <v>-0.3701</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8278</v>
+        <v>-0.919</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.9637</v>
+        <v>-0.6224</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.9637</v>
+        <v>-0.6224</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.9637</v>
+        <v>-0.6224</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.9637</v>
+        <v>-0.6224</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>121</v>
+        <v>41</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.9637</v>
+        <v>-0.6224</v>
       </c>
       <c r="N71" t="n">
-        <v>121</v>
+        <v>41</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.9675</v>
+        <v>-0.6373</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.5752</v>
+        <v>-0.3789</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8294</v>
+        <v>-0.9257</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.9675</v>
+        <v>-0.6373</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.9675</v>
+        <v>-0.6373</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.9675</v>
+        <v>-0.6373</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.9675</v>
+        <v>-0.6373</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.9675</v>
+        <v>-0.6373</v>
       </c>
       <c r="N72" t="n">
-        <v>92</v>
+        <v>42</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.0068</v>
+        <v>-0.6965</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.5986</v>
+        <v>-0.4141</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.845</v>
+        <v>-0.9524</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.0068</v>
+        <v>-0.6965</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.0068</v>
+        <v>-0.6965</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.0068</v>
+        <v>-0.6965</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.0068</v>
+        <v>-0.6965</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.0068</v>
+        <v>-0.6965</v>
       </c>
       <c r="N73" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74">
@@ -3808,28 +3808,28 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.0296</v>
+        <v>-0.732</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.6122</v>
+        <v>-0.4352</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.8541</v>
+        <v>-0.9685</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.0296</v>
+        <v>-0.732</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.0296</v>
+        <v>-0.732</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.0296</v>
+        <v>-0.732</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.0296</v>
+        <v>-0.732</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.0296</v>
+        <v>-0.732</v>
       </c>
       <c r="N74" t="n">
         <v>41</v>
@@ -3854,28 +3854,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.0629</v>
+        <v>-0.7529</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.632</v>
+        <v>-0.4476</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.8673999999999999</v>
+        <v>-0.9779</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.0629</v>
+        <v>-0.7529</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.0629</v>
+        <v>-0.7529</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.0629</v>
+        <v>-0.7529</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.0629</v>
+        <v>-0.7529</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.0629</v>
+        <v>-0.7529</v>
       </c>
       <c r="N75" t="n">
         <v>42</v>
@@ -3896,32 +3896,32 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.1141</v>
+        <v>-0.7974</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.6624</v>
+        <v>-0.4741</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.8878</v>
+        <v>-0.998</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.1141</v>
+        <v>-0.7974</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.1141</v>
+        <v>-0.7974</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.1141</v>
+        <v>-0.7974</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.1141</v>
+        <v>-0.7974</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.1141</v>
+        <v>-0.7974</v>
       </c>
       <c r="N76" t="n">
         <v>92</v>
@@ -3946,28 +3946,28 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.3516</v>
+        <v>-0.9288</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.8036</v>
+        <v>-0.5522</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.9824000000000001</v>
+        <v>-1.0573</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.3516</v>
+        <v>-0.9288</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.3516</v>
+        <v>-0.9288</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.3516</v>
+        <v>-0.9288</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.3516</v>
+        <v>-0.9288</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.3516</v>
+        <v>-0.9288</v>
       </c>
       <c r="N77" t="n">
         <v>42</v>
@@ -3988,93 +3988,93 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Surreal</t>
+          <t>seang@res</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.4079</v>
+        <v>-0.9546</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.8371</v>
+        <v>-0.5676</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.0048</v>
+        <v>-1.069</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.4079</v>
+        <v>-0.9546</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.4079</v>
+        <v>-0.9546</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.4079</v>
+        <v>-0.9546</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.4079</v>
+        <v>-0.9546</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.4079</v>
+        <v>-0.9546</v>
       </c>
       <c r="N78" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>seang@res</t>
+          <t>Surreal</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.4108</v>
+        <v>-0.9641999999999999</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.8388</v>
+        <v>-0.5733</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.006</v>
+        <v>-1.0733</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.4108</v>
+        <v>-0.9641999999999999</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.4108</v>
+        <v>-0.9641999999999999</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.4108</v>
+        <v>-0.9641999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.4108</v>
+        <v>-0.9641999999999999</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.4108</v>
+        <v>-0.9641999999999999</v>
       </c>
       <c r="N79" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="80">
@@ -4084,31 +4084,31 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.5755</v>
+        <v>-1.2208</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.9367</v>
+        <v>-0.7258</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.0716</v>
+        <v>-1.1891</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.5755</v>
+        <v>-1.2208</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.928</v>
+        <v>-0.7803</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.6475</v>
+        <v>-0.4405</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.928</v>
+        <v>-0.7803</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.928</v>
+        <v>-0.7803</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.6475</v>
+        <v>-0.4405</v>
       </c>
       <c r="K80" t="n">
         <v>54</v>
@@ -4117,7 +4117,7 @@
         <v>54</v>
       </c>
       <c r="M80" t="n">
-        <v>-1.5755</v>
+        <v>-1.2208</v>
       </c>
       <c r="N80" t="n">
         <v>108</v>
@@ -4130,31 +4130,31 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-1.9731</v>
+        <v>-1.6145</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.1731</v>
+        <v>-0.9599</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.23</v>
+        <v>-1.3669</v>
       </c>
       <c r="E81" t="n">
-        <v>-1.9731</v>
+        <v>-1.6145</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.9731</v>
+        <v>-0.8314</v>
       </c>
       <c r="G81" t="n">
-        <v>-1</v>
+        <v>-0.7831</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.9731</v>
+        <v>-0.8314</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.9731</v>
+        <v>-0.8314</v>
       </c>
       <c r="J81" t="n">
-        <v>-1</v>
+        <v>-0.7831</v>
       </c>
       <c r="K81" t="n">
         <v>54</v>
@@ -4163,7 +4163,7 @@
         <v>54</v>
       </c>
       <c r="M81" t="n">
-        <v>-1.9731</v>
+        <v>-1.6145</v>
       </c>
       <c r="N81" t="n">
         <v>108</v>
@@ -4269,10 +4269,10 @@
         <v>1.05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2351</v>
+        <v>0.175</v>
       </c>
       <c r="J2" t="n">
-        <v>5.6424</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="3">
@@ -4309,10 +4309,10 @@
         <v>0.88</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1363</v>
+        <v>-0.1258</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.2712</v>
+        <v>-3.0192</v>
       </c>
     </row>
     <row r="4">
@@ -4349,10 +4349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2538</v>
+        <v>-0.2007</v>
       </c>
       <c r="J4" t="n">
-        <v>-6.0912</v>
+        <v>-4.8168</v>
       </c>
     </row>
     <row r="5">
@@ -4389,10 +4389,10 @@
         <v>0.68</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4829</v>
+        <v>-0.3234</v>
       </c>
       <c r="J5" t="n">
-        <v>-11.5896</v>
+        <v>-7.7616</v>
       </c>
     </row>
     <row r="6">
@@ -4429,10 +4429,10 @@
         <v>0.37</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8831</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>-21.1944</v>
+        <v>-14.6736</v>
       </c>
     </row>
     <row r="7">
@@ -4469,10 +4469,10 @@
         <v>1.73</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8995</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>21.588</v>
+        <v>19.7784</v>
       </c>
     </row>
     <row r="8">
@@ -4509,10 +4509,10 @@
         <v>1.64</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8037</v>
+        <v>0.7339</v>
       </c>
       <c r="J8" t="n">
-        <v>19.2888</v>
+        <v>17.6136</v>
       </c>
     </row>
     <row r="9">
@@ -4549,10 +4549,10 @@
         <v>1.49</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6322</v>
+        <v>0.5807</v>
       </c>
       <c r="J9" t="n">
-        <v>15.1728</v>
+        <v>13.9368</v>
       </c>
     </row>
     <row r="10">
@@ -4589,10 +4589,10 @@
         <v>1.22</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2655</v>
+        <v>0.2855</v>
       </c>
       <c r="J10" t="n">
-        <v>6.372</v>
+        <v>6.852</v>
       </c>
     </row>
     <row r="11">
@@ -4629,10 +4629,10 @@
         <v>0.95</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.22</v>
+        <v>-0.1144</v>
       </c>
       <c r="J11" t="n">
-        <v>-5.28</v>
+        <v>-2.7456</v>
       </c>
     </row>
     <row r="12">
@@ -4669,10 +4669,10 @@
         <v>1.58</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3684</v>
+        <v>1.2371</v>
       </c>
       <c r="J12" t="n">
-        <v>36.9468</v>
+        <v>33.4017</v>
       </c>
     </row>
     <row r="13">
@@ -4709,10 +4709,10 @@
         <v>1.43</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0678</v>
+        <v>1.0455</v>
       </c>
       <c r="J13" t="n">
-        <v>28.8306</v>
+        <v>28.2285</v>
       </c>
     </row>
     <row r="14">
@@ -4749,10 +4749,10 @@
         <v>1.08</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1675</v>
+        <v>0.2395</v>
       </c>
       <c r="J14" t="n">
-        <v>4.5225</v>
+        <v>6.4665</v>
       </c>
     </row>
     <row r="15">
@@ -4789,10 +4789,10 @@
         <v>1.08</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1675</v>
+        <v>0.2395</v>
       </c>
       <c r="J15" t="n">
-        <v>4.5225</v>
+        <v>6.4665</v>
       </c>
     </row>
     <row r="16">
@@ -4829,10 +4829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3669</v>
+        <v>-0.2882</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.9063</v>
+        <v>-7.7814</v>
       </c>
     </row>
     <row r="17">
@@ -4869,10 +4869,10 @@
         <v>1.29</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.6645</v>
       </c>
       <c r="J17" t="n">
-        <v>15.039</v>
+        <v>17.9415</v>
       </c>
     </row>
     <row r="18">
@@ -4909,10 +4909,10 @@
         <v>0.98</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0089</v>
+        <v>-0.02</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2403</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="19">
@@ -4949,10 +4949,10 @@
         <v>0.86</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2342</v>
+        <v>-0.1625</v>
       </c>
       <c r="J19" t="n">
-        <v>-6.3234</v>
+        <v>-4.3875</v>
       </c>
     </row>
     <row r="20">
@@ -4989,10 +4989,10 @@
         <v>0.64</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5703</v>
+        <v>-0.3759</v>
       </c>
       <c r="J20" t="n">
-        <v>-15.3981</v>
+        <v>-10.1493</v>
       </c>
     </row>
     <row r="21">
@@ -5029,10 +5029,10 @@
         <v>0.54</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6969</v>
+        <v>-0.4686</v>
       </c>
       <c r="J21" t="n">
-        <v>-18.8163</v>
+        <v>-12.6522</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         <v>1.36</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9702</v>
+        <v>0.9552</v>
       </c>
       <c r="J22" t="n">
-        <v>28.1358</v>
+        <v>27.7008</v>
       </c>
     </row>
     <row r="23">
@@ -5109,10 +5109,10 @@
         <v>1.35</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9483</v>
+        <v>0.9342</v>
       </c>
       <c r="J23" t="n">
-        <v>27.5007</v>
+        <v>27.0918</v>
       </c>
     </row>
     <row r="24">
@@ -5149,10 +5149,10 @@
         <v>1.15</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4549</v>
+        <v>0.4504</v>
       </c>
       <c r="J24" t="n">
-        <v>13.1921</v>
+        <v>13.0616</v>
       </c>
     </row>
     <row r="25">
@@ -5189,10 +5189,10 @@
         <v>0.88</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5058</v>
+        <v>-0.4403</v>
       </c>
       <c r="J25" t="n">
-        <v>-14.6682</v>
+        <v>-12.7687</v>
       </c>
     </row>
     <row r="26">
@@ -5229,10 +5229,10 @@
         <v>0.87</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5326</v>
+        <v>-0.4683</v>
       </c>
       <c r="J26" t="n">
-        <v>-15.4454</v>
+        <v>-13.5807</v>
       </c>
     </row>
     <row r="27">
@@ -5269,10 +5269,10 @@
         <v>1.34</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5538</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>16.0602</v>
+        <v>19.3082</v>
       </c>
     </row>
     <row r="28">
@@ -5309,10 +5309,10 @@
         <v>1.26</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4491</v>
+        <v>0.5291</v>
       </c>
       <c r="J28" t="n">
-        <v>13.0239</v>
+        <v>15.3439</v>
       </c>
     </row>
     <row r="29">
@@ -5349,10 +5349,10 @@
         <v>1.24</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4217</v>
+        <v>0.4941</v>
       </c>
       <c r="J29" t="n">
-        <v>12.2293</v>
+        <v>14.3289</v>
       </c>
     </row>
     <row r="30">
@@ -5389,10 +5389,10 @@
         <v>0.79</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4092</v>
+        <v>-0.2551</v>
       </c>
       <c r="J30" t="n">
-        <v>-11.8668</v>
+        <v>-7.3979</v>
       </c>
     </row>
     <row r="31">
@@ -5429,10 +5429,10 @@
         <v>0.64</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6046</v>
+        <v>-0.398</v>
       </c>
       <c r="J31" t="n">
-        <v>-17.5334</v>
+        <v>-11.542</v>
       </c>
     </row>
     <row r="32">
@@ -5469,10 +5469,10 @@
         <v>1.09</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2383</v>
+        <v>0.2462</v>
       </c>
       <c r="J32" t="n">
-        <v>7.149</v>
+        <v>7.386</v>
       </c>
     </row>
     <row r="33">
@@ -5509,10 +5509,10 @@
         <v>1.07</v>
       </c>
       <c r="I33" t="n">
-        <v>0.203</v>
+        <v>0.2028</v>
       </c>
       <c r="J33" t="n">
-        <v>6.09</v>
+        <v>6.084</v>
       </c>
     </row>
     <row r="34">
@@ -5549,10 +5549,10 @@
         <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1453</v>
+        <v>0.1332</v>
       </c>
       <c r="J34" t="n">
-        <v>4.359</v>
+        <v>3.996</v>
       </c>
     </row>
     <row r="35">
@@ -5589,10 +5589,10 @@
         <v>0.73</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.465</v>
+        <v>-0.299</v>
       </c>
       <c r="J35" t="n">
-        <v>-13.95</v>
+        <v>-8.970000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -5629,10 +5629,10 @@
         <v>0.71</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4923</v>
+        <v>-0.3182</v>
       </c>
       <c r="J36" t="n">
-        <v>-14.769</v>
+        <v>-9.545999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -5669,10 +5669,10 @@
         <v>1.63</v>
       </c>
       <c r="I37" t="n">
-        <v>1.4501</v>
+        <v>1.0183</v>
       </c>
       <c r="J37" t="n">
-        <v>43.503</v>
+        <v>30.549</v>
       </c>
     </row>
     <row r="38">
@@ -5709,10 +5709,10 @@
         <v>1.57</v>
       </c>
       <c r="I38" t="n">
-        <v>1.3357</v>
+        <v>0.944</v>
       </c>
       <c r="J38" t="n">
-        <v>40.071</v>
+        <v>28.32</v>
       </c>
     </row>
     <row r="39">
@@ -5749,10 +5749,10 @@
         <v>1.14</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3239</v>
+        <v>0.3729</v>
       </c>
       <c r="J39" t="n">
-        <v>9.717000000000001</v>
+        <v>11.187</v>
       </c>
     </row>
     <row r="40">
@@ -5789,10 +5789,10 @@
         <v>1.01</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.0825</v>
+        <v>-0.006</v>
       </c>
       <c r="J40" t="n">
-        <v>-2.475</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="41">
@@ -5829,10 +5829,10 @@
         <v>0.9</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4902</v>
+        <v>-0.4156</v>
       </c>
       <c r="J41" t="n">
-        <v>-14.706</v>
+        <v>-12.468</v>
       </c>
     </row>
     <row r="42">
@@ -5869,10 +5869,10 @@
         <v>1.16</v>
       </c>
       <c r="I42" t="n">
-        <v>0.37</v>
+        <v>0.3787</v>
       </c>
       <c r="J42" t="n">
-        <v>9.25</v>
+        <v>9.467499999999999</v>
       </c>
     </row>
     <row r="43">
@@ -5909,10 +5909,10 @@
         <v>0.98</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0029</v>
+        <v>-0.0224</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0725</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -5949,10 +5949,10 @@
         <v>0.84</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2815</v>
+        <v>-0.1839</v>
       </c>
       <c r="J44" t="n">
-        <v>-7.0375</v>
+        <v>-4.5975</v>
       </c>
     </row>
     <row r="45">
@@ -5989,10 +5989,10 @@
         <v>0.72</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4654</v>
+        <v>-0.3019</v>
       </c>
       <c r="J45" t="n">
-        <v>-11.635</v>
+        <v>-7.5475</v>
       </c>
     </row>
     <row r="46">
@@ -6029,10 +6029,10 @@
         <v>0.68</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5204</v>
+        <v>-0.34</v>
       </c>
       <c r="J46" t="n">
-        <v>-13.01</v>
+        <v>-8.5</v>
       </c>
     </row>
     <row r="47">
@@ -6069,10 +6069,10 @@
         <v>1.47</v>
       </c>
       <c r="I47" t="n">
-        <v>1.1408</v>
+        <v>0.8199</v>
       </c>
       <c r="J47" t="n">
-        <v>28.52</v>
+        <v>20.4975</v>
       </c>
     </row>
     <row r="48">
@@ -6109,10 +6109,10 @@
         <v>1.46</v>
       </c>
       <c r="I48" t="n">
-        <v>1.1202</v>
+        <v>0.8071</v>
       </c>
       <c r="J48" t="n">
-        <v>28.005</v>
+        <v>20.1775</v>
       </c>
     </row>
     <row r="49">
@@ -6149,10 +6149,10 @@
         <v>1.35</v>
       </c>
       <c r="I49" t="n">
-        <v>0.8834</v>
+        <v>0.6647</v>
       </c>
       <c r="J49" t="n">
-        <v>22.085</v>
+        <v>16.6175</v>
       </c>
     </row>
     <row r="50">
@@ -6189,10 +6189,10 @@
         <v>1.16</v>
       </c>
       <c r="I50" t="n">
-        <v>0.3813</v>
+        <v>0.4046</v>
       </c>
       <c r="J50" t="n">
-        <v>9.532500000000001</v>
+        <v>10.115</v>
       </c>
     </row>
     <row r="51">
@@ -6229,10 +6229,10 @@
         <v>0.77</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.8090000000000001</v>
+        <v>-0.7612</v>
       </c>
       <c r="J51" t="n">
-        <v>-20.225</v>
+        <v>-19.03</v>
       </c>
     </row>
     <row r="52">
@@ -6269,10 +6269,10 @@
         <v>1.76</v>
       </c>
       <c r="I52" t="n">
-        <v>1.5677</v>
+        <v>1.1149</v>
       </c>
       <c r="J52" t="n">
-        <v>29.7863</v>
+        <v>21.1831</v>
       </c>
     </row>
     <row r="53">
@@ -6309,10 +6309,10 @@
         <v>1.72</v>
       </c>
       <c r="I53" t="n">
-        <v>1.4945</v>
+        <v>1.0696</v>
       </c>
       <c r="J53" t="n">
-        <v>28.3955</v>
+        <v>20.3224</v>
       </c>
     </row>
     <row r="54">
@@ -6349,10 +6349,10 @@
         <v>1.71</v>
       </c>
       <c r="I54" t="n">
-        <v>1.4759</v>
+        <v>1.0582</v>
       </c>
       <c r="J54" t="n">
-        <v>28.0421</v>
+        <v>20.1058</v>
       </c>
     </row>
     <row r="55">
@@ -6389,10 +6389,10 @@
         <v>1.24</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4699</v>
+        <v>0.4851</v>
       </c>
       <c r="J55" t="n">
-        <v>8.928100000000001</v>
+        <v>9.216900000000001</v>
       </c>
     </row>
     <row r="56">
@@ -6429,10 +6429,10 @@
         <v>1.22</v>
       </c>
       <c r="I56" t="n">
-        <v>0.4245</v>
+        <v>0.4567</v>
       </c>
       <c r="J56" t="n">
-        <v>8.0655</v>
+        <v>8.677300000000001</v>
       </c>
     </row>
     <row r="57">
@@ -6469,10 +6469,10 @@
         <v>0.68</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.3724</v>
+        <v>-0.2989</v>
       </c>
       <c r="J57" t="n">
-        <v>-7.0756</v>
+        <v>-5.6791</v>
       </c>
     </row>
     <row r="58">
@@ -6509,10 +6509,10 @@
         <v>0.62</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.4709</v>
+        <v>-0.3563</v>
       </c>
       <c r="J58" t="n">
-        <v>-8.947100000000001</v>
+        <v>-6.7697</v>
       </c>
     </row>
     <row r="59">
@@ -6549,10 +6549,10 @@
         <v>0.59</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.536</v>
+        <v>-0.3822</v>
       </c>
       <c r="J59" t="n">
-        <v>-10.184</v>
+        <v>-7.2618</v>
       </c>
     </row>
     <row r="60">
@@ -6589,10 +6589,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.588</v>
+        <v>-0.4092</v>
       </c>
       <c r="J60" t="n">
-        <v>-11.172</v>
+        <v>-7.7748</v>
       </c>
     </row>
     <row r="61">
@@ -6629,10 +6629,10 @@
         <v>0.55</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6039</v>
+        <v>-0.4183</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.4741</v>
+        <v>-7.9477</v>
       </c>
     </row>
     <row r="62">
@@ -6669,10 +6669,10 @@
         <v>1.02</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1228</v>
+        <v>0.0745</v>
       </c>
       <c r="J62" t="n">
-        <v>3.07</v>
+        <v>1.8625</v>
       </c>
     </row>
     <row r="63">
@@ -6709,10 +6709,10 @@
         <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>0.063</v>
+        <v>0.0215</v>
       </c>
       <c r="J63" t="n">
-        <v>1.575</v>
+        <v>0.5375</v>
       </c>
     </row>
     <row r="64">
@@ -6749,10 +6749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-0.0761</v>
       </c>
       <c r="J64" t="n">
-        <v>-2.0525</v>
+        <v>-1.9025</v>
       </c>
     </row>
     <row r="65">
@@ -6789,10 +6789,10 @@
         <v>0.76</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.4079</v>
+        <v>-0.2632</v>
       </c>
       <c r="J65" t="n">
-        <v>-10.1975</v>
+        <v>-6.58</v>
       </c>
     </row>
     <row r="66">
@@ -6829,10 +6829,10 @@
         <v>0.66</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5471</v>
+        <v>-0.3589</v>
       </c>
       <c r="J66" t="n">
-        <v>-13.6775</v>
+        <v>-8.9725</v>
       </c>
     </row>
     <row r="67">
@@ -6869,10 +6869,10 @@
         <v>1.56</v>
       </c>
       <c r="I67" t="n">
-        <v>0.767</v>
+        <v>0.5414</v>
       </c>
       <c r="J67" t="n">
-        <v>19.175</v>
+        <v>13.535</v>
       </c>
     </row>
     <row r="68">
@@ -6909,10 +6909,10 @@
         <v>1.51</v>
       </c>
       <c r="I68" t="n">
-        <v>0.7105</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="J68" t="n">
-        <v>17.7625</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="69">
@@ -6949,10 +6949,10 @@
         <v>1.2</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2935</v>
+        <v>0.281</v>
       </c>
       <c r="J69" t="n">
-        <v>7.3375</v>
+        <v>7.025</v>
       </c>
     </row>
     <row r="70">
@@ -6989,10 +6989,10 @@
         <v>1.06</v>
       </c>
       <c r="I70" t="n">
-        <v>0.0635</v>
+        <v>0.0911</v>
       </c>
       <c r="J70" t="n">
-        <v>1.5875</v>
+        <v>2.2775</v>
       </c>
     </row>
     <row r="71">
@@ -7029,10 +7029,10 @@
         <v>0.73</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5129</v>
+        <v>-0.3286</v>
       </c>
       <c r="J71" t="n">
-        <v>-12.8225</v>
+        <v>-8.215</v>
       </c>
     </row>
     <row r="72">
@@ -7069,10 +7069,10 @@
         <v>1.87</v>
       </c>
       <c r="I72" t="n">
-        <v>1.7531</v>
+        <v>1.2482</v>
       </c>
       <c r="J72" t="n">
-        <v>35.062</v>
+        <v>24.964</v>
       </c>
     </row>
     <row r="73">
@@ -7109,10 +7109,10 @@
         <v>1.62</v>
       </c>
       <c r="I73" t="n">
-        <v>1.3269</v>
+        <v>0.9617</v>
       </c>
       <c r="J73" t="n">
-        <v>26.538</v>
+        <v>19.234</v>
       </c>
     </row>
     <row r="74">
@@ -7149,10 +7149,10 @@
         <v>1.45</v>
       </c>
       <c r="I74" t="n">
-        <v>0.9487</v>
+        <v>0.7634</v>
       </c>
       <c r="J74" t="n">
-        <v>18.974</v>
+        <v>15.268</v>
       </c>
     </row>
     <row r="75">
@@ -7189,10 +7189,10 @@
         <v>1.29</v>
       </c>
       <c r="I75" t="n">
-        <v>0.5966</v>
+        <v>0.5598</v>
       </c>
       <c r="J75" t="n">
-        <v>11.932</v>
+        <v>11.196</v>
       </c>
     </row>
     <row r="76">
@@ -7229,10 +7229,10 @@
         <v>1.17</v>
       </c>
       <c r="I76" t="n">
-        <v>0.3203</v>
+        <v>0.3893</v>
       </c>
       <c r="J76" t="n">
-        <v>6.406</v>
+        <v>7.786</v>
       </c>
     </row>
     <row r="77">
@@ -7269,10 +7269,10 @@
         <v>1.17</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4933</v>
+        <v>0.4914</v>
       </c>
       <c r="J77" t="n">
-        <v>9.866</v>
+        <v>9.827999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -7309,10 +7309,10 @@
         <v>0.72</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.3322</v>
+        <v>-0.268</v>
       </c>
       <c r="J78" t="n">
-        <v>-6.644</v>
+        <v>-5.36</v>
       </c>
     </row>
     <row r="79">
@@ -7349,10 +7349,10 @@
         <v>0.47</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.7336</v>
+        <v>-0.5004</v>
       </c>
       <c r="J79" t="n">
-        <v>-14.672</v>
+        <v>-10.008</v>
       </c>
     </row>
     <row r="80">
@@ -7389,10 +7389,10 @@
         <v>0.45</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.76</v>
+        <v>-0.5193</v>
       </c>
       <c r="J80" t="n">
-        <v>-15.2</v>
+        <v>-10.386</v>
       </c>
     </row>
     <row r="81">
@@ -7429,10 +7429,10 @@
         <v>0.38</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.8496</v>
+        <v>-0.5856</v>
       </c>
       <c r="J81" t="n">
-        <v>-16.992</v>
+        <v>-11.712</v>
       </c>
     </row>
     <row r="82">
@@ -7469,10 +7469,10 @@
         <v>1.29</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8616</v>
+        <v>0.6267</v>
       </c>
       <c r="J82" t="n">
-        <v>40.4952</v>
+        <v>29.4549</v>
       </c>
     </row>
     <row r="83">
@@ -7509,10 +7509,10 @@
         <v>1.15</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5149</v>
+        <v>0.417</v>
       </c>
       <c r="J83" t="n">
-        <v>24.2003</v>
+        <v>19.599</v>
       </c>
     </row>
     <row r="84">
@@ -7549,10 +7549,10 @@
         <v>0.93</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.3241</v>
+        <v>-0.2699</v>
       </c>
       <c r="J84" t="n">
-        <v>-15.2327</v>
+        <v>-12.6853</v>
       </c>
     </row>
     <row r="85">
@@ -7589,10 +7589,10 @@
         <v>0.92</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3552</v>
+        <v>-0.3003</v>
       </c>
       <c r="J85" t="n">
-        <v>-16.6944</v>
+        <v>-14.1141</v>
       </c>
     </row>
     <row r="86">
@@ -7629,10 +7629,10 @@
         <v>0.89</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4438</v>
+        <v>-0.3879</v>
       </c>
       <c r="J86" t="n">
-        <v>-20.8586</v>
+        <v>-18.2313</v>
       </c>
     </row>
     <row r="87">
@@ -7669,10 +7669,10 @@
         <v>1.17</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3303</v>
+        <v>0.3585</v>
       </c>
       <c r="J87" t="n">
-        <v>15.5241</v>
+        <v>16.8495</v>
       </c>
     </row>
     <row r="88">
@@ -7709,10 +7709,10 @@
         <v>1.05</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1228</v>
+        <v>0.1346</v>
       </c>
       <c r="J88" t="n">
-        <v>5.7716</v>
+        <v>6.3262</v>
       </c>
     </row>
     <row r="89">
@@ -7749,10 +7749,10 @@
         <v>1.01</v>
       </c>
       <c r="I89" t="n">
-        <v>0.0182</v>
+        <v>0.0348</v>
       </c>
       <c r="J89" t="n">
-        <v>0.8554</v>
+        <v>1.6356</v>
       </c>
     </row>
     <row r="90">
@@ -7789,10 +7789,10 @@
         <v>0.98</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.0383</v>
       </c>
       <c r="J90" t="n">
-        <v>-3.7694</v>
+        <v>-1.8001</v>
       </c>
     </row>
     <row r="91">
@@ -7829,10 +7829,10 @@
         <v>0.92</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2012</v>
+        <v>-0.1145</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.4564</v>
+        <v>-5.3815</v>
       </c>
     </row>
     <row r="92">
@@ -7869,10 +7869,10 @@
         <v>1.63</v>
       </c>
       <c r="I92" t="n">
-        <v>1.3759</v>
+        <v>0.9836</v>
       </c>
       <c r="J92" t="n">
-        <v>31.6457</v>
+        <v>22.6228</v>
       </c>
     </row>
     <row r="93">
@@ -7909,10 +7909,10 @@
         <v>1.45</v>
       </c>
       <c r="I93" t="n">
-        <v>1.0077</v>
+        <v>0.7683</v>
       </c>
       <c r="J93" t="n">
-        <v>23.1771</v>
+        <v>17.6709</v>
       </c>
     </row>
     <row r="94">
@@ -7949,10 +7949,10 @@
         <v>1.43</v>
       </c>
       <c r="I94" t="n">
-        <v>0.9604</v>
+        <v>0.7443</v>
       </c>
       <c r="J94" t="n">
-        <v>22.0892</v>
+        <v>17.1189</v>
       </c>
     </row>
     <row r="95">
@@ -7989,10 +7989,10 @@
         <v>1.36</v>
       </c>
       <c r="I95" t="n">
-        <v>0.7808</v>
+        <v>0.6589</v>
       </c>
       <c r="J95" t="n">
-        <v>17.9584</v>
+        <v>15.1547</v>
       </c>
     </row>
     <row r="96">
@@ -8029,10 +8029,10 @@
         <v>1.2</v>
       </c>
       <c r="I96" t="n">
-        <v>0.4118</v>
+        <v>0.4419</v>
       </c>
       <c r="J96" t="n">
-        <v>9.471399999999999</v>
+        <v>10.1637</v>
       </c>
     </row>
     <row r="97">
@@ -8069,10 +8069,10 @@
         <v>0.97</v>
       </c>
       <c r="I97" t="n">
-        <v>0.0747</v>
+        <v>0.0322</v>
       </c>
       <c r="J97" t="n">
-        <v>1.7181</v>
+        <v>0.7406</v>
       </c>
     </row>
     <row r="98">
@@ -8109,10 +8109,10 @@
         <v>0.74</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.3167</v>
+        <v>-0.2542</v>
       </c>
       <c r="J98" t="n">
-        <v>-7.2841</v>
+        <v>-5.8466</v>
       </c>
     </row>
     <row r="99">
@@ -8149,10 +8149,10 @@
         <v>0.74</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.3167</v>
+        <v>-0.2542</v>
       </c>
       <c r="J99" t="n">
-        <v>-7.2841</v>
+        <v>-5.8466</v>
       </c>
     </row>
     <row r="100">
@@ -8189,10 +8189,10 @@
         <v>0.5</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.7022</v>
+        <v>-0.4771</v>
       </c>
       <c r="J100" t="n">
-        <v>-16.1506</v>
+        <v>-10.9733</v>
       </c>
     </row>
     <row r="101">
@@ -8229,10 +8229,10 @@
         <v>0.38</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8555</v>
+        <v>-0.5899</v>
       </c>
       <c r="J101" t="n">
-        <v>-19.6765</v>
+        <v>-13.5677</v>
       </c>
     </row>
     <row r="102">
@@ -8269,10 +8269,10 @@
         <v>1.75</v>
       </c>
       <c r="I102" t="n">
-        <v>1.5844</v>
+        <v>1.118</v>
       </c>
       <c r="J102" t="n">
-        <v>34.8568</v>
+        <v>24.596</v>
       </c>
     </row>
     <row r="103">
@@ -8309,10 +8309,10 @@
         <v>1.71</v>
       </c>
       <c r="I103" t="n">
-        <v>1.5116</v>
+        <v>1.0717</v>
       </c>
       <c r="J103" t="n">
-        <v>33.2552</v>
+        <v>23.5774</v>
       </c>
     </row>
     <row r="104">
@@ -8349,10 +8349,10 @@
         <v>1.49</v>
       </c>
       <c r="I104" t="n">
-        <v>1.0773</v>
+        <v>0.8129</v>
       </c>
       <c r="J104" t="n">
-        <v>23.7006</v>
+        <v>17.8838</v>
       </c>
     </row>
     <row r="105">
@@ -8389,10 +8389,10 @@
         <v>1.18</v>
       </c>
       <c r="I105" t="n">
-        <v>0.3539</v>
+        <v>0.4084</v>
       </c>
       <c r="J105" t="n">
-        <v>7.7858</v>
+        <v>8.9848</v>
       </c>
     </row>
     <row r="106">
@@ -8429,10 +8429,10 @@
         <v>1.1</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1512</v>
+        <v>0.2469</v>
       </c>
       <c r="J106" t="n">
-        <v>3.3264</v>
+        <v>5.4318</v>
       </c>
     </row>
     <row r="107">
@@ -8469,10 +8469,10 @@
         <v>0.75</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.3202</v>
+        <v>-0.2508</v>
       </c>
       <c r="J107" t="n">
-        <v>-7.0444</v>
+        <v>-5.5176</v>
       </c>
     </row>
     <row r="108">
@@ -8509,10 +8509,10 @@
         <v>0.73</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.3537</v>
+        <v>-0.2701</v>
       </c>
       <c r="J108" t="n">
-        <v>-7.7814</v>
+        <v>-5.9422</v>
       </c>
     </row>
     <row r="109">
@@ -8549,10 +8549,10 @@
         <v>0.7</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.4121</v>
+        <v>-0.2974</v>
       </c>
       <c r="J109" t="n">
-        <v>-9.0662</v>
+        <v>-6.5428</v>
       </c>
     </row>
     <row r="110">
@@ -8589,10 +8589,10 @@
         <v>0.66</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.486</v>
+        <v>-0.3335</v>
       </c>
       <c r="J110" t="n">
-        <v>-10.692</v>
+        <v>-7.337</v>
       </c>
     </row>
     <row r="111">
@@ -8629,10 +8629,10 @@
         <v>0.66</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.486</v>
+        <v>-0.3335</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.692</v>
+        <v>-7.337</v>
       </c>
     </row>
     <row r="112">
@@ -8669,10 +8669,10 @@
         <v>1.49</v>
       </c>
       <c r="I112" t="n">
-        <v>1.16</v>
+        <v>0.8364</v>
       </c>
       <c r="J112" t="n">
-        <v>26.68</v>
+        <v>19.2372</v>
       </c>
     </row>
     <row r="113">
@@ -8709,10 +8709,10 @@
         <v>1.35</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8578</v>
+        <v>0.6583</v>
       </c>
       <c r="J113" t="n">
-        <v>19.7294</v>
+        <v>15.1409</v>
       </c>
     </row>
     <row r="114">
@@ -8749,10 +8749,10 @@
         <v>1.32</v>
       </c>
       <c r="I114" t="n">
-        <v>0.7858000000000001</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="J114" t="n">
-        <v>18.0734</v>
+        <v>14.2485</v>
       </c>
     </row>
     <row r="115">
@@ -8789,10 +8789,10 @@
         <v>1.19</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4375</v>
+        <v>0.4435</v>
       </c>
       <c r="J115" t="n">
-        <v>10.0625</v>
+        <v>10.2005</v>
       </c>
     </row>
     <row r="116">
@@ -8829,10 +8829,10 @@
         <v>1.08</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1427</v>
+        <v>0.2243</v>
       </c>
       <c r="J116" t="n">
-        <v>3.2821</v>
+        <v>5.1589</v>
       </c>
     </row>
     <row r="117">
@@ -8869,10 +8869,10 @@
         <v>0.84</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.1946</v>
+        <v>-0.1661</v>
       </c>
       <c r="J117" t="n">
-        <v>-4.4758</v>
+        <v>-3.8203</v>
       </c>
     </row>
     <row r="118">
@@ -8909,10 +8909,10 @@
         <v>0.84</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1946</v>
+        <v>-0.1661</v>
       </c>
       <c r="J118" t="n">
-        <v>-4.4758</v>
+        <v>-3.8203</v>
       </c>
     </row>
     <row r="119">
@@ -8949,10 +8949,10 @@
         <v>0.82</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2276</v>
+        <v>-0.1873</v>
       </c>
       <c r="J119" t="n">
-        <v>-5.2348</v>
+        <v>-4.3079</v>
       </c>
     </row>
     <row r="120">
@@ -8989,10 +8989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4595</v>
+        <v>-0.3114</v>
       </c>
       <c r="J120" t="n">
-        <v>-10.5685</v>
+        <v>-7.1622</v>
       </c>
     </row>
     <row r="121">
@@ -9029,10 +9029,10 @@
         <v>0.51</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.7093</v>
+        <v>-0.4797</v>
       </c>
       <c r="J121" t="n">
-        <v>-16.3139</v>
+        <v>-11.0331</v>
       </c>
     </row>
     <row r="122">
@@ -9069,10 +9069,10 @@
         <v>1.08</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2419</v>
+        <v>0.2439</v>
       </c>
       <c r="J122" t="n">
-        <v>5.8056</v>
+        <v>5.8536</v>
       </c>
     </row>
     <row r="123">
@@ -9109,10 +9109,10 @@
         <v>1.04</v>
       </c>
       <c r="I123" t="n">
-        <v>0.167</v>
+        <v>0.1506</v>
       </c>
       <c r="J123" t="n">
-        <v>4.008</v>
+        <v>3.6144</v>
       </c>
     </row>
     <row r="124">
@@ -9149,10 +9149,10 @@
         <v>0.92</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.12</v>
+        <v>-0.0997</v>
       </c>
       <c r="J124" t="n">
-        <v>-2.88</v>
+        <v>-2.3928</v>
       </c>
     </row>
     <row r="125">
@@ -9189,10 +9189,10 @@
         <v>0.77</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3924</v>
+        <v>-0.2532</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.4176</v>
+        <v>-6.0768</v>
       </c>
     </row>
     <row r="126">
@@ -9229,10 +9229,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6745</v>
+        <v>-0.4517</v>
       </c>
       <c r="J126" t="n">
-        <v>-16.188</v>
+        <v>-10.8408</v>
       </c>
     </row>
     <row r="127">
@@ -9269,10 +9269,10 @@
         <v>1.36</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9265</v>
+        <v>0.6845</v>
       </c>
       <c r="J127" t="n">
-        <v>22.236</v>
+        <v>16.428</v>
       </c>
     </row>
     <row r="128">
@@ -9309,10 +9309,10 @@
         <v>1.29</v>
       </c>
       <c r="I128" t="n">
-        <v>0.7658</v>
+        <v>0.5905</v>
       </c>
       <c r="J128" t="n">
-        <v>18.3792</v>
+        <v>14.172</v>
       </c>
     </row>
     <row r="129">
@@ -9349,10 +9349,10 @@
         <v>1.24</v>
       </c>
       <c r="I129" t="n">
-        <v>0.641</v>
+        <v>0.5221</v>
       </c>
       <c r="J129" t="n">
-        <v>15.384</v>
+        <v>12.5304</v>
       </c>
     </row>
     <row r="130">
@@ -9389,10 +9389,10 @@
         <v>1.08</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1754</v>
+        <v>0.2439</v>
       </c>
       <c r="J130" t="n">
-        <v>4.2096</v>
+        <v>5.8536</v>
       </c>
     </row>
     <row r="131">
@@ -9429,10 +9429,10 @@
         <v>1.05</v>
       </c>
       <c r="I131" t="n">
-        <v>0.0818</v>
+        <v>0.1513</v>
       </c>
       <c r="J131" t="n">
-        <v>1.9632</v>
+        <v>3.6312</v>
       </c>
     </row>
     <row r="132">
@@ -9469,10 +9469,10 @@
         <v>1.64</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9054</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="J132" t="n">
-        <v>27.162</v>
+        <v>24.54</v>
       </c>
     </row>
     <row r="133">
@@ -9509,10 +9509,10 @@
         <v>1.35</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5703</v>
+        <v>0.5419</v>
       </c>
       <c r="J133" t="n">
-        <v>17.109</v>
+        <v>16.257</v>
       </c>
     </row>
     <row r="134">
@@ -9549,10 +9549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.3785</v>
+        <v>-0.2338</v>
       </c>
       <c r="J134" t="n">
-        <v>-11.355</v>
+        <v>-7.014</v>
       </c>
     </row>
     <row r="135">
@@ -9589,10 +9589,10 @@
         <v>0.71</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.3314</v>
       </c>
       <c r="J135" t="n">
-        <v>-15.438</v>
+        <v>-9.942</v>
       </c>
     </row>
     <row r="136">
@@ -9629,10 +9629,10 @@
         <v>0.7</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5275</v>
+        <v>-0.3408</v>
       </c>
       <c r="J136" t="n">
-        <v>-15.825</v>
+        <v>-10.224</v>
       </c>
     </row>
     <row r="137">
@@ -9669,10 +9669,10 @@
         <v>1.33</v>
       </c>
       <c r="I137" t="n">
-        <v>0.9137999999999999</v>
+        <v>0.6654</v>
       </c>
       <c r="J137" t="n">
-        <v>27.414</v>
+        <v>19.962</v>
       </c>
     </row>
     <row r="138">
@@ -9709,10 +9709,10 @@
         <v>1.13</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4099</v>
+        <v>0.3742</v>
       </c>
       <c r="J138" t="n">
-        <v>12.297</v>
+        <v>11.226</v>
       </c>
     </row>
     <row r="139">
@@ -9749,10 +9749,10 @@
         <v>1.04</v>
       </c>
       <c r="I139" t="n">
-        <v>0.0974</v>
+        <v>0.143</v>
       </c>
       <c r="J139" t="n">
-        <v>2.922</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="140">
@@ -9789,10 +9789,10 @@
         <v>1.03</v>
       </c>
       <c r="I140" t="n">
-        <v>0.0606</v>
+        <v>0.1085</v>
       </c>
       <c r="J140" t="n">
-        <v>1.818</v>
+        <v>3.255</v>
       </c>
     </row>
     <row r="141">
@@ -9829,10 +9829,10 @@
         <v>0.99</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.1415</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="J141" t="n">
-        <v>-4.245</v>
+        <v>-2.361</v>
       </c>
     </row>
     <row r="142">
@@ -9869,10 +9869,10 @@
         <v>1.35</v>
       </c>
       <c r="I142" t="n">
-        <v>0.6136</v>
+        <v>0.5747</v>
       </c>
       <c r="J142" t="n">
-        <v>16.5672</v>
+        <v>15.5169</v>
       </c>
     </row>
     <row r="143">
@@ -9909,10 +9909,10 @@
         <v>1.04</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1501</v>
+        <v>0.1368</v>
       </c>
       <c r="J143" t="n">
-        <v>4.0527</v>
+        <v>3.6936</v>
       </c>
     </row>
     <row r="144">
@@ -9949,10 +9949,10 @@
         <v>0.85</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2821</v>
+        <v>-0.1781</v>
       </c>
       <c r="J144" t="n">
-        <v>-7.6167</v>
+        <v>-4.8087</v>
       </c>
     </row>
     <row r="145">
@@ -9989,10 +9989,10 @@
         <v>0.77</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4054</v>
+        <v>-0.2586</v>
       </c>
       <c r="J145" t="n">
-        <v>-10.9458</v>
+        <v>-6.9822</v>
       </c>
     </row>
     <row r="146">
@@ -10029,10 +10029,10 @@
         <v>0.57</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6694</v>
+        <v>-0.4475</v>
       </c>
       <c r="J146" t="n">
-        <v>-18.0738</v>
+        <v>-12.0825</v>
       </c>
     </row>
     <row r="147">
@@ -10069,10 +10069,10 @@
         <v>1.59</v>
       </c>
       <c r="I147" t="n">
-        <v>1.3761</v>
+        <v>0.9698</v>
       </c>
       <c r="J147" t="n">
-        <v>37.1547</v>
+        <v>26.1846</v>
       </c>
     </row>
     <row r="148">
@@ -10109,10 +10109,10 @@
         <v>1.35</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8811</v>
+        <v>0.664</v>
       </c>
       <c r="J148" t="n">
-        <v>23.7897</v>
+        <v>17.928</v>
       </c>
     </row>
     <row r="149">
@@ -10149,10 +10149,10 @@
         <v>1.32</v>
       </c>
       <c r="I149" t="n">
-        <v>0.8118</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="J149" t="n">
-        <v>21.9186</v>
+        <v>16.8615</v>
       </c>
     </row>
     <row r="150">
@@ -10189,10 +10189,10 @@
         <v>0.99</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1974</v>
+        <v>-0.1149</v>
       </c>
       <c r="J150" t="n">
-        <v>-5.3298</v>
+        <v>-3.1023</v>
       </c>
     </row>
     <row r="151">
@@ -10229,10 +10229,10 @@
         <v>0.98</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2389</v>
+        <v>-0.1561</v>
       </c>
       <c r="J151" t="n">
-        <v>-6.4503</v>
+        <v>-4.2147</v>
       </c>
     </row>
     <row r="152">
@@ -10269,10 +10269,10 @@
         <v>1.36</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5894</v>
+        <v>0.5563</v>
       </c>
       <c r="J152" t="n">
-        <v>24.7548</v>
+        <v>23.3646</v>
       </c>
     </row>
     <row r="153">
@@ -10309,10 +10309,10 @@
         <v>1.11</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2363</v>
+        <v>0.2612</v>
       </c>
       <c r="J153" t="n">
-        <v>9.9246</v>
+        <v>10.9704</v>
       </c>
     </row>
     <row r="154">
@@ -10349,10 +10349,10 @@
         <v>0.97</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1018</v>
+        <v>-0.0521</v>
       </c>
       <c r="J154" t="n">
-        <v>-4.2756</v>
+        <v>-2.1882</v>
       </c>
     </row>
     <row r="155">
@@ -10389,10 +10389,10 @@
         <v>0.92</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1999</v>
+        <v>-0.114</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.395799999999999</v>
+        <v>-4.788</v>
       </c>
     </row>
     <row r="156">
@@ -10429,10 +10429,10 @@
         <v>0.75</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.458</v>
+        <v>-0.2908</v>
       </c>
       <c r="J156" t="n">
-        <v>-19.236</v>
+        <v>-12.2136</v>
       </c>
     </row>
     <row r="157">
@@ -10469,10 +10469,10 @@
         <v>1.32</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8914</v>
+        <v>0.6515</v>
       </c>
       <c r="J157" t="n">
-        <v>37.4388</v>
+        <v>27.363</v>
       </c>
     </row>
     <row r="158">
@@ -10509,10 +10509,10 @@
         <v>1.13</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4099</v>
+        <v>0.3742</v>
       </c>
       <c r="J158" t="n">
-        <v>17.2158</v>
+        <v>15.7164</v>
       </c>
     </row>
     <row r="159">
@@ -10549,10 +10549,10 @@
         <v>1.12</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3786</v>
+        <v>0.3586</v>
       </c>
       <c r="J159" t="n">
-        <v>15.9012</v>
+        <v>15.0612</v>
       </c>
     </row>
     <row r="160">
@@ -10589,10 +10589,10 @@
         <v>1.08</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2341</v>
+        <v>0.2667</v>
       </c>
       <c r="J160" t="n">
-        <v>9.8322</v>
+        <v>11.2014</v>
       </c>
     </row>
     <row r="161">
@@ -10629,10 +10629,10 @@
         <v>0.87</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5264</v>
+        <v>-0.4634</v>
       </c>
       <c r="J161" t="n">
-        <v>-22.1088</v>
+        <v>-19.4628</v>
       </c>
     </row>
     <row r="162">
@@ -10669,10 +10669,10 @@
         <v>1.53</v>
       </c>
       <c r="I162" t="n">
-        <v>1.2052</v>
+        <v>1.1465</v>
       </c>
       <c r="J162" t="n">
-        <v>26.5144</v>
+        <v>25.223</v>
       </c>
     </row>
     <row r="163">
@@ -10709,10 +10709,10 @@
         <v>1.48</v>
       </c>
       <c r="I163" t="n">
-        <v>1.1029</v>
+        <v>1.0853</v>
       </c>
       <c r="J163" t="n">
-        <v>24.2638</v>
+        <v>23.8766</v>
       </c>
     </row>
     <row r="164">
@@ -10749,10 +10749,10 @@
         <v>1.48</v>
       </c>
       <c r="I164" t="n">
-        <v>1.1029</v>
+        <v>1.0853</v>
       </c>
       <c r="J164" t="n">
-        <v>24.2638</v>
+        <v>23.8766</v>
       </c>
     </row>
     <row r="165">
@@ -10789,10 +10789,10 @@
         <v>1.23</v>
       </c>
       <c r="I165" t="n">
-        <v>0.5032</v>
+        <v>0.6016</v>
       </c>
       <c r="J165" t="n">
-        <v>11.0704</v>
+        <v>13.2352</v>
       </c>
     </row>
     <row r="166">
@@ -10829,10 +10829,10 @@
         <v>1.08</v>
       </c>
       <c r="I166" t="n">
-        <v>0.119</v>
+        <v>0.2074</v>
       </c>
       <c r="J166" t="n">
-        <v>2.618</v>
+        <v>4.5628</v>
       </c>
     </row>
     <row r="167">
@@ -10869,10 +10869,10 @@
         <v>0.97</v>
       </c>
       <c r="I167" t="n">
-        <v>0.0393</v>
+        <v>-0.0072</v>
       </c>
       <c r="J167" t="n">
-        <v>0.8646</v>
+        <v>-0.1584</v>
       </c>
     </row>
     <row r="168">
@@ -10909,10 +10909,10 @@
         <v>0.89</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1106</v>
+        <v>-0.1102</v>
       </c>
       <c r="J168" t="n">
-        <v>-2.4332</v>
+        <v>-2.4244</v>
       </c>
     </row>
     <row r="169">
@@ -10949,10 +10949,10 @@
         <v>0.87</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1447</v>
+        <v>-0.1331</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.1834</v>
+        <v>-2.9282</v>
       </c>
     </row>
     <row r="170">
@@ -10989,10 +10989,10 @@
         <v>0.59</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.6041</v>
+        <v>-0.405</v>
       </c>
       <c r="J170" t="n">
-        <v>-13.2902</v>
+        <v>-8.91</v>
       </c>
     </row>
     <row r="171">
@@ -11029,10 +11029,10 @@
         <v>0.38</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.8686</v>
+        <v>-0.6001</v>
       </c>
       <c r="J171" t="n">
-        <v>-19.1092</v>
+        <v>-13.2022</v>
       </c>
     </row>
     <row r="172">
@@ -11069,10 +11069,10 @@
         <v>1.09</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2299</v>
+        <v>0.1831</v>
       </c>
       <c r="J172" t="n">
-        <v>6.6671</v>
+        <v>5.3099</v>
       </c>
     </row>
     <row r="173">
@@ -11109,10 +11109,10 @@
         <v>1.04</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1363</v>
+        <v>0.0974</v>
       </c>
       <c r="J173" t="n">
-        <v>3.9527</v>
+        <v>2.8246</v>
       </c>
     </row>
     <row r="174">
@@ -11149,10 +11149,10 @@
         <v>0.97</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0556</v>
+        <v>-0.0464</v>
       </c>
       <c r="J174" t="n">
-        <v>-1.6124</v>
+        <v>-1.3456</v>
       </c>
     </row>
     <row r="175">
@@ -11189,10 +11189,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2448</v>
+        <v>-0.1505</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.0992</v>
+        <v>-4.3645</v>
       </c>
     </row>
     <row r="176">
@@ -11229,10 +11229,10 @@
         <v>0.77</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4145</v>
+        <v>-0.2628</v>
       </c>
       <c r="J176" t="n">
-        <v>-12.0205</v>
+        <v>-7.6212</v>
       </c>
     </row>
     <row r="177">
@@ -11269,10 +11269,10 @@
         <v>1.31</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4994</v>
+        <v>0.4271</v>
       </c>
       <c r="J177" t="n">
-        <v>14.4826</v>
+        <v>12.3859</v>
       </c>
     </row>
     <row r="178">
@@ -11309,10 +11309,10 @@
         <v>1.2</v>
       </c>
       <c r="I178" t="n">
-        <v>0.3472</v>
+        <v>0.2926</v>
       </c>
       <c r="J178" t="n">
-        <v>10.0688</v>
+        <v>8.4854</v>
       </c>
     </row>
     <row r="179">
@@ -11349,10 +11349,10 @@
         <v>1.06</v>
       </c>
       <c r="I179" t="n">
-        <v>0.096</v>
+        <v>0.1042</v>
       </c>
       <c r="J179" t="n">
-        <v>2.784</v>
+        <v>3.0218</v>
       </c>
     </row>
     <row r="180">
@@ -11389,10 +11389,10 @@
         <v>0.99</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0813</v>
+        <v>-0.0303</v>
       </c>
       <c r="J180" t="n">
-        <v>-2.3577</v>
+        <v>-0.8787</v>
       </c>
     </row>
     <row r="181">
@@ -11429,10 +11429,10 @@
         <v>0.96</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1485</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="J181" t="n">
-        <v>-4.3065</v>
+        <v>-2.1431</v>
       </c>
     </row>
     <row r="182">
@@ -11469,10 +11469,10 @@
         <v>1.33</v>
       </c>
       <c r="I182" t="n">
-        <v>0.849</v>
+        <v>0.8558</v>
       </c>
       <c r="J182" t="n">
-        <v>22.923</v>
+        <v>23.1066</v>
       </c>
     </row>
     <row r="183">
@@ -11509,10 +11509,10 @@
         <v>1.26</v>
       </c>
       <c r="I183" t="n">
-        <v>0.68</v>
+        <v>0.696</v>
       </c>
       <c r="J183" t="n">
-        <v>18.36</v>
+        <v>18.792</v>
       </c>
     </row>
     <row r="184">
@@ -11549,10 +11549,10 @@
         <v>1.26</v>
       </c>
       <c r="I184" t="n">
-        <v>0.68</v>
+        <v>0.696</v>
       </c>
       <c r="J184" t="n">
-        <v>18.36</v>
+        <v>18.792</v>
       </c>
     </row>
     <row r="185">
@@ -11589,10 +11589,10 @@
         <v>1.2</v>
       </c>
       <c r="I185" t="n">
-        <v>0.502</v>
+        <v>0.5571</v>
       </c>
       <c r="J185" t="n">
-        <v>13.554</v>
+        <v>15.0417</v>
       </c>
     </row>
     <row r="186">
@@ -11629,10 +11629,10 @@
         <v>1.06</v>
       </c>
       <c r="I186" t="n">
-        <v>0.1064</v>
+        <v>0.1788</v>
       </c>
       <c r="J186" t="n">
-        <v>2.8728</v>
+        <v>4.8276</v>
       </c>
     </row>
     <row r="187">
@@ -11669,10 +11669,10 @@
         <v>1.23</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4358</v>
+        <v>0.5033</v>
       </c>
       <c r="J187" t="n">
-        <v>11.7666</v>
+        <v>13.5891</v>
       </c>
     </row>
     <row r="188">
@@ -11709,10 +11709,10 @@
         <v>1.02</v>
       </c>
       <c r="I188" t="n">
-        <v>0.0822</v>
+        <v>0.0712</v>
       </c>
       <c r="J188" t="n">
-        <v>2.2194</v>
+        <v>1.9224</v>
       </c>
     </row>
     <row r="189">
@@ -11749,10 +11749,10 @@
         <v>0.99</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0165</v>
+        <v>-0.0188</v>
       </c>
       <c r="J189" t="n">
-        <v>-0.4455</v>
+        <v>-0.5076000000000001</v>
       </c>
     </row>
     <row r="190">
@@ -11789,10 +11789,10 @@
         <v>0.91</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2006</v>
+        <v>-0.12</v>
       </c>
       <c r="J190" t="n">
-        <v>-5.4162</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="191">
@@ -11829,10 +11829,10 @@
         <v>0.71</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5018</v>
+        <v>-0.3235</v>
       </c>
       <c r="J191" t="n">
-        <v>-13.5486</v>
+        <v>-8.734500000000001</v>
       </c>
     </row>
     <row r="192">
@@ -11869,10 +11869,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.213</v>
+        <v>-0.1848</v>
       </c>
       <c r="J192" t="n">
-        <v>-3.834</v>
+        <v>-3.3264</v>
       </c>
     </row>
     <row r="193">
@@ -11909,10 +11909,10 @@
         <v>0.78</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.2608</v>
+        <v>-0.2165</v>
       </c>
       <c r="J193" t="n">
-        <v>-4.6944</v>
+        <v>-3.897</v>
       </c>
     </row>
     <row r="194">
@@ -11949,10 +11949,10 @@
         <v>0.71</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.3744</v>
+        <v>-0.2859</v>
       </c>
       <c r="J194" t="n">
-        <v>-6.7392</v>
+        <v>-5.1462</v>
       </c>
     </row>
     <row r="195">
@@ -11989,10 +11989,10 @@
         <v>0.7</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3917</v>
+        <v>-0.2953</v>
       </c>
       <c r="J195" t="n">
-        <v>-7.0506</v>
+        <v>-5.3154</v>
       </c>
     </row>
     <row r="196">
@@ -12029,10 +12029,10 @@
         <v>0.4</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.8337</v>
+        <v>-0.5732</v>
       </c>
       <c r="J196" t="n">
-        <v>-15.0066</v>
+        <v>-10.3176</v>
       </c>
     </row>
     <row r="197">
@@ -12069,10 +12069,10 @@
         <v>1.92</v>
       </c>
       <c r="I197" t="n">
-        <v>1.0553</v>
+        <v>0.976</v>
       </c>
       <c r="J197" t="n">
-        <v>18.9954</v>
+        <v>17.568</v>
       </c>
     </row>
     <row r="198">
@@ -12109,10 +12109,10 @@
         <v>1.54</v>
       </c>
       <c r="I198" t="n">
-        <v>0.633</v>
+        <v>0.6189</v>
       </c>
       <c r="J198" t="n">
-        <v>11.394</v>
+        <v>11.1402</v>
       </c>
     </row>
     <row r="199">
@@ -12149,10 +12149,10 @@
         <v>1.53</v>
       </c>
       <c r="I199" t="n">
-        <v>0.6201</v>
+        <v>0.6091</v>
       </c>
       <c r="J199" t="n">
-        <v>11.1618</v>
+        <v>10.9638</v>
       </c>
     </row>
     <row r="200">
@@ -12189,10 +12189,10 @@
         <v>1.48</v>
       </c>
       <c r="I200" t="n">
-        <v>0.5586</v>
+        <v>0.5589</v>
       </c>
       <c r="J200" t="n">
-        <v>10.0548</v>
+        <v>10.0602</v>
       </c>
     </row>
     <row r="201">
@@ -12229,10 +12229,10 @@
         <v>1.33</v>
       </c>
       <c r="I201" t="n">
-        <v>0.3782</v>
+        <v>0.3983</v>
       </c>
       <c r="J201" t="n">
-        <v>6.8076</v>
+        <v>7.1694</v>
       </c>
     </row>
     <row r="202">
@@ -12269,10 +12269,10 @@
         <v>1.37</v>
       </c>
       <c r="I202" t="n">
-        <v>0.9771</v>
+        <v>0.9656</v>
       </c>
       <c r="J202" t="n">
-        <v>21.4962</v>
+        <v>21.2432</v>
       </c>
     </row>
     <row r="203">
@@ -12309,10 +12309,10 @@
         <v>1.32</v>
       </c>
       <c r="I203" t="n">
-        <v>0.8662</v>
+        <v>0.8555</v>
       </c>
       <c r="J203" t="n">
-        <v>19.0564</v>
+        <v>18.821</v>
       </c>
     </row>
     <row r="204">
@@ -12349,10 +12349,10 @@
         <v>1.28</v>
       </c>
       <c r="I204" t="n">
-        <v>0.7736</v>
+        <v>0.7618</v>
       </c>
       <c r="J204" t="n">
-        <v>17.0192</v>
+        <v>16.7596</v>
       </c>
     </row>
     <row r="205">
@@ -12389,10 +12389,10 @@
         <v>1.11</v>
       </c>
       <c r="I205" t="n">
-        <v>0.2945</v>
+        <v>0.3415</v>
       </c>
       <c r="J205" t="n">
-        <v>6.479</v>
+        <v>7.513</v>
       </c>
     </row>
     <row r="206">
@@ -12429,10 +12429,10 @@
         <v>0.67</v>
       </c>
       <c r="I206" t="n">
-        <v>-1.0096</v>
+        <v>-0.9857</v>
       </c>
       <c r="J206" t="n">
-        <v>-22.2112</v>
+        <v>-21.6854</v>
       </c>
     </row>
     <row r="207">
@@ -12469,10 +12469,10 @@
         <v>1.56</v>
       </c>
       <c r="I207" t="n">
-        <v>0.8428</v>
+        <v>1.0391</v>
       </c>
       <c r="J207" t="n">
-        <v>18.5416</v>
+        <v>22.8602</v>
       </c>
     </row>
     <row r="208">
@@ -12509,10 +12509,10 @@
         <v>0.9</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.2169</v>
+        <v>-0.1307</v>
       </c>
       <c r="J208" t="n">
-        <v>-4.7718</v>
+        <v>-2.8754</v>
       </c>
     </row>
     <row r="209">
@@ -12549,10 +12549,10 @@
         <v>0.83</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.331</v>
+        <v>-0.2049</v>
       </c>
       <c r="J209" t="n">
-        <v>-7.282</v>
+        <v>-4.5078</v>
       </c>
     </row>
     <row r="210">
@@ -12589,10 +12589,10 @@
         <v>0.82</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3461</v>
+        <v>-0.2151</v>
       </c>
       <c r="J210" t="n">
-        <v>-7.6142</v>
+        <v>-4.7322</v>
       </c>
     </row>
     <row r="211">
@@ -12629,10 +12629,10 @@
         <v>0.73</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4741</v>
+        <v>-0.3039</v>
       </c>
       <c r="J211" t="n">
-        <v>-10.4302</v>
+        <v>-6.6858</v>
       </c>
     </row>
     <row r="212">
@@ -12669,10 +12669,10 @@
         <v>1.24</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7008</v>
+        <v>0.6788</v>
       </c>
       <c r="J212" t="n">
-        <v>20.3232</v>
+        <v>19.6852</v>
       </c>
     </row>
     <row r="213">
@@ -12709,10 +12709,10 @@
         <v>1.2</v>
       </c>
       <c r="I213" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="J213" t="n">
-        <v>17.4087</v>
+        <v>16.8229</v>
       </c>
     </row>
     <row r="214">
@@ -12749,10 +12749,10 @@
         <v>1.1</v>
       </c>
       <c r="I214" t="n">
-        <v>0.296</v>
+        <v>0.3218</v>
       </c>
       <c r="J214" t="n">
-        <v>8.584</v>
+        <v>9.3322</v>
       </c>
     </row>
     <row r="215">
@@ -12789,10 +12789,10 @@
         <v>1.08</v>
       </c>
       <c r="I215" t="n">
-        <v>0.2293</v>
+        <v>0.2655</v>
       </c>
       <c r="J215" t="n">
-        <v>6.6497</v>
+        <v>7.6995</v>
       </c>
     </row>
     <row r="216">
@@ -12829,10 +12829,10 @@
         <v>0.93</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3582</v>
+        <v>-0.2904</v>
       </c>
       <c r="J216" t="n">
-        <v>-10.3878</v>
+        <v>-8.4216</v>
       </c>
     </row>
     <row r="217">
@@ -12869,10 +12869,10 @@
         <v>1.31</v>
       </c>
       <c r="I217" t="n">
-        <v>0.5359</v>
+        <v>0.6377</v>
       </c>
       <c r="J217" t="n">
-        <v>15.5411</v>
+        <v>18.4933</v>
       </c>
     </row>
     <row r="218">
@@ -12909,10 +12909,10 @@
         <v>1.19</v>
       </c>
       <c r="I218" t="n">
-        <v>0.3719</v>
+        <v>0.4228</v>
       </c>
       <c r="J218" t="n">
-        <v>10.7851</v>
+        <v>12.2612</v>
       </c>
     </row>
     <row r="219">
@@ -12949,10 +12949,10 @@
         <v>0.84</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3223</v>
+        <v>-0.1974</v>
       </c>
       <c r="J219" t="n">
-        <v>-9.3467</v>
+        <v>-5.7246</v>
       </c>
     </row>
     <row r="220">
@@ -12989,10 +12989,10 @@
         <v>0.84</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3223</v>
+        <v>-0.1974</v>
       </c>
       <c r="J220" t="n">
-        <v>-9.3467</v>
+        <v>-5.7246</v>
       </c>
     </row>
     <row r="221">
@@ -13029,10 +13029,10 @@
         <v>0.78</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4103</v>
+        <v>-0.258</v>
       </c>
       <c r="J221" t="n">
-        <v>-11.8987</v>
+        <v>-7.482</v>
       </c>
     </row>
     <row r="222">
@@ -13069,10 +13069,10 @@
         <v>1.22</v>
       </c>
       <c r="I222" t="n">
-        <v>0.4607</v>
+        <v>0.5313</v>
       </c>
       <c r="J222" t="n">
-        <v>11.5175</v>
+        <v>13.2825</v>
       </c>
     </row>
     <row r="223">
@@ -13109,10 +13109,10 @@
         <v>0.83</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.2937</v>
+        <v>-0.1928</v>
       </c>
       <c r="J223" t="n">
-        <v>-7.3425</v>
+        <v>-4.82</v>
       </c>
     </row>
     <row r="224">
@@ -13149,10 +13149,10 @@
         <v>0.8</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.3432</v>
+        <v>-0.2226</v>
       </c>
       <c r="J224" t="n">
-        <v>-8.58</v>
+        <v>-5.565</v>
       </c>
     </row>
     <row r="225">
@@ -13189,10 +13189,10 @@
         <v>0.76</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4046</v>
+        <v>-0.2619</v>
       </c>
       <c r="J225" t="n">
-        <v>-10.115</v>
+        <v>-6.5475</v>
       </c>
     </row>
     <row r="226">
@@ -13229,10 +13229,10 @@
         <v>0.72</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4625</v>
+        <v>-0.3006</v>
       </c>
       <c r="J226" t="n">
-        <v>-11.5625</v>
+        <v>-7.515</v>
       </c>
     </row>
     <row r="227">
@@ -13269,10 +13269,10 @@
         <v>1.59</v>
       </c>
       <c r="I227" t="n">
-        <v>1.409</v>
+        <v>1.2619</v>
       </c>
       <c r="J227" t="n">
-        <v>35.225</v>
+        <v>31.5475</v>
       </c>
     </row>
     <row r="228">
@@ -13309,10 +13309,10 @@
         <v>1.28</v>
       </c>
       <c r="I228" t="n">
-        <v>0.7574</v>
+        <v>0.7533</v>
       </c>
       <c r="J228" t="n">
-        <v>18.935</v>
+        <v>18.8325</v>
       </c>
     </row>
     <row r="229">
@@ -13349,10 +13349,10 @@
         <v>1.23</v>
       </c>
       <c r="I229" t="n">
-        <v>0.6333</v>
+        <v>0.6353</v>
       </c>
       <c r="J229" t="n">
-        <v>15.8325</v>
+        <v>15.8825</v>
       </c>
     </row>
     <row r="230">
@@ -13389,10 +13389,10 @@
         <v>0.91</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4414</v>
+        <v>-0.3687</v>
       </c>
       <c r="J230" t="n">
-        <v>-11.035</v>
+        <v>-9.217499999999999</v>
       </c>
     </row>
     <row r="231">
@@ -13429,10 +13429,10 @@
         <v>0.88</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5238</v>
+        <v>-0.455</v>
       </c>
       <c r="J231" t="n">
-        <v>-13.095</v>
+        <v>-11.375</v>
       </c>
     </row>
     <row r="232">
@@ -13469,10 +13469,10 @@
         <v>0.78</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.206</v>
+        <v>-0.1864</v>
       </c>
       <c r="J232" t="n">
-        <v>-3.708</v>
+        <v>-3.3552</v>
       </c>
     </row>
     <row r="233">
@@ -13509,10 +13509,10 @@
         <v>0.78</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.206</v>
+        <v>-0.1864</v>
       </c>
       <c r="J233" t="n">
-        <v>-3.708</v>
+        <v>-3.3552</v>
       </c>
     </row>
     <row r="234">
@@ -13549,10 +13549,10 @@
         <v>0.72</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.2985</v>
+        <v>-0.252</v>
       </c>
       <c r="J234" t="n">
-        <v>-5.373</v>
+        <v>-4.536</v>
       </c>
     </row>
     <row r="235">
@@ -13589,10 +13589,10 @@
         <v>0.35</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.8738</v>
+        <v>-0.6044</v>
       </c>
       <c r="J235" t="n">
-        <v>-15.7284</v>
+        <v>-10.8792</v>
       </c>
     </row>
     <row r="236">
@@ -13629,10 +13629,10 @@
         <v>0.27</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.9739</v>
+        <v>-0.6821</v>
       </c>
       <c r="J236" t="n">
-        <v>-17.5302</v>
+        <v>-12.2778</v>
       </c>
     </row>
     <row r="237">
@@ -13669,10 +13669,10 @@
         <v>2.22</v>
       </c>
       <c r="I237" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J237" t="n">
-        <v>37.0674</v>
+        <v>33.0084</v>
       </c>
     </row>
     <row r="238">
@@ -13709,10 +13709,10 @@
         <v>1.51</v>
       </c>
       <c r="I238" t="n">
-        <v>1.0238</v>
+        <v>1.099</v>
       </c>
       <c r="J238" t="n">
-        <v>18.4284</v>
+        <v>19.782</v>
       </c>
     </row>
     <row r="239">
@@ -13749,10 +13749,10 @@
         <v>1.46</v>
       </c>
       <c r="I239" t="n">
-        <v>0.9206</v>
+        <v>1.0376</v>
       </c>
       <c r="J239" t="n">
-        <v>16.5708</v>
+        <v>18.6768</v>
       </c>
     </row>
     <row r="240">
@@ -13789,10 +13789,10 @@
         <v>1.4</v>
       </c>
       <c r="I240" t="n">
-        <v>0.7971</v>
+        <v>0.9383</v>
       </c>
       <c r="J240" t="n">
-        <v>14.3478</v>
+        <v>16.8894</v>
       </c>
     </row>
     <row r="241">
@@ -13829,10 +13829,10 @@
         <v>1.33</v>
       </c>
       <c r="I241" t="n">
-        <v>0.6509</v>
+        <v>0.7874</v>
       </c>
       <c r="J241" t="n">
-        <v>11.7162</v>
+        <v>14.1732</v>
       </c>
     </row>
     <row r="242">
@@ -13869,10 +13869,10 @@
         <v>2.23</v>
       </c>
       <c r="I242" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J242" t="n">
-        <v>37.0674</v>
+        <v>33.0084</v>
       </c>
     </row>
     <row r="243">
@@ -13909,10 +13909,10 @@
         <v>1.79</v>
       </c>
       <c r="I243" t="n">
-        <v>1.5932</v>
+        <v>1.412</v>
       </c>
       <c r="J243" t="n">
-        <v>28.6776</v>
+        <v>25.416</v>
       </c>
     </row>
     <row r="244">
@@ -13949,10 +13949,10 @@
         <v>1.51</v>
       </c>
       <c r="I244" t="n">
-        <v>1.0167</v>
+        <v>1.0975</v>
       </c>
       <c r="J244" t="n">
-        <v>18.3006</v>
+        <v>19.755</v>
       </c>
     </row>
     <row r="245">
@@ -13989,10 +13989,10 @@
         <v>1.26</v>
       </c>
       <c r="I245" t="n">
-        <v>0.4963</v>
+        <v>0.6242</v>
       </c>
       <c r="J245" t="n">
-        <v>8.933400000000001</v>
+        <v>11.2356</v>
       </c>
     </row>
     <row r="246">
@@ -14029,10 +14029,10 @@
         <v>1.21</v>
       </c>
       <c r="I246" t="n">
-        <v>0.3847</v>
+        <v>0.5044</v>
       </c>
       <c r="J246" t="n">
-        <v>6.9246</v>
+        <v>9.0792</v>
       </c>
     </row>
     <row r="247">
@@ -14069,10 +14069,10 @@
         <v>0.78</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.1906</v>
+        <v>-0.1757</v>
       </c>
       <c r="J247" t="n">
-        <v>-3.4308</v>
+        <v>-3.1626</v>
       </c>
     </row>
     <row r="248">
@@ -14109,10 +14109,10 @@
         <v>0.6</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.4699</v>
+        <v>-0.3659</v>
       </c>
       <c r="J248" t="n">
-        <v>-8.4582</v>
+        <v>-6.5862</v>
       </c>
     </row>
     <row r="249">
@@ -14149,10 +14149,10 @@
         <v>0.58</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.5037</v>
+        <v>-0.3847</v>
       </c>
       <c r="J249" t="n">
-        <v>-9.066599999999999</v>
+        <v>-6.9246</v>
       </c>
     </row>
     <row r="250">
@@ -14189,10 +14189,10 @@
         <v>0.41</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.7866</v>
+        <v>-0.5414</v>
       </c>
       <c r="J250" t="n">
-        <v>-14.1588</v>
+        <v>-9.745200000000001</v>
       </c>
     </row>
     <row r="251">
@@ -14229,10 +14229,10 @@
         <v>0.4</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.8003</v>
+        <v>-0.551</v>
       </c>
       <c r="J251" t="n">
-        <v>-14.4054</v>
+        <v>-9.917999999999999</v>
       </c>
     </row>
     <row r="252">
@@ -14269,10 +14269,10 @@
         <v>1.65</v>
       </c>
       <c r="I252" t="n">
-        <v>1.4672</v>
+        <v>1.3056</v>
       </c>
       <c r="J252" t="n">
-        <v>33.7456</v>
+        <v>30.0288</v>
       </c>
     </row>
     <row r="253">
@@ -14309,10 +14309,10 @@
         <v>1.33</v>
       </c>
       <c r="I253" t="n">
-        <v>0.8048999999999999</v>
+        <v>0.839</v>
       </c>
       <c r="J253" t="n">
-        <v>18.5127</v>
+        <v>19.297</v>
       </c>
     </row>
     <row r="254">
@@ -14349,10 +14349,10 @@
         <v>1.23</v>
       </c>
       <c r="I254" t="n">
-        <v>0.5344</v>
+        <v>0.6152</v>
       </c>
       <c r="J254" t="n">
-        <v>12.2912</v>
+        <v>14.1496</v>
       </c>
     </row>
     <row r="255">
@@ -14389,10 +14389,10 @@
         <v>1.18</v>
       </c>
       <c r="I255" t="n">
-        <v>0.4084</v>
+        <v>0.4932</v>
       </c>
       <c r="J255" t="n">
-        <v>9.3932</v>
+        <v>11.3436</v>
       </c>
     </row>
     <row r="256">
@@ -14429,10 +14429,10 @@
         <v>1.08</v>
       </c>
       <c r="I256" t="n">
-        <v>0.14</v>
+        <v>0.2225</v>
       </c>
       <c r="J256" t="n">
-        <v>3.22</v>
+        <v>5.1175</v>
       </c>
     </row>
     <row r="257">
@@ -14469,10 +14469,10 @@
         <v>0.96</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.0161</v>
+        <v>-0.0404</v>
       </c>
       <c r="J257" t="n">
-        <v>-0.3703</v>
+        <v>-0.9292</v>
       </c>
     </row>
     <row r="258">
@@ -14509,10 +14509,10 @@
         <v>0.91</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.1116</v>
+        <v>-0.1029</v>
       </c>
       <c r="J258" t="n">
-        <v>-2.5668</v>
+        <v>-2.3667</v>
       </c>
     </row>
     <row r="259">
@@ -14549,10 +14549,10 @@
         <v>0.86</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.2005</v>
+        <v>-0.1581</v>
       </c>
       <c r="J259" t="n">
-        <v>-4.6115</v>
+        <v>-3.6363</v>
       </c>
     </row>
     <row r="260">
@@ -14589,10 +14589,10 @@
         <v>0.82</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2761</v>
+        <v>-0.1982</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.3503</v>
+        <v>-4.5586</v>
       </c>
     </row>
     <row r="261">
@@ -14629,10 +14629,10 @@
         <v>0.54</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.6886</v>
+        <v>-0.4629</v>
       </c>
       <c r="J261" t="n">
-        <v>-15.8378</v>
+        <v>-10.6467</v>
       </c>
     </row>
     <row r="262">
@@ -14669,10 +14669,10 @@
         <v>1.08</v>
       </c>
       <c r="I262" t="n">
-        <v>0.2194</v>
+        <v>0.2235</v>
       </c>
       <c r="J262" t="n">
-        <v>5.7044</v>
+        <v>5.811</v>
       </c>
     </row>
     <row r="263">
@@ -14709,10 +14709,10 @@
         <v>0.98</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.0222</v>
+        <v>-0.0303</v>
       </c>
       <c r="J263" t="n">
-        <v>-0.5772</v>
+        <v>-0.7877999999999999</v>
       </c>
     </row>
     <row r="264">
@@ -14749,10 +14749,10 @@
         <v>0.96</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.0578</v>
       </c>
       <c r="J264" t="n">
-        <v>-1.781</v>
+        <v>-1.5028</v>
       </c>
     </row>
     <row r="265">
@@ -14789,10 +14789,10 @@
         <v>0.95</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.0905</v>
+        <v>-0.0704</v>
       </c>
       <c r="J265" t="n">
-        <v>-2.353</v>
+        <v>-1.8304</v>
       </c>
     </row>
     <row r="266">
@@ -14829,10 +14829,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.52</v>
+        <v>-0.3377</v>
       </c>
       <c r="J266" t="n">
-        <v>-13.52</v>
+        <v>-8.780200000000001</v>
       </c>
     </row>
     <row r="267">
@@ -14869,10 +14869,10 @@
         <v>1.74</v>
       </c>
       <c r="I267" t="n">
-        <v>1.6819</v>
+        <v>1.4458</v>
       </c>
       <c r="J267" t="n">
-        <v>43.7294</v>
+        <v>37.5908</v>
       </c>
     </row>
     <row r="268">
@@ -14909,10 +14909,10 @@
         <v>1.36</v>
       </c>
       <c r="I268" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9327</v>
       </c>
       <c r="J268" t="n">
-        <v>24.31</v>
+        <v>24.2502</v>
       </c>
     </row>
     <row r="269">
@@ -14949,10 +14949,10 @@
         <v>1.02</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.018</v>
+        <v>0.0504</v>
       </c>
       <c r="J269" t="n">
-        <v>-0.468</v>
+        <v>1.3104</v>
       </c>
     </row>
     <row r="270">
@@ -14989,10 +14989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.356</v>
+        <v>-0.2796</v>
       </c>
       <c r="J270" t="n">
-        <v>-9.256</v>
+        <v>-7.2696</v>
       </c>
     </row>
     <row r="271">
@@ -15029,10 +15029,10 @@
         <v>0.88</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5268</v>
+        <v>-0.4575</v>
       </c>
       <c r="J271" t="n">
-        <v>-13.6968</v>
+        <v>-11.895</v>
       </c>
     </row>
     <row r="272">
@@ -15069,10 +15069,10 @@
         <v>1.71</v>
       </c>
       <c r="I272" t="n">
-        <v>1.5184</v>
+        <v>1.3484</v>
       </c>
       <c r="J272" t="n">
-        <v>33.4048</v>
+        <v>29.6648</v>
       </c>
     </row>
     <row r="273">
@@ -15109,10 +15109,10 @@
         <v>1.59</v>
       </c>
       <c r="I273" t="n">
-        <v>1.2914</v>
+        <v>1.2075</v>
       </c>
       <c r="J273" t="n">
-        <v>28.4108</v>
+        <v>26.565</v>
       </c>
     </row>
     <row r="274">
@@ -15149,10 +15149,10 @@
         <v>1.35</v>
       </c>
       <c r="I274" t="n">
-        <v>0.7499</v>
+        <v>0.8611</v>
       </c>
       <c r="J274" t="n">
-        <v>16.4978</v>
+        <v>18.9442</v>
       </c>
     </row>
     <row r="275">
@@ -15189,10 +15189,10 @@
         <v>1.32</v>
       </c>
       <c r="I275" t="n">
-        <v>0.6823</v>
+        <v>0.795</v>
       </c>
       <c r="J275" t="n">
-        <v>15.0106</v>
+        <v>17.49</v>
       </c>
     </row>
     <row r="276">
@@ -15229,10 +15229,10 @@
         <v>1.18</v>
       </c>
       <c r="I276" t="n">
-        <v>0.3587</v>
+        <v>0.4636</v>
       </c>
       <c r="J276" t="n">
-        <v>7.8914</v>
+        <v>10.1992</v>
       </c>
     </row>
     <row r="277">
@@ -15269,10 +15269,10 @@
         <v>0.86</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.1721</v>
+        <v>-0.1488</v>
       </c>
       <c r="J277" t="n">
-        <v>-3.7862</v>
+        <v>-3.2736</v>
       </c>
     </row>
     <row r="278">
@@ -15309,10 +15309,10 @@
         <v>0.84</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.2057</v>
+        <v>-0.1703</v>
       </c>
       <c r="J278" t="n">
-        <v>-4.5254</v>
+        <v>-3.7466</v>
       </c>
     </row>
     <row r="279">
@@ -15349,10 +15349,10 @@
         <v>0.82</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.2392</v>
+        <v>-0.1912</v>
       </c>
       <c r="J279" t="n">
-        <v>-5.2624</v>
+        <v>-4.2064</v>
       </c>
     </row>
     <row r="280">
@@ -15389,10 +15389,10 @@
         <v>0.65</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.528</v>
+        <v>-0.3522</v>
       </c>
       <c r="J280" t="n">
-        <v>-11.616</v>
+        <v>-7.7484</v>
       </c>
     </row>
     <row r="281">
@@ -15429,10 +15429,10 @@
         <v>0.64</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5422</v>
+        <v>-0.3616</v>
       </c>
       <c r="J281" t="n">
-        <v>-11.9284</v>
+        <v>-7.9552</v>
       </c>
     </row>
     <row r="282">
@@ -15469,10 +15469,10 @@
         <v>1.09</v>
       </c>
       <c r="I282" t="n">
-        <v>0.2702</v>
+        <v>0.2777</v>
       </c>
       <c r="J282" t="n">
-        <v>7.0252</v>
+        <v>7.2202</v>
       </c>
     </row>
     <row r="283">
@@ -15509,10 +15509,10 @@
         <v>0.9</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.1433</v>
+        <v>-0.1186</v>
       </c>
       <c r="J283" t="n">
-        <v>-3.7258</v>
+        <v>-3.0836</v>
       </c>
     </row>
     <row r="284">
@@ -15549,10 +15549,10 @@
         <v>0.78</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.3666</v>
+        <v>-0.2398</v>
       </c>
       <c r="J284" t="n">
-        <v>-9.531599999999999</v>
+        <v>-6.2348</v>
       </c>
     </row>
     <row r="285">
@@ -15589,10 +15589,10 @@
         <v>0.77</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.3822</v>
+        <v>-0.2496</v>
       </c>
       <c r="J285" t="n">
-        <v>-9.937200000000001</v>
+        <v>-6.4896</v>
       </c>
     </row>
     <row r="286">
@@ -15629,10 +15629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4987</v>
+        <v>-0.3265</v>
       </c>
       <c r="J286" t="n">
-        <v>-12.9662</v>
+        <v>-8.489000000000001</v>
       </c>
     </row>
     <row r="287">
@@ -15669,10 +15669,10 @@
         <v>1.82</v>
       </c>
       <c r="I287" t="n">
-        <v>1.7482</v>
+        <v>1.4937</v>
       </c>
       <c r="J287" t="n">
-        <v>45.4532</v>
+        <v>38.8362</v>
       </c>
     </row>
     <row r="288">
@@ -15709,10 +15709,10 @@
         <v>1.35</v>
       </c>
       <c r="I288" t="n">
-        <v>0.802</v>
+        <v>0.8735000000000001</v>
       </c>
       <c r="J288" t="n">
-        <v>20.852</v>
+        <v>22.711</v>
       </c>
     </row>
     <row r="289">
@@ -15749,10 +15749,10 @@
         <v>1.27</v>
       </c>
       <c r="I289" t="n">
-        <v>0.6022</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="J289" t="n">
-        <v>15.6572</v>
+        <v>18.1246</v>
       </c>
     </row>
     <row r="290">
@@ -15789,10 +15789,10 @@
         <v>1.26</v>
       </c>
       <c r="I290" t="n">
-        <v>0.5784</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="J290" t="n">
-        <v>15.0384</v>
+        <v>17.5214</v>
       </c>
     </row>
     <row r="291">
@@ -15829,10 +15829,10 @@
         <v>1.06</v>
       </c>
       <c r="I291" t="n">
-        <v>0.0624</v>
+        <v>0.1483</v>
       </c>
       <c r="J291" t="n">
-        <v>1.6224</v>
+        <v>3.8558</v>
       </c>
     </row>
     <row r="292">
@@ -15869,10 +15869,10 @@
         <v>1.51</v>
       </c>
       <c r="I292" t="n">
-        <v>1.1812</v>
+        <v>1.1277</v>
       </c>
       <c r="J292" t="n">
-        <v>29.53</v>
+        <v>28.1925</v>
       </c>
     </row>
     <row r="293">
@@ -15909,10 +15909,10 @@
         <v>1.49</v>
       </c>
       <c r="I293" t="n">
-        <v>1.1405</v>
+        <v>1.103</v>
       </c>
       <c r="J293" t="n">
-        <v>28.5125</v>
+        <v>27.575</v>
       </c>
     </row>
     <row r="294">
@@ -15949,10 +15949,10 @@
         <v>1.38</v>
       </c>
       <c r="I294" t="n">
-        <v>0.9029</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="J294" t="n">
-        <v>22.5725</v>
+        <v>23.475</v>
       </c>
     </row>
     <row r="295">
@@ -15989,10 +15989,10 @@
         <v>1.26</v>
       </c>
       <c r="I295" t="n">
-        <v>0.5914</v>
+        <v>0.6791</v>
       </c>
       <c r="J295" t="n">
-        <v>14.785</v>
+        <v>16.9775</v>
       </c>
     </row>
     <row r="296">
@@ -16029,10 +16029,10 @@
         <v>0.99</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2208</v>
+        <v>-0.1337</v>
       </c>
       <c r="J296" t="n">
-        <v>-5.52</v>
+        <v>-3.3425</v>
       </c>
     </row>
     <row r="297">
@@ -16069,10 +16069,10 @@
         <v>0.97</v>
       </c>
       <c r="I297" t="n">
-        <v>0.0348</v>
+        <v>-0.0101</v>
       </c>
       <c r="J297" t="n">
-        <v>0.87</v>
+        <v>-0.2525</v>
       </c>
     </row>
     <row r="298">
@@ -16109,10 +16109,10 @@
         <v>0.86</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.1663</v>
+        <v>-0.1464</v>
       </c>
       <c r="J298" t="n">
-        <v>-4.1575</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="299">
@@ -16149,10 +16149,10 @@
         <v>0.84</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1996</v>
+        <v>-0.1681</v>
       </c>
       <c r="J299" t="n">
-        <v>-4.99</v>
+        <v>-4.2025</v>
       </c>
     </row>
     <row r="300">
@@ -16189,10 +16189,10 @@
         <v>0.68</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.4795</v>
+        <v>-0.3222</v>
       </c>
       <c r="J300" t="n">
-        <v>-11.9875</v>
+        <v>-8.055</v>
       </c>
     </row>
     <row r="301">
@@ -16229,10 +16229,10 @@
         <v>0.4</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.8465</v>
+        <v>-0.5829</v>
       </c>
       <c r="J301" t="n">
-        <v>-21.1625</v>
+        <v>-14.5725</v>
       </c>
     </row>
     <row r="302">
@@ -16269,10 +16269,10 @@
         <v>1.22</v>
       </c>
       <c r="I302" t="n">
-        <v>0.4916</v>
+        <v>0.5759</v>
       </c>
       <c r="J302" t="n">
-        <v>10.8152</v>
+        <v>12.6698</v>
       </c>
     </row>
     <row r="303">
@@ -16309,10 +16309,10 @@
         <v>0.74</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.4049</v>
+        <v>-0.2711</v>
       </c>
       <c r="J303" t="n">
-        <v>-8.9078</v>
+        <v>-5.9642</v>
       </c>
     </row>
     <row r="304">
@@ -16349,10 +16349,10 @@
         <v>0.72</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.436</v>
+        <v>-0.2901</v>
       </c>
       <c r="J304" t="n">
-        <v>-9.592000000000001</v>
+        <v>-6.3822</v>
       </c>
     </row>
     <row r="305">
@@ -16389,10 +16389,10 @@
         <v>0.71</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4511</v>
+        <v>-0.2996</v>
       </c>
       <c r="J305" t="n">
-        <v>-9.924200000000001</v>
+        <v>-6.5912</v>
       </c>
     </row>
     <row r="306">
@@ -16429,10 +16429,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.6572</v>
+        <v>-0.4405</v>
       </c>
       <c r="J306" t="n">
-        <v>-14.4584</v>
+        <v>-9.691000000000001</v>
       </c>
     </row>
     <row r="307">
@@ -16469,10 +16469,10 @@
         <v>1.5</v>
       </c>
       <c r="I307" t="n">
-        <v>1.1784</v>
+        <v>1.1219</v>
       </c>
       <c r="J307" t="n">
-        <v>25.9248</v>
+        <v>24.6818</v>
       </c>
     </row>
     <row r="308">
@@ -16509,10 +16509,10 @@
         <v>1.45</v>
       </c>
       <c r="I308" t="n">
-        <v>1.0755</v>
+        <v>1.0589</v>
       </c>
       <c r="J308" t="n">
-        <v>23.661</v>
+        <v>23.2958</v>
       </c>
     </row>
     <row r="309">
@@ -16549,10 +16549,10 @@
         <v>1.3</v>
       </c>
       <c r="I309" t="n">
-        <v>0.7306</v>
+        <v>0.774</v>
       </c>
       <c r="J309" t="n">
-        <v>16.0732</v>
+        <v>17.028</v>
       </c>
     </row>
     <row r="310">
@@ -16589,10 +16589,10 @@
         <v>1.21</v>
       </c>
       <c r="I310" t="n">
-        <v>0.4862</v>
+        <v>0.5681</v>
       </c>
       <c r="J310" t="n">
-        <v>10.6964</v>
+        <v>12.4982</v>
       </c>
     </row>
     <row r="311">
@@ -16629,10 +16629,10 @@
         <v>0.99</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.2108</v>
+        <v>-0.1254</v>
       </c>
       <c r="J311" t="n">
-        <v>-4.6376</v>
+        <v>-2.7588</v>
       </c>
     </row>
     <row r="312">
@@ -16669,10 +16669,10 @@
         <v>1.09</v>
       </c>
       <c r="I312" t="n">
-        <v>0.3133</v>
+        <v>0.3326</v>
       </c>
       <c r="J312" t="n">
-        <v>6.5793</v>
+        <v>6.9846</v>
       </c>
     </row>
     <row r="313">
@@ -16709,10 +16709,10 @@
         <v>1.04</v>
       </c>
       <c r="I313" t="n">
-        <v>0.2216</v>
+        <v>0.2113</v>
       </c>
       <c r="J313" t="n">
-        <v>4.6536</v>
+        <v>4.4373</v>
       </c>
     </row>
     <row r="314">
@@ -16749,10 +16749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.4615</v>
+        <v>-0.312</v>
       </c>
       <c r="J314" t="n">
-        <v>-9.6915</v>
+        <v>-6.552</v>
       </c>
     </row>
     <row r="315">
@@ -16789,10 +16789,10 @@
         <v>0.47</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.7604</v>
+        <v>-0.5174</v>
       </c>
       <c r="J315" t="n">
-        <v>-15.9684</v>
+        <v>-10.8654</v>
       </c>
     </row>
     <row r="316">
@@ -16829,10 +16829,10 @@
         <v>0.43</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.8094</v>
+        <v>-0.5544</v>
       </c>
       <c r="J316" t="n">
-        <v>-16.9974</v>
+        <v>-11.6424</v>
       </c>
     </row>
     <row r="317">
@@ -16869,10 +16869,10 @@
         <v>1.87</v>
       </c>
       <c r="I317" t="n">
-        <v>1.7795</v>
+        <v>1.5208</v>
       </c>
       <c r="J317" t="n">
-        <v>37.3695</v>
+        <v>31.9368</v>
       </c>
     </row>
     <row r="318">
@@ -16909,10 +16909,10 @@
         <v>1.58</v>
       </c>
       <c r="I318" t="n">
-        <v>1.2448</v>
+        <v>1.1881</v>
       </c>
       <c r="J318" t="n">
-        <v>26.1408</v>
+        <v>24.9501</v>
       </c>
     </row>
     <row r="319">
@@ -16949,10 +16949,10 @@
         <v>1.37</v>
       </c>
       <c r="I319" t="n">
-        <v>0.7694</v>
+        <v>0.894</v>
       </c>
       <c r="J319" t="n">
-        <v>16.1574</v>
+        <v>18.774</v>
       </c>
     </row>
     <row r="320">
@@ -16989,10 +16989,10 @@
         <v>1.37</v>
       </c>
       <c r="I320" t="n">
-        <v>0.7694</v>
+        <v>0.894</v>
       </c>
       <c r="J320" t="n">
-        <v>16.1574</v>
+        <v>18.774</v>
       </c>
     </row>
     <row r="321">
@@ -17029,10 +17029,10 @@
         <v>1.24</v>
       </c>
       <c r="I321" t="n">
-        <v>0.4824</v>
+        <v>0.5992</v>
       </c>
       <c r="J321" t="n">
-        <v>10.1304</v>
+        <v>12.5832</v>
       </c>
     </row>
     <row r="322">
@@ -17069,10 +17069,10 @@
         <v>1.19</v>
       </c>
       <c r="I322" t="n">
-        <v>0.4355</v>
+        <v>0.4969</v>
       </c>
       <c r="J322" t="n">
-        <v>10.8875</v>
+        <v>12.4225</v>
       </c>
     </row>
     <row r="323">
@@ -17109,10 +17109,10 @@
         <v>1.19</v>
       </c>
       <c r="I323" t="n">
-        <v>0.4355</v>
+        <v>0.4969</v>
       </c>
       <c r="J323" t="n">
-        <v>10.8875</v>
+        <v>12.4225</v>
       </c>
     </row>
     <row r="324">
@@ -17149,10 +17149,10 @@
         <v>0.82</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.2829</v>
+        <v>-0.1984</v>
       </c>
       <c r="J324" t="n">
-        <v>-7.0725</v>
+        <v>-4.96</v>
       </c>
     </row>
     <row r="325">
@@ -17189,10 +17189,10 @@
         <v>0.55</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.6768999999999999</v>
+        <v>-0.4542</v>
       </c>
       <c r="J325" t="n">
-        <v>-16.9225</v>
+        <v>-11.355</v>
       </c>
     </row>
     <row r="326">
@@ -17229,10 +17229,10 @@
         <v>0.36</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.9029</v>
+        <v>-0.6274</v>
       </c>
       <c r="J326" t="n">
-        <v>-22.5725</v>
+        <v>-15.685</v>
       </c>
     </row>
     <row r="327">
@@ -17269,10 +17269,10 @@
         <v>1.74</v>
       </c>
       <c r="I327" t="n">
-        <v>1.6503</v>
+        <v>1.4252</v>
       </c>
       <c r="J327" t="n">
-        <v>41.2575</v>
+        <v>35.63</v>
       </c>
     </row>
     <row r="328">
@@ -17309,10 +17309,10 @@
         <v>1.34</v>
       </c>
       <c r="I328" t="n">
-        <v>0.8537</v>
+        <v>0.8699</v>
       </c>
       <c r="J328" t="n">
-        <v>21.3425</v>
+        <v>21.7475</v>
       </c>
     </row>
     <row r="329">
@@ -17349,10 +17349,10 @@
         <v>1.12</v>
       </c>
       <c r="I329" t="n">
-        <v>0.2678</v>
+        <v>0.3454</v>
       </c>
       <c r="J329" t="n">
-        <v>6.695</v>
+        <v>8.635</v>
       </c>
     </row>
     <row r="330">
@@ -17389,10 +17389,10 @@
         <v>1.04</v>
       </c>
       <c r="I330" t="n">
-        <v>0.0296</v>
+        <v>0.106</v>
       </c>
       <c r="J330" t="n">
-        <v>0.74</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="331">
@@ -17429,10 +17429,10 @@
         <v>1.03</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.005</v>
+        <v>0.0712</v>
       </c>
       <c r="J331" t="n">
-        <v>-0.125</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="332">
@@ -17469,10 +17469,10 @@
         <v>0.98</v>
       </c>
       <c r="I332" t="n">
-        <v>0.0636</v>
+        <v>0.0171</v>
       </c>
       <c r="J332" t="n">
-        <v>1.272</v>
+        <v>0.342</v>
       </c>
     </row>
     <row r="333">
@@ -17509,10 +17509,10 @@
         <v>0.78</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.2917</v>
+        <v>-0.2273</v>
       </c>
       <c r="J333" t="n">
-        <v>-5.834</v>
+        <v>-4.546</v>
       </c>
     </row>
     <row r="334">
@@ -17549,10 +17549,10 @@
         <v>0.75</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.3439</v>
+        <v>-0.2561</v>
       </c>
       <c r="J334" t="n">
-        <v>-6.878</v>
+        <v>-5.122</v>
       </c>
     </row>
     <row r="335">
@@ -17589,10 +17589,10 @@
         <v>0.72</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.4074</v>
+        <v>-0.2831</v>
       </c>
       <c r="J335" t="n">
-        <v>-8.148</v>
+        <v>-5.662</v>
       </c>
     </row>
     <row r="336">
@@ -17629,10 +17629,10 @@
         <v>0.45</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.7835</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="J336" t="n">
-        <v>-15.67</v>
+        <v>-10.696</v>
       </c>
     </row>
     <row r="337">
@@ -17669,10 +17669,10 @@
         <v>1.69</v>
       </c>
       <c r="I337" t="n">
-        <v>1.5304</v>
+        <v>1.3482</v>
       </c>
       <c r="J337" t="n">
-        <v>30.608</v>
+        <v>26.964</v>
       </c>
     </row>
     <row r="338">
@@ -17709,10 +17709,10 @@
         <v>1.28</v>
       </c>
       <c r="I338" t="n">
-        <v>0.6455</v>
+        <v>0.7262</v>
       </c>
       <c r="J338" t="n">
-        <v>12.91</v>
+        <v>14.524</v>
       </c>
     </row>
     <row r="339">
@@ -17749,10 +17749,10 @@
         <v>1.27</v>
       </c>
       <c r="I339" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.7036</v>
       </c>
       <c r="J339" t="n">
-        <v>12.41</v>
+        <v>14.072</v>
       </c>
     </row>
     <row r="340">
@@ -17789,10 +17789,10 @@
         <v>1.2</v>
       </c>
       <c r="I340" t="n">
-        <v>0.448</v>
+        <v>0.5377</v>
       </c>
       <c r="J340" t="n">
-        <v>8.960000000000001</v>
+        <v>10.754</v>
       </c>
     </row>
     <row r="341">
@@ -17829,10 +17829,10 @@
         <v>1.15</v>
       </c>
       <c r="I341" t="n">
-        <v>0.3217</v>
+        <v>0.4109</v>
       </c>
       <c r="J341" t="n">
-        <v>6.434</v>
+        <v>8.218</v>
       </c>
     </row>
     <row r="342">
@@ -17869,10 +17869,10 @@
         <v>1.22</v>
       </c>
       <c r="I342" t="n">
-        <v>0.4142</v>
+        <v>0.4772</v>
       </c>
       <c r="J342" t="n">
-        <v>11.5976</v>
+        <v>13.3616</v>
       </c>
     </row>
     <row r="343">
@@ -17909,10 +17909,10 @@
         <v>1.2</v>
       </c>
       <c r="I343" t="n">
-        <v>0.3857</v>
+        <v>0.4406</v>
       </c>
       <c r="J343" t="n">
-        <v>10.7996</v>
+        <v>12.3368</v>
       </c>
     </row>
     <row r="344">
@@ -17949,10 +17949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.1529</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="J344" t="n">
-        <v>-4.2812</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="345">
@@ -17989,10 +17989,10 @@
         <v>0.87</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.2758</v>
+        <v>-0.1662</v>
       </c>
       <c r="J345" t="n">
-        <v>-7.7224</v>
+        <v>-4.6536</v>
       </c>
     </row>
     <row r="346">
@@ -18029,10 +18029,10 @@
         <v>0.74</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.466</v>
+        <v>-0.2973</v>
       </c>
       <c r="J346" t="n">
-        <v>-13.048</v>
+        <v>-8.324400000000001</v>
       </c>
     </row>
     <row r="347">
@@ -18069,10 +18069,10 @@
         <v>1.81</v>
       </c>
       <c r="I347" t="n">
-        <v>1.783</v>
+        <v>1.5151</v>
       </c>
       <c r="J347" t="n">
-        <v>49.924</v>
+        <v>42.4228</v>
       </c>
     </row>
     <row r="348">
@@ -18109,10 +18109,10 @@
         <v>1.32</v>
       </c>
       <c r="I348" t="n">
-        <v>0.8177</v>
+        <v>0.8296</v>
       </c>
       <c r="J348" t="n">
-        <v>22.8956</v>
+        <v>23.2288</v>
       </c>
     </row>
     <row r="349">
@@ -18149,10 +18149,10 @@
         <v>1.27</v>
       </c>
       <c r="I349" t="n">
-        <v>0.6956</v>
+        <v>0.7161</v>
       </c>
       <c r="J349" t="n">
-        <v>19.4768</v>
+        <v>20.0508</v>
       </c>
     </row>
     <row r="350">
@@ -18189,10 +18189,10 @@
         <v>0.93</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.4012</v>
+        <v>-0.3228</v>
       </c>
       <c r="J350" t="n">
-        <v>-11.2336</v>
+        <v>-9.038399999999999</v>
       </c>
     </row>
     <row r="351">
@@ -18229,10 +18229,10 @@
         <v>0.85</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.6171</v>
+        <v>-0.5518</v>
       </c>
       <c r="J351" t="n">
-        <v>-17.2788</v>
+        <v>-15.4504</v>
       </c>
     </row>
     <row r="352">
@@ -18269,10 +18269,10 @@
         <v>1.17</v>
       </c>
       <c r="I352" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.5301</v>
       </c>
       <c r="J352" t="n">
-        <v>17.163</v>
+        <v>15.903</v>
       </c>
     </row>
     <row r="353">
@@ -18309,10 +18309,10 @@
         <v>1.11</v>
       </c>
       <c r="I353" t="n">
-        <v>0.4057</v>
+        <v>0.3673</v>
       </c>
       <c r="J353" t="n">
-        <v>12.171</v>
+        <v>11.019</v>
       </c>
     </row>
     <row r="354">
@@ -18349,10 +18349,10 @@
         <v>1</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.0352</v>
+        <v>-0.0056</v>
       </c>
       <c r="J354" t="n">
-        <v>-1.056</v>
+        <v>-0.168</v>
       </c>
     </row>
     <row r="355">
@@ -18389,10 +18389,10 @@
         <v>0.98</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.1423</v>
+        <v>-0.1005</v>
       </c>
       <c r="J355" t="n">
-        <v>-4.269</v>
+        <v>-3.015</v>
       </c>
     </row>
     <row r="356">
@@ -18429,10 +18429,10 @@
         <v>0.89</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.441</v>
+        <v>-0.3862</v>
       </c>
       <c r="J356" t="n">
-        <v>-13.23</v>
+        <v>-11.586</v>
       </c>
     </row>
     <row r="357">
@@ -18469,10 +18469,10 @@
         <v>1.22</v>
       </c>
       <c r="I357" t="n">
-        <v>0.4011</v>
+        <v>0.4651</v>
       </c>
       <c r="J357" t="n">
-        <v>12.033</v>
+        <v>13.953</v>
       </c>
     </row>
     <row r="358">
@@ -18509,10 +18509,10 @@
         <v>1.19</v>
       </c>
       <c r="I358" t="n">
-        <v>0.3579</v>
+        <v>0.4108</v>
       </c>
       <c r="J358" t="n">
-        <v>10.737</v>
+        <v>12.324</v>
       </c>
     </row>
     <row r="359">
@@ -18549,10 +18549,10 @@
         <v>0.96</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.127</v>
+        <v>-0.0664</v>
       </c>
       <c r="J359" t="n">
-        <v>-3.81</v>
+        <v>-1.992</v>
       </c>
     </row>
     <row r="360">
@@ -18589,10 +18589,10 @@
         <v>0.95</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.1472</v>
+        <v>-0.07920000000000001</v>
       </c>
       <c r="J360" t="n">
-        <v>-4.416</v>
+        <v>-2.376</v>
       </c>
     </row>
     <row r="361">
@@ -18629,10 +18629,10 @@
         <v>0.84</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.3323</v>
+        <v>-0.202</v>
       </c>
       <c r="J361" t="n">
-        <v>-9.968999999999999</v>
+        <v>-6.06</v>
       </c>
     </row>
     <row r="362">
@@ -18669,10 +18669,10 @@
         <v>1.14</v>
       </c>
       <c r="I362" t="n">
-        <v>0.2985</v>
+        <v>0.3297</v>
       </c>
       <c r="J362" t="n">
-        <v>8.955</v>
+        <v>9.891</v>
       </c>
     </row>
     <row r="363">
@@ -18709,10 +18709,10 @@
         <v>1.06</v>
       </c>
       <c r="I363" t="n">
-        <v>0.1612</v>
+        <v>0.1648</v>
       </c>
       <c r="J363" t="n">
-        <v>4.836</v>
+        <v>4.944</v>
       </c>
     </row>
     <row r="364">
@@ -18749,10 +18749,10 @@
         <v>1.04</v>
       </c>
       <c r="I364" t="n">
-        <v>0.1209</v>
+        <v>0.1189</v>
       </c>
       <c r="J364" t="n">
-        <v>3.627</v>
+        <v>3.567</v>
       </c>
     </row>
     <row r="365">
@@ -18789,10 +18789,10 @@
         <v>0.98</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.0592</v>
+        <v>-0.0349</v>
       </c>
       <c r="J365" t="n">
-        <v>-1.776</v>
+        <v>-1.047</v>
       </c>
     </row>
     <row r="366">
@@ -18829,10 +18829,10 @@
         <v>0.71</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.5044999999999999</v>
+        <v>-0.3251</v>
       </c>
       <c r="J366" t="n">
-        <v>-15.135</v>
+        <v>-9.753</v>
       </c>
     </row>
     <row r="367">
@@ -18869,10 +18869,10 @@
         <v>1.82</v>
       </c>
       <c r="I367" t="n">
-        <v>1.8342</v>
+        <v>1.5519</v>
       </c>
       <c r="J367" t="n">
-        <v>55.026</v>
+        <v>46.557</v>
       </c>
     </row>
     <row r="368">
@@ -18909,10 +18909,10 @@
         <v>1.37</v>
       </c>
       <c r="I368" t="n">
-        <v>0.9686</v>
+        <v>0.9603</v>
       </c>
       <c r="J368" t="n">
-        <v>29.058</v>
+        <v>28.809</v>
       </c>
     </row>
     <row r="369">
@@ -18949,10 +18949,10 @@
         <v>0.92</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.4087</v>
+        <v>-0.3358</v>
       </c>
       <c r="J369" t="n">
-        <v>-12.261</v>
+        <v>-10.074</v>
       </c>
     </row>
     <row r="370">
@@ -18989,10 +18989,10 @@
         <v>0.88</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.5202</v>
+        <v>-0.4519</v>
       </c>
       <c r="J370" t="n">
-        <v>-15.606</v>
+        <v>-13.557</v>
       </c>
     </row>
     <row r="371">
@@ -19029,10 +19029,10 @@
         <v>0.84</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.6236</v>
+        <v>-0.5616</v>
       </c>
       <c r="J371" t="n">
-        <v>-18.708</v>
+        <v>-16.848</v>
       </c>
     </row>
     <row r="372">
@@ -19069,10 +19069,10 @@
         <v>1.84</v>
       </c>
       <c r="I372" t="n">
-        <v>1.7299</v>
+        <v>1.488</v>
       </c>
       <c r="J372" t="n">
-        <v>36.3279</v>
+        <v>31.248</v>
       </c>
     </row>
     <row r="373">
@@ -19109,10 +19109,10 @@
         <v>1.65</v>
       </c>
       <c r="I373" t="n">
-        <v>1.3847</v>
+        <v>1.2703</v>
       </c>
       <c r="J373" t="n">
-        <v>29.0787</v>
+        <v>26.6763</v>
       </c>
     </row>
     <row r="374">
@@ -19149,10 +19149,10 @@
         <v>1.41</v>
       </c>
       <c r="I374" t="n">
-        <v>0.8593</v>
+        <v>0.9738</v>
       </c>
       <c r="J374" t="n">
-        <v>18.0453</v>
+        <v>20.4498</v>
       </c>
     </row>
     <row r="375">
@@ -19189,10 +19189,10 @@
         <v>1.3</v>
       </c>
       <c r="I375" t="n">
-        <v>0.6187</v>
+        <v>0.7401</v>
       </c>
       <c r="J375" t="n">
-        <v>12.9927</v>
+        <v>15.5421</v>
       </c>
     </row>
     <row r="376">
@@ -19229,10 +19229,10 @@
         <v>1.2</v>
       </c>
       <c r="I376" t="n">
-        <v>0.3918</v>
+        <v>0.5033</v>
       </c>
       <c r="J376" t="n">
-        <v>8.2278</v>
+        <v>10.5693</v>
       </c>
     </row>
     <row r="377">
@@ -19269,10 +19269,10 @@
         <v>1.02</v>
       </c>
       <c r="I377" t="n">
-        <v>0.1869</v>
+        <v>0.1669</v>
       </c>
       <c r="J377" t="n">
-        <v>3.9249</v>
+        <v>3.5049</v>
       </c>
     </row>
     <row r="378">
@@ -19309,10 +19309,10 @@
         <v>0.91</v>
       </c>
       <c r="I378" t="n">
-        <v>-0.0692</v>
+        <v>-0.0829</v>
       </c>
       <c r="J378" t="n">
-        <v>-1.4532</v>
+        <v>-1.7409</v>
       </c>
     </row>
     <row r="379">
@@ -19349,10 +19349,10 @@
         <v>0.77</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.3025</v>
+        <v>-0.2355</v>
       </c>
       <c r="J379" t="n">
-        <v>-6.3525</v>
+        <v>-4.9455</v>
       </c>
     </row>
     <row r="380">
@@ -19389,10 +19389,10 @@
         <v>0.57</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.6268</v>
+        <v>-0.4215</v>
       </c>
       <c r="J380" t="n">
-        <v>-13.1628</v>
+        <v>-8.8515</v>
       </c>
     </row>
     <row r="381">
@@ -19429,10 +19429,10 @@
         <v>0.36</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.8901</v>
+        <v>-0.6168</v>
       </c>
       <c r="J381" t="n">
-        <v>-18.6921</v>
+        <v>-12.9528</v>
       </c>
     </row>
     <row r="382">
@@ -19469,10 +19469,10 @@
         <v>0.99</v>
       </c>
       <c r="I382" t="n">
-        <v>0.0375</v>
+        <v>-0.0023</v>
       </c>
       <c r="J382" t="n">
-        <v>0.9</v>
+        <v>-0.0552</v>
       </c>
     </row>
     <row r="383">
@@ -19509,10 +19509,10 @@
         <v>0.96</v>
       </c>
       <c r="I383" t="n">
-        <v>-0.0318</v>
+        <v>-0.0471</v>
       </c>
       <c r="J383" t="n">
-        <v>-0.7632</v>
+        <v>-1.1304</v>
       </c>
     </row>
     <row r="384">
@@ -19549,10 +19549,10 @@
         <v>0.89</v>
       </c>
       <c r="I384" t="n">
-        <v>-0.1659</v>
+        <v>-0.1307</v>
       </c>
       <c r="J384" t="n">
-        <v>-3.9816</v>
+        <v>-3.1368</v>
       </c>
     </row>
     <row r="385">
@@ -19589,10 +19589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.3217</v>
+        <v>-0.2113</v>
       </c>
       <c r="J385" t="n">
-        <v>-7.7208</v>
+        <v>-5.0712</v>
       </c>
     </row>
     <row r="386">
@@ -19629,10 +19629,10 @@
         <v>0.62</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.5945</v>
+        <v>-0.3935</v>
       </c>
       <c r="J386" t="n">
-        <v>-14.268</v>
+        <v>-9.444000000000001</v>
       </c>
     </row>
     <row r="387">
@@ -19669,10 +19669,10 @@
         <v>1.67</v>
       </c>
       <c r="I387" t="n">
-        <v>1.5035</v>
+        <v>1.3294</v>
       </c>
       <c r="J387" t="n">
-        <v>36.084</v>
+        <v>31.9056</v>
       </c>
     </row>
     <row r="388">
@@ -19709,10 +19709,10 @@
         <v>1.53</v>
       </c>
       <c r="I388" t="n">
-        <v>1.2356</v>
+        <v>1.1581</v>
       </c>
       <c r="J388" t="n">
-        <v>29.6544</v>
+        <v>27.7944</v>
       </c>
     </row>
     <row r="389">
@@ -19749,10 +19749,10 @@
         <v>1.15</v>
       </c>
       <c r="I389" t="n">
-        <v>0.3304</v>
+        <v>0.4159</v>
       </c>
       <c r="J389" t="n">
-        <v>7.9296</v>
+        <v>9.9816</v>
       </c>
     </row>
     <row r="390">
@@ -19789,10 +19789,10 @@
         <v>1.09</v>
       </c>
       <c r="I390" t="n">
-        <v>0.168</v>
+        <v>0.2513</v>
       </c>
       <c r="J390" t="n">
-        <v>4.032</v>
+        <v>6.0312</v>
       </c>
     </row>
     <row r="391">
@@ -19829,10 +19829,10 @@
         <v>1.04</v>
       </c>
       <c r="I391" t="n">
-        <v>0.0157</v>
+        <v>0.096</v>
       </c>
       <c r="J391" t="n">
-        <v>0.3768</v>
+        <v>2.304</v>
       </c>
     </row>
     <row r="392">
@@ -19869,10 +19869,10 @@
         <v>1.49</v>
       </c>
       <c r="I392" t="n">
-        <v>1.249</v>
+        <v>1.1538</v>
       </c>
       <c r="J392" t="n">
-        <v>34.972</v>
+        <v>32.3064</v>
       </c>
     </row>
     <row r="393">
@@ -19909,10 +19909,10 @@
         <v>1.16</v>
       </c>
       <c r="I393" t="n">
-        <v>0.4942</v>
+        <v>0.4793</v>
       </c>
       <c r="J393" t="n">
-        <v>13.8376</v>
+        <v>13.4204</v>
       </c>
     </row>
     <row r="394">
@@ -19949,10 +19949,10 @@
         <v>1</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.0838</v>
+        <v>-0.025</v>
       </c>
       <c r="J394" t="n">
-        <v>-2.3464</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="395">
@@ -19989,10 +19989,10 @@
         <v>0.97</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.2246</v>
+        <v>-0.1581</v>
       </c>
       <c r="J395" t="n">
-        <v>-6.2888</v>
+        <v>-4.4268</v>
       </c>
     </row>
     <row r="396">
@@ -20029,10 +20029,10 @@
         <v>0.92</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.3875</v>
+        <v>-0.3203</v>
       </c>
       <c r="J396" t="n">
-        <v>-10.85</v>
+        <v>-8.968400000000001</v>
       </c>
     </row>
     <row r="397">
@@ -20069,10 +20069,10 @@
         <v>1.31</v>
       </c>
       <c r="I397" t="n">
-        <v>0.5319</v>
+        <v>0.633</v>
       </c>
       <c r="J397" t="n">
-        <v>14.8932</v>
+        <v>17.724</v>
       </c>
     </row>
     <row r="398">
@@ -20109,10 +20109,10 @@
         <v>1.17</v>
       </c>
       <c r="I398" t="n">
-        <v>0.3381</v>
+        <v>0.3817</v>
       </c>
       <c r="J398" t="n">
-        <v>9.466799999999999</v>
+        <v>10.6876</v>
       </c>
     </row>
     <row r="399">
@@ -20149,10 +20149,10 @@
         <v>0.97</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.0941</v>
+        <v>-0.0504</v>
       </c>
       <c r="J399" t="n">
-        <v>-2.6348</v>
+        <v>-1.4112</v>
       </c>
     </row>
     <row r="400">
@@ -20189,10 +20189,10 @@
         <v>0.86</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.2945</v>
+        <v>-0.1779</v>
       </c>
       <c r="J400" t="n">
-        <v>-8.246</v>
+        <v>-4.9812</v>
       </c>
     </row>
     <row r="401">
@@ -20229,10 +20229,10 @@
         <v>0.71</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.5079</v>
+        <v>-0.3272</v>
       </c>
       <c r="J401" t="n">
-        <v>-14.2212</v>
+        <v>-9.1616</v>
       </c>
     </row>
     <row r="402">
@@ -20269,10 +20269,10 @@
         <v>1.03</v>
       </c>
       <c r="I402" t="n">
-        <v>0.1493</v>
+        <v>0.128</v>
       </c>
       <c r="J402" t="n">
-        <v>4.0311</v>
+        <v>3.456</v>
       </c>
     </row>
     <row r="403">
@@ -20309,10 +20309,10 @@
         <v>0.96</v>
       </c>
       <c r="I403" t="n">
-        <v>-0.0371</v>
+        <v>-0.0491</v>
       </c>
       <c r="J403" t="n">
-        <v>-1.0017</v>
+        <v>-1.3257</v>
       </c>
     </row>
     <row r="404">
@@ -20349,10 +20349,10 @@
         <v>0.8</v>
       </c>
       <c r="I404" t="n">
-        <v>-0.3432</v>
+        <v>-0.2226</v>
       </c>
       <c r="J404" t="n">
-        <v>-9.266400000000001</v>
+        <v>-6.0102</v>
       </c>
     </row>
     <row r="405">
@@ -20389,10 +20389,10 @@
         <v>0.79</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.3589</v>
+        <v>-0.2325</v>
       </c>
       <c r="J405" t="n">
-        <v>-9.690300000000001</v>
+        <v>-6.2775</v>
       </c>
     </row>
     <row r="406">
@@ -20429,10 +20429,10 @@
         <v>0.75</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.4193</v>
+        <v>-0.2716</v>
       </c>
       <c r="J406" t="n">
-        <v>-11.3211</v>
+        <v>-7.3332</v>
       </c>
     </row>
     <row r="407">
@@ -20469,10 +20469,10 @@
         <v>1.4</v>
       </c>
       <c r="I407" t="n">
-        <v>1.0031</v>
+        <v>0.9991</v>
       </c>
       <c r="J407" t="n">
-        <v>27.0837</v>
+        <v>26.9757</v>
       </c>
     </row>
     <row r="408">
@@ -20509,10 +20509,10 @@
         <v>1.38</v>
       </c>
       <c r="I408" t="n">
-        <v>0.9598</v>
+        <v>0.9627</v>
       </c>
       <c r="J408" t="n">
-        <v>25.9146</v>
+        <v>25.9929</v>
       </c>
     </row>
     <row r="409">
@@ -20549,10 +20549,10 @@
         <v>1.19</v>
       </c>
       <c r="I409" t="n">
-        <v>0.4727</v>
+        <v>0.5326</v>
       </c>
       <c r="J409" t="n">
-        <v>12.7629</v>
+        <v>14.3802</v>
       </c>
     </row>
     <row r="410">
@@ -20589,10 +20589,10 @@
         <v>1.1</v>
       </c>
       <c r="I410" t="n">
-        <v>0.2249</v>
+        <v>0.2969</v>
       </c>
       <c r="J410" t="n">
-        <v>6.0723</v>
+        <v>8.016299999999999</v>
       </c>
     </row>
     <row r="411">
@@ -20629,10 +20629,10 @@
         <v>1.05</v>
       </c>
       <c r="I411" t="n">
-        <v>0.0737</v>
+        <v>0.1464</v>
       </c>
       <c r="J411" t="n">
-        <v>1.9899</v>
+        <v>3.9528</v>
       </c>
     </row>
     <row r="412">
@@ -20669,10 +20669,10 @@
         <v>1.97</v>
       </c>
       <c r="I412" t="n">
-        <v>1.9512</v>
+        <v>1.6497</v>
       </c>
       <c r="J412" t="n">
-        <v>40.9752</v>
+        <v>34.6437</v>
       </c>
     </row>
     <row r="413">
@@ -20709,10 +20709,10 @@
         <v>1.5</v>
       </c>
       <c r="I413" t="n">
-        <v>1.1158</v>
+        <v>1.102</v>
       </c>
       <c r="J413" t="n">
-        <v>23.4318</v>
+        <v>23.142</v>
       </c>
     </row>
     <row r="414">
@@ -20749,10 +20749,10 @@
         <v>1.35</v>
       </c>
       <c r="I414" t="n">
-        <v>0.7568</v>
+        <v>0.8636</v>
       </c>
       <c r="J414" t="n">
-        <v>15.8928</v>
+        <v>18.1356</v>
       </c>
     </row>
     <row r="415">
@@ -20789,10 +20789,10 @@
         <v>1.21</v>
       </c>
       <c r="I415" t="n">
-        <v>0.4349</v>
+        <v>0.5412</v>
       </c>
       <c r="J415" t="n">
-        <v>9.132899999999999</v>
+        <v>11.3652</v>
       </c>
     </row>
     <row r="416">
@@ -20829,10 +20829,10 @@
         <v>1.05</v>
       </c>
       <c r="I416" t="n">
-        <v>0.0146</v>
+        <v>0.1025</v>
       </c>
       <c r="J416" t="n">
-        <v>0.3066</v>
+        <v>2.1525</v>
       </c>
     </row>
     <row r="417">
@@ -20869,10 +20869,10 @@
         <v>0.8</v>
       </c>
       <c r="I417" t="n">
-        <v>-0.1917</v>
+        <v>-0.1749</v>
       </c>
       <c r="J417" t="n">
-        <v>-4.0257</v>
+        <v>-3.6729</v>
       </c>
     </row>
     <row r="418">
@@ -20909,10 +20909,10 @@
         <v>0.64</v>
       </c>
       <c r="I418" t="n">
-        <v>-0.4439</v>
+        <v>-0.3397</v>
       </c>
       <c r="J418" t="n">
-        <v>-9.321899999999999</v>
+        <v>-7.1337</v>
       </c>
     </row>
     <row r="419">
@@ -20949,10 +20949,10 @@
         <v>0.61</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.503</v>
+        <v>-0.3663</v>
       </c>
       <c r="J419" t="n">
-        <v>-10.563</v>
+        <v>-7.6923</v>
       </c>
     </row>
     <row r="420">
@@ -20989,10 +20989,10 @@
         <v>0.54</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.6244</v>
+        <v>-0.4294</v>
       </c>
       <c r="J420" t="n">
-        <v>-13.1124</v>
+        <v>-9.0174</v>
       </c>
     </row>
     <row r="421">
@@ -21029,10 +21029,10 @@
         <v>0.46</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.7379</v>
+        <v>-0.5047</v>
       </c>
       <c r="J421" t="n">
-        <v>-15.4959</v>
+        <v>-10.5987</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2541/event_2541_evp_summary.xlsx
+++ b/database/event/2541/event_2541_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.6007</v>
+        <v>7.6391</v>
       </c>
       <c r="C2" t="n">
-        <v>4.519</v>
+        <v>4.5419</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7933</v>
+        <v>2.8533</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6007</v>
+        <v>7.6391</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6903</v>
+        <v>2.4639</v>
       </c>
       <c r="G2" t="n">
-        <v>4.9105</v>
+        <v>5.1753</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6903</v>
+        <v>2.6677</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6903</v>
+        <v>2.6677</v>
       </c>
       <c r="J2" t="n">
-        <v>4.9105</v>
+        <v>5.1753</v>
       </c>
       <c r="K2" t="n">
         <v>43</v>
@@ -529,7 +529,7 @@
         <v>205</v>
       </c>
       <c r="M2" t="n">
-        <v>7.6008</v>
+        <v>7.843</v>
       </c>
       <c r="N2" t="n">
         <v>248</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.5446</v>
+        <v>6.8014</v>
       </c>
       <c r="C3" t="n">
-        <v>3.8911</v>
+        <v>4.0438</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3165</v>
+        <v>2.4719</v>
       </c>
       <c r="E3" t="n">
-        <v>6.5446</v>
+        <v>6.8014</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0653</v>
+        <v>2.0155</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4793</v>
+        <v>4.7859</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0653</v>
+        <v>2.0155</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0653</v>
+        <v>2.0155</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4793</v>
+        <v>4.7859</v>
       </c>
       <c r="K3" t="n">
         <v>43</v>
@@ -575,7 +575,7 @@
         <v>205</v>
       </c>
       <c r="M3" t="n">
-        <v>6.544600000000001</v>
+        <v>6.801399999999999</v>
       </c>
       <c r="N3" t="n">
         <v>248</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.1762</v>
+        <v>6.193</v>
       </c>
       <c r="C4" t="n">
-        <v>3.6721</v>
+        <v>3.6821</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1502</v>
+        <v>2.195</v>
       </c>
       <c r="E4" t="n">
-        <v>6.1762</v>
+        <v>6.193</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1621</v>
+        <v>2.8546</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0141</v>
+        <v>3.3384</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5836</v>
+        <v>3.5228</v>
       </c>
       <c r="I4" t="n">
-        <v>3.731</v>
+        <v>3.6136</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0141</v>
+        <v>3.3384</v>
       </c>
       <c r="K4" t="n">
         <v>97</v>
@@ -621,7 +621,7 @@
         <v>198</v>
       </c>
       <c r="M4" t="n">
-        <v>6.7451</v>
+        <v>6.952</v>
       </c>
       <c r="N4" t="n">
         <v>295</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.795</v>
+        <v>5.0241</v>
       </c>
       <c r="C5" t="n">
-        <v>2.8509</v>
+        <v>2.9871</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5267</v>
+        <v>1.6629</v>
       </c>
       <c r="E5" t="n">
-        <v>4.795</v>
+        <v>5.0241</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6228</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1722</v>
+        <v>4.4258</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6228</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6484</v>
+        <v>0.6137</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1722</v>
+        <v>4.4258</v>
       </c>
       <c r="K5" t="n">
         <v>97</v>
@@ -667,7 +667,7 @@
         <v>198</v>
       </c>
       <c r="M5" t="n">
-        <v>4.8206</v>
+        <v>5.039499999999999</v>
       </c>
       <c r="N5" t="n">
         <v>295</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.6488</v>
+        <v>4.7579</v>
       </c>
       <c r="C6" t="n">
-        <v>2.764</v>
+        <v>2.8288</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4607</v>
+        <v>1.5417</v>
       </c>
       <c r="E6" t="n">
-        <v>4.6488</v>
+        <v>4.7579</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2003</v>
+        <v>1.155</v>
       </c>
       <c r="G6" t="n">
-        <v>3.4485</v>
+        <v>3.6029</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2003</v>
+        <v>1.155</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2497</v>
+        <v>1.1848</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4485</v>
+        <v>3.6029</v>
       </c>
       <c r="K6" t="n">
         <v>97</v>
@@ -713,7 +713,7 @@
         <v>198</v>
       </c>
       <c r="M6" t="n">
-        <v>4.6982</v>
+        <v>4.7877</v>
       </c>
       <c r="N6" t="n">
         <v>295</v>
@@ -722,139 +722,139 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0824</v>
+        <v>4.2333</v>
       </c>
       <c r="C7" t="n">
-        <v>2.4272</v>
+        <v>2.5169</v>
       </c>
       <c r="D7" t="n">
-        <v>1.205</v>
+        <v>1.3029</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0824</v>
+        <v>4.2333</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7343</v>
+        <v>2.1186</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3481</v>
+        <v>2.1147</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7343</v>
+        <v>2.1186</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7343</v>
+        <v>2.1732</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3481</v>
+        <v>2.1147</v>
       </c>
       <c r="K7" t="n">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="L7" t="n">
-        <v>109</v>
+        <v>198</v>
       </c>
       <c r="M7" t="n">
-        <v>4.0824</v>
+        <v>4.2879</v>
       </c>
       <c r="N7" t="n">
-        <v>155</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.9983</v>
+        <v>4.0212</v>
       </c>
       <c r="C8" t="n">
-        <v>2.3772</v>
+        <v>2.3908</v>
       </c>
       <c r="D8" t="n">
-        <v>1.167</v>
+        <v>1.2063</v>
       </c>
       <c r="E8" t="n">
-        <v>3.9983</v>
+        <v>4.0212</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0633</v>
+        <v>2.4995</v>
       </c>
       <c r="G8" t="n">
-        <v>1.935</v>
+        <v>1.5217</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0633</v>
+        <v>2.7457</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1482</v>
+        <v>2.7457</v>
       </c>
       <c r="J8" t="n">
-        <v>1.935</v>
+        <v>1.5217</v>
       </c>
       <c r="K8" t="n">
-        <v>97</v>
+        <v>46</v>
       </c>
       <c r="L8" t="n">
-        <v>198</v>
+        <v>109</v>
       </c>
       <c r="M8" t="n">
-        <v>4.0832</v>
+        <v>4.2674</v>
       </c>
       <c r="N8" t="n">
-        <v>295</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5009</v>
+        <v>3.522</v>
       </c>
       <c r="C9" t="n">
-        <v>2.0815</v>
+        <v>2.094</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9425</v>
+        <v>0.9791</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5009</v>
+        <v>3.522</v>
       </c>
       <c r="F9" t="n">
-        <v>2.439</v>
+        <v>1.5063</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0619</v>
+        <v>2.0157</v>
       </c>
       <c r="H9" t="n">
-        <v>2.439</v>
+        <v>1.5063</v>
       </c>
       <c r="I9" t="n">
-        <v>2.439</v>
+        <v>1.5451</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0619</v>
+        <v>2.0157</v>
       </c>
       <c r="K9" t="n">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="L9" t="n">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5009</v>
+        <v>3.5608</v>
       </c>
       <c r="N9" t="n">
-        <v>108</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4103</v>
+        <v>3.5128</v>
       </c>
       <c r="C10" t="n">
-        <v>2.0276</v>
+        <v>2.0886</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9016</v>
+        <v>0.9749</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4103</v>
+        <v>3.5128</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9666</v>
+        <v>1.8903</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4437</v>
+        <v>1.6225</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9666</v>
+        <v>1.8903</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9666</v>
+        <v>1.8903</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4437</v>
+        <v>1.6225</v>
       </c>
       <c r="K10" t="n">
         <v>46</v>
@@ -897,7 +897,7 @@
         <v>109</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4103</v>
+        <v>3.5128</v>
       </c>
       <c r="N10" t="n">
         <v>155</v>
@@ -906,139 +906,139 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.3928</v>
+        <v>3.4847</v>
       </c>
       <c r="C11" t="n">
-        <v>2.0172</v>
+        <v>2.0718</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8937</v>
+        <v>0.9621</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3928</v>
+        <v>3.4847</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5353</v>
+        <v>2.3311</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8575</v>
+        <v>1.1536</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5353</v>
+        <v>2.3772</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5984</v>
+        <v>2.3772</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8575</v>
+        <v>1.1536</v>
       </c>
       <c r="K11" t="n">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="L11" t="n">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4559</v>
+        <v>3.5308</v>
       </c>
       <c r="N11" t="n">
-        <v>212</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.3605</v>
+        <v>3.4</v>
       </c>
       <c r="C12" t="n">
-        <v>1.998</v>
+        <v>2.0215</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8791</v>
+        <v>0.9235</v>
       </c>
       <c r="E12" t="n">
-        <v>3.3605</v>
+        <v>3.4</v>
       </c>
       <c r="F12" t="n">
-        <v>3.0228</v>
+        <v>1.5372</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3377</v>
+        <v>1.8628</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2779</v>
+        <v>1.5372</v>
       </c>
       <c r="I12" t="n">
-        <v>3.4127</v>
+        <v>1.5372</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3377</v>
+        <v>1.8628</v>
       </c>
       <c r="K12" t="n">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="L12" t="n">
-        <v>124</v>
+        <v>205</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7504</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>212</v>
+        <v>248</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.3048</v>
+        <v>3.1724</v>
       </c>
       <c r="C13" t="n">
-        <v>1.9649</v>
+        <v>1.8862</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8539</v>
+        <v>0.8199</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3048</v>
+        <v>3.1724</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6012</v>
+        <v>2.7245</v>
       </c>
       <c r="G13" t="n">
-        <v>1.7036</v>
+        <v>0.4479</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6012</v>
+        <v>3.2382</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6012</v>
+        <v>3.3216</v>
       </c>
       <c r="J13" t="n">
-        <v>1.7036</v>
+        <v>0.4479</v>
       </c>
       <c r="K13" t="n">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="L13" t="n">
-        <v>205</v>
+        <v>124</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3048</v>
+        <v>3.7695</v>
       </c>
       <c r="N13" t="n">
-        <v>248</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.2291</v>
+        <v>2.944</v>
       </c>
       <c r="C14" t="n">
-        <v>1.9199</v>
+        <v>1.7504</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8198</v>
+        <v>0.716</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2291</v>
+        <v>2.944</v>
       </c>
       <c r="F14" t="n">
-        <v>3.015</v>
+        <v>2.7269</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2141</v>
+        <v>0.2171</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2606</v>
+        <v>3.2433</v>
       </c>
       <c r="I14" t="n">
-        <v>3.3947</v>
+        <v>3.3269</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2141</v>
+        <v>0.2171</v>
       </c>
       <c r="K14" t="n">
         <v>88</v>
@@ -1081,7 +1081,7 @@
         <v>124</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6088</v>
+        <v>3.544</v>
       </c>
       <c r="N14" t="n">
         <v>212</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.007</v>
+        <v>2.9376</v>
       </c>
       <c r="C15" t="n">
-        <v>1.7878</v>
+        <v>1.7466</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7195</v>
+        <v>0.7131</v>
       </c>
       <c r="E15" t="n">
-        <v>3.007</v>
+        <v>2.9376</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6078</v>
+        <v>2.4692</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3992</v>
+        <v>0.4684</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6078</v>
+        <v>2.6795</v>
       </c>
       <c r="I15" t="n">
-        <v>2.7151</v>
+        <v>2.7485</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3992</v>
+        <v>0.4684</v>
       </c>
       <c r="K15" t="n">
         <v>88</v>
@@ -1127,7 +1127,7 @@
         <v>124</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1143</v>
+        <v>3.2169</v>
       </c>
       <c r="N15" t="n">
         <v>212</v>
@@ -1136,35 +1136,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3373</v>
+        <v>2.2418</v>
       </c>
       <c r="C16" t="n">
-        <v>1.3897</v>
+        <v>1.3329</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4172</v>
+        <v>0.3963</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3373</v>
+        <v>2.2418</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5567</v>
+        <v>1.8708</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2194</v>
+        <v>0.371</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5567</v>
+        <v>1.8708</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6618</v>
+        <v>1.919</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2194</v>
+        <v>0.371</v>
       </c>
       <c r="K16" t="n">
         <v>128</v>
@@ -1173,7 +1173,7 @@
         <v>70</v>
       </c>
       <c r="M16" t="n">
-        <v>2.4424</v>
+        <v>2.29</v>
       </c>
       <c r="N16" t="n">
         <v>198</v>
@@ -1182,81 +1182,81 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.285</v>
+        <v>2.1732</v>
       </c>
       <c r="C17" t="n">
-        <v>1.3586</v>
+        <v>1.2921</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3935</v>
+        <v>0.3651</v>
       </c>
       <c r="E17" t="n">
-        <v>2.285</v>
+        <v>2.1732</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8943</v>
+        <v>0.7911</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3907</v>
+        <v>1.3821</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8943</v>
+        <v>0.7911</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9722</v>
+        <v>0.7911</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3907</v>
+        <v>1.3821</v>
       </c>
       <c r="K17" t="n">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="L17" t="n">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="M17" t="n">
-        <v>2.3629</v>
+        <v>2.1732</v>
       </c>
       <c r="N17" t="n">
-        <v>198</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.2758</v>
+        <v>2.1721</v>
       </c>
       <c r="C18" t="n">
-        <v>1.3531</v>
+        <v>1.2914</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3894</v>
+        <v>0.3646</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2758</v>
+        <v>2.1721</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7912</v>
+        <v>2.4073</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5154</v>
+        <v>-0.2352</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7912</v>
+        <v>2.5438</v>
       </c>
       <c r="I18" t="n">
-        <v>2.906</v>
+        <v>2.6094</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5154</v>
+        <v>-0.2352</v>
       </c>
       <c r="K18" t="n">
         <v>128</v>
@@ -1265,7 +1265,7 @@
         <v>70</v>
       </c>
       <c r="M18" t="n">
-        <v>2.3906</v>
+        <v>2.3742</v>
       </c>
       <c r="N18" t="n">
         <v>198</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.2521</v>
+        <v>2.1247</v>
       </c>
       <c r="C19" t="n">
-        <v>1.339</v>
+        <v>1.2633</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3787</v>
+        <v>0.343</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2521</v>
+        <v>2.1247</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2521</v>
+        <v>2.1247</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2521</v>
+        <v>2.1247</v>
       </c>
       <c r="I19" t="n">
-        <v>2.2521</v>
+        <v>2.1247</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.2521</v>
+        <v>2.1247</v>
       </c>
       <c r="N19" t="n">
         <v>121</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.0769</v>
+        <v>2.0165</v>
       </c>
       <c r="C20" t="n">
-        <v>1.2348</v>
+        <v>1.1989</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2996</v>
+        <v>0.2937</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0769</v>
+        <v>2.0165</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1601</v>
+        <v>2.113</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0832</v>
+        <v>-0.0965</v>
       </c>
       <c r="H20" t="n">
-        <v>2.1601</v>
+        <v>2.113</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1601</v>
+        <v>2.113</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0832</v>
+        <v>-0.0965</v>
       </c>
       <c r="K20" t="n">
         <v>54</v>
@@ -1357,7 +1357,7 @@
         <v>54</v>
       </c>
       <c r="M20" t="n">
-        <v>2.0769</v>
+        <v>2.0165</v>
       </c>
       <c r="N20" t="n">
         <v>108</v>
@@ -1366,127 +1366,127 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.0212</v>
+        <v>2.0141</v>
       </c>
       <c r="C21" t="n">
-        <v>1.2017</v>
+        <v>1.1975</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2745</v>
+        <v>0.2927</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0212</v>
+        <v>2.0141</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0212</v>
+        <v>1.6065</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.4076</v>
       </c>
       <c r="H21" t="n">
-        <v>2.0212</v>
+        <v>1.6065</v>
       </c>
       <c r="I21" t="n">
-        <v>2.0212</v>
+        <v>1.6065</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.4076</v>
       </c>
       <c r="K21" t="n">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M21" t="n">
-        <v>2.0212</v>
+        <v>2.0141</v>
       </c>
       <c r="N21" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.9916</v>
+        <v>1.9962</v>
       </c>
       <c r="C22" t="n">
-        <v>1.1841</v>
+        <v>1.1869</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2611</v>
+        <v>0.2845</v>
       </c>
       <c r="E22" t="n">
-        <v>1.9916</v>
+        <v>1.9962</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1112</v>
+        <v>1.9962</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1196</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.1112</v>
+        <v>1.9962</v>
       </c>
       <c r="I22" t="n">
-        <v>2.198</v>
+        <v>1.9962</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1196</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="L22" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.0784</v>
+        <v>1.9962</v>
       </c>
       <c r="N22" t="n">
-        <v>198</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.9818</v>
+        <v>1.9933</v>
       </c>
       <c r="C23" t="n">
-        <v>1.1783</v>
+        <v>1.1851</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2567</v>
+        <v>0.2832</v>
       </c>
       <c r="E23" t="n">
-        <v>1.9818</v>
+        <v>1.9933</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5838</v>
+        <v>1.4837</v>
       </c>
       <c r="G23" t="n">
-        <v>0.398</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>1.5838</v>
+        <v>1.4837</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5838</v>
+        <v>1.4837</v>
       </c>
       <c r="J23" t="n">
-        <v>0.398</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="K23" t="n">
         <v>50</v>
@@ -1495,7 +1495,7 @@
         <v>69</v>
       </c>
       <c r="M23" t="n">
-        <v>1.9818</v>
+        <v>1.9933</v>
       </c>
       <c r="N23" t="n">
         <v>119</v>
@@ -1504,93 +1504,93 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.9561</v>
+        <v>1.953</v>
       </c>
       <c r="C24" t="n">
-        <v>1.163</v>
+        <v>1.1612</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2451</v>
+        <v>0.2648</v>
       </c>
       <c r="E24" t="n">
-        <v>1.9561</v>
+        <v>1.953</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7816</v>
+        <v>2.4871</v>
       </c>
       <c r="G24" t="n">
-        <v>1.1745</v>
+        <v>-0.5341</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7816</v>
+        <v>2.7186</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7816</v>
+        <v>2.7887</v>
       </c>
       <c r="J24" t="n">
-        <v>1.1745</v>
+        <v>-0.5341</v>
       </c>
       <c r="K24" t="n">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="L24" t="n">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="M24" t="n">
-        <v>1.9561</v>
+        <v>2.2546</v>
       </c>
       <c r="N24" t="n">
-        <v>155</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.9384</v>
+        <v>1.9196</v>
       </c>
       <c r="C25" t="n">
-        <v>1.1525</v>
+        <v>1.1413</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2371</v>
+        <v>0.2496</v>
       </c>
       <c r="E25" t="n">
-        <v>1.9384</v>
+        <v>1.9196</v>
       </c>
       <c r="F25" t="n">
-        <v>1.4777</v>
+        <v>2.0516</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4607</v>
+        <v>-0.132</v>
       </c>
       <c r="H25" t="n">
-        <v>1.4777</v>
+        <v>2.0516</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4777</v>
+        <v>2.1045</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4607</v>
+        <v>-0.132</v>
       </c>
       <c r="K25" t="n">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="L25" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M25" t="n">
-        <v>1.9384</v>
+        <v>1.9725</v>
       </c>
       <c r="N25" t="n">
-        <v>119</v>
+        <v>198</v>
       </c>
     </row>
     <row r="26">
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.6878</v>
+        <v>1.7867</v>
       </c>
       <c r="C26" t="n">
-        <v>1.0035</v>
+        <v>1.0623</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1239</v>
+        <v>0.1891</v>
       </c>
       <c r="E26" t="n">
-        <v>1.6878</v>
+        <v>1.7867</v>
       </c>
       <c r="F26" t="n">
-        <v>1.4374</v>
+        <v>1.3946</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2504</v>
+        <v>0.3921</v>
       </c>
       <c r="H26" t="n">
-        <v>1.4374</v>
+        <v>1.3946</v>
       </c>
       <c r="I26" t="n">
-        <v>1.4374</v>
+        <v>1.3946</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2504</v>
+        <v>0.3921</v>
       </c>
       <c r="K26" t="n">
         <v>43</v>
@@ -1633,7 +1633,7 @@
         <v>205</v>
       </c>
       <c r="M26" t="n">
-        <v>1.6878</v>
+        <v>1.7867</v>
       </c>
       <c r="N26" t="n">
         <v>248</v>
@@ -1642,93 +1642,93 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.6676</v>
+        <v>1.7022</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9915</v>
+        <v>1.0121</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1148</v>
+        <v>0.1507</v>
       </c>
       <c r="E27" t="n">
-        <v>1.6676</v>
+        <v>1.7022</v>
       </c>
       <c r="F27" t="n">
-        <v>1.2894</v>
+        <v>0.955</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3782</v>
+        <v>0.7472</v>
       </c>
       <c r="H27" t="n">
-        <v>1.2894</v>
+        <v>0.955</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2894</v>
+        <v>0.955</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3782</v>
+        <v>0.7472</v>
       </c>
       <c r="K27" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L27" t="n">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="M27" t="n">
-        <v>1.6676</v>
+        <v>1.7022</v>
       </c>
       <c r="N27" t="n">
-        <v>119</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.5877</v>
+        <v>1.6744</v>
       </c>
       <c r="C28" t="n">
-        <v>0.944</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0788</v>
+        <v>0.138</v>
       </c>
       <c r="E28" t="n">
-        <v>1.5877</v>
+        <v>1.6744</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9683</v>
+        <v>1.2482</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6194</v>
+        <v>0.4262</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9683</v>
+        <v>1.2482</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9683</v>
+        <v>1.2482</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6194</v>
+        <v>0.4262</v>
       </c>
       <c r="K28" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L28" t="n">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="M28" t="n">
-        <v>1.5877</v>
+        <v>1.6744</v>
       </c>
       <c r="N28" t="n">
-        <v>155</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29">
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.5445</v>
+        <v>1.466</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9183</v>
+        <v>0.8716</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0593</v>
+        <v>0.0432</v>
       </c>
       <c r="E29" t="n">
-        <v>1.5445</v>
+        <v>1.466</v>
       </c>
       <c r="F29" t="n">
-        <v>1.8552</v>
+        <v>1.7996</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.3107</v>
+        <v>-0.3336</v>
       </c>
       <c r="H29" t="n">
-        <v>1.8552</v>
+        <v>1.7996</v>
       </c>
       <c r="I29" t="n">
-        <v>1.8552</v>
+        <v>1.7996</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.3107</v>
+        <v>-0.3336</v>
       </c>
       <c r="K29" t="n">
         <v>50</v>
@@ -1771,7 +1771,7 @@
         <v>69</v>
       </c>
       <c r="M29" t="n">
-        <v>1.5445</v>
+        <v>1.466</v>
       </c>
       <c r="N29" t="n">
         <v>119</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.3854</v>
+        <v>1.4296</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8237</v>
+        <v>0.85</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0126</v>
+        <v>0.0266</v>
       </c>
       <c r="E30" t="n">
-        <v>1.3854</v>
+        <v>1.4296</v>
       </c>
       <c r="F30" t="n">
-        <v>1.4802</v>
+        <v>1.4252</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0948</v>
+        <v>0.0044</v>
       </c>
       <c r="H30" t="n">
-        <v>1.4802</v>
+        <v>1.4252</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4802</v>
+        <v>1.4252</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.0948</v>
+        <v>0.0044</v>
       </c>
       <c r="K30" t="n">
         <v>46</v>
@@ -1817,7 +1817,7 @@
         <v>109</v>
       </c>
       <c r="M30" t="n">
-        <v>1.3854</v>
+        <v>1.4296</v>
       </c>
       <c r="N30" t="n">
         <v>155</v>
@@ -1826,323 +1826,323 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.2682</v>
+        <v>1.4144</v>
       </c>
       <c r="C31" t="n">
-        <v>0.754</v>
+        <v>0.8409</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0655</v>
+        <v>0.0197</v>
       </c>
       <c r="E31" t="n">
-        <v>1.2682</v>
+        <v>1.4144</v>
       </c>
       <c r="F31" t="n">
-        <v>1.8304</v>
+        <v>0.1879</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.5622</v>
+        <v>1.2265</v>
       </c>
       <c r="H31" t="n">
-        <v>1.8304</v>
+        <v>0.1879</v>
       </c>
       <c r="I31" t="n">
-        <v>1.9057</v>
+        <v>0.1927</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.5622</v>
+        <v>1.2265</v>
       </c>
       <c r="K31" t="n">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="L31" t="n">
-        <v>45</v>
+        <v>198</v>
       </c>
       <c r="M31" t="n">
-        <v>1.3435</v>
+        <v>1.4192</v>
       </c>
       <c r="N31" t="n">
-        <v>165</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>loWel</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.2494</v>
+        <v>1.1912</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7428</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.074</v>
+        <v>-0.0819</v>
       </c>
       <c r="E32" t="n">
-        <v>1.2494</v>
+        <v>1.1912</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2099</v>
+        <v>0.8561</v>
       </c>
       <c r="G32" t="n">
-        <v>1.0395</v>
+        <v>0.3351</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2099</v>
+        <v>0.8561</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2185</v>
+        <v>0.8561</v>
       </c>
       <c r="J32" t="n">
-        <v>1.0395</v>
+        <v>0.3351</v>
       </c>
       <c r="K32" t="n">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="L32" t="n">
-        <v>198</v>
+        <v>54</v>
       </c>
       <c r="M32" t="n">
-        <v>1.258</v>
+        <v>1.1912</v>
       </c>
       <c r="N32" t="n">
-        <v>295</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.2069</v>
+        <v>1.1806</v>
       </c>
       <c r="C33" t="n">
-        <v>0.7176</v>
+        <v>0.7019</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.0868</v>
       </c>
       <c r="E33" t="n">
-        <v>1.2069</v>
+        <v>1.1806</v>
       </c>
       <c r="F33" t="n">
-        <v>1.6643</v>
+        <v>1.8402</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.4574</v>
+        <v>-0.6596</v>
       </c>
       <c r="H33" t="n">
-        <v>1.6643</v>
+        <v>1.8402</v>
       </c>
       <c r="I33" t="n">
-        <v>1.7327</v>
+        <v>1.8402</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.4574</v>
+        <v>-0.6596</v>
       </c>
       <c r="K33" t="n">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="L33" t="n">
-        <v>45</v>
+        <v>205</v>
       </c>
       <c r="M33" t="n">
-        <v>1.2753</v>
+        <v>1.1806</v>
       </c>
       <c r="N33" t="n">
-        <v>165</v>
+        <v>248</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>loWel</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.1687</v>
+        <v>1.1283</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6949</v>
+        <v>0.6708</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1104</v>
+        <v>-0.1106</v>
       </c>
       <c r="E34" t="n">
-        <v>1.1687</v>
+        <v>1.1283</v>
       </c>
       <c r="F34" t="n">
-        <v>0.88</v>
+        <v>1.7304</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2887</v>
+        <v>-0.6021</v>
       </c>
       <c r="H34" t="n">
-        <v>0.88</v>
+        <v>1.7304</v>
       </c>
       <c r="I34" t="n">
-        <v>0.88</v>
+        <v>1.775</v>
       </c>
       <c r="J34" t="n">
-        <v>0.2887</v>
+        <v>-0.6021</v>
       </c>
       <c r="K34" t="n">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="L34" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="M34" t="n">
-        <v>1.1687</v>
+        <v>1.1729</v>
       </c>
       <c r="N34" t="n">
-        <v>108</v>
+        <v>165</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.1299</v>
+        <v>1.114</v>
       </c>
       <c r="C35" t="n">
-        <v>0.6718</v>
+        <v>0.6623</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1279</v>
+        <v>-0.1171</v>
       </c>
       <c r="E35" t="n">
-        <v>1.1299</v>
+        <v>1.114</v>
       </c>
       <c r="F35" t="n">
-        <v>1.1299</v>
+        <v>1.6129</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.4989</v>
       </c>
       <c r="H35" t="n">
-        <v>1.1299</v>
+        <v>1.6129</v>
       </c>
       <c r="I35" t="n">
-        <v>1.1299</v>
+        <v>1.6545</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.4989</v>
       </c>
       <c r="K35" t="n">
-        <v>53</v>
+        <v>120</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M35" t="n">
-        <v>1.1299</v>
+        <v>1.1556</v>
       </c>
       <c r="N35" t="n">
-        <v>53</v>
+        <v>165</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.1021</v>
+        <v>1.0851</v>
       </c>
       <c r="C36" t="n">
-        <v>0.6553</v>
+        <v>0.6452</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1405</v>
+        <v>-0.1302</v>
       </c>
       <c r="E36" t="n">
-        <v>1.1021</v>
+        <v>1.0851</v>
       </c>
       <c r="F36" t="n">
-        <v>1.1021</v>
+        <v>1.0851</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.1021</v>
+        <v>1.0851</v>
       </c>
       <c r="I36" t="n">
-        <v>1.1021</v>
+        <v>1.0851</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.1021</v>
+        <v>1.0851</v>
       </c>
       <c r="N36" t="n">
-        <v>92</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.0224</v>
+        <v>0.9927</v>
       </c>
       <c r="C37" t="n">
-        <v>0.6079</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1765</v>
+        <v>-0.1723</v>
       </c>
       <c r="E37" t="n">
-        <v>1.0224</v>
+        <v>0.9927</v>
       </c>
       <c r="F37" t="n">
-        <v>1.8517</v>
+        <v>0.9927</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.8293</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.8517</v>
+        <v>0.9927</v>
       </c>
       <c r="I37" t="n">
-        <v>1.8517</v>
+        <v>0.9927</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.8293</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="L37" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.0224</v>
+        <v>0.9927</v>
       </c>
       <c r="N37" t="n">
-        <v>248</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8786</v>
+        <v>0.854</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5224</v>
+        <v>0.5078</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2414</v>
+        <v>-0.2354</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8786</v>
+        <v>0.854</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8786</v>
+        <v>0.854</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8786</v>
+        <v>0.854</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8786</v>
+        <v>0.854</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8786</v>
+        <v>0.854</v>
       </c>
       <c r="N38" t="n">
         <v>53</v>
@@ -2194,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pyth</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8542999999999999</v>
+        <v>0.762</v>
       </c>
       <c r="C39" t="n">
-        <v>0.5079</v>
+        <v>0.4531</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2523</v>
+        <v>-0.2773</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8542999999999999</v>
+        <v>0.762</v>
       </c>
       <c r="F39" t="n">
-        <v>1.6314</v>
+        <v>0.8955</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.7771</v>
+        <v>-0.1335</v>
       </c>
       <c r="H39" t="n">
-        <v>1.6314</v>
+        <v>0.8955</v>
       </c>
       <c r="I39" t="n">
-        <v>1.6985</v>
+        <v>0.9186</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.7771</v>
+        <v>-0.1335</v>
       </c>
       <c r="K39" t="n">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="L39" t="n">
-        <v>45</v>
+        <v>124</v>
       </c>
       <c r="M39" t="n">
-        <v>0.9213999999999999</v>
+        <v>0.7850999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>165</v>
+        <v>212</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>pyth</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.7612</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4349</v>
+        <v>0.4526</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3078</v>
+        <v>-0.2777</v>
       </c>
       <c r="E40" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.7612</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8695000000000001</v>
+        <v>1.5689</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.1381</v>
+        <v>-0.8077</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8695000000000001</v>
+        <v>1.5689</v>
       </c>
       <c r="I40" t="n">
-        <v>0.9053</v>
+        <v>1.6093</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.1381</v>
+        <v>-0.8077</v>
       </c>
       <c r="K40" t="n">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="L40" t="n">
-        <v>124</v>
+        <v>45</v>
       </c>
       <c r="M40" t="n">
-        <v>0.7672</v>
+        <v>0.8016</v>
       </c>
       <c r="N40" t="n">
-        <v>212</v>
+        <v>165</v>
       </c>
     </row>
     <row r="41">
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5426</v>
+        <v>0.5034</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3226</v>
+        <v>0.2993</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3931</v>
+        <v>-0.395</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5426</v>
+        <v>0.5034</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5426</v>
+        <v>0.5034</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5426</v>
+        <v>0.5034</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5426</v>
+        <v>0.5034</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.5426</v>
+        <v>0.5034</v>
       </c>
       <c r="N41" t="n">
         <v>121</v>
@@ -2332,231 +2332,231 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>USTILO</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.467</v>
       </c>
       <c r="C42" t="n">
-        <v>0.303</v>
+        <v>0.2777</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.408</v>
+        <v>-0.4116</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.467</v>
       </c>
       <c r="F42" t="n">
-        <v>1.0092</v>
+        <v>0.467</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.4996</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.0092</v>
+        <v>0.467</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0507</v>
+        <v>0.467</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.4996</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="L42" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.5510999999999999</v>
+        <v>0.467</v>
       </c>
       <c r="N42" t="n">
-        <v>165</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>USTILO</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5095</v>
+        <v>0.4663</v>
       </c>
       <c r="C43" t="n">
-        <v>0.3029</v>
+        <v>0.2772</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.408</v>
+        <v>-0.4119</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5095</v>
+        <v>0.4663</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5095</v>
+        <v>0.4663</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5095</v>
+        <v>0.4663</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5095</v>
+        <v>0.4663</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>52</v>
+        <v>134</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.5095</v>
+        <v>0.4663</v>
       </c>
       <c r="N43" t="n">
-        <v>52</v>
+        <v>134</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4895</v>
+        <v>0.4053</v>
       </c>
       <c r="C44" t="n">
-        <v>0.291</v>
+        <v>0.241</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.417</v>
+        <v>-0.4397</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4895</v>
+        <v>0.4053</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4895</v>
+        <v>0.9449</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>-0.5396</v>
       </c>
       <c r="H44" t="n">
-        <v>0.4895</v>
+        <v>0.9449</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4895</v>
+        <v>0.9692</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>-0.5396</v>
       </c>
       <c r="K44" t="n">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M44" t="n">
-        <v>0.4895</v>
+        <v>0.4296</v>
       </c>
       <c r="N44" t="n">
-        <v>134</v>
+        <v>165</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.3782</v>
+        <v>0.4023</v>
       </c>
       <c r="C45" t="n">
-        <v>0.2249</v>
+        <v>0.2392</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4673</v>
+        <v>-0.4411</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3782</v>
+        <v>0.4023</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3782</v>
+        <v>0.9419</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>-0.5396</v>
       </c>
       <c r="H45" t="n">
-        <v>0.3782</v>
+        <v>0.9419</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3782</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>-0.5396</v>
       </c>
       <c r="K45" t="n">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M45" t="n">
-        <v>0.3782</v>
+        <v>0.4266</v>
       </c>
       <c r="N45" t="n">
-        <v>42</v>
+        <v>165</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.3563</v>
+        <v>0.3415</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2118</v>
+        <v>0.203</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4772</v>
+        <v>-0.4687</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3563</v>
+        <v>0.3415</v>
       </c>
       <c r="F46" t="n">
-        <v>0.8559</v>
+        <v>0.3415</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.4996</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.8559</v>
+        <v>0.3415</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8911</v>
+        <v>0.3415</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.4996</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="L46" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.3915</v>
+        <v>0.3415</v>
       </c>
       <c r="N46" t="n">
-        <v>165</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47">
@@ -2566,28 +2566,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.3381</v>
+        <v>0.2889</v>
       </c>
       <c r="C47" t="n">
-        <v>0.201</v>
+        <v>0.1718</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4854</v>
+        <v>-0.4927</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3381</v>
+        <v>0.2889</v>
       </c>
       <c r="F47" t="n">
-        <v>0.3381</v>
+        <v>0.2889</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.3381</v>
+        <v>0.2889</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3381</v>
+        <v>0.2889</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.3381</v>
+        <v>0.2889</v>
       </c>
       <c r="N47" t="n">
         <v>92</v>
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.2882</v>
+        <v>0.173</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1714</v>
+        <v>0.1029</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.5079</v>
+        <v>-0.5455</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2882</v>
+        <v>0.173</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2882</v>
+        <v>0.173</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2882</v>
+        <v>0.173</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2882</v>
+        <v>0.173</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.2882</v>
+        <v>0.173</v>
       </c>
       <c r="N48" t="n">
         <v>93</v>
@@ -2654,93 +2654,93 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.2147</v>
+        <v>0.1617</v>
       </c>
       <c r="C49" t="n">
-        <v>0.1277</v>
+        <v>0.0961</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.5411</v>
+        <v>-0.5506</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2147</v>
+        <v>0.1617</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9191</v>
+        <v>0.9208</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.7044</v>
+        <v>-0.7591</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9191</v>
+        <v>0.9208</v>
       </c>
       <c r="I49" t="n">
-        <v>0.9569</v>
+        <v>0.9208</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.7044</v>
+        <v>-0.7591</v>
       </c>
       <c r="K49" t="n">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="L49" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M49" t="n">
-        <v>0.2524999999999999</v>
+        <v>0.1617</v>
       </c>
       <c r="N49" t="n">
-        <v>198</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.1869</v>
+        <v>0.1536</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1111</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5536</v>
+        <v>-0.5543</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1869</v>
+        <v>0.1536</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9252</v>
+        <v>0.8739</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.7383</v>
+        <v>-0.7203000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>0.9252</v>
+        <v>0.8739</v>
       </c>
       <c r="I50" t="n">
-        <v>0.9252</v>
+        <v>0.8964</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.7383</v>
+        <v>-0.7203000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="L50" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1869000000000001</v>
+        <v>0.1760999999999999</v>
       </c>
       <c r="N50" t="n">
-        <v>119</v>
+        <v>198</v>
       </c>
     </row>
     <row r="51">
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.1207</v>
+        <v>0.1017</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0718</v>
+        <v>0.0605</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5835</v>
+        <v>-0.5779</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1207</v>
+        <v>0.1017</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1207</v>
+        <v>0.1017</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1207</v>
+        <v>0.1017</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1207</v>
+        <v>0.1017</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1207</v>
+        <v>0.1017</v>
       </c>
       <c r="N51" t="n">
         <v>52</v>
@@ -2796,28 +2796,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.0246</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0146</v>
+        <v>0.0047</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.6269</v>
+        <v>-0.6206</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0246</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0246</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0246</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>0.0246</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.0246</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="N52" t="n">
         <v>52</v>
@@ -2838,32 +2838,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.0353</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.021</v>
+        <v>-0.0428</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.654</v>
+        <v>-0.657</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.0353</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.0353</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.0353</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0353</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.0353</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="N53" t="n">
         <v>134</v>
@@ -2884,32 +2884,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.0584</v>
+        <v>-0.1075</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0347</v>
+        <v>-0.0639</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.6644</v>
+        <v>-0.6731</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.0584</v>
+        <v>-0.1075</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.0584</v>
+        <v>-0.1075</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.0584</v>
+        <v>-0.1075</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.0584</v>
+        <v>-0.1075</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.0584</v>
+        <v>-0.1075</v>
       </c>
       <c r="N54" t="n">
         <v>134</v>
@@ -2934,28 +2934,28 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.1246</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0529</v>
+        <v>-0.0741</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6781</v>
+        <v>-0.6808999999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.1246</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.1246</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.1246</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.1246</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.1246</v>
       </c>
       <c r="N55" t="n">
         <v>42</v>
@@ -2976,170 +2976,170 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.2723</v>
+        <v>-0.307</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1619</v>
+        <v>-0.1825</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.7609</v>
+        <v>-0.764</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.2723</v>
+        <v>-0.307</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.2723</v>
+        <v>-0.307</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.2723</v>
+        <v>-0.307</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2723</v>
+        <v>-0.307</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>92</v>
+        <v>134</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.2723</v>
+        <v>-0.307</v>
       </c>
       <c r="N56" t="n">
-        <v>92</v>
+        <v>134</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.2741</v>
+        <v>-0.3263</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.163</v>
+        <v>-0.194</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.7618</v>
+        <v>-0.7727000000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.2741</v>
+        <v>-0.3263</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.2741</v>
+        <v>-0.3263</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.2741</v>
+        <v>-0.3263</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.2741</v>
+        <v>-0.3263</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.2741</v>
+        <v>-0.3263</v>
       </c>
       <c r="N57" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.2912</v>
+        <v>-0.3282</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1731</v>
+        <v>-0.1951</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.7695</v>
+        <v>-0.7736</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.2912</v>
+        <v>-0.3282</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.2912</v>
+        <v>-0.3282</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.2912</v>
+        <v>-0.3282</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2912</v>
+        <v>-0.3282</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.2912</v>
+        <v>-0.3282</v>
       </c>
       <c r="N58" t="n">
-        <v>134</v>
+        <v>93</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.295</v>
+        <v>-0.3617</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1754</v>
+        <v>-0.2151</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.7712</v>
+        <v>-0.7889</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.295</v>
+        <v>-0.3617</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.295</v>
+        <v>-0.3617</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.295</v>
+        <v>-0.3617</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.295</v>
+        <v>-0.3617</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.295</v>
+        <v>-0.3617</v>
       </c>
       <c r="N59" t="n">
         <v>93</v>
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.3226</v>
+        <v>-0.3684</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.1918</v>
+        <v>-0.219</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7837</v>
+        <v>-0.7919</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.3226</v>
+        <v>-0.3684</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.3226</v>
+        <v>-0.3684</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.3226</v>
+        <v>-0.3684</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3226</v>
+        <v>-0.3684</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.3226</v>
+        <v>-0.3684</v>
       </c>
       <c r="N60" t="n">
         <v>41</v>
@@ -3206,47 +3206,47 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.3739</v>
+        <v>-0.4059</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.2223</v>
+        <v>-0.2413</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.8068</v>
+        <v>-0.8090000000000001</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.3739</v>
+        <v>-0.4059</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.3739</v>
+        <v>-0.4059</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.3739</v>
+        <v>-0.4059</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3739</v>
+        <v>-0.4059</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.3739</v>
+        <v>-0.4059</v>
       </c>
       <c r="N61" t="n">
-        <v>93</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62">
@@ -3256,28 +3256,28 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.3763</v>
+        <v>-0.4079</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.2237</v>
+        <v>-0.2425</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.8079</v>
+        <v>-0.8099</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.3763</v>
+        <v>-0.4079</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.3763</v>
+        <v>-0.4079</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.3763</v>
+        <v>-0.4079</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.3763</v>
+        <v>-0.4079</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.3763</v>
+        <v>-0.4079</v>
       </c>
       <c r="N62" t="n">
         <v>53</v>
@@ -3298,185 +3298,185 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.3788</v>
+        <v>-0.4137</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.2252</v>
+        <v>-0.246</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8090000000000001</v>
+        <v>-0.8125</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.3788</v>
+        <v>-0.4137</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.3788</v>
+        <v>-0.4137</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.3788</v>
+        <v>-0.4137</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.3788</v>
+        <v>-0.4137</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>52</v>
+        <v>134</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.3788</v>
+        <v>-0.4137</v>
       </c>
       <c r="N63" t="n">
-        <v>52</v>
+        <v>134</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.3959</v>
+        <v>-0.4253</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.2354</v>
+        <v>-0.2529</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8167</v>
+        <v>-0.8178</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.3959</v>
+        <v>-0.4253</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.3959</v>
+        <v>-0.4253</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.3959</v>
+        <v>-0.4253</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.3959</v>
+        <v>-0.4253</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.3959</v>
+        <v>-0.4253</v>
       </c>
       <c r="N64" t="n">
-        <v>134</v>
+        <v>93</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>dephh</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.458</v>
+        <v>-0.5043</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.2723</v>
+        <v>-0.2998</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8448</v>
+        <v>-0.8538</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.458</v>
+        <v>-0.5043</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.458</v>
+        <v>-0.5043</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.458</v>
+        <v>-0.5043</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.458</v>
+        <v>-0.5043</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.458</v>
+        <v>-0.5043</v>
       </c>
       <c r="N65" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>dephh</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.4731</v>
+        <v>-0.5053</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.2813</v>
+        <v>-0.3004</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8516</v>
+        <v>-0.8542</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.4731</v>
+        <v>-0.5053</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.4731</v>
+        <v>-0.5053</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.4731</v>
+        <v>-0.5053</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4731</v>
+        <v>-0.5053</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.4731</v>
+        <v>-0.5053</v>
       </c>
       <c r="N66" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="67">
@@ -3486,28 +3486,28 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.5046</v>
+        <v>-0.5229</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.3</v>
+        <v>-0.3109</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8658</v>
+        <v>-0.8622</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.5046</v>
+        <v>-0.5229</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.5046</v>
+        <v>-0.5229</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.5046</v>
+        <v>-0.5229</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.5046</v>
+        <v>-0.5229</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.5046</v>
+        <v>-0.5229</v>
       </c>
       <c r="N67" t="n">
         <v>53</v>
@@ -3532,28 +3532,28 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.5646</v>
+        <v>-0.5724</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.3357</v>
+        <v>-0.3403</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8929</v>
+        <v>-0.8848</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.5646</v>
+        <v>-0.5724</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.5646</v>
+        <v>-0.5724</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.5646</v>
+        <v>-0.5724</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.5646</v>
+        <v>-0.5724</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.5646</v>
+        <v>-0.5724</v>
       </c>
       <c r="N68" t="n">
         <v>121</v>
@@ -3578,28 +3578,28 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.5744</v>
+        <v>-0.5753</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.3415</v>
+        <v>-0.342</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8973</v>
+        <v>-0.8861</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.5744</v>
+        <v>-0.5753</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.5744</v>
+        <v>-0.5753</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.5744</v>
+        <v>-0.5753</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.5744</v>
+        <v>-0.5753</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.5744</v>
+        <v>-0.5753</v>
       </c>
       <c r="N69" t="n">
         <v>121</v>
@@ -3620,139 +3620,139 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>desi</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.6625</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.3677</v>
+        <v>-0.3939</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9172</v>
+        <v>-0.9258</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.6625</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.6625</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.6625</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.6625</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.6625</v>
       </c>
       <c r="N70" t="n">
-        <v>93</v>
+        <v>41</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>desi</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.6224</v>
+        <v>-0.6644</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.3701</v>
+        <v>-0.395</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.919</v>
+        <v>-0.9267</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.6224</v>
+        <v>-0.6644</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.6224</v>
+        <v>-0.6644</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.6224</v>
+        <v>-0.6644</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6224</v>
+        <v>-0.6644</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.6224</v>
+        <v>-0.6644</v>
       </c>
       <c r="N71" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.6373</v>
+        <v>-0.6797</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.3789</v>
+        <v>-0.4041</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9257</v>
+        <v>-0.9336</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.6373</v>
+        <v>-0.6797</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.6373</v>
+        <v>-0.6797</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.6373</v>
+        <v>-0.6797</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.6373</v>
+        <v>-0.6797</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.6373</v>
+        <v>-0.6797</v>
       </c>
       <c r="N72" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
     </row>
     <row r="73">
@@ -3762,28 +3762,28 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.6965</v>
+        <v>-0.7328</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.4141</v>
+        <v>-0.4357</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9524</v>
+        <v>-0.9578</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.6965</v>
+        <v>-0.7328</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.6965</v>
+        <v>-0.7328</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.6965</v>
+        <v>-0.7328</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.6965</v>
+        <v>-0.7328</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.6965</v>
+        <v>-0.7328</v>
       </c>
       <c r="N73" t="n">
         <v>92</v>
@@ -3808,28 +3808,28 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.732</v>
+        <v>-0.7645</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.4352</v>
+        <v>-0.4545</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9685</v>
+        <v>-0.9722</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.732</v>
+        <v>-0.7645</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.732</v>
+        <v>-0.7645</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.732</v>
+        <v>-0.7645</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.732</v>
+        <v>-0.7645</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.732</v>
+        <v>-0.7645</v>
       </c>
       <c r="N74" t="n">
         <v>41</v>
@@ -3854,28 +3854,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.7529</v>
+        <v>-0.7816</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.4476</v>
+        <v>-0.4647</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9779</v>
+        <v>-0.98</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.7529</v>
+        <v>-0.7816</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.7529</v>
+        <v>-0.7816</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.7529</v>
+        <v>-0.7816</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.7529</v>
+        <v>-0.7816</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.7529</v>
+        <v>-0.7816</v>
       </c>
       <c r="N75" t="n">
         <v>42</v>
@@ -3900,28 +3900,28 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.7974</v>
+        <v>-0.8044</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.4741</v>
+        <v>-0.4783</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.998</v>
+        <v>-0.9903999999999999</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.7974</v>
+        <v>-0.8044</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.7974</v>
+        <v>-0.8044</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.7974</v>
+        <v>-0.8044</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7974</v>
+        <v>-0.8044</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-0.7974</v>
+        <v>-0.8044</v>
       </c>
       <c r="N76" t="n">
         <v>92</v>
@@ -3946,28 +3946,28 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.9288</v>
+        <v>-0.9487</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.5522</v>
+        <v>-0.5641</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0573</v>
+        <v>-1.0561</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.9288</v>
+        <v>-0.9487</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.9288</v>
+        <v>-0.9487</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.9288</v>
+        <v>-0.9487</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.9288</v>
+        <v>-0.9487</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.9288</v>
+        <v>-0.9487</v>
       </c>
       <c r="N77" t="n">
         <v>42</v>
@@ -3992,28 +3992,28 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.9546</v>
+        <v>-0.9655</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.5676</v>
+        <v>-0.574</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.069</v>
+        <v>-1.0637</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.9546</v>
+        <v>-0.9655</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.9546</v>
+        <v>-0.9655</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.9546</v>
+        <v>-0.9655</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.9546</v>
+        <v>-0.9655</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-0.9546</v>
+        <v>-0.9655</v>
       </c>
       <c r="N78" t="n">
         <v>53</v>
@@ -4038,28 +4038,28 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.9641999999999999</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.5733</v>
+        <v>-0.5877</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.0733</v>
+        <v>-1.0741</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.9641999999999999</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.9641999999999999</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.9641999999999999</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.9641999999999999</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-0.9641999999999999</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="N79" t="n">
         <v>41</v>
@@ -4084,31 +4084,31 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.2208</v>
+        <v>-1.1994</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.7258</v>
+        <v>-0.7131</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.1891</v>
+        <v>-1.1702</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.2208</v>
+        <v>-1.1994</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.7803</v>
+        <v>-0.7336</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.4405</v>
+        <v>-0.4658</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.7803</v>
+        <v>-0.7336</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.7803</v>
+        <v>-0.7336</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.4405</v>
+        <v>-0.4658</v>
       </c>
       <c r="K80" t="n">
         <v>54</v>
@@ -4117,7 +4117,7 @@
         <v>54</v>
       </c>
       <c r="M80" t="n">
-        <v>-1.2208</v>
+        <v>-1.1994</v>
       </c>
       <c r="N80" t="n">
         <v>108</v>
@@ -4130,31 +4130,31 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-1.6145</v>
+        <v>-1.5819</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.9599</v>
+        <v>-0.9405</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.3669</v>
+        <v>-1.3443</v>
       </c>
       <c r="E81" t="n">
-        <v>-1.6145</v>
+        <v>-1.5819</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.8314</v>
+        <v>-0.7789</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.7831</v>
+        <v>-0.803</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.8314</v>
+        <v>-0.7789</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.8314</v>
+        <v>-0.7789</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.7831</v>
+        <v>-0.803</v>
       </c>
       <c r="K81" t="n">
         <v>54</v>
@@ -4163,7 +4163,7 @@
         <v>54</v>
       </c>
       <c r="M81" t="n">
-        <v>-1.6145</v>
+        <v>-1.5819</v>
       </c>
       <c r="N81" t="n">
         <v>108</v>
@@ -4269,10 +4269,10 @@
         <v>1.05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.175</v>
+        <v>0.1671</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2</v>
+        <v>4.0104</v>
       </c>
     </row>
     <row r="3">
@@ -4309,10 +4309,10 @@
         <v>0.88</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1258</v>
+        <v>-0.146</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.0192</v>
+        <v>-3.504</v>
       </c>
     </row>
     <row r="4">
@@ -4349,10 +4349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2007</v>
+        <v>-0.2207</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.8168</v>
+        <v>-5.2968</v>
       </c>
     </row>
     <row r="5">
@@ -4389,10 +4389,10 @@
         <v>0.68</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3234</v>
+        <v>-0.3411</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.7616</v>
+        <v>-8.186400000000001</v>
       </c>
     </row>
     <row r="6">
@@ -4429,10 +4429,10 @@
         <v>0.37</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.6127</v>
       </c>
       <c r="J6" t="n">
-        <v>-14.6736</v>
+        <v>-14.7048</v>
       </c>
     </row>
     <row r="7">
@@ -4469,10 +4469,10 @@
         <v>1.73</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8241000000000001</v>
+        <v>0.8172</v>
       </c>
       <c r="J7" t="n">
-        <v>19.7784</v>
+        <v>19.6128</v>
       </c>
     </row>
     <row r="8">
@@ -4509,10 +4509,10 @@
         <v>1.64</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7339</v>
+        <v>0.7337</v>
       </c>
       <c r="J8" t="n">
-        <v>17.6136</v>
+        <v>17.6088</v>
       </c>
     </row>
     <row r="9">
@@ -4549,10 +4549,10 @@
         <v>1.49</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5807</v>
+        <v>0.5906</v>
       </c>
       <c r="J9" t="n">
-        <v>13.9368</v>
+        <v>14.1744</v>
       </c>
     </row>
     <row r="10">
@@ -4589,10 +4589,10 @@
         <v>1.22</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2855</v>
+        <v>0.3075</v>
       </c>
       <c r="J10" t="n">
-        <v>6.852</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="11">
@@ -4629,10 +4629,10 @@
         <v>0.95</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1144</v>
+        <v>-0.1161</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.7456</v>
+        <v>-2.7864</v>
       </c>
     </row>
     <row r="12">
@@ -4669,10 +4669,10 @@
         <v>1.58</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2371</v>
+        <v>1.2793</v>
       </c>
       <c r="J12" t="n">
-        <v>33.4017</v>
+        <v>34.5411</v>
       </c>
     </row>
     <row r="13">
@@ -4709,10 +4709,10 @@
         <v>1.43</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0455</v>
+        <v>1.0023</v>
       </c>
       <c r="J13" t="n">
-        <v>28.2285</v>
+        <v>27.0621</v>
       </c>
     </row>
     <row r="14">
@@ -4749,10 +4749,10 @@
         <v>1.08</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2395</v>
+        <v>0.253</v>
       </c>
       <c r="J14" t="n">
-        <v>6.4665</v>
+        <v>6.831</v>
       </c>
     </row>
     <row r="15">
@@ -4789,10 +4789,10 @@
         <v>1.08</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2395</v>
+        <v>0.253</v>
       </c>
       <c r="J15" t="n">
-        <v>6.4665</v>
+        <v>6.831</v>
       </c>
     </row>
     <row r="16">
@@ -4829,10 +4829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2882</v>
+        <v>-0.2716</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.7814</v>
+        <v>-7.3332</v>
       </c>
     </row>
     <row r="17">
@@ -4869,10 +4869,10 @@
         <v>1.29</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6645</v>
+        <v>0.6294</v>
       </c>
       <c r="J17" t="n">
-        <v>17.9415</v>
+        <v>16.9938</v>
       </c>
     </row>
     <row r="18">
@@ -4909,10 +4909,10 @@
         <v>0.98</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.02</v>
+        <v>-0.0304</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.54</v>
+        <v>-0.8208</v>
       </c>
     </row>
     <row r="19">
@@ -4949,10 +4949,10 @@
         <v>0.86</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1625</v>
+        <v>-0.1794</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.3875</v>
+        <v>-4.8438</v>
       </c>
     </row>
     <row r="20">
@@ -4989,10 +4989,10 @@
         <v>0.64</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3759</v>
+        <v>-0.3889</v>
       </c>
       <c r="J20" t="n">
-        <v>-10.1493</v>
+        <v>-10.5003</v>
       </c>
     </row>
     <row r="21">
@@ -5029,10 +5029,10 @@
         <v>0.54</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4686</v>
+        <v>-0.4772</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.6522</v>
+        <v>-12.8844</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         <v>1.36</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9552</v>
+        <v>0.8925</v>
       </c>
       <c r="J22" t="n">
-        <v>27.7008</v>
+        <v>25.8825</v>
       </c>
     </row>
     <row r="23">
@@ -5109,10 +5109,10 @@
         <v>1.35</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9342</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>27.0918</v>
+        <v>25.3025</v>
       </c>
     </row>
     <row r="24">
@@ -5149,10 +5149,10 @@
         <v>1.15</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4504</v>
+        <v>0.4426</v>
       </c>
       <c r="J24" t="n">
-        <v>13.0616</v>
+        <v>12.8354</v>
       </c>
     </row>
     <row r="25">
@@ -5189,10 +5189,10 @@
         <v>0.88</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4403</v>
+        <v>-0.4182</v>
       </c>
       <c r="J25" t="n">
-        <v>-12.7687</v>
+        <v>-12.1278</v>
       </c>
     </row>
     <row r="26">
@@ -5229,10 +5229,10 @@
         <v>0.87</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4683</v>
+        <v>-0.4436</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.5807</v>
+        <v>-12.8644</v>
       </c>
     </row>
     <row r="27">
@@ -5269,10 +5269,10 @@
         <v>1.34</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.6449</v>
       </c>
       <c r="J27" t="n">
-        <v>19.3082</v>
+        <v>18.7021</v>
       </c>
     </row>
     <row r="28">
@@ -5309,10 +5309,10 @@
         <v>1.26</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5291</v>
+        <v>0.5203</v>
       </c>
       <c r="J28" t="n">
-        <v>15.3439</v>
+        <v>15.0887</v>
       </c>
     </row>
     <row r="29">
@@ -5349,10 +5349,10 @@
         <v>1.24</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4941</v>
+        <v>0.4882</v>
       </c>
       <c r="J29" t="n">
-        <v>14.3289</v>
+        <v>14.1578</v>
       </c>
     </row>
     <row r="30">
@@ -5389,10 +5389,10 @@
         <v>0.79</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2551</v>
+        <v>-0.2671</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.3979</v>
+        <v>-7.7459</v>
       </c>
     </row>
     <row r="31">
@@ -5429,10 +5429,10 @@
         <v>0.64</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.398</v>
+        <v>-0.4063</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.542</v>
+        <v>-11.7827</v>
       </c>
     </row>
     <row r="32">
@@ -5469,10 +5469,10 @@
         <v>1.09</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2462</v>
+        <v>0.2475</v>
       </c>
       <c r="J32" t="n">
-        <v>7.386</v>
+        <v>7.425</v>
       </c>
     </row>
     <row r="33">
@@ -5509,10 +5509,10 @@
         <v>1.07</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2028</v>
+        <v>0.2055</v>
       </c>
       <c r="J33" t="n">
-        <v>6.084</v>
+        <v>6.165</v>
       </c>
     </row>
     <row r="34">
@@ -5549,10 +5549,10 @@
         <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1332</v>
+        <v>0.137</v>
       </c>
       <c r="J34" t="n">
-        <v>3.996</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="35">
@@ -5589,10 +5589,10 @@
         <v>0.73</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.299</v>
+        <v>-0.3131</v>
       </c>
       <c r="J35" t="n">
-        <v>-8.970000000000001</v>
+        <v>-9.393000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -5629,10 +5629,10 @@
         <v>0.71</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3182</v>
+        <v>-0.3317</v>
       </c>
       <c r="J36" t="n">
-        <v>-9.545999999999999</v>
+        <v>-9.951000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -5669,10 +5669,10 @@
         <v>1.63</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0183</v>
+        <v>1.12</v>
       </c>
       <c r="J37" t="n">
-        <v>30.549</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="38">
@@ -5709,10 +5709,10 @@
         <v>1.57</v>
       </c>
       <c r="I38" t="n">
-        <v>0.944</v>
+        <v>1.0409</v>
       </c>
       <c r="J38" t="n">
-        <v>28.32</v>
+        <v>31.227</v>
       </c>
     </row>
     <row r="39">
@@ -5749,10 +5749,10 @@
         <v>1.14</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3729</v>
+        <v>0.4021</v>
       </c>
       <c r="J39" t="n">
-        <v>11.187</v>
+        <v>12.063</v>
       </c>
     </row>
     <row r="40">
@@ -5789,10 +5789,10 @@
         <v>1.01</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.006</v>
+        <v>0.0176</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.18</v>
+        <v>0.528</v>
       </c>
     </row>
     <row r="41">
@@ -5829,10 +5829,10 @@
         <v>0.9</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4156</v>
+        <v>-0.3887</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.468</v>
+        <v>-11.661</v>
       </c>
     </row>
     <row r="42">
@@ -5869,10 +5869,10 @@
         <v>1.16</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3787</v>
+        <v>0.3976</v>
       </c>
       <c r="J42" t="n">
-        <v>9.467499999999999</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="43">
@@ -5909,10 +5909,10 @@
         <v>0.98</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.0224</v>
+        <v>-0.0323</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.8075</v>
       </c>
     </row>
     <row r="44">
@@ -5949,10 +5949,10 @@
         <v>0.84</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1839</v>
+        <v>-0.2007</v>
       </c>
       <c r="J44" t="n">
-        <v>-4.5975</v>
+        <v>-5.0175</v>
       </c>
     </row>
     <row r="45">
@@ -5989,10 +5989,10 @@
         <v>0.72</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3019</v>
+        <v>-0.3172</v>
       </c>
       <c r="J45" t="n">
-        <v>-7.5475</v>
+        <v>-7.93</v>
       </c>
     </row>
     <row r="46">
@@ -6029,10 +6029,10 @@
         <v>0.68</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.34</v>
+        <v>-0.3541</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.5</v>
+        <v>-8.852499999999999</v>
       </c>
     </row>
     <row r="47">
@@ -6069,10 +6069,10 @@
         <v>1.47</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8199</v>
+        <v>0.9073</v>
       </c>
       <c r="J47" t="n">
-        <v>20.4975</v>
+        <v>22.6825</v>
       </c>
     </row>
     <row r="48">
@@ -6109,10 +6109,10 @@
         <v>1.46</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8071</v>
+        <v>0.8935999999999999</v>
       </c>
       <c r="J48" t="n">
-        <v>20.1775</v>
+        <v>22.34</v>
       </c>
     </row>
     <row r="49">
@@ -6149,10 +6149,10 @@
         <v>1.35</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6647</v>
+        <v>0.7386</v>
       </c>
       <c r="J49" t="n">
-        <v>16.6175</v>
+        <v>18.465</v>
       </c>
     </row>
     <row r="50">
@@ -6189,10 +6189,10 @@
         <v>1.16</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4046</v>
+        <v>0.4461</v>
       </c>
       <c r="J50" t="n">
-        <v>10.115</v>
+        <v>11.1525</v>
       </c>
     </row>
     <row r="51">
@@ -6229,10 +6229,10 @@
         <v>0.77</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.7612</v>
+        <v>-0.6999</v>
       </c>
       <c r="J51" t="n">
-        <v>-19.03</v>
+        <v>-17.4975</v>
       </c>
     </row>
     <row r="52">
@@ -6269,10 +6269,10 @@
         <v>1.76</v>
       </c>
       <c r="I52" t="n">
-        <v>1.1149</v>
+        <v>1.233</v>
       </c>
       <c r="J52" t="n">
-        <v>21.1831</v>
+        <v>23.427</v>
       </c>
     </row>
     <row r="53">
@@ -6309,10 +6309,10 @@
         <v>1.72</v>
       </c>
       <c r="I53" t="n">
-        <v>1.0696</v>
+        <v>1.1847</v>
       </c>
       <c r="J53" t="n">
-        <v>20.3224</v>
+        <v>22.5093</v>
       </c>
     </row>
     <row r="54">
@@ -6349,10 +6349,10 @@
         <v>1.71</v>
       </c>
       <c r="I54" t="n">
-        <v>1.0582</v>
+        <v>1.1726</v>
       </c>
       <c r="J54" t="n">
-        <v>20.1058</v>
+        <v>22.2794</v>
       </c>
     </row>
     <row r="55">
@@ -6389,10 +6389,10 @@
         <v>1.24</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4851</v>
+        <v>0.5473</v>
       </c>
       <c r="J55" t="n">
-        <v>9.216900000000001</v>
+        <v>10.3987</v>
       </c>
     </row>
     <row r="56">
@@ -6429,10 +6429,10 @@
         <v>1.22</v>
       </c>
       <c r="I56" t="n">
-        <v>0.4567</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>8.677300000000001</v>
+        <v>9.7964</v>
       </c>
     </row>
     <row r="57">
@@ -6469,10 +6469,10 @@
         <v>0.68</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.2989</v>
+        <v>-0.3224</v>
       </c>
       <c r="J57" t="n">
-        <v>-5.6791</v>
+        <v>-6.1256</v>
       </c>
     </row>
     <row r="58">
@@ -6509,10 +6509,10 @@
         <v>0.62</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.3563</v>
+        <v>-0.3772</v>
       </c>
       <c r="J58" t="n">
-        <v>-6.7697</v>
+        <v>-7.1668</v>
       </c>
     </row>
     <row r="59">
@@ -6549,10 +6549,10 @@
         <v>0.59</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3822</v>
+        <v>-0.4021</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.2618</v>
+        <v>-7.6399</v>
       </c>
     </row>
     <row r="60">
@@ -6589,10 +6589,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4092</v>
+        <v>-0.4277</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.7748</v>
+        <v>-8.126300000000001</v>
       </c>
     </row>
     <row r="61">
@@ -6629,10 +6629,10 @@
         <v>0.55</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4183</v>
+        <v>-0.4363</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.9477</v>
+        <v>-8.2897</v>
       </c>
     </row>
     <row r="62">
@@ -6669,10 +6669,10 @@
         <v>1.02</v>
       </c>
       <c r="I62" t="n">
-        <v>0.0745</v>
+        <v>0.0752</v>
       </c>
       <c r="J62" t="n">
-        <v>1.8625</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="63">
@@ -6709,10 +6709,10 @@
         <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0215</v>
+        <v>0.0158</v>
       </c>
       <c r="J63" t="n">
-        <v>0.5375</v>
+        <v>0.395</v>
       </c>
     </row>
     <row r="64">
@@ -6749,10 +6749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0761</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="J64" t="n">
-        <v>-1.9025</v>
+        <v>-2.2475</v>
       </c>
     </row>
     <row r="65">
@@ -6789,10 +6789,10 @@
         <v>0.76</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2632</v>
+        <v>-0.2794</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.58</v>
+        <v>-6.985</v>
       </c>
     </row>
     <row r="66">
@@ -6829,10 +6829,10 @@
         <v>0.66</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3589</v>
+        <v>-0.3723</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.9725</v>
+        <v>-9.307499999999999</v>
       </c>
     </row>
     <row r="67">
@@ -6869,10 +6869,10 @@
         <v>1.56</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5414</v>
+        <v>0.6198</v>
       </c>
       <c r="J67" t="n">
-        <v>13.535</v>
+        <v>15.495</v>
       </c>
     </row>
     <row r="68">
@@ -6909,10 +6909,10 @@
         <v>1.51</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.5826</v>
       </c>
       <c r="J68" t="n">
-        <v>12.74</v>
+        <v>14.565</v>
       </c>
     </row>
     <row r="69">
@@ -6949,10 +6949,10 @@
         <v>1.2</v>
       </c>
       <c r="I69" t="n">
-        <v>0.281</v>
+        <v>0.2986</v>
       </c>
       <c r="J69" t="n">
-        <v>7.025</v>
+        <v>7.465</v>
       </c>
     </row>
     <row r="70">
@@ -6989,10 +6989,10 @@
         <v>1.06</v>
       </c>
       <c r="I70" t="n">
-        <v>0.0911</v>
+        <v>0.1084</v>
       </c>
       <c r="J70" t="n">
-        <v>2.2775</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="71">
@@ -7029,10 +7029,10 @@
         <v>0.73</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3286</v>
+        <v>-0.3364</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.215</v>
+        <v>-8.41</v>
       </c>
     </row>
     <row r="72">
@@ -7069,10 +7069,10 @@
         <v>1.87</v>
       </c>
       <c r="I72" t="n">
-        <v>1.2482</v>
+        <v>1.3722</v>
       </c>
       <c r="J72" t="n">
-        <v>24.964</v>
+        <v>27.444</v>
       </c>
     </row>
     <row r="73">
@@ -7109,10 +7109,10 @@
         <v>1.62</v>
       </c>
       <c r="I73" t="n">
-        <v>0.9617</v>
+        <v>1.0681</v>
       </c>
       <c r="J73" t="n">
-        <v>19.234</v>
+        <v>21.362</v>
       </c>
     </row>
     <row r="74">
@@ -7149,10 +7149,10 @@
         <v>1.45</v>
       </c>
       <c r="I74" t="n">
-        <v>0.7634</v>
+        <v>0.853</v>
       </c>
       <c r="J74" t="n">
-        <v>15.268</v>
+        <v>17.06</v>
       </c>
     </row>
     <row r="75">
@@ -7189,10 +7189,10 @@
         <v>1.29</v>
       </c>
       <c r="I75" t="n">
-        <v>0.5598</v>
+        <v>0.6291</v>
       </c>
       <c r="J75" t="n">
-        <v>11.196</v>
+        <v>12.582</v>
       </c>
     </row>
     <row r="76">
@@ -7229,10 +7229,10 @@
         <v>1.17</v>
       </c>
       <c r="I76" t="n">
-        <v>0.3893</v>
+        <v>0.4353</v>
       </c>
       <c r="J76" t="n">
-        <v>7.786</v>
+        <v>8.706</v>
       </c>
     </row>
     <row r="77">
@@ -7269,10 +7269,10 @@
         <v>1.17</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4914</v>
+        <v>0.5161</v>
       </c>
       <c r="J77" t="n">
-        <v>9.827999999999999</v>
+        <v>10.322</v>
       </c>
     </row>
     <row r="78">
@@ -7309,10 +7309,10 @@
         <v>0.72</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.268</v>
+        <v>-0.2911</v>
       </c>
       <c r="J78" t="n">
-        <v>-5.36</v>
+        <v>-5.822</v>
       </c>
     </row>
     <row r="79">
@@ -7349,10 +7349,10 @@
         <v>0.47</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.5004</v>
+        <v>-0.512</v>
       </c>
       <c r="J79" t="n">
-        <v>-10.008</v>
+        <v>-10.24</v>
       </c>
     </row>
     <row r="80">
@@ -7389,10 +7389,10 @@
         <v>0.45</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.5193</v>
+        <v>-0.5296</v>
       </c>
       <c r="J80" t="n">
-        <v>-10.386</v>
+        <v>-10.592</v>
       </c>
     </row>
     <row r="81">
@@ -7429,10 +7429,10 @@
         <v>0.38</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5856</v>
+        <v>-0.591</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.712</v>
+        <v>-11.82</v>
       </c>
     </row>
     <row r="82">
@@ -7469,10 +7469,10 @@
         <v>1.29</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6267</v>
+        <v>0.6872</v>
       </c>
       <c r="J82" t="n">
-        <v>29.4549</v>
+        <v>32.2984</v>
       </c>
     </row>
     <row r="83">
@@ -7509,10 +7509,10 @@
         <v>1.15</v>
       </c>
       <c r="I83" t="n">
-        <v>0.417</v>
+        <v>0.4532</v>
       </c>
       <c r="J83" t="n">
-        <v>19.599</v>
+        <v>21.3004</v>
       </c>
     </row>
     <row r="84">
@@ -7549,10 +7549,10 @@
         <v>0.93</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2699</v>
+        <v>-0.2664</v>
       </c>
       <c r="J84" t="n">
-        <v>-12.6853</v>
+        <v>-12.5208</v>
       </c>
     </row>
     <row r="85">
@@ -7589,10 +7589,10 @@
         <v>0.92</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3003</v>
+        <v>-0.2947</v>
       </c>
       <c r="J85" t="n">
-        <v>-14.1141</v>
+        <v>-13.8509</v>
       </c>
     </row>
     <row r="86">
@@ -7629,10 +7629,10 @@
         <v>0.89</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3879</v>
+        <v>-0.3755</v>
       </c>
       <c r="J86" t="n">
-        <v>-18.2313</v>
+        <v>-17.6485</v>
       </c>
     </row>
     <row r="87">
@@ -7669,10 +7669,10 @@
         <v>1.17</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3585</v>
+        <v>0.3764</v>
       </c>
       <c r="J87" t="n">
-        <v>16.8495</v>
+        <v>17.6908</v>
       </c>
     </row>
     <row r="88">
@@ -7709,10 +7709,10 @@
         <v>1.05</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1346</v>
+        <v>0.1445</v>
       </c>
       <c r="J88" t="n">
-        <v>6.3262</v>
+        <v>6.7915</v>
       </c>
     </row>
     <row r="89">
@@ -7749,10 +7749,10 @@
         <v>1.01</v>
       </c>
       <c r="I89" t="n">
-        <v>0.0348</v>
+        <v>0.0413</v>
       </c>
       <c r="J89" t="n">
-        <v>1.6356</v>
+        <v>1.9411</v>
       </c>
     </row>
     <row r="90">
@@ -7789,10 +7789,10 @@
         <v>0.98</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0383</v>
+        <v>-0.0445</v>
       </c>
       <c r="J90" t="n">
-        <v>-1.8001</v>
+        <v>-2.0915</v>
       </c>
     </row>
     <row r="91">
@@ -7829,10 +7829,10 @@
         <v>0.92</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1145</v>
+        <v>-0.1258</v>
       </c>
       <c r="J91" t="n">
-        <v>-5.3815</v>
+        <v>-5.9126</v>
       </c>
     </row>
     <row r="92">
@@ -7869,10 +7869,10 @@
         <v>1.63</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9836</v>
+        <v>1.0895</v>
       </c>
       <c r="J92" t="n">
-        <v>22.6228</v>
+        <v>25.0585</v>
       </c>
     </row>
     <row r="93">
@@ -7909,10 +7909,10 @@
         <v>1.45</v>
       </c>
       <c r="I93" t="n">
-        <v>0.7683</v>
+        <v>0.8571</v>
       </c>
       <c r="J93" t="n">
-        <v>17.6709</v>
+        <v>19.7133</v>
       </c>
     </row>
     <row r="94">
@@ -7949,10 +7949,10 @@
         <v>1.43</v>
       </c>
       <c r="I94" t="n">
-        <v>0.7443</v>
+        <v>0.8308</v>
       </c>
       <c r="J94" t="n">
-        <v>17.1189</v>
+        <v>19.1084</v>
       </c>
     </row>
     <row r="95">
@@ -7989,10 +7989,10 @@
         <v>1.36</v>
       </c>
       <c r="I95" t="n">
-        <v>0.6589</v>
+        <v>0.7368</v>
       </c>
       <c r="J95" t="n">
-        <v>15.1547</v>
+        <v>16.9464</v>
       </c>
     </row>
     <row r="96">
@@ -8029,10 +8029,10 @@
         <v>1.2</v>
       </c>
       <c r="I96" t="n">
-        <v>0.4419</v>
+        <v>0.4954</v>
       </c>
       <c r="J96" t="n">
-        <v>10.1637</v>
+        <v>11.3942</v>
       </c>
     </row>
     <row r="97">
@@ -8069,10 +8069,10 @@
         <v>0.97</v>
       </c>
       <c r="I97" t="n">
-        <v>0.0322</v>
+        <v>-0.0054</v>
       </c>
       <c r="J97" t="n">
-        <v>0.7406</v>
+        <v>-0.1242</v>
       </c>
     </row>
     <row r="98">
@@ -8109,10 +8109,10 @@
         <v>0.74</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.2542</v>
+        <v>-0.2765</v>
       </c>
       <c r="J98" t="n">
-        <v>-5.8466</v>
+        <v>-6.3595</v>
       </c>
     </row>
     <row r="99">
@@ -8149,10 +8149,10 @@
         <v>0.74</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2542</v>
+        <v>-0.2765</v>
       </c>
       <c r="J99" t="n">
-        <v>-5.8466</v>
+        <v>-6.3595</v>
       </c>
     </row>
     <row r="100">
@@ -8189,10 +8189,10 @@
         <v>0.5</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4771</v>
+        <v>-0.4896</v>
       </c>
       <c r="J100" t="n">
-        <v>-10.9733</v>
+        <v>-11.2608</v>
       </c>
     </row>
     <row r="101">
@@ -8229,10 +8229,10 @@
         <v>0.38</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5899</v>
+        <v>-0.5945</v>
       </c>
       <c r="J101" t="n">
-        <v>-13.5677</v>
+        <v>-13.6735</v>
       </c>
     </row>
     <row r="102">
@@ -8269,10 +8269,10 @@
         <v>1.75</v>
       </c>
       <c r="I102" t="n">
-        <v>1.118</v>
+        <v>1.2335</v>
       </c>
       <c r="J102" t="n">
-        <v>24.596</v>
+        <v>27.137</v>
       </c>
     </row>
     <row r="103">
@@ -8309,10 +8309,10 @@
         <v>1.71</v>
       </c>
       <c r="I103" t="n">
-        <v>1.0717</v>
+        <v>1.1844</v>
       </c>
       <c r="J103" t="n">
-        <v>23.5774</v>
+        <v>26.0568</v>
       </c>
     </row>
     <row r="104">
@@ -8349,10 +8349,10 @@
         <v>1.49</v>
       </c>
       <c r="I104" t="n">
-        <v>0.8129</v>
+        <v>0.9065</v>
       </c>
       <c r="J104" t="n">
-        <v>17.8838</v>
+        <v>19.943</v>
       </c>
     </row>
     <row r="105">
@@ -8389,10 +8389,10 @@
         <v>1.18</v>
       </c>
       <c r="I105" t="n">
-        <v>0.4084</v>
+        <v>0.4583</v>
       </c>
       <c r="J105" t="n">
-        <v>8.9848</v>
+        <v>10.0826</v>
       </c>
     </row>
     <row r="106">
@@ -8429,10 +8429,10 @@
         <v>1.1</v>
       </c>
       <c r="I106" t="n">
-        <v>0.2469</v>
+        <v>0.2714</v>
       </c>
       <c r="J106" t="n">
-        <v>5.4318</v>
+        <v>5.9708</v>
       </c>
     </row>
     <row r="107">
@@ -8469,10 +8469,10 @@
         <v>0.75</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.2508</v>
+        <v>-0.272</v>
       </c>
       <c r="J107" t="n">
-        <v>-5.5176</v>
+        <v>-5.984</v>
       </c>
     </row>
     <row r="108">
@@ -8509,10 +8509,10 @@
         <v>0.73</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.2701</v>
+        <v>-0.2908</v>
       </c>
       <c r="J108" t="n">
-        <v>-5.9422</v>
+        <v>-6.3976</v>
       </c>
     </row>
     <row r="109">
@@ -8549,10 +8549,10 @@
         <v>0.7</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2974</v>
+        <v>-0.3175</v>
       </c>
       <c r="J109" t="n">
-        <v>-6.5428</v>
+        <v>-6.985</v>
       </c>
     </row>
     <row r="110">
@@ -8589,10 +8589,10 @@
         <v>0.66</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3335</v>
+        <v>-0.3525</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.337</v>
+        <v>-7.755</v>
       </c>
     </row>
     <row r="111">
@@ -8629,10 +8629,10 @@
         <v>0.66</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3335</v>
+        <v>-0.3525</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.337</v>
+        <v>-7.755</v>
       </c>
     </row>
     <row r="112">
@@ -8669,10 +8669,10 @@
         <v>1.49</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8364</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="J112" t="n">
-        <v>19.2372</v>
+        <v>21.3187</v>
       </c>
     </row>
     <row r="113">
@@ -8709,10 +8709,10 @@
         <v>1.35</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6583</v>
+        <v>0.733</v>
       </c>
       <c r="J113" t="n">
-        <v>15.1409</v>
+        <v>16.859</v>
       </c>
     </row>
     <row r="114">
@@ -8749,10 +8749,10 @@
         <v>1.32</v>
       </c>
       <c r="I114" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.6902</v>
       </c>
       <c r="J114" t="n">
-        <v>14.2485</v>
+        <v>15.8746</v>
       </c>
     </row>
     <row r="115">
@@ -8789,10 +8789,10 @@
         <v>1.19</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4435</v>
+        <v>0.4932</v>
       </c>
       <c r="J115" t="n">
-        <v>10.2005</v>
+        <v>11.3436</v>
       </c>
     </row>
     <row r="116">
@@ -8829,10 +8829,10 @@
         <v>1.08</v>
       </c>
       <c r="I116" t="n">
-        <v>0.2243</v>
+        <v>0.2424</v>
       </c>
       <c r="J116" t="n">
-        <v>5.1589</v>
+        <v>5.5752</v>
       </c>
     </row>
     <row r="117">
@@ -8869,10 +8869,10 @@
         <v>0.84</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.1661</v>
+        <v>-0.1871</v>
       </c>
       <c r="J117" t="n">
-        <v>-3.8203</v>
+        <v>-4.3033</v>
       </c>
     </row>
     <row r="118">
@@ -8909,10 +8909,10 @@
         <v>0.84</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1661</v>
+        <v>-0.1871</v>
       </c>
       <c r="J118" t="n">
-        <v>-3.8203</v>
+        <v>-4.3033</v>
       </c>
     </row>
     <row r="119">
@@ -8949,10 +8949,10 @@
         <v>0.82</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1873</v>
+        <v>-0.2081</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.3079</v>
+        <v>-4.7863</v>
       </c>
     </row>
     <row r="120">
@@ -8989,10 +8989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3114</v>
+        <v>-0.3301</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.1622</v>
+        <v>-7.5923</v>
       </c>
     </row>
     <row r="121">
@@ -9029,10 +9029,10 @@
         <v>0.51</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4797</v>
+        <v>-0.4902</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.0331</v>
+        <v>-11.2746</v>
       </c>
     </row>
     <row r="122">
@@ -9069,10 +9069,10 @@
         <v>1.08</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2439</v>
+        <v>0.2408</v>
       </c>
       <c r="J122" t="n">
-        <v>5.8536</v>
+        <v>5.7792</v>
       </c>
     </row>
     <row r="123">
@@ -9109,10 +9109,10 @@
         <v>1.04</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1506</v>
+        <v>0.1497</v>
       </c>
       <c r="J123" t="n">
-        <v>3.6144</v>
+        <v>3.5928</v>
       </c>
     </row>
     <row r="124">
@@ -9149,10 +9149,10 @@
         <v>0.92</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0997</v>
+        <v>-0.1145</v>
       </c>
       <c r="J124" t="n">
-        <v>-2.3928</v>
+        <v>-2.748</v>
       </c>
     </row>
     <row r="125">
@@ -9189,10 +9189,10 @@
         <v>0.77</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2532</v>
+        <v>-0.2696</v>
       </c>
       <c r="J125" t="n">
-        <v>-6.0768</v>
+        <v>-6.4704</v>
       </c>
     </row>
     <row r="126">
@@ -9229,10 +9229,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4517</v>
+        <v>-0.4609</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.8408</v>
+        <v>-11.0616</v>
       </c>
     </row>
     <row r="127">
@@ -9269,10 +9269,10 @@
         <v>1.36</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6845</v>
+        <v>0.7588</v>
       </c>
       <c r="J127" t="n">
-        <v>16.428</v>
+        <v>18.2112</v>
       </c>
     </row>
     <row r="128">
@@ -9309,10 +9309,10 @@
         <v>1.29</v>
       </c>
       <c r="I128" t="n">
-        <v>0.5905</v>
+        <v>0.6555</v>
       </c>
       <c r="J128" t="n">
-        <v>14.172</v>
+        <v>15.732</v>
       </c>
     </row>
     <row r="129">
@@ -9349,10 +9349,10 @@
         <v>1.24</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5221</v>
+        <v>0.5794</v>
       </c>
       <c r="J129" t="n">
-        <v>12.5304</v>
+        <v>13.9056</v>
       </c>
     </row>
     <row r="130">
@@ -9389,10 +9389,10 @@
         <v>1.08</v>
       </c>
       <c r="I130" t="n">
-        <v>0.2439</v>
+        <v>0.256</v>
       </c>
       <c r="J130" t="n">
-        <v>5.8536</v>
+        <v>6.144</v>
       </c>
     </row>
     <row r="131">
@@ -9429,10 +9429,10 @@
         <v>1.05</v>
       </c>
       <c r="I131" t="n">
-        <v>0.1513</v>
+        <v>0.1688</v>
       </c>
       <c r="J131" t="n">
-        <v>3.6312</v>
+        <v>4.0512</v>
       </c>
     </row>
     <row r="132">
@@ -9469,10 +9469,10 @@
         <v>1.64</v>
       </c>
       <c r="I132" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="J132" t="n">
-        <v>24.54</v>
+        <v>27.384</v>
       </c>
     </row>
     <row r="133">
@@ -9509,10 +9509,10 @@
         <v>1.35</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5419</v>
+        <v>0.6047</v>
       </c>
       <c r="J133" t="n">
-        <v>16.257</v>
+        <v>18.141</v>
       </c>
     </row>
     <row r="134">
@@ -9549,10 +9549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2338</v>
+        <v>-0.2462</v>
       </c>
       <c r="J134" t="n">
-        <v>-7.014</v>
+        <v>-7.386</v>
       </c>
     </row>
     <row r="135">
@@ -9589,10 +9589,10 @@
         <v>0.71</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3314</v>
+        <v>-0.3421</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.942</v>
+        <v>-10.263</v>
       </c>
     </row>
     <row r="136">
@@ -9629,10 +9629,10 @@
         <v>0.7</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3408</v>
+        <v>-0.3513</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.224</v>
+        <v>-10.539</v>
       </c>
     </row>
     <row r="137">
@@ -9669,10 +9669,10 @@
         <v>1.33</v>
       </c>
       <c r="I137" t="n">
-        <v>0.6654</v>
+        <v>0.7333</v>
       </c>
       <c r="J137" t="n">
-        <v>19.962</v>
+        <v>21.999</v>
       </c>
     </row>
     <row r="138">
@@ -9709,10 +9709,10 @@
         <v>1.13</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3742</v>
+        <v>0.3976</v>
       </c>
       <c r="J138" t="n">
-        <v>11.226</v>
+        <v>11.928</v>
       </c>
     </row>
     <row r="139">
@@ -9749,10 +9749,10 @@
         <v>1.04</v>
       </c>
       <c r="I139" t="n">
-        <v>0.143</v>
+        <v>0.1543</v>
       </c>
       <c r="J139" t="n">
-        <v>4.29</v>
+        <v>4.629</v>
       </c>
     </row>
     <row r="140">
@@ -9789,10 +9789,10 @@
         <v>1.03</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1085</v>
+        <v>0.1208</v>
       </c>
       <c r="J140" t="n">
-        <v>3.255</v>
+        <v>3.624</v>
       </c>
     </row>
     <row r="141">
@@ -9829,10 +9829,10 @@
         <v>0.99</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0761</v>
       </c>
       <c r="J141" t="n">
-        <v>-2.361</v>
+        <v>-2.283</v>
       </c>
     </row>
     <row r="142">
@@ -9869,10 +9869,10 @@
         <v>1.35</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5747</v>
+        <v>0.6351</v>
       </c>
       <c r="J142" t="n">
-        <v>15.5169</v>
+        <v>17.1477</v>
       </c>
     </row>
     <row r="143">
@@ -9909,10 +9909,10 @@
         <v>1.04</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1368</v>
+        <v>0.1396</v>
       </c>
       <c r="J143" t="n">
-        <v>3.6936</v>
+        <v>3.7692</v>
       </c>
     </row>
     <row r="144">
@@ -9949,10 +9949,10 @@
         <v>0.85</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1781</v>
+        <v>-0.1939</v>
       </c>
       <c r="J144" t="n">
-        <v>-4.8087</v>
+        <v>-5.2353</v>
       </c>
     </row>
     <row r="145">
@@ -9989,10 +9989,10 @@
         <v>0.77</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2586</v>
+        <v>-0.2738</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.9822</v>
+        <v>-7.3926</v>
       </c>
     </row>
     <row r="146">
@@ -10029,10 +10029,10 @@
         <v>0.57</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4475</v>
+        <v>-0.4562</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.0825</v>
+        <v>-12.3174</v>
       </c>
     </row>
     <row r="147">
@@ -10069,10 +10069,10 @@
         <v>1.59</v>
       </c>
       <c r="I147" t="n">
-        <v>0.9698</v>
+        <v>1.0683</v>
       </c>
       <c r="J147" t="n">
-        <v>26.1846</v>
+        <v>28.8441</v>
       </c>
     </row>
     <row r="148">
@@ -10109,10 +10109,10 @@
         <v>1.35</v>
       </c>
       <c r="I148" t="n">
-        <v>0.664</v>
+        <v>0.738</v>
       </c>
       <c r="J148" t="n">
-        <v>17.928</v>
+        <v>19.926</v>
       </c>
     </row>
     <row r="149">
@@ -10149,10 +10149,10 @@
         <v>1.32</v>
       </c>
       <c r="I149" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.6945</v>
       </c>
       <c r="J149" t="n">
-        <v>16.8615</v>
+        <v>18.7515</v>
       </c>
     </row>
     <row r="150">
@@ -10189,10 +10189,10 @@
         <v>0.99</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1149</v>
+        <v>-0.1014</v>
       </c>
       <c r="J150" t="n">
-        <v>-3.1023</v>
+        <v>-2.7378</v>
       </c>
     </row>
     <row r="151">
@@ -10229,10 +10229,10 @@
         <v>0.98</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.1561</v>
+        <v>-0.1428</v>
       </c>
       <c r="J151" t="n">
-        <v>-4.2147</v>
+        <v>-3.8556</v>
       </c>
     </row>
     <row r="152">
@@ -10269,10 +10269,10 @@
         <v>1.36</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5563</v>
+        <v>0.6201</v>
       </c>
       <c r="J152" t="n">
-        <v>23.3646</v>
+        <v>26.0442</v>
       </c>
     </row>
     <row r="153">
@@ -10309,10 +10309,10 @@
         <v>1.11</v>
       </c>
       <c r="I153" t="n">
-        <v>0.2612</v>
+        <v>0.268</v>
       </c>
       <c r="J153" t="n">
-        <v>10.9704</v>
+        <v>11.256</v>
       </c>
     </row>
     <row r="154">
@@ -10349,10 +10349,10 @@
         <v>0.97</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0521</v>
+        <v>-0.0598</v>
       </c>
       <c r="J154" t="n">
-        <v>-2.1882</v>
+        <v>-2.5116</v>
       </c>
     </row>
     <row r="155">
@@ -10389,10 +10389,10 @@
         <v>0.92</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.114</v>
+        <v>-0.1255</v>
       </c>
       <c r="J155" t="n">
-        <v>-4.788</v>
+        <v>-5.271</v>
       </c>
     </row>
     <row r="156">
@@ -10429,10 +10429,10 @@
         <v>0.75</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2908</v>
+        <v>-0.3029</v>
       </c>
       <c r="J156" t="n">
-        <v>-12.2136</v>
+        <v>-12.7218</v>
       </c>
     </row>
     <row r="157">
@@ -10469,10 +10469,10 @@
         <v>1.32</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6515</v>
+        <v>0.7181</v>
       </c>
       <c r="J157" t="n">
-        <v>27.363</v>
+        <v>30.1602</v>
       </c>
     </row>
     <row r="158">
@@ -10509,10 +10509,10 @@
         <v>1.13</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3742</v>
+        <v>0.3976</v>
       </c>
       <c r="J158" t="n">
-        <v>15.7164</v>
+        <v>16.6992</v>
       </c>
     </row>
     <row r="159">
@@ -10549,10 +10549,10 @@
         <v>1.12</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3586</v>
+        <v>0.3733</v>
       </c>
       <c r="J159" t="n">
-        <v>15.0612</v>
+        <v>15.6786</v>
       </c>
     </row>
     <row r="160">
@@ -10589,10 +10589,10 @@
         <v>1.08</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2667</v>
+        <v>0.2717</v>
       </c>
       <c r="J160" t="n">
-        <v>11.2014</v>
+        <v>11.4114</v>
       </c>
     </row>
     <row r="161">
@@ -10629,10 +10629,10 @@
         <v>0.87</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4634</v>
+        <v>-0.4402</v>
       </c>
       <c r="J161" t="n">
-        <v>-19.4628</v>
+        <v>-18.4884</v>
       </c>
     </row>
     <row r="162">
@@ -10669,10 +10669,10 @@
         <v>1.53</v>
       </c>
       <c r="I162" t="n">
-        <v>1.1465</v>
+        <v>1.116</v>
       </c>
       <c r="J162" t="n">
-        <v>25.223</v>
+        <v>24.552</v>
       </c>
     </row>
     <row r="163">
@@ -10709,10 +10709,10 @@
         <v>1.48</v>
       </c>
       <c r="I163" t="n">
-        <v>1.0853</v>
+        <v>1.0489</v>
       </c>
       <c r="J163" t="n">
-        <v>23.8766</v>
+        <v>23.0758</v>
       </c>
     </row>
     <row r="164">
@@ -10749,10 +10749,10 @@
         <v>1.48</v>
       </c>
       <c r="I164" t="n">
-        <v>1.0853</v>
+        <v>1.0489</v>
       </c>
       <c r="J164" t="n">
-        <v>23.8766</v>
+        <v>23.0758</v>
       </c>
     </row>
     <row r="165">
@@ -10789,10 +10789,10 @@
         <v>1.23</v>
       </c>
       <c r="I165" t="n">
-        <v>0.6016</v>
+        <v>0.5888</v>
       </c>
       <c r="J165" t="n">
-        <v>13.2352</v>
+        <v>12.9536</v>
       </c>
     </row>
     <row r="166">
@@ -10829,10 +10829,10 @@
         <v>1.08</v>
       </c>
       <c r="I166" t="n">
-        <v>0.2074</v>
+        <v>0.2306</v>
       </c>
       <c r="J166" t="n">
-        <v>4.5628</v>
+        <v>5.0732</v>
       </c>
     </row>
     <row r="167">
@@ -10869,10 +10869,10 @@
         <v>0.97</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.0072</v>
+        <v>-0.025</v>
       </c>
       <c r="J167" t="n">
-        <v>-0.1584</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="168">
@@ -10909,10 +10909,10 @@
         <v>0.89</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1102</v>
+        <v>-0.1312</v>
       </c>
       <c r="J168" t="n">
-        <v>-2.4244</v>
+        <v>-2.8864</v>
       </c>
     </row>
     <row r="169">
@@ -10949,10 +10949,10 @@
         <v>0.87</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1331</v>
+        <v>-0.1542</v>
       </c>
       <c r="J169" t="n">
-        <v>-2.9282</v>
+        <v>-3.3924</v>
       </c>
     </row>
     <row r="170">
@@ -10989,10 +10989,10 @@
         <v>0.59</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.405</v>
+        <v>-0.4197</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.91</v>
+        <v>-9.2334</v>
       </c>
     </row>
     <row r="171">
@@ -11029,10 +11029,10 @@
         <v>0.38</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6001</v>
+        <v>-0.6025</v>
       </c>
       <c r="J171" t="n">
-        <v>-13.2022</v>
+        <v>-13.255</v>
       </c>
     </row>
     <row r="172">
@@ -11069,10 +11069,10 @@
         <v>1.09</v>
       </c>
       <c r="I172" t="n">
-        <v>0.1831</v>
+        <v>0.1899</v>
       </c>
       <c r="J172" t="n">
-        <v>5.3099</v>
+        <v>5.5071</v>
       </c>
     </row>
     <row r="173">
@@ -11109,10 +11109,10 @@
         <v>1.04</v>
       </c>
       <c r="I173" t="n">
-        <v>0.0974</v>
+        <v>0.1039</v>
       </c>
       <c r="J173" t="n">
-        <v>2.8246</v>
+        <v>3.0131</v>
       </c>
     </row>
     <row r="174">
@@ -11149,10 +11149,10 @@
         <v>0.97</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0464</v>
+        <v>-0.0554</v>
       </c>
       <c r="J174" t="n">
-        <v>-1.3456</v>
+        <v>-1.6066</v>
       </c>
     </row>
     <row r="175">
@@ -11189,10 +11189,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1505</v>
+        <v>-0.1649</v>
       </c>
       <c r="J175" t="n">
-        <v>-4.3645</v>
+        <v>-4.7821</v>
       </c>
     </row>
     <row r="176">
@@ -11229,10 +11229,10 @@
         <v>0.77</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2628</v>
+        <v>-0.2771</v>
       </c>
       <c r="J176" t="n">
-        <v>-7.6212</v>
+        <v>-8.0359</v>
       </c>
     </row>
     <row r="177">
@@ -11269,10 +11269,10 @@
         <v>1.31</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4271</v>
+        <v>0.4367</v>
       </c>
       <c r="J177" t="n">
-        <v>12.3859</v>
+        <v>12.6643</v>
       </c>
     </row>
     <row r="178">
@@ -11309,10 +11309,10 @@
         <v>1.2</v>
       </c>
       <c r="I178" t="n">
-        <v>0.2926</v>
+        <v>0.3073</v>
       </c>
       <c r="J178" t="n">
-        <v>8.4854</v>
+        <v>8.9117</v>
       </c>
     </row>
     <row r="179">
@@ -11349,10 +11349,10 @@
         <v>1.06</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1042</v>
+        <v>0.1183</v>
       </c>
       <c r="J179" t="n">
-        <v>3.0218</v>
+        <v>3.4307</v>
       </c>
     </row>
     <row r="180">
@@ -11389,10 +11389,10 @@
         <v>0.99</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0303</v>
+        <v>-0.0327</v>
       </c>
       <c r="J180" t="n">
-        <v>-0.8787</v>
+        <v>-0.9483</v>
       </c>
     </row>
     <row r="181">
@@ -11429,10 +11429,10 @@
         <v>0.96</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="J181" t="n">
-        <v>-2.1431</v>
+        <v>-2.3403</v>
       </c>
     </row>
     <row r="182">
@@ -11469,10 +11469,10 @@
         <v>1.33</v>
       </c>
       <c r="I182" t="n">
-        <v>0.8558</v>
+        <v>0.8088</v>
       </c>
       <c r="J182" t="n">
-        <v>23.1066</v>
+        <v>21.8376</v>
       </c>
     </row>
     <row r="183">
@@ -11509,10 +11509,10 @@
         <v>1.26</v>
       </c>
       <c r="I183" t="n">
-        <v>0.696</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="J183" t="n">
-        <v>18.792</v>
+        <v>18.0306</v>
       </c>
     </row>
     <row r="184">
@@ -11549,10 +11549,10 @@
         <v>1.26</v>
       </c>
       <c r="I184" t="n">
-        <v>0.696</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="J184" t="n">
-        <v>18.792</v>
+        <v>18.0306</v>
       </c>
     </row>
     <row r="185">
@@ -11589,10 +11589,10 @@
         <v>1.2</v>
       </c>
       <c r="I185" t="n">
-        <v>0.5571</v>
+        <v>0.5432</v>
       </c>
       <c r="J185" t="n">
-        <v>15.0417</v>
+        <v>14.6664</v>
       </c>
     </row>
     <row r="186">
@@ -11629,10 +11629,10 @@
         <v>1.06</v>
       </c>
       <c r="I186" t="n">
-        <v>0.1788</v>
+        <v>0.1959</v>
       </c>
       <c r="J186" t="n">
-        <v>4.8276</v>
+        <v>5.2893</v>
       </c>
     </row>
     <row r="187">
@@ -11669,10 +11669,10 @@
         <v>1.23</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5033</v>
+        <v>0.4915</v>
       </c>
       <c r="J187" t="n">
-        <v>13.5891</v>
+        <v>13.2705</v>
       </c>
     </row>
     <row r="188">
@@ -11709,10 +11709,10 @@
         <v>1.02</v>
       </c>
       <c r="I188" t="n">
-        <v>0.0712</v>
+        <v>0.077</v>
       </c>
       <c r="J188" t="n">
-        <v>1.9224</v>
+        <v>2.079</v>
       </c>
     </row>
     <row r="189">
@@ -11749,10 +11749,10 @@
         <v>0.99</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0188</v>
+        <v>-0.0239</v>
       </c>
       <c r="J189" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.6453</v>
       </c>
     </row>
     <row r="190">
@@ -11789,10 +11789,10 @@
         <v>0.91</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.12</v>
+        <v>-0.1331</v>
       </c>
       <c r="J190" t="n">
-        <v>-3.24</v>
+        <v>-3.5937</v>
       </c>
     </row>
     <row r="191">
@@ -11829,10 +11829,10 @@
         <v>0.71</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3235</v>
+        <v>-0.3359</v>
       </c>
       <c r="J191" t="n">
-        <v>-8.734500000000001</v>
+        <v>-9.0693</v>
       </c>
     </row>
     <row r="192">
@@ -11869,10 +11869,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.1848</v>
+        <v>-0.2083</v>
       </c>
       <c r="J192" t="n">
-        <v>-3.3264</v>
+        <v>-3.7494</v>
       </c>
     </row>
     <row r="193">
@@ -11909,10 +11909,10 @@
         <v>0.78</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.2165</v>
+        <v>-0.2393</v>
       </c>
       <c r="J193" t="n">
-        <v>-3.897</v>
+        <v>-4.3074</v>
       </c>
     </row>
     <row r="194">
@@ -11949,10 +11949,10 @@
         <v>0.71</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2859</v>
+        <v>-0.3068</v>
       </c>
       <c r="J194" t="n">
-        <v>-5.1462</v>
+        <v>-5.5224</v>
       </c>
     </row>
     <row r="195">
@@ -11989,10 +11989,10 @@
         <v>0.7</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2953</v>
+        <v>-0.3159</v>
       </c>
       <c r="J195" t="n">
-        <v>-5.3154</v>
+        <v>-5.6862</v>
       </c>
     </row>
     <row r="196">
@@ -12029,10 +12029,10 @@
         <v>0.4</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5732</v>
+        <v>-0.5787</v>
       </c>
       <c r="J196" t="n">
-        <v>-10.3176</v>
+        <v>-10.4166</v>
       </c>
     </row>
     <row r="197">
@@ -12069,10 +12069,10 @@
         <v>1.92</v>
       </c>
       <c r="I197" t="n">
-        <v>0.976</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="J197" t="n">
-        <v>17.568</v>
+        <v>17.3556</v>
       </c>
     </row>
     <row r="198">
@@ -12109,10 +12109,10 @@
         <v>1.54</v>
       </c>
       <c r="I198" t="n">
-        <v>0.6189</v>
+        <v>0.6291</v>
       </c>
       <c r="J198" t="n">
-        <v>11.1402</v>
+        <v>11.3238</v>
       </c>
     </row>
     <row r="199">
@@ -12149,10 +12149,10 @@
         <v>1.53</v>
       </c>
       <c r="I199" t="n">
-        <v>0.6091</v>
+        <v>0.6198</v>
       </c>
       <c r="J199" t="n">
-        <v>10.9638</v>
+        <v>11.1564</v>
       </c>
     </row>
     <row r="200">
@@ -12189,10 +12189,10 @@
         <v>1.48</v>
       </c>
       <c r="I200" t="n">
-        <v>0.5589</v>
+        <v>0.5724</v>
       </c>
       <c r="J200" t="n">
-        <v>10.0602</v>
+        <v>10.3032</v>
       </c>
     </row>
     <row r="201">
@@ -12229,10 +12229,10 @@
         <v>1.33</v>
       </c>
       <c r="I201" t="n">
-        <v>0.3983</v>
+        <v>0.4196</v>
       </c>
       <c r="J201" t="n">
-        <v>7.1694</v>
+        <v>7.5528</v>
       </c>
     </row>
     <row r="202">
@@ -12269,10 +12269,10 @@
         <v>1.37</v>
       </c>
       <c r="I202" t="n">
-        <v>0.9656</v>
+        <v>0.9045</v>
       </c>
       <c r="J202" t="n">
-        <v>21.2432</v>
+        <v>19.899</v>
       </c>
     </row>
     <row r="203">
@@ -12309,10 +12309,10 @@
         <v>1.32</v>
       </c>
       <c r="I203" t="n">
-        <v>0.8555</v>
+        <v>0.8044</v>
       </c>
       <c r="J203" t="n">
-        <v>18.821</v>
+        <v>17.6968</v>
       </c>
     </row>
     <row r="204">
@@ -12349,10 +12349,10 @@
         <v>1.28</v>
       </c>
       <c r="I204" t="n">
-        <v>0.7618</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="J204" t="n">
-        <v>16.7596</v>
+        <v>15.8906</v>
       </c>
     </row>
     <row r="205">
@@ -12389,10 +12389,10 @@
         <v>1.11</v>
       </c>
       <c r="I205" t="n">
-        <v>0.3415</v>
+        <v>0.3436</v>
       </c>
       <c r="J205" t="n">
-        <v>7.513</v>
+        <v>7.5592</v>
       </c>
     </row>
     <row r="206">
@@ -12429,10 +12429,10 @@
         <v>0.67</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.9857</v>
+        <v>-0.8999</v>
       </c>
       <c r="J206" t="n">
-        <v>-21.6854</v>
+        <v>-19.7978</v>
       </c>
     </row>
     <row r="207">
@@ -12469,10 +12469,10 @@
         <v>1.56</v>
       </c>
       <c r="I207" t="n">
-        <v>1.0391</v>
+        <v>0.9922</v>
       </c>
       <c r="J207" t="n">
-        <v>22.8602</v>
+        <v>21.8284</v>
       </c>
     </row>
     <row r="208">
@@ -12509,10 +12509,10 @@
         <v>0.9</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.1307</v>
+        <v>-0.1442</v>
       </c>
       <c r="J208" t="n">
-        <v>-2.8754</v>
+        <v>-3.1724</v>
       </c>
     </row>
     <row r="209">
@@ -12549,10 +12549,10 @@
         <v>0.83</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2049</v>
+        <v>-0.2193</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.5078</v>
+        <v>-4.8246</v>
       </c>
     </row>
     <row r="210">
@@ -12589,10 +12589,10 @@
         <v>0.82</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2151</v>
+        <v>-0.2294</v>
       </c>
       <c r="J210" t="n">
-        <v>-4.7322</v>
+        <v>-5.0468</v>
       </c>
     </row>
     <row r="211">
@@ -12629,10 +12629,10 @@
         <v>0.73</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3039</v>
+        <v>-0.3169</v>
       </c>
       <c r="J211" t="n">
-        <v>-6.6858</v>
+        <v>-6.9718</v>
       </c>
     </row>
     <row r="212">
@@ -12669,10 +12669,10 @@
         <v>1.24</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6788</v>
+        <v>0.6466</v>
       </c>
       <c r="J212" t="n">
-        <v>19.6852</v>
+        <v>18.7514</v>
       </c>
     </row>
     <row r="213">
@@ -12709,10 +12709,10 @@
         <v>1.2</v>
       </c>
       <c r="I213" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.5588</v>
       </c>
       <c r="J213" t="n">
-        <v>16.8229</v>
+        <v>16.2052</v>
       </c>
     </row>
     <row r="214">
@@ -12749,10 +12749,10 @@
         <v>1.1</v>
       </c>
       <c r="I214" t="n">
-        <v>0.3218</v>
+        <v>0.3234</v>
       </c>
       <c r="J214" t="n">
-        <v>9.3322</v>
+        <v>9.3786</v>
       </c>
     </row>
     <row r="215">
@@ -12789,10 +12789,10 @@
         <v>1.08</v>
       </c>
       <c r="I215" t="n">
-        <v>0.2655</v>
+        <v>0.2709</v>
       </c>
       <c r="J215" t="n">
-        <v>7.6995</v>
+        <v>7.8561</v>
       </c>
     </row>
     <row r="216">
@@ -12829,10 +12829,10 @@
         <v>0.93</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2904</v>
+        <v>-0.2806</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.4216</v>
+        <v>-8.1374</v>
       </c>
     </row>
     <row r="217">
@@ -12869,10 +12869,10 @@
         <v>1.31</v>
       </c>
       <c r="I217" t="n">
-        <v>0.6377</v>
+        <v>0.6155</v>
       </c>
       <c r="J217" t="n">
-        <v>18.4933</v>
+        <v>17.8495</v>
       </c>
     </row>
     <row r="218">
@@ -12909,10 +12909,10 @@
         <v>1.19</v>
       </c>
       <c r="I218" t="n">
-        <v>0.4228</v>
+        <v>0.4185</v>
       </c>
       <c r="J218" t="n">
-        <v>12.2612</v>
+        <v>12.1365</v>
       </c>
     </row>
     <row r="219">
@@ -12949,10 +12949,10 @@
         <v>0.84</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1974</v>
+        <v>-0.2112</v>
       </c>
       <c r="J219" t="n">
-        <v>-5.7246</v>
+        <v>-6.1248</v>
       </c>
     </row>
     <row r="220">
@@ -12989,10 +12989,10 @@
         <v>0.84</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1974</v>
+        <v>-0.2112</v>
       </c>
       <c r="J220" t="n">
-        <v>-5.7246</v>
+        <v>-6.1248</v>
       </c>
     </row>
     <row r="221">
@@ -13029,10 +13029,10 @@
         <v>0.78</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.258</v>
+        <v>-0.2713</v>
       </c>
       <c r="J221" t="n">
-        <v>-7.482</v>
+        <v>-7.8677</v>
       </c>
     </row>
     <row r="222">
@@ -13069,10 +13069,10 @@
         <v>1.22</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5313</v>
+        <v>0.5088</v>
       </c>
       <c r="J222" t="n">
-        <v>13.2825</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="223">
@@ -13109,10 +13109,10 @@
         <v>0.83</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.1928</v>
+        <v>-0.2099</v>
       </c>
       <c r="J223" t="n">
-        <v>-4.82</v>
+        <v>-5.2475</v>
       </c>
     </row>
     <row r="224">
@@ -13149,10 +13149,10 @@
         <v>0.8</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2226</v>
+        <v>-0.2397</v>
       </c>
       <c r="J224" t="n">
-        <v>-5.565</v>
+        <v>-5.9925</v>
       </c>
     </row>
     <row r="225">
@@ -13189,10 +13189,10 @@
         <v>0.76</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2619</v>
+        <v>-0.2784</v>
       </c>
       <c r="J225" t="n">
-        <v>-6.5475</v>
+        <v>-6.96</v>
       </c>
     </row>
     <row r="226">
@@ -13229,10 +13229,10 @@
         <v>0.72</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3006</v>
+        <v>-0.3161</v>
       </c>
       <c r="J226" t="n">
-        <v>-7.515</v>
+        <v>-7.9025</v>
       </c>
     </row>
     <row r="227">
@@ -13269,10 +13269,10 @@
         <v>1.59</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2619</v>
+        <v>1.2318</v>
       </c>
       <c r="J227" t="n">
-        <v>31.5475</v>
+        <v>30.795</v>
       </c>
     </row>
     <row r="228">
@@ -13309,10 +13309,10 @@
         <v>1.28</v>
       </c>
       <c r="I228" t="n">
-        <v>0.7533</v>
+        <v>0.7164</v>
       </c>
       <c r="J228" t="n">
-        <v>18.8325</v>
+        <v>17.91</v>
       </c>
     </row>
     <row r="229">
@@ -13349,10 +13349,10 @@
         <v>1.23</v>
       </c>
       <c r="I229" t="n">
-        <v>0.6353</v>
+        <v>0.6118</v>
       </c>
       <c r="J229" t="n">
-        <v>15.8825</v>
+        <v>15.295</v>
       </c>
     </row>
     <row r="230">
@@ -13389,10 +13389,10 @@
         <v>0.91</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3687</v>
+        <v>-0.3493</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.217499999999999</v>
+        <v>-8.7325</v>
       </c>
     </row>
     <row r="231">
@@ -13429,10 +13429,10 @@
         <v>0.88</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.455</v>
+        <v>-0.4284</v>
       </c>
       <c r="J231" t="n">
-        <v>-11.375</v>
+        <v>-10.71</v>
       </c>
     </row>
     <row r="232">
@@ -13469,10 +13469,10 @@
         <v>0.78</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.1864</v>
+        <v>-0.2157</v>
       </c>
       <c r="J232" t="n">
-        <v>-3.3552</v>
+        <v>-3.8826</v>
       </c>
     </row>
     <row r="233">
@@ -13509,10 +13509,10 @@
         <v>0.78</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.1864</v>
+        <v>-0.2157</v>
       </c>
       <c r="J233" t="n">
-        <v>-3.3552</v>
+        <v>-3.8826</v>
       </c>
     </row>
     <row r="234">
@@ -13549,10 +13549,10 @@
         <v>0.72</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.252</v>
+        <v>-0.2785</v>
       </c>
       <c r="J234" t="n">
-        <v>-4.536</v>
+        <v>-5.013</v>
       </c>
     </row>
     <row r="235">
@@ -13589,10 +13589,10 @@
         <v>0.35</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.6044</v>
+        <v>-0.6097</v>
       </c>
       <c r="J235" t="n">
-        <v>-10.8792</v>
+        <v>-10.9746</v>
       </c>
     </row>
     <row r="236">
@@ -13629,10 +13629,10 @@
         <v>0.27</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.6821</v>
+        <v>-0.6807</v>
       </c>
       <c r="J236" t="n">
-        <v>-12.2778</v>
+        <v>-12.2526</v>
       </c>
     </row>
     <row r="237">
@@ -13669,10 +13669,10 @@
         <v>2.22</v>
       </c>
       <c r="I237" t="n">
-        <v>1.8338</v>
+        <v>1.9005</v>
       </c>
       <c r="J237" t="n">
-        <v>33.0084</v>
+        <v>34.209</v>
       </c>
     </row>
     <row r="238">
@@ -13709,10 +13709,10 @@
         <v>1.51</v>
       </c>
       <c r="I238" t="n">
-        <v>1.099</v>
+        <v>1.0696</v>
       </c>
       <c r="J238" t="n">
-        <v>19.782</v>
+        <v>19.2528</v>
       </c>
     </row>
     <row r="239">
@@ -13749,10 +13749,10 @@
         <v>1.46</v>
       </c>
       <c r="I239" t="n">
-        <v>1.0376</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="J239" t="n">
-        <v>18.6768</v>
+        <v>17.973</v>
       </c>
     </row>
     <row r="240">
@@ -13789,10 +13789,10 @@
         <v>1.4</v>
       </c>
       <c r="I240" t="n">
-        <v>0.9383</v>
+        <v>0.8954</v>
       </c>
       <c r="J240" t="n">
-        <v>16.8894</v>
+        <v>16.1172</v>
       </c>
     </row>
     <row r="241">
@@ -13829,10 +13829,10 @@
         <v>1.33</v>
       </c>
       <c r="I241" t="n">
-        <v>0.7874</v>
+        <v>0.7617</v>
       </c>
       <c r="J241" t="n">
-        <v>14.1732</v>
+        <v>13.7106</v>
       </c>
     </row>
     <row r="242">
@@ -13869,10 +13869,10 @@
         <v>2.23</v>
       </c>
       <c r="I242" t="n">
-        <v>1.8338</v>
+        <v>1.9083</v>
       </c>
       <c r="J242" t="n">
-        <v>33.0084</v>
+        <v>34.3494</v>
       </c>
     </row>
     <row r="243">
@@ -13909,10 +13909,10 @@
         <v>1.79</v>
       </c>
       <c r="I243" t="n">
-        <v>1.412</v>
+        <v>1.407</v>
       </c>
       <c r="J243" t="n">
-        <v>25.416</v>
+        <v>25.326</v>
       </c>
     </row>
     <row r="244">
@@ -13949,10 +13949,10 @@
         <v>1.51</v>
       </c>
       <c r="I244" t="n">
-        <v>1.0975</v>
+        <v>1.0683</v>
       </c>
       <c r="J244" t="n">
-        <v>19.755</v>
+        <v>19.2294</v>
       </c>
     </row>
     <row r="245">
@@ -13989,10 +13989,10 @@
         <v>1.26</v>
       </c>
       <c r="I245" t="n">
-        <v>0.6242</v>
+        <v>0.6182</v>
       </c>
       <c r="J245" t="n">
-        <v>11.2356</v>
+        <v>11.1276</v>
       </c>
     </row>
     <row r="246">
@@ -14029,10 +14029,10 @@
         <v>1.21</v>
       </c>
       <c r="I246" t="n">
-        <v>0.5044</v>
+        <v>0.5115</v>
       </c>
       <c r="J246" t="n">
-        <v>9.0792</v>
+        <v>9.207000000000001</v>
       </c>
     </row>
     <row r="247">
@@ -14069,10 +14069,10 @@
         <v>0.78</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.1757</v>
+        <v>-0.2073</v>
       </c>
       <c r="J247" t="n">
-        <v>-3.1626</v>
+        <v>-3.7314</v>
       </c>
     </row>
     <row r="248">
@@ -14109,10 +14109,10 @@
         <v>0.6</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.3659</v>
+        <v>-0.3879</v>
       </c>
       <c r="J248" t="n">
-        <v>-6.5862</v>
+        <v>-6.9822</v>
       </c>
     </row>
     <row r="249">
@@ -14149,10 +14149,10 @@
         <v>0.58</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.3847</v>
+        <v>-0.4057</v>
       </c>
       <c r="J249" t="n">
-        <v>-6.9246</v>
+        <v>-7.3026</v>
       </c>
     </row>
     <row r="250">
@@ -14189,10 +14189,10 @@
         <v>0.41</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.5414</v>
+        <v>-0.5524</v>
       </c>
       <c r="J250" t="n">
-        <v>-9.745200000000001</v>
+        <v>-9.943199999999999</v>
       </c>
     </row>
     <row r="251">
@@ -14229,10 +14229,10 @@
         <v>0.4</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.551</v>
+        <v>-0.5613</v>
       </c>
       <c r="J251" t="n">
-        <v>-9.917999999999999</v>
+        <v>-10.1034</v>
       </c>
     </row>
     <row r="252">
@@ -14269,10 +14269,10 @@
         <v>1.65</v>
       </c>
       <c r="I252" t="n">
-        <v>1.3056</v>
+        <v>1.2837</v>
       </c>
       <c r="J252" t="n">
-        <v>30.0288</v>
+        <v>29.5251</v>
       </c>
     </row>
     <row r="253">
@@ -14309,10 +14309,10 @@
         <v>1.33</v>
       </c>
       <c r="I253" t="n">
-        <v>0.839</v>
+        <v>0.7972</v>
       </c>
       <c r="J253" t="n">
-        <v>19.297</v>
+        <v>18.3356</v>
       </c>
     </row>
     <row r="254">
@@ -14349,10 +14349,10 @@
         <v>1.23</v>
       </c>
       <c r="I254" t="n">
-        <v>0.6152</v>
+        <v>0.5982</v>
       </c>
       <c r="J254" t="n">
-        <v>14.1496</v>
+        <v>13.7586</v>
       </c>
     </row>
     <row r="255">
@@ -14389,10 +14389,10 @@
         <v>1.18</v>
       </c>
       <c r="I255" t="n">
-        <v>0.4932</v>
+        <v>0.4888</v>
       </c>
       <c r="J255" t="n">
-        <v>11.3436</v>
+        <v>11.2424</v>
       </c>
     </row>
     <row r="256">
@@ -14429,10 +14429,10 @@
         <v>1.08</v>
       </c>
       <c r="I256" t="n">
-        <v>0.2225</v>
+        <v>0.2411</v>
       </c>
       <c r="J256" t="n">
-        <v>5.1175</v>
+        <v>5.5453</v>
       </c>
     </row>
     <row r="257">
@@ -14469,10 +14469,10 @@
         <v>0.96</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.0404</v>
+        <v>-0.0549</v>
       </c>
       <c r="J257" t="n">
-        <v>-0.9292</v>
+        <v>-1.2627</v>
       </c>
     </row>
     <row r="258">
@@ -14509,10 +14509,10 @@
         <v>0.91</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.1029</v>
+        <v>-0.12</v>
       </c>
       <c r="J258" t="n">
-        <v>-2.3667</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="259">
@@ -14549,10 +14549,10 @@
         <v>0.86</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1581</v>
+        <v>-0.176</v>
       </c>
       <c r="J259" t="n">
-        <v>-3.6363</v>
+        <v>-4.048</v>
       </c>
     </row>
     <row r="260">
@@ -14589,10 +14589,10 @@
         <v>0.82</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1982</v>
+        <v>-0.2164</v>
       </c>
       <c r="J260" t="n">
-        <v>-4.5586</v>
+        <v>-4.9772</v>
       </c>
     </row>
     <row r="261">
@@ -14629,10 +14629,10 @@
         <v>0.54</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4629</v>
+        <v>-0.4727</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.6467</v>
+        <v>-10.8721</v>
       </c>
     </row>
     <row r="262">
@@ -14669,10 +14669,10 @@
         <v>1.08</v>
       </c>
       <c r="I262" t="n">
-        <v>0.2235</v>
+        <v>0.2259</v>
       </c>
       <c r="J262" t="n">
-        <v>5.811</v>
+        <v>5.8734</v>
       </c>
     </row>
     <row r="263">
@@ -14709,10 +14709,10 @@
         <v>0.98</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.0303</v>
+        <v>-0.0384</v>
       </c>
       <c r="J263" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.9984</v>
       </c>
     </row>
     <row r="264">
@@ -14749,10 +14749,10 @@
         <v>0.96</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.0578</v>
+        <v>-0.0684</v>
       </c>
       <c r="J264" t="n">
-        <v>-1.5028</v>
+        <v>-1.7784</v>
       </c>
     </row>
     <row r="265">
@@ -14789,10 +14789,10 @@
         <v>0.95</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.0704</v>
+        <v>-0.0819</v>
       </c>
       <c r="J265" t="n">
-        <v>-1.8304</v>
+        <v>-2.1294</v>
       </c>
     </row>
     <row r="266">
@@ -14829,10 +14829,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3377</v>
+        <v>-0.3506</v>
       </c>
       <c r="J266" t="n">
-        <v>-8.780200000000001</v>
+        <v>-9.115600000000001</v>
       </c>
     </row>
     <row r="267">
@@ -14869,10 +14869,10 @@
         <v>1.74</v>
       </c>
       <c r="I267" t="n">
-        <v>1.4458</v>
+        <v>1.4267</v>
       </c>
       <c r="J267" t="n">
-        <v>37.5908</v>
+        <v>37.0942</v>
       </c>
     </row>
     <row r="268">
@@ -14909,10 +14909,10 @@
         <v>1.36</v>
       </c>
       <c r="I268" t="n">
-        <v>0.9327</v>
+        <v>0.8752</v>
       </c>
       <c r="J268" t="n">
-        <v>24.2502</v>
+        <v>22.7552</v>
       </c>
     </row>
     <row r="269">
@@ -14949,10 +14949,10 @@
         <v>1.02</v>
       </c>
       <c r="I269" t="n">
-        <v>0.0504</v>
+        <v>0.0697</v>
       </c>
       <c r="J269" t="n">
-        <v>1.3104</v>
+        <v>1.8122</v>
       </c>
     </row>
     <row r="270">
@@ -14989,10 +14989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2796</v>
+        <v>-0.2656</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.2696</v>
+        <v>-6.9056</v>
       </c>
     </row>
     <row r="271">
@@ -15029,10 +15029,10 @@
         <v>0.88</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4575</v>
+        <v>-0.4302</v>
       </c>
       <c r="J271" t="n">
-        <v>-11.895</v>
+        <v>-11.1852</v>
       </c>
     </row>
     <row r="272">
@@ -15069,10 +15069,10 @@
         <v>1.71</v>
       </c>
       <c r="I272" t="n">
-        <v>1.3484</v>
+        <v>1.3343</v>
       </c>
       <c r="J272" t="n">
-        <v>29.6648</v>
+        <v>29.3546</v>
       </c>
     </row>
     <row r="273">
@@ -15109,10 +15109,10 @@
         <v>1.59</v>
       </c>
       <c r="I273" t="n">
-        <v>1.2075</v>
+        <v>1.1839</v>
       </c>
       <c r="J273" t="n">
-        <v>26.565</v>
+        <v>26.0458</v>
       </c>
     </row>
     <row r="274">
@@ -15149,10 +15149,10 @@
         <v>1.35</v>
       </c>
       <c r="I274" t="n">
-        <v>0.8611</v>
+        <v>0.8209</v>
       </c>
       <c r="J274" t="n">
-        <v>18.9442</v>
+        <v>18.0598</v>
       </c>
     </row>
     <row r="275">
@@ -15189,10 +15189,10 @@
         <v>1.32</v>
       </c>
       <c r="I275" t="n">
-        <v>0.795</v>
+        <v>0.7628</v>
       </c>
       <c r="J275" t="n">
-        <v>17.49</v>
+        <v>16.7816</v>
       </c>
     </row>
     <row r="276">
@@ -15229,10 +15229,10 @@
         <v>1.18</v>
       </c>
       <c r="I276" t="n">
-        <v>0.4636</v>
+        <v>0.4682</v>
       </c>
       <c r="J276" t="n">
-        <v>10.1992</v>
+        <v>10.3004</v>
       </c>
     </row>
     <row r="277">
@@ -15269,10 +15269,10 @@
         <v>0.86</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.1488</v>
+        <v>-0.1689</v>
       </c>
       <c r="J277" t="n">
-        <v>-3.2736</v>
+        <v>-3.7158</v>
       </c>
     </row>
     <row r="278">
@@ -15309,10 +15309,10 @@
         <v>0.84</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.1703</v>
+        <v>-0.1904</v>
       </c>
       <c r="J278" t="n">
-        <v>-3.7466</v>
+        <v>-4.1888</v>
       </c>
     </row>
     <row r="279">
@@ -15349,10 +15349,10 @@
         <v>0.82</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.1912</v>
+        <v>-0.2111</v>
       </c>
       <c r="J279" t="n">
-        <v>-4.2064</v>
+        <v>-4.6442</v>
       </c>
     </row>
     <row r="280">
@@ -15389,10 +15389,10 @@
         <v>0.65</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3522</v>
+        <v>-0.3687</v>
       </c>
       <c r="J280" t="n">
-        <v>-7.7484</v>
+        <v>-8.1114</v>
       </c>
     </row>
     <row r="281">
@@ -15429,10 +15429,10 @@
         <v>0.64</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3616</v>
+        <v>-0.3777</v>
       </c>
       <c r="J281" t="n">
-        <v>-7.9552</v>
+        <v>-8.3094</v>
       </c>
     </row>
     <row r="282">
@@ -15469,10 +15469,10 @@
         <v>1.09</v>
       </c>
       <c r="I282" t="n">
-        <v>0.2777</v>
+        <v>0.2706</v>
       </c>
       <c r="J282" t="n">
-        <v>7.2202</v>
+        <v>7.0356</v>
       </c>
     </row>
     <row r="283">
@@ -15509,10 +15509,10 @@
         <v>0.9</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.1186</v>
+        <v>-0.135</v>
       </c>
       <c r="J283" t="n">
-        <v>-3.0836</v>
+        <v>-3.51</v>
       </c>
     </row>
     <row r="284">
@@ -15549,10 +15549,10 @@
         <v>0.78</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.2398</v>
+        <v>-0.2572</v>
       </c>
       <c r="J284" t="n">
-        <v>-6.2348</v>
+        <v>-6.6872</v>
       </c>
     </row>
     <row r="285">
@@ -15589,10 +15589,10 @@
         <v>0.77</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2496</v>
+        <v>-0.2668</v>
       </c>
       <c r="J285" t="n">
-        <v>-6.4896</v>
+        <v>-6.9368</v>
       </c>
     </row>
     <row r="286">
@@ -15629,10 +15629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3265</v>
+        <v>-0.3418</v>
       </c>
       <c r="J286" t="n">
-        <v>-8.489000000000001</v>
+        <v>-8.886799999999999</v>
       </c>
     </row>
     <row r="287">
@@ -15669,10 +15669,10 @@
         <v>1.82</v>
       </c>
       <c r="I287" t="n">
-        <v>1.4937</v>
+        <v>1.4849</v>
       </c>
       <c r="J287" t="n">
-        <v>38.8362</v>
+        <v>38.6074</v>
       </c>
     </row>
     <row r="288">
@@ -15709,10 +15709,10 @@
         <v>1.35</v>
       </c>
       <c r="I288" t="n">
-        <v>0.8735000000000001</v>
+        <v>0.8293</v>
       </c>
       <c r="J288" t="n">
-        <v>22.711</v>
+        <v>21.5618</v>
       </c>
     </row>
     <row r="289">
@@ -15749,10 +15749,10 @@
         <v>1.27</v>
       </c>
       <c r="I289" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.6734</v>
       </c>
       <c r="J289" t="n">
-        <v>18.1246</v>
+        <v>17.5084</v>
       </c>
     </row>
     <row r="290">
@@ -15789,10 +15789,10 @@
         <v>1.26</v>
       </c>
       <c r="I290" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.6528</v>
       </c>
       <c r="J290" t="n">
-        <v>17.5214</v>
+        <v>16.9728</v>
       </c>
     </row>
     <row r="291">
@@ -15829,10 +15829,10 @@
         <v>1.06</v>
       </c>
       <c r="I291" t="n">
-        <v>0.1483</v>
+        <v>0.1747</v>
       </c>
       <c r="J291" t="n">
-        <v>3.8558</v>
+        <v>4.5422</v>
       </c>
     </row>
     <row r="292">
@@ -15869,10 +15869,10 @@
         <v>1.51</v>
       </c>
       <c r="I292" t="n">
-        <v>1.1277</v>
+        <v>1.0946</v>
       </c>
       <c r="J292" t="n">
-        <v>28.1925</v>
+        <v>27.365</v>
       </c>
     </row>
     <row r="293">
@@ -15909,10 +15909,10 @@
         <v>1.49</v>
       </c>
       <c r="I293" t="n">
-        <v>1.103</v>
+        <v>1.0677</v>
       </c>
       <c r="J293" t="n">
-        <v>27.575</v>
+        <v>26.6925</v>
       </c>
     </row>
     <row r="294">
@@ -15949,10 +15949,10 @@
         <v>1.38</v>
       </c>
       <c r="I294" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.8879</v>
       </c>
       <c r="J294" t="n">
-        <v>23.475</v>
+        <v>22.1975</v>
       </c>
     </row>
     <row r="295">
@@ -15989,10 +15989,10 @@
         <v>1.26</v>
       </c>
       <c r="I295" t="n">
-        <v>0.6791</v>
+        <v>0.6564</v>
       </c>
       <c r="J295" t="n">
-        <v>16.9775</v>
+        <v>16.41</v>
       </c>
     </row>
     <row r="296">
@@ -16029,10 +16029,10 @@
         <v>0.99</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.1337</v>
+        <v>-0.1145</v>
       </c>
       <c r="J296" t="n">
-        <v>-3.3425</v>
+        <v>-2.8625</v>
       </c>
     </row>
     <row r="297">
@@ -16069,10 +16069,10 @@
         <v>0.97</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.0101</v>
+        <v>-0.0272</v>
       </c>
       <c r="J297" t="n">
-        <v>-0.2525</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="298">
@@ -16109,10 +16109,10 @@
         <v>0.86</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.1464</v>
+        <v>-0.167</v>
       </c>
       <c r="J298" t="n">
-        <v>-3.66</v>
+        <v>-4.175</v>
       </c>
     </row>
     <row r="299">
@@ -16149,10 +16149,10 @@
         <v>0.84</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1681</v>
+        <v>-0.1887</v>
       </c>
       <c r="J299" t="n">
-        <v>-4.2025</v>
+        <v>-4.7175</v>
       </c>
     </row>
     <row r="300">
@@ -16189,10 +16189,10 @@
         <v>0.68</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3222</v>
+        <v>-0.3402</v>
       </c>
       <c r="J300" t="n">
-        <v>-8.055</v>
+        <v>-8.505000000000001</v>
       </c>
     </row>
     <row r="301">
@@ -16229,10 +16229,10 @@
         <v>0.4</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5829</v>
+        <v>-0.5864</v>
       </c>
       <c r="J301" t="n">
-        <v>-14.5725</v>
+        <v>-14.66</v>
       </c>
     </row>
     <row r="302">
@@ -16269,10 +16269,10 @@
         <v>1.22</v>
       </c>
       <c r="I302" t="n">
-        <v>0.5759</v>
+        <v>0.5419</v>
       </c>
       <c r="J302" t="n">
-        <v>12.6698</v>
+        <v>11.9218</v>
       </c>
     </row>
     <row r="303">
@@ -16309,10 +16309,10 @@
         <v>0.74</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.2711</v>
+        <v>-0.2895</v>
       </c>
       <c r="J303" t="n">
-        <v>-5.9642</v>
+        <v>-6.369</v>
       </c>
     </row>
     <row r="304">
@@ -16349,10 +16349,10 @@
         <v>0.72</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.2901</v>
+        <v>-0.308</v>
       </c>
       <c r="J304" t="n">
-        <v>-6.3822</v>
+        <v>-6.776</v>
       </c>
     </row>
     <row r="305">
@@ -16389,10 +16389,10 @@
         <v>0.71</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.2996</v>
+        <v>-0.3173</v>
       </c>
       <c r="J305" t="n">
-        <v>-6.5912</v>
+        <v>-6.9806</v>
       </c>
     </row>
     <row r="306">
@@ -16429,10 +16429,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4405</v>
+        <v>-0.4522</v>
       </c>
       <c r="J306" t="n">
-        <v>-9.691000000000001</v>
+        <v>-9.948399999999999</v>
       </c>
     </row>
     <row r="307">
@@ -16469,10 +16469,10 @@
         <v>1.5</v>
       </c>
       <c r="I307" t="n">
-        <v>1.1219</v>
+        <v>1.087</v>
       </c>
       <c r="J307" t="n">
-        <v>24.6818</v>
+        <v>23.914</v>
       </c>
     </row>
     <row r="308">
@@ -16509,10 +16509,10 @@
         <v>1.45</v>
       </c>
       <c r="I308" t="n">
-        <v>1.0589</v>
+        <v>1.0152</v>
       </c>
       <c r="J308" t="n">
-        <v>23.2958</v>
+        <v>22.3344</v>
       </c>
     </row>
     <row r="309">
@@ -16549,10 +16549,10 @@
         <v>1.3</v>
       </c>
       <c r="I309" t="n">
-        <v>0.774</v>
+        <v>0.7396</v>
       </c>
       <c r="J309" t="n">
-        <v>17.028</v>
+        <v>16.2712</v>
       </c>
     </row>
     <row r="310">
@@ -16589,10 +16589,10 @@
         <v>1.21</v>
       </c>
       <c r="I310" t="n">
-        <v>0.5681</v>
+        <v>0.5558</v>
       </c>
       <c r="J310" t="n">
-        <v>12.4982</v>
+        <v>12.2276</v>
       </c>
     </row>
     <row r="311">
@@ -16629,10 +16629,10 @@
         <v>0.99</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.1254</v>
+        <v>-0.1087</v>
       </c>
       <c r="J311" t="n">
-        <v>-2.7588</v>
+        <v>-2.3914</v>
       </c>
     </row>
     <row r="312">
@@ -16669,10 +16669,10 @@
         <v>1.09</v>
       </c>
       <c r="I312" t="n">
-        <v>0.3326</v>
+        <v>0.3111</v>
       </c>
       <c r="J312" t="n">
-        <v>6.9846</v>
+        <v>6.5331</v>
       </c>
     </row>
     <row r="313">
@@ -16709,10 +16709,10 @@
         <v>1.04</v>
       </c>
       <c r="I313" t="n">
-        <v>0.2113</v>
+        <v>0.1943</v>
       </c>
       <c r="J313" t="n">
-        <v>4.4373</v>
+        <v>4.0803</v>
       </c>
     </row>
     <row r="314">
@@ -16749,10 +16749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.312</v>
+        <v>-0.3305</v>
       </c>
       <c r="J314" t="n">
-        <v>-6.552</v>
+        <v>-6.9405</v>
       </c>
     </row>
     <row r="315">
@@ -16789,10 +16789,10 @@
         <v>0.47</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.5174</v>
+        <v>-0.5255</v>
       </c>
       <c r="J315" t="n">
-        <v>-10.8654</v>
+        <v>-11.0355</v>
       </c>
     </row>
     <row r="316">
@@ -16829,10 +16829,10 @@
         <v>0.43</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5544</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J316" t="n">
-        <v>-11.6424</v>
+        <v>-11.76</v>
       </c>
     </row>
     <row r="317">
@@ -16869,10 +16869,10 @@
         <v>1.87</v>
       </c>
       <c r="I317" t="n">
-        <v>1.5208</v>
+        <v>1.5185</v>
       </c>
       <c r="J317" t="n">
-        <v>31.9368</v>
+        <v>31.8885</v>
       </c>
     </row>
     <row r="318">
@@ -16909,10 +16909,10 @@
         <v>1.58</v>
       </c>
       <c r="I318" t="n">
-        <v>1.1881</v>
+        <v>1.1646</v>
       </c>
       <c r="J318" t="n">
-        <v>24.9501</v>
+        <v>24.4566</v>
       </c>
     </row>
     <row r="319">
@@ -16949,10 +16949,10 @@
         <v>1.37</v>
       </c>
       <c r="I319" t="n">
-        <v>0.894</v>
+        <v>0.8517</v>
       </c>
       <c r="J319" t="n">
-        <v>18.774</v>
+        <v>17.8857</v>
       </c>
     </row>
     <row r="320">
@@ -16989,10 +16989,10 @@
         <v>1.37</v>
       </c>
       <c r="I320" t="n">
-        <v>0.894</v>
+        <v>0.8517</v>
       </c>
       <c r="J320" t="n">
-        <v>18.774</v>
+        <v>17.8857</v>
       </c>
     </row>
     <row r="321">
@@ -17029,10 +17029,10 @@
         <v>1.24</v>
       </c>
       <c r="I321" t="n">
-        <v>0.5992</v>
+        <v>0.5918</v>
       </c>
       <c r="J321" t="n">
-        <v>12.5832</v>
+        <v>12.4278</v>
       </c>
     </row>
     <row r="322">
@@ -17069,10 +17069,10 @@
         <v>1.19</v>
       </c>
       <c r="I322" t="n">
-        <v>0.4969</v>
+        <v>0.4731</v>
       </c>
       <c r="J322" t="n">
-        <v>12.4225</v>
+        <v>11.8275</v>
       </c>
     </row>
     <row r="323">
@@ -17109,10 +17109,10 @@
         <v>1.19</v>
       </c>
       <c r="I323" t="n">
-        <v>0.4969</v>
+        <v>0.4731</v>
       </c>
       <c r="J323" t="n">
-        <v>12.4225</v>
+        <v>11.8275</v>
       </c>
     </row>
     <row r="324">
@@ -17149,10 +17149,10 @@
         <v>0.82</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.1984</v>
+        <v>-0.2166</v>
       </c>
       <c r="J324" t="n">
-        <v>-4.96</v>
+        <v>-5.415</v>
       </c>
     </row>
     <row r="325">
@@ -17189,10 +17189,10 @@
         <v>0.55</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.4542</v>
+        <v>-0.4644</v>
       </c>
       <c r="J325" t="n">
-        <v>-11.355</v>
+        <v>-11.61</v>
       </c>
     </row>
     <row r="326">
@@ -17229,10 +17229,10 @@
         <v>0.36</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.6274</v>
+        <v>-0.6267</v>
       </c>
       <c r="J326" t="n">
-        <v>-15.685</v>
+        <v>-15.6675</v>
       </c>
     </row>
     <row r="327">
@@ -17269,10 +17269,10 @@
         <v>1.74</v>
       </c>
       <c r="I327" t="n">
-        <v>1.4252</v>
+        <v>1.4083</v>
       </c>
       <c r="J327" t="n">
-        <v>35.63</v>
+        <v>35.2075</v>
       </c>
     </row>
     <row r="328">
@@ -17309,10 +17309,10 @@
         <v>1.34</v>
       </c>
       <c r="I328" t="n">
-        <v>0.8699</v>
+        <v>0.8226</v>
       </c>
       <c r="J328" t="n">
-        <v>21.7475</v>
+        <v>20.565</v>
       </c>
     </row>
     <row r="329">
@@ -17349,10 +17349,10 @@
         <v>1.12</v>
       </c>
       <c r="I329" t="n">
-        <v>0.3454</v>
+        <v>0.3526</v>
       </c>
       <c r="J329" t="n">
-        <v>8.635</v>
+        <v>8.815</v>
       </c>
     </row>
     <row r="330">
@@ -17389,10 +17389,10 @@
         <v>1.04</v>
       </c>
       <c r="I330" t="n">
-        <v>0.106</v>
+        <v>0.1286</v>
       </c>
       <c r="J330" t="n">
-        <v>2.65</v>
+        <v>3.215</v>
       </c>
     </row>
     <row r="331">
@@ -17429,10 +17429,10 @@
         <v>1.03</v>
       </c>
       <c r="I331" t="n">
-        <v>0.0712</v>
+        <v>0.0949</v>
       </c>
       <c r="J331" t="n">
-        <v>1.78</v>
+        <v>2.3725</v>
       </c>
     </row>
     <row r="332">
@@ -17469,10 +17469,10 @@
         <v>0.98</v>
       </c>
       <c r="I332" t="n">
-        <v>0.0171</v>
+        <v>-0.0075</v>
       </c>
       <c r="J332" t="n">
-        <v>0.342</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="333">
@@ -17509,10 +17509,10 @@
         <v>0.78</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.2273</v>
+        <v>-0.2477</v>
       </c>
       <c r="J333" t="n">
-        <v>-4.546</v>
+        <v>-4.954</v>
       </c>
     </row>
     <row r="334">
@@ -17549,10 +17549,10 @@
         <v>0.75</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.2561</v>
+        <v>-0.276</v>
       </c>
       <c r="J334" t="n">
-        <v>-5.122</v>
+        <v>-5.52</v>
       </c>
     </row>
     <row r="335">
@@ -17589,10 +17589,10 @@
         <v>0.72</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.2831</v>
+        <v>-0.3026</v>
       </c>
       <c r="J335" t="n">
-        <v>-5.662</v>
+        <v>-6.052</v>
       </c>
     </row>
     <row r="336">
@@ -17629,10 +17629,10 @@
         <v>0.45</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.5419</v>
       </c>
       <c r="J336" t="n">
-        <v>-10.696</v>
+        <v>-10.838</v>
       </c>
     </row>
     <row r="337">
@@ -17669,10 +17669,10 @@
         <v>1.69</v>
       </c>
       <c r="I337" t="n">
-        <v>1.3482</v>
+        <v>1.3299</v>
       </c>
       <c r="J337" t="n">
-        <v>26.964</v>
+        <v>26.598</v>
       </c>
     </row>
     <row r="338">
@@ -17709,10 +17709,10 @@
         <v>1.28</v>
       </c>
       <c r="I338" t="n">
-        <v>0.7262</v>
+        <v>0.6979</v>
       </c>
       <c r="J338" t="n">
-        <v>14.524</v>
+        <v>13.958</v>
       </c>
     </row>
     <row r="339">
@@ -17749,10 +17749,10 @@
         <v>1.27</v>
       </c>
       <c r="I339" t="n">
-        <v>0.7036</v>
+        <v>0.6778</v>
       </c>
       <c r="J339" t="n">
-        <v>14.072</v>
+        <v>13.556</v>
       </c>
     </row>
     <row r="340">
@@ -17789,10 +17789,10 @@
         <v>1.2</v>
       </c>
       <c r="I340" t="n">
-        <v>0.5377</v>
+        <v>0.5299</v>
       </c>
       <c r="J340" t="n">
-        <v>10.754</v>
+        <v>10.598</v>
       </c>
     </row>
     <row r="341">
@@ -17829,10 +17829,10 @@
         <v>1.15</v>
       </c>
       <c r="I341" t="n">
-        <v>0.4109</v>
+        <v>0.4155</v>
       </c>
       <c r="J341" t="n">
-        <v>8.218</v>
+        <v>8.31</v>
       </c>
     </row>
     <row r="342">
@@ -17869,10 +17869,10 @@
         <v>1.22</v>
       </c>
       <c r="I342" t="n">
-        <v>0.4772</v>
+        <v>0.469</v>
       </c>
       <c r="J342" t="n">
-        <v>13.3616</v>
+        <v>13.132</v>
       </c>
     </row>
     <row r="343">
@@ -17909,10 +17909,10 @@
         <v>1.2</v>
       </c>
       <c r="I343" t="n">
-        <v>0.4406</v>
+        <v>0.4351</v>
       </c>
       <c r="J343" t="n">
-        <v>12.3368</v>
+        <v>12.1828</v>
       </c>
     </row>
     <row r="344">
@@ -17949,10 +17949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.0985</v>
       </c>
       <c r="J344" t="n">
-        <v>-2.45</v>
+        <v>-2.758</v>
       </c>
     </row>
     <row r="345">
@@ -17989,10 +17989,10 @@
         <v>0.87</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.1662</v>
+        <v>-0.1797</v>
       </c>
       <c r="J345" t="n">
-        <v>-4.6536</v>
+        <v>-5.0316</v>
       </c>
     </row>
     <row r="346">
@@ -18029,10 +18029,10 @@
         <v>0.74</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.2973</v>
+        <v>-0.3099</v>
       </c>
       <c r="J346" t="n">
-        <v>-8.324400000000001</v>
+        <v>-8.677199999999999</v>
       </c>
     </row>
     <row r="347">
@@ -18069,10 +18069,10 @@
         <v>1.81</v>
       </c>
       <c r="I347" t="n">
-        <v>1.5151</v>
+        <v>1.502</v>
       </c>
       <c r="J347" t="n">
-        <v>42.4228</v>
+        <v>42.056</v>
       </c>
     </row>
     <row r="348">
@@ -18109,10 +18109,10 @@
         <v>1.32</v>
       </c>
       <c r="I348" t="n">
-        <v>0.8296</v>
+        <v>0.7864</v>
       </c>
       <c r="J348" t="n">
-        <v>23.2288</v>
+        <v>22.0192</v>
       </c>
     </row>
     <row r="349">
@@ -18149,10 +18149,10 @@
         <v>1.27</v>
       </c>
       <c r="I349" t="n">
-        <v>0.7161</v>
+        <v>0.6863</v>
       </c>
       <c r="J349" t="n">
-        <v>20.0508</v>
+        <v>19.2164</v>
       </c>
     </row>
     <row r="350">
@@ -18189,10 +18189,10 @@
         <v>0.93</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.3228</v>
+        <v>-0.3034</v>
       </c>
       <c r="J350" t="n">
-        <v>-9.038399999999999</v>
+        <v>-8.495200000000001</v>
       </c>
     </row>
     <row r="351">
@@ -18229,10 +18229,10 @@
         <v>0.85</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.5518</v>
+        <v>-0.5133</v>
       </c>
       <c r="J351" t="n">
-        <v>-15.4504</v>
+        <v>-14.3724</v>
       </c>
     </row>
     <row r="352">
@@ -18269,10 +18269,10 @@
         <v>1.17</v>
       </c>
       <c r="I352" t="n">
-        <v>0.5301</v>
+        <v>0.5087</v>
       </c>
       <c r="J352" t="n">
-        <v>15.903</v>
+        <v>15.261</v>
       </c>
     </row>
     <row r="353">
@@ -18309,10 +18309,10 @@
         <v>1.11</v>
       </c>
       <c r="I353" t="n">
-        <v>0.3673</v>
+        <v>0.3612</v>
       </c>
       <c r="J353" t="n">
-        <v>11.019</v>
+        <v>10.836</v>
       </c>
     </row>
     <row r="354">
@@ -18349,10 +18349,10 @@
         <v>1</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.0056</v>
+        <v>-0.0038</v>
       </c>
       <c r="J354" t="n">
-        <v>-0.168</v>
+        <v>-0.114</v>
       </c>
     </row>
     <row r="355">
@@ -18389,10 +18389,10 @@
         <v>0.98</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.1005</v>
+        <v>-0.1042</v>
       </c>
       <c r="J355" t="n">
-        <v>-3.015</v>
+        <v>-3.126</v>
       </c>
     </row>
     <row r="356">
@@ -18429,10 +18429,10 @@
         <v>0.89</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.3862</v>
+        <v>-0.3743</v>
       </c>
       <c r="J356" t="n">
-        <v>-11.586</v>
+        <v>-11.229</v>
       </c>
     </row>
     <row r="357">
@@ -18469,10 +18469,10 @@
         <v>1.22</v>
       </c>
       <c r="I357" t="n">
-        <v>0.4651</v>
+        <v>0.4601</v>
       </c>
       <c r="J357" t="n">
-        <v>13.953</v>
+        <v>13.803</v>
       </c>
     </row>
     <row r="358">
@@ -18509,10 +18509,10 @@
         <v>1.19</v>
       </c>
       <c r="I358" t="n">
-        <v>0.4108</v>
+        <v>0.4097</v>
       </c>
       <c r="J358" t="n">
-        <v>12.324</v>
+        <v>12.291</v>
       </c>
     </row>
     <row r="359">
@@ -18549,10 +18549,10 @@
         <v>0.96</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.0664</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="J359" t="n">
-        <v>-1.992</v>
+        <v>-2.247</v>
       </c>
     </row>
     <row r="360">
@@ -18589,10 +18589,10 @@
         <v>0.95</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.07920000000000001</v>
+        <v>-0.0886</v>
       </c>
       <c r="J360" t="n">
-        <v>-2.376</v>
+        <v>-2.658</v>
       </c>
     </row>
     <row r="361">
@@ -18629,10 +18629,10 @@
         <v>0.84</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.202</v>
+        <v>-0.2148</v>
       </c>
       <c r="J361" t="n">
-        <v>-6.06</v>
+        <v>-6.444</v>
       </c>
     </row>
     <row r="362">
@@ -18669,10 +18669,10 @@
         <v>1.14</v>
       </c>
       <c r="I362" t="n">
-        <v>0.3297</v>
+        <v>0.331</v>
       </c>
       <c r="J362" t="n">
-        <v>9.891</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="363">
@@ -18709,10 +18709,10 @@
         <v>1.06</v>
       </c>
       <c r="I363" t="n">
-        <v>0.1648</v>
+        <v>0.1724</v>
       </c>
       <c r="J363" t="n">
-        <v>4.944</v>
+        <v>5.172</v>
       </c>
     </row>
     <row r="364">
@@ -18749,10 +18749,10 @@
         <v>1.04</v>
       </c>
       <c r="I364" t="n">
-        <v>0.1189</v>
+        <v>0.1266</v>
       </c>
       <c r="J364" t="n">
-        <v>3.567</v>
+        <v>3.798</v>
       </c>
     </row>
     <row r="365">
@@ -18789,10 +18789,10 @@
         <v>0.98</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.0349</v>
+        <v>-0.0419</v>
       </c>
       <c r="J365" t="n">
-        <v>-1.047</v>
+        <v>-1.257</v>
       </c>
     </row>
     <row r="366">
@@ -18829,10 +18829,10 @@
         <v>0.71</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.3251</v>
+        <v>-0.3372</v>
       </c>
       <c r="J366" t="n">
-        <v>-9.753</v>
+        <v>-10.116</v>
       </c>
     </row>
     <row r="367">
@@ -18869,10 +18869,10 @@
         <v>1.82</v>
       </c>
       <c r="I367" t="n">
-        <v>1.5519</v>
+        <v>1.5366</v>
       </c>
       <c r="J367" t="n">
-        <v>46.557</v>
+        <v>46.098</v>
       </c>
     </row>
     <row r="368">
@@ -18909,10 +18909,10 @@
         <v>1.37</v>
       </c>
       <c r="I368" t="n">
-        <v>0.9603</v>
+        <v>0.9003</v>
       </c>
       <c r="J368" t="n">
-        <v>28.809</v>
+        <v>27.009</v>
       </c>
     </row>
     <row r="369">
@@ -18949,10 +18949,10 @@
         <v>0.92</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.3358</v>
+        <v>-0.3195</v>
       </c>
       <c r="J369" t="n">
-        <v>-10.074</v>
+        <v>-9.585000000000001</v>
       </c>
     </row>
     <row r="370">
@@ -18989,10 +18989,10 @@
         <v>0.88</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.4519</v>
+        <v>-0.4263</v>
       </c>
       <c r="J370" t="n">
-        <v>-13.557</v>
+        <v>-12.789</v>
       </c>
     </row>
     <row r="371">
@@ -19029,10 +19029,10 @@
         <v>0.84</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.5616</v>
+        <v>-0.5255</v>
       </c>
       <c r="J371" t="n">
-        <v>-16.848</v>
+        <v>-15.765</v>
       </c>
     </row>
     <row r="372">
@@ -19069,10 +19069,10 @@
         <v>1.84</v>
       </c>
       <c r="I372" t="n">
-        <v>1.488</v>
+        <v>1.4838</v>
       </c>
       <c r="J372" t="n">
-        <v>31.248</v>
+        <v>31.1598</v>
       </c>
     </row>
     <row r="373">
@@ -19109,10 +19109,10 @@
         <v>1.65</v>
       </c>
       <c r="I373" t="n">
-        <v>1.2703</v>
+        <v>1.2527</v>
       </c>
       <c r="J373" t="n">
-        <v>26.6763</v>
+        <v>26.3067</v>
       </c>
     </row>
     <row r="374">
@@ -19149,10 +19149,10 @@
         <v>1.41</v>
       </c>
       <c r="I374" t="n">
-        <v>0.9738</v>
+        <v>0.9264</v>
       </c>
       <c r="J374" t="n">
-        <v>20.4498</v>
+        <v>19.4544</v>
       </c>
     </row>
     <row r="375">
@@ -19189,10 +19189,10 @@
         <v>1.3</v>
       </c>
       <c r="I375" t="n">
-        <v>0.7401</v>
+        <v>0.7163</v>
       </c>
       <c r="J375" t="n">
-        <v>15.5421</v>
+        <v>15.0423</v>
       </c>
     </row>
     <row r="376">
@@ -19229,10 +19229,10 @@
         <v>1.2</v>
       </c>
       <c r="I376" t="n">
-        <v>0.5033</v>
+        <v>0.5059</v>
       </c>
       <c r="J376" t="n">
-        <v>10.5693</v>
+        <v>10.6239</v>
       </c>
     </row>
     <row r="377">
@@ -19269,10 +19269,10 @@
         <v>1.02</v>
       </c>
       <c r="I377" t="n">
-        <v>0.1669</v>
+        <v>0.1472</v>
       </c>
       <c r="J377" t="n">
-        <v>3.5049</v>
+        <v>3.0912</v>
       </c>
     </row>
     <row r="378">
@@ -19309,10 +19309,10 @@
         <v>0.91</v>
       </c>
       <c r="I378" t="n">
-        <v>-0.0829</v>
+        <v>-0.1044</v>
       </c>
       <c r="J378" t="n">
-        <v>-1.7409</v>
+        <v>-2.1924</v>
       </c>
     </row>
     <row r="379">
@@ -19349,10 +19349,10 @@
         <v>0.77</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.2355</v>
+        <v>-0.2561</v>
       </c>
       <c r="J379" t="n">
-        <v>-4.9455</v>
+        <v>-5.3781</v>
       </c>
     </row>
     <row r="380">
@@ -19389,10 +19389,10 @@
         <v>0.57</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.4215</v>
+        <v>-0.4357</v>
       </c>
       <c r="J380" t="n">
-        <v>-8.8515</v>
+        <v>-9.149699999999999</v>
       </c>
     </row>
     <row r="381">
@@ -19429,10 +19429,10 @@
         <v>0.36</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.6168</v>
+        <v>-0.6182</v>
       </c>
       <c r="J381" t="n">
-        <v>-12.9528</v>
+        <v>-12.9822</v>
       </c>
     </row>
     <row r="382">
@@ -19469,10 +19469,10 @@
         <v>0.99</v>
       </c>
       <c r="I382" t="n">
-        <v>-0.0023</v>
+        <v>-0.0112</v>
       </c>
       <c r="J382" t="n">
-        <v>-0.0552</v>
+        <v>-0.2688</v>
       </c>
     </row>
     <row r="383">
@@ -19509,10 +19509,10 @@
         <v>0.96</v>
       </c>
       <c r="I383" t="n">
-        <v>-0.0471</v>
+        <v>-0.0602</v>
       </c>
       <c r="J383" t="n">
-        <v>-1.1304</v>
+        <v>-1.4448</v>
       </c>
     </row>
     <row r="384">
@@ -19549,10 +19549,10 @@
         <v>0.89</v>
       </c>
       <c r="I384" t="n">
-        <v>-0.1307</v>
+        <v>-0.1471</v>
       </c>
       <c r="J384" t="n">
-        <v>-3.1368</v>
+        <v>-3.5304</v>
       </c>
     </row>
     <row r="385">
@@ -19589,10 +19589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.2113</v>
+        <v>-0.2288</v>
       </c>
       <c r="J385" t="n">
-        <v>-5.0712</v>
+        <v>-5.4912</v>
       </c>
     </row>
     <row r="386">
@@ -19629,10 +19629,10 @@
         <v>0.62</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.3935</v>
+        <v>-0.406</v>
       </c>
       <c r="J386" t="n">
-        <v>-9.444000000000001</v>
+        <v>-9.744</v>
       </c>
     </row>
     <row r="387">
@@ -19669,10 +19669,10 @@
         <v>1.67</v>
       </c>
       <c r="I387" t="n">
-        <v>1.3294</v>
+        <v>1.309</v>
       </c>
       <c r="J387" t="n">
-        <v>31.9056</v>
+        <v>31.416</v>
       </c>
     </row>
     <row r="388">
@@ -19709,10 +19709,10 @@
         <v>1.53</v>
       </c>
       <c r="I388" t="n">
-        <v>1.1581</v>
+        <v>1.1262</v>
       </c>
       <c r="J388" t="n">
-        <v>27.7944</v>
+        <v>27.0288</v>
       </c>
     </row>
     <row r="389">
@@ -19749,10 +19749,10 @@
         <v>1.15</v>
       </c>
       <c r="I389" t="n">
-        <v>0.4159</v>
+        <v>0.4189</v>
       </c>
       <c r="J389" t="n">
-        <v>9.9816</v>
+        <v>10.0536</v>
       </c>
     </row>
     <row r="390">
@@ -19789,10 +19789,10 @@
         <v>1.09</v>
       </c>
       <c r="I390" t="n">
-        <v>0.2513</v>
+        <v>0.268</v>
       </c>
       <c r="J390" t="n">
-        <v>6.0312</v>
+        <v>6.432</v>
       </c>
     </row>
     <row r="391">
@@ -19829,10 +19829,10 @@
         <v>1.04</v>
       </c>
       <c r="I391" t="n">
-        <v>0.096</v>
+        <v>0.1216</v>
       </c>
       <c r="J391" t="n">
-        <v>2.304</v>
+        <v>2.9184</v>
       </c>
     </row>
     <row r="392">
@@ -19869,10 +19869,10 @@
         <v>1.49</v>
       </c>
       <c r="I392" t="n">
-        <v>1.1538</v>
+        <v>1.1127</v>
       </c>
       <c r="J392" t="n">
-        <v>32.3064</v>
+        <v>31.1556</v>
       </c>
     </row>
     <row r="393">
@@ -19909,10 +19909,10 @@
         <v>1.16</v>
       </c>
       <c r="I393" t="n">
-        <v>0.4793</v>
+        <v>0.4681</v>
       </c>
       <c r="J393" t="n">
-        <v>13.4204</v>
+        <v>13.1068</v>
       </c>
     </row>
     <row r="394">
@@ -19949,10 +19949,10 @@
         <v>1</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.025</v>
+        <v>-0.0171</v>
       </c>
       <c r="J394" t="n">
-        <v>-0.7</v>
+        <v>-0.4788</v>
       </c>
     </row>
     <row r="395">
@@ -19989,10 +19989,10 @@
         <v>0.97</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.1581</v>
+        <v>-0.1548</v>
       </c>
       <c r="J395" t="n">
-        <v>-4.4268</v>
+        <v>-4.3344</v>
       </c>
     </row>
     <row r="396">
@@ -20029,10 +20029,10 @@
         <v>0.92</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.3203</v>
+        <v>-0.3087</v>
       </c>
       <c r="J396" t="n">
-        <v>-8.968400000000001</v>
+        <v>-8.643599999999999</v>
       </c>
     </row>
     <row r="397">
@@ -20069,10 +20069,10 @@
         <v>1.31</v>
       </c>
       <c r="I397" t="n">
-        <v>0.633</v>
+        <v>0.612</v>
       </c>
       <c r="J397" t="n">
-        <v>17.724</v>
+        <v>17.136</v>
       </c>
     </row>
     <row r="398">
@@ -20109,10 +20109,10 @@
         <v>1.17</v>
       </c>
       <c r="I398" t="n">
-        <v>0.3817</v>
+        <v>0.3809</v>
       </c>
       <c r="J398" t="n">
-        <v>10.6876</v>
+        <v>10.6652</v>
       </c>
     </row>
     <row r="399">
@@ -20149,10 +20149,10 @@
         <v>0.97</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.0504</v>
+        <v>-0.0585</v>
       </c>
       <c r="J399" t="n">
-        <v>-1.4112</v>
+        <v>-1.638</v>
       </c>
     </row>
     <row r="400">
@@ -20189,10 +20189,10 @@
         <v>0.86</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.1779</v>
+        <v>-0.1913</v>
       </c>
       <c r="J400" t="n">
-        <v>-4.9812</v>
+        <v>-5.3564</v>
       </c>
     </row>
     <row r="401">
@@ -20229,10 +20229,10 @@
         <v>0.71</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.3272</v>
+        <v>-0.3388</v>
       </c>
       <c r="J401" t="n">
-        <v>-9.1616</v>
+        <v>-9.4864</v>
       </c>
     </row>
     <row r="402">
@@ -20269,10 +20269,10 @@
         <v>1.03</v>
       </c>
       <c r="I402" t="n">
-        <v>0.128</v>
+        <v>0.1262</v>
       </c>
       <c r="J402" t="n">
-        <v>3.456</v>
+        <v>3.4074</v>
       </c>
     </row>
     <row r="403">
@@ -20309,10 +20309,10 @@
         <v>0.96</v>
       </c>
       <c r="I403" t="n">
-        <v>-0.0491</v>
+        <v>-0.0617</v>
       </c>
       <c r="J403" t="n">
-        <v>-1.3257</v>
+        <v>-1.6659</v>
       </c>
     </row>
     <row r="404">
@@ -20349,10 +20349,10 @@
         <v>0.8</v>
       </c>
       <c r="I404" t="n">
-        <v>-0.2226</v>
+        <v>-0.2397</v>
       </c>
       <c r="J404" t="n">
-        <v>-6.0102</v>
+        <v>-6.4719</v>
       </c>
     </row>
     <row r="405">
@@ -20389,10 +20389,10 @@
         <v>0.79</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.2325</v>
+        <v>-0.2495</v>
       </c>
       <c r="J405" t="n">
-        <v>-6.2775</v>
+        <v>-6.7365</v>
       </c>
     </row>
     <row r="406">
@@ -20429,10 +20429,10 @@
         <v>0.75</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.2716</v>
+        <v>-0.2879</v>
       </c>
       <c r="J406" t="n">
-        <v>-7.3332</v>
+        <v>-7.7733</v>
       </c>
     </row>
     <row r="407">
@@ -20469,10 +20469,10 @@
         <v>1.4</v>
       </c>
       <c r="I407" t="n">
-        <v>0.9991</v>
+        <v>0.9434</v>
       </c>
       <c r="J407" t="n">
-        <v>26.9757</v>
+        <v>25.4718</v>
       </c>
     </row>
     <row r="408">
@@ -20509,10 +20509,10 @@
         <v>1.38</v>
       </c>
       <c r="I408" t="n">
-        <v>0.9627</v>
+        <v>0.906</v>
       </c>
       <c r="J408" t="n">
-        <v>25.9929</v>
+        <v>24.462</v>
       </c>
     </row>
     <row r="409">
@@ -20549,10 +20549,10 @@
         <v>1.19</v>
       </c>
       <c r="I409" t="n">
-        <v>0.5326</v>
+        <v>0.5211</v>
       </c>
       <c r="J409" t="n">
-        <v>14.3802</v>
+        <v>14.0697</v>
       </c>
     </row>
     <row r="410">
@@ -20589,10 +20589,10 @@
         <v>1.1</v>
       </c>
       <c r="I410" t="n">
-        <v>0.2969</v>
+        <v>0.3063</v>
       </c>
       <c r="J410" t="n">
-        <v>8.016299999999999</v>
+        <v>8.270099999999999</v>
       </c>
     </row>
     <row r="411">
@@ -20629,10 +20629,10 @@
         <v>1.05</v>
       </c>
       <c r="I411" t="n">
-        <v>0.1464</v>
+        <v>0.1654</v>
       </c>
       <c r="J411" t="n">
-        <v>3.9528</v>
+        <v>4.4658</v>
       </c>
     </row>
     <row r="412">
@@ -20669,10 +20669,10 @@
         <v>1.97</v>
       </c>
       <c r="I412" t="n">
-        <v>1.6497</v>
+        <v>1.6511</v>
       </c>
       <c r="J412" t="n">
-        <v>34.6437</v>
+        <v>34.6731</v>
       </c>
     </row>
     <row r="413">
@@ -20709,10 +20709,10 @@
         <v>1.5</v>
       </c>
       <c r="I413" t="n">
-        <v>1.102</v>
+        <v>1.0695</v>
       </c>
       <c r="J413" t="n">
-        <v>23.142</v>
+        <v>22.4595</v>
       </c>
     </row>
     <row r="414">
@@ -20749,10 +20749,10 @@
         <v>1.35</v>
       </c>
       <c r="I414" t="n">
-        <v>0.8636</v>
+        <v>0.8226</v>
       </c>
       <c r="J414" t="n">
-        <v>18.1356</v>
+        <v>17.2746</v>
       </c>
     </row>
     <row r="415">
@@ -20789,10 +20789,10 @@
         <v>1.21</v>
       </c>
       <c r="I415" t="n">
-        <v>0.5412</v>
+        <v>0.5373</v>
       </c>
       <c r="J415" t="n">
-        <v>11.3652</v>
+        <v>11.2833</v>
       </c>
     </row>
     <row r="416">
@@ -20829,10 +20829,10 @@
         <v>1.05</v>
       </c>
       <c r="I416" t="n">
-        <v>0.1025</v>
+        <v>0.1347</v>
       </c>
       <c r="J416" t="n">
-        <v>2.1525</v>
+        <v>2.8287</v>
       </c>
     </row>
     <row r="417">
@@ -20869,10 +20869,10 @@
         <v>0.8</v>
       </c>
       <c r="I417" t="n">
-        <v>-0.1749</v>
+        <v>-0.2027</v>
       </c>
       <c r="J417" t="n">
-        <v>-3.6729</v>
+        <v>-4.2567</v>
       </c>
     </row>
     <row r="418">
@@ -20909,10 +20909,10 @@
         <v>0.64</v>
       </c>
       <c r="I418" t="n">
-        <v>-0.3397</v>
+        <v>-0.3609</v>
       </c>
       <c r="J418" t="n">
-        <v>-7.1337</v>
+        <v>-7.5789</v>
       </c>
     </row>
     <row r="419">
@@ -20949,10 +20949,10 @@
         <v>0.61</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.3663</v>
+        <v>-0.3865</v>
       </c>
       <c r="J419" t="n">
-        <v>-7.6923</v>
+        <v>-8.1165</v>
       </c>
     </row>
     <row r="420">
@@ -20989,10 +20989,10 @@
         <v>0.54</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.4294</v>
+        <v>-0.4465</v>
       </c>
       <c r="J420" t="n">
-        <v>-9.0174</v>
+        <v>-9.3765</v>
       </c>
     </row>
     <row r="421">
@@ -21029,10 +21029,10 @@
         <v>0.46</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.5047</v>
+        <v>-0.5168</v>
       </c>
       <c r="J421" t="n">
-        <v>-10.5987</v>
+        <v>-10.8528</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2541/event_2541_evp_summary.xlsx
+++ b/database/event/2541/event_2541_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.6391</v>
+        <v>7.3907</v>
       </c>
       <c r="C2" t="n">
-        <v>4.5419</v>
+        <v>4.3942</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8533</v>
+        <v>2.761</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6391</v>
+        <v>7.3907</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4639</v>
+        <v>2.4719</v>
       </c>
       <c r="G2" t="n">
-        <v>5.1753</v>
+        <v>4.9187</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6677</v>
+        <v>2.7148</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6677</v>
+        <v>2.7148</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1753</v>
+        <v>4.9187</v>
       </c>
       <c r="K2" t="n">
         <v>43</v>
@@ -529,7 +529,7 @@
         <v>205</v>
       </c>
       <c r="M2" t="n">
-        <v>7.843</v>
+        <v>7.6335</v>
       </c>
       <c r="N2" t="n">
         <v>248</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.8014</v>
+        <v>6.6221</v>
       </c>
       <c r="C3" t="n">
-        <v>4.0438</v>
+        <v>3.9372</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4719</v>
+        <v>2.4109</v>
       </c>
       <c r="E3" t="n">
-        <v>6.8014</v>
+        <v>6.6221</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0155</v>
+        <v>2.0192</v>
       </c>
       <c r="G3" t="n">
-        <v>4.7859</v>
+        <v>4.6029</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0155</v>
+        <v>2.0192</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0155</v>
+        <v>2.0192</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7859</v>
+        <v>4.6029</v>
       </c>
       <c r="K3" t="n">
         <v>43</v>
@@ -575,7 +575,7 @@
         <v>205</v>
       </c>
       <c r="M3" t="n">
-        <v>6.801399999999999</v>
+        <v>6.6221</v>
       </c>
       <c r="N3" t="n">
         <v>248</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.193</v>
+        <v>6.2281</v>
       </c>
       <c r="C4" t="n">
-        <v>3.6821</v>
+        <v>3.703</v>
       </c>
       <c r="D4" t="n">
-        <v>2.195</v>
+        <v>2.2314</v>
       </c>
       <c r="E4" t="n">
-        <v>6.193</v>
+        <v>6.2281</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8546</v>
+        <v>2.8203</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3384</v>
+        <v>3.4078</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5228</v>
+        <v>3.5133</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6136</v>
+        <v>3.6071</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3384</v>
+        <v>3.4078</v>
       </c>
       <c r="K4" t="n">
         <v>97</v>
@@ -621,7 +621,7 @@
         <v>198</v>
       </c>
       <c r="M4" t="n">
-        <v>6.952</v>
+        <v>7.0149</v>
       </c>
       <c r="N4" t="n">
         <v>295</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.0241</v>
+        <v>4.9703</v>
       </c>
       <c r="C5" t="n">
-        <v>2.9871</v>
+        <v>2.9551</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6629</v>
+        <v>1.6584</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0241</v>
+        <v>4.9703</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5983000000000001</v>
+        <v>0.6048</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4258</v>
+        <v>4.3654</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5983000000000001</v>
+        <v>0.6048</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6137</v>
+        <v>0.621</v>
       </c>
       <c r="J5" t="n">
-        <v>4.4258</v>
+        <v>4.3654</v>
       </c>
       <c r="K5" t="n">
         <v>97</v>
@@ -667,7 +667,7 @@
         <v>198</v>
       </c>
       <c r="M5" t="n">
-        <v>5.039499999999999</v>
+        <v>4.9864</v>
       </c>
       <c r="N5" t="n">
         <v>295</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.7579</v>
+        <v>4.6719</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8288</v>
+        <v>2.7777</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5417</v>
+        <v>1.5225</v>
       </c>
       <c r="E6" t="n">
-        <v>4.7579</v>
+        <v>4.6719</v>
       </c>
       <c r="F6" t="n">
-        <v>1.155</v>
+        <v>1.185</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6029</v>
+        <v>3.4869</v>
       </c>
       <c r="H6" t="n">
-        <v>1.155</v>
+        <v>1.185</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1848</v>
+        <v>1.2167</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6029</v>
+        <v>3.4869</v>
       </c>
       <c r="K6" t="n">
         <v>97</v>
@@ -713,7 +713,7 @@
         <v>198</v>
       </c>
       <c r="M6" t="n">
-        <v>4.7877</v>
+        <v>4.7036</v>
       </c>
       <c r="N6" t="n">
         <v>295</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.2333</v>
+        <v>4.3049</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5169</v>
+        <v>2.5595</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3029</v>
+        <v>1.3553</v>
       </c>
       <c r="E7" t="n">
-        <v>4.2333</v>
+        <v>4.3049</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1186</v>
+        <v>2.2091</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1147</v>
+        <v>2.0958</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1186</v>
+        <v>2.2091</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1732</v>
+        <v>2.2681</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1147</v>
+        <v>2.0958</v>
       </c>
       <c r="K7" t="n">
         <v>97</v>
@@ -759,7 +759,7 @@
         <v>198</v>
       </c>
       <c r="M7" t="n">
-        <v>4.2879</v>
+        <v>4.3639</v>
       </c>
       <c r="N7" t="n">
         <v>295</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.0212</v>
+        <v>4.0117</v>
       </c>
       <c r="C8" t="n">
-        <v>2.3908</v>
+        <v>2.3852</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2063</v>
+        <v>1.2217</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0212</v>
+        <v>4.0117</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4995</v>
+        <v>2.5099</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5217</v>
+        <v>1.5018</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7457</v>
+        <v>2.8019</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7457</v>
+        <v>2.8019</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5217</v>
+        <v>1.5018</v>
       </c>
       <c r="K8" t="n">
         <v>46</v>
@@ -805,7 +805,7 @@
         <v>109</v>
       </c>
       <c r="M8" t="n">
-        <v>4.2674</v>
+        <v>4.3037</v>
       </c>
       <c r="N8" t="n">
         <v>155</v>
@@ -814,139 +814,139 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.522</v>
+        <v>3.4486</v>
       </c>
       <c r="C9" t="n">
-        <v>2.094</v>
+        <v>2.0504</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9791</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>3.522</v>
+        <v>3.4486</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5063</v>
+        <v>1.8875</v>
       </c>
       <c r="G9" t="n">
-        <v>2.0157</v>
+        <v>1.5611</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5063</v>
+        <v>1.8875</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5451</v>
+        <v>1.8875</v>
       </c>
       <c r="J9" t="n">
-        <v>2.0157</v>
+        <v>1.5611</v>
       </c>
       <c r="K9" t="n">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="L9" t="n">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5608</v>
+        <v>3.4486</v>
       </c>
       <c r="N9" t="n">
-        <v>212</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.5128</v>
+        <v>3.3972</v>
       </c>
       <c r="C10" t="n">
-        <v>2.0886</v>
+        <v>2.0198</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9749</v>
+        <v>0.9418</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5128</v>
+        <v>3.3972</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8903</v>
+        <v>2.3314</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6225</v>
+        <v>1.0658</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8903</v>
+        <v>2.3927</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8903</v>
+        <v>2.3927</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6225</v>
+        <v>1.0658</v>
       </c>
       <c r="K10" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="L10" t="n">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5128</v>
+        <v>3.4585</v>
       </c>
       <c r="N10" t="n">
-        <v>155</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.4847</v>
+        <v>3.3355</v>
       </c>
       <c r="C11" t="n">
-        <v>2.0718</v>
+        <v>1.9831</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9621</v>
+        <v>0.9137</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4847</v>
+        <v>3.3355</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3311</v>
+        <v>1.4468</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1536</v>
+        <v>1.8887</v>
       </c>
       <c r="H11" t="n">
-        <v>2.3772</v>
+        <v>1.4468</v>
       </c>
       <c r="I11" t="n">
-        <v>2.3772</v>
+        <v>1.4855</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1536</v>
+        <v>1.8887</v>
       </c>
       <c r="K11" t="n">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="L11" t="n">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5308</v>
+        <v>3.3742</v>
       </c>
       <c r="N11" t="n">
-        <v>108</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.4</v>
+        <v>3.3093</v>
       </c>
       <c r="C12" t="n">
-        <v>2.0215</v>
+        <v>1.9676</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9235</v>
+        <v>0.9018</v>
       </c>
       <c r="E12" t="n">
-        <v>3.4</v>
+        <v>3.3093</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5372</v>
+        <v>1.5074</v>
       </c>
       <c r="G12" t="n">
-        <v>1.8628</v>
+        <v>1.8019</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5372</v>
+        <v>1.5074</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5372</v>
+        <v>1.5074</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8628</v>
+        <v>1.8019</v>
       </c>
       <c r="K12" t="n">
         <v>43</v>
@@ -989,7 +989,7 @@
         <v>205</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.3093</v>
       </c>
       <c r="N12" t="n">
         <v>248</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.1724</v>
+        <v>3.1586</v>
       </c>
       <c r="C13" t="n">
-        <v>1.8862</v>
+        <v>1.878</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8199</v>
+        <v>0.8331</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1724</v>
+        <v>3.1586</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7245</v>
+        <v>2.6942</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4479</v>
+        <v>0.4644</v>
       </c>
       <c r="H13" t="n">
-        <v>3.2382</v>
+        <v>3.2241</v>
       </c>
       <c r="I13" t="n">
-        <v>3.3216</v>
+        <v>3.3102</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4479</v>
+        <v>0.4644</v>
       </c>
       <c r="K13" t="n">
         <v>88</v>
@@ -1035,7 +1035,7 @@
         <v>124</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7695</v>
+        <v>3.7746</v>
       </c>
       <c r="N13" t="n">
         <v>212</v>
@@ -1044,35 +1044,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.944</v>
+        <v>2.9157</v>
       </c>
       <c r="C14" t="n">
-        <v>1.7504</v>
+        <v>1.7335</v>
       </c>
       <c r="D14" t="n">
-        <v>0.716</v>
+        <v>0.7225</v>
       </c>
       <c r="E14" t="n">
-        <v>2.944</v>
+        <v>2.9157</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7269</v>
+        <v>2.4675</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2171</v>
+        <v>0.4482</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2433</v>
+        <v>2.7045</v>
       </c>
       <c r="I14" t="n">
-        <v>3.3269</v>
+        <v>2.7768</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2171</v>
+        <v>0.4482</v>
       </c>
       <c r="K14" t="n">
         <v>88</v>
@@ -1081,7 +1081,7 @@
         <v>124</v>
       </c>
       <c r="M14" t="n">
-        <v>3.544</v>
+        <v>3.225</v>
       </c>
       <c r="N14" t="n">
         <v>212</v>
@@ -1090,35 +1090,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.9376</v>
+        <v>2.8918</v>
       </c>
       <c r="C15" t="n">
-        <v>1.7466</v>
+        <v>1.7193</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7131</v>
+        <v>0.7116</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9376</v>
+        <v>2.8918</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4692</v>
+        <v>2.7157</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4684</v>
+        <v>0.1761</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6795</v>
+        <v>3.2734</v>
       </c>
       <c r="I15" t="n">
-        <v>2.7485</v>
+        <v>3.3609</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4684</v>
+        <v>0.1761</v>
       </c>
       <c r="K15" t="n">
         <v>88</v>
@@ -1127,7 +1127,7 @@
         <v>124</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2169</v>
+        <v>3.537</v>
       </c>
       <c r="N15" t="n">
         <v>212</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2418</v>
+        <v>2.1479</v>
       </c>
       <c r="C16" t="n">
-        <v>1.3329</v>
+        <v>1.277</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3963</v>
+        <v>0.3727</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2418</v>
+        <v>2.1479</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8708</v>
+        <v>1.8124</v>
       </c>
       <c r="G16" t="n">
-        <v>0.371</v>
+        <v>0.3356</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8708</v>
+        <v>1.8124</v>
       </c>
       <c r="I16" t="n">
-        <v>1.919</v>
+        <v>1.8608</v>
       </c>
       <c r="J16" t="n">
-        <v>0.371</v>
+        <v>0.3356</v>
       </c>
       <c r="K16" t="n">
         <v>128</v>
@@ -1173,7 +1173,7 @@
         <v>70</v>
       </c>
       <c r="M16" t="n">
-        <v>2.29</v>
+        <v>2.1964</v>
       </c>
       <c r="N16" t="n">
         <v>198</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1732</v>
+        <v>2.1106</v>
       </c>
       <c r="C17" t="n">
-        <v>1.2921</v>
+        <v>1.2549</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3651</v>
+        <v>0.3557</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1732</v>
+        <v>2.1106</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7911</v>
+        <v>2.3454</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3821</v>
+        <v>-0.2348</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7911</v>
+        <v>2.4249</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7911</v>
+        <v>2.4897</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3821</v>
+        <v>-0.2348</v>
       </c>
       <c r="K17" t="n">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="L17" t="n">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="M17" t="n">
-        <v>2.1732</v>
+        <v>2.2549</v>
       </c>
       <c r="N17" t="n">
-        <v>155</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.1721</v>
+        <v>2.0716</v>
       </c>
       <c r="C18" t="n">
-        <v>1.2914</v>
+        <v>1.2317</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3646</v>
+        <v>0.3379</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1721</v>
+        <v>2.0716</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4073</v>
+        <v>0.7381</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2352</v>
+        <v>1.3335</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5438</v>
+        <v>0.7381</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6094</v>
+        <v>0.7381</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2352</v>
+        <v>1.3335</v>
       </c>
       <c r="K18" t="n">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="L18" t="n">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="M18" t="n">
-        <v>2.3742</v>
+        <v>2.0716</v>
       </c>
       <c r="N18" t="n">
-        <v>198</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.1247</v>
+        <v>2.01</v>
       </c>
       <c r="C19" t="n">
-        <v>1.2633</v>
+        <v>1.1951</v>
       </c>
       <c r="D19" t="n">
-        <v>0.343</v>
+        <v>0.3099</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1247</v>
+        <v>2.01</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1247</v>
+        <v>2.01</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1247</v>
+        <v>2.01</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1247</v>
+        <v>2.01</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.1247</v>
+        <v>2.01</v>
       </c>
       <c r="N19" t="n">
         <v>121</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.0165</v>
+        <v>2.0037</v>
       </c>
       <c r="C20" t="n">
-        <v>1.1989</v>
+        <v>1.1913</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2937</v>
+        <v>0.307</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0165</v>
+        <v>2.0037</v>
       </c>
       <c r="F20" t="n">
-        <v>2.113</v>
+        <v>2.1145</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0965</v>
+        <v>-0.1108</v>
       </c>
       <c r="H20" t="n">
-        <v>2.113</v>
+        <v>2.1145</v>
       </c>
       <c r="I20" t="n">
-        <v>2.113</v>
+        <v>2.1145</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0965</v>
+        <v>-0.1108</v>
       </c>
       <c r="K20" t="n">
         <v>54</v>
@@ -1357,7 +1357,7 @@
         <v>54</v>
       </c>
       <c r="M20" t="n">
-        <v>2.0165</v>
+        <v>2.0037</v>
       </c>
       <c r="N20" t="n">
         <v>108</v>
@@ -1366,35 +1366,35 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.0141</v>
+        <v>1.9736</v>
       </c>
       <c r="C21" t="n">
-        <v>1.1975</v>
+        <v>1.1734</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2927</v>
+        <v>0.2933</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0141</v>
+        <v>1.9736</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6065</v>
+        <v>1.475</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4076</v>
+        <v>0.4986</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6065</v>
+        <v>1.475</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6065</v>
+        <v>1.475</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4076</v>
+        <v>0.4986</v>
       </c>
       <c r="K21" t="n">
         <v>50</v>
@@ -1403,7 +1403,7 @@
         <v>69</v>
       </c>
       <c r="M21" t="n">
-        <v>2.0141</v>
+        <v>1.9736</v>
       </c>
       <c r="N21" t="n">
         <v>119</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.9962</v>
+        <v>1.9437</v>
       </c>
       <c r="C22" t="n">
-        <v>1.1869</v>
+        <v>1.1556</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2845</v>
+        <v>0.2797</v>
       </c>
       <c r="E22" t="n">
-        <v>1.9962</v>
+        <v>1.9437</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9962</v>
+        <v>1.9437</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9962</v>
+        <v>1.9437</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9962</v>
+        <v>1.9437</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.9962</v>
+        <v>1.9437</v>
       </c>
       <c r="N22" t="n">
         <v>121</v>
@@ -1458,35 +1458,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.9933</v>
+        <v>1.9375</v>
       </c>
       <c r="C23" t="n">
-        <v>1.1851</v>
+        <v>1.152</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2832</v>
+        <v>0.2768</v>
       </c>
       <c r="E23" t="n">
-        <v>1.9933</v>
+        <v>1.9375</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4837</v>
+        <v>1.6134</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.3241</v>
       </c>
       <c r="H23" t="n">
-        <v>1.4837</v>
+        <v>1.6134</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4837</v>
+        <v>1.6134</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.3241</v>
       </c>
       <c r="K23" t="n">
         <v>50</v>
@@ -1495,7 +1495,7 @@
         <v>69</v>
       </c>
       <c r="M23" t="n">
-        <v>1.9933</v>
+        <v>1.9375</v>
       </c>
       <c r="N23" t="n">
         <v>119</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.953</v>
+        <v>1.9183</v>
       </c>
       <c r="C24" t="n">
-        <v>1.1612</v>
+        <v>1.1405</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2648</v>
+        <v>0.2681</v>
       </c>
       <c r="E24" t="n">
-        <v>1.953</v>
+        <v>1.9183</v>
       </c>
       <c r="F24" t="n">
-        <v>2.4871</v>
+        <v>2.4384</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.5341</v>
+        <v>-0.5201</v>
       </c>
       <c r="H24" t="n">
-        <v>2.7186</v>
+        <v>2.6379</v>
       </c>
       <c r="I24" t="n">
-        <v>2.7887</v>
+        <v>2.7084</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5341</v>
+        <v>-0.5201</v>
       </c>
       <c r="K24" t="n">
         <v>128</v>
@@ -1541,7 +1541,7 @@
         <v>70</v>
       </c>
       <c r="M24" t="n">
-        <v>2.2546</v>
+        <v>2.1883</v>
       </c>
       <c r="N24" t="n">
         <v>198</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.9196</v>
+        <v>1.8843</v>
       </c>
       <c r="C25" t="n">
-        <v>1.1413</v>
+        <v>1.1203</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2496</v>
+        <v>0.2526</v>
       </c>
       <c r="E25" t="n">
-        <v>1.9196</v>
+        <v>1.8843</v>
       </c>
       <c r="F25" t="n">
-        <v>2.0516</v>
+        <v>2.0359</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.132</v>
+        <v>-0.1516</v>
       </c>
       <c r="H25" t="n">
-        <v>2.0516</v>
+        <v>2.0359</v>
       </c>
       <c r="I25" t="n">
-        <v>2.1045</v>
+        <v>2.0903</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.132</v>
+        <v>-0.1516</v>
       </c>
       <c r="K25" t="n">
         <v>128</v>
@@ -1587,7 +1587,7 @@
         <v>70</v>
       </c>
       <c r="M25" t="n">
-        <v>1.9725</v>
+        <v>1.9387</v>
       </c>
       <c r="N25" t="n">
         <v>198</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.7867</v>
+        <v>1.6889</v>
       </c>
       <c r="C26" t="n">
-        <v>1.0623</v>
+        <v>1.0041</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1891</v>
+        <v>0.1636</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7867</v>
+        <v>1.6889</v>
       </c>
       <c r="F26" t="n">
-        <v>1.3946</v>
+        <v>1.3624</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3921</v>
+        <v>0.3265</v>
       </c>
       <c r="H26" t="n">
-        <v>1.3946</v>
+        <v>1.3624</v>
       </c>
       <c r="I26" t="n">
-        <v>1.3946</v>
+        <v>1.3624</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3921</v>
+        <v>0.3265</v>
       </c>
       <c r="K26" t="n">
         <v>43</v>
@@ -1633,7 +1633,7 @@
         <v>205</v>
       </c>
       <c r="M26" t="n">
-        <v>1.7867</v>
+        <v>1.6889</v>
       </c>
       <c r="N26" t="n">
         <v>248</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.7022</v>
+        <v>1.6466</v>
       </c>
       <c r="C27" t="n">
-        <v>1.0121</v>
+        <v>0.979</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1507</v>
+        <v>0.1443</v>
       </c>
       <c r="E27" t="n">
-        <v>1.7022</v>
+        <v>1.6466</v>
       </c>
       <c r="F27" t="n">
-        <v>0.955</v>
+        <v>0.987</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7472</v>
+        <v>0.6596</v>
       </c>
       <c r="H27" t="n">
-        <v>0.955</v>
+        <v>0.987</v>
       </c>
       <c r="I27" t="n">
-        <v>0.955</v>
+        <v>0.987</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7472</v>
+        <v>0.6596</v>
       </c>
       <c r="K27" t="n">
         <v>46</v>
@@ -1679,7 +1679,7 @@
         <v>109</v>
       </c>
       <c r="M27" t="n">
-        <v>1.7022</v>
+        <v>1.6466</v>
       </c>
       <c r="N27" t="n">
         <v>155</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.6744</v>
+        <v>1.6149</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9955000000000001</v>
+        <v>0.9601</v>
       </c>
       <c r="D28" t="n">
-        <v>0.138</v>
+        <v>0.1299</v>
       </c>
       <c r="E28" t="n">
-        <v>1.6744</v>
+        <v>1.6149</v>
       </c>
       <c r="F28" t="n">
-        <v>1.2482</v>
+        <v>1.201</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4262</v>
+        <v>0.4139</v>
       </c>
       <c r="H28" t="n">
-        <v>1.2482</v>
+        <v>1.201</v>
       </c>
       <c r="I28" t="n">
-        <v>1.2482</v>
+        <v>1.201</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4262</v>
+        <v>0.4139</v>
       </c>
       <c r="K28" t="n">
         <v>50</v>
@@ -1725,7 +1725,7 @@
         <v>69</v>
       </c>
       <c r="M28" t="n">
-        <v>1.6744</v>
+        <v>1.6149</v>
       </c>
       <c r="N28" t="n">
         <v>119</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.466</v>
+        <v>1.4876</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8716</v>
+        <v>0.8845</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0432</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>1.466</v>
+        <v>1.4876</v>
       </c>
       <c r="F29" t="n">
-        <v>1.7996</v>
+        <v>1.789</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.3336</v>
+        <v>-0.3014</v>
       </c>
       <c r="H29" t="n">
-        <v>1.7996</v>
+        <v>1.789</v>
       </c>
       <c r="I29" t="n">
-        <v>1.7996</v>
+        <v>1.789</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.3336</v>
+        <v>-0.3014</v>
       </c>
       <c r="K29" t="n">
         <v>50</v>
@@ -1771,7 +1771,7 @@
         <v>69</v>
       </c>
       <c r="M29" t="n">
-        <v>1.466</v>
+        <v>1.4876</v>
       </c>
       <c r="N29" t="n">
         <v>119</v>
@@ -1780,185 +1780,185 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.4296</v>
+        <v>1.4326</v>
       </c>
       <c r="C30" t="n">
-        <v>0.85</v>
+        <v>0.8518</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0266</v>
+        <v>0.0468</v>
       </c>
       <c r="E30" t="n">
-        <v>1.4296</v>
+        <v>1.4326</v>
       </c>
       <c r="F30" t="n">
-        <v>1.4252</v>
+        <v>0.2488</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0044</v>
+        <v>1.1838</v>
       </c>
       <c r="H30" t="n">
-        <v>1.4252</v>
+        <v>0.2488</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4252</v>
+        <v>0.2554</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0044</v>
+        <v>1.1838</v>
       </c>
       <c r="K30" t="n">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="L30" t="n">
-        <v>109</v>
+        <v>198</v>
       </c>
       <c r="M30" t="n">
-        <v>1.4296</v>
+        <v>1.4392</v>
       </c>
       <c r="N30" t="n">
-        <v>155</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.4144</v>
+        <v>1.3439</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8409</v>
+        <v>0.799</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0197</v>
+        <v>0.0064</v>
       </c>
       <c r="E31" t="n">
-        <v>1.4144</v>
+        <v>1.3439</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1879</v>
+        <v>1.3844</v>
       </c>
       <c r="G31" t="n">
-        <v>1.2265</v>
+        <v>-0.0405</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1879</v>
+        <v>1.3844</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1927</v>
+        <v>1.3844</v>
       </c>
       <c r="J31" t="n">
-        <v>1.2265</v>
+        <v>-0.0405</v>
       </c>
       <c r="K31" t="n">
-        <v>97</v>
+        <v>46</v>
       </c>
       <c r="L31" t="n">
-        <v>198</v>
+        <v>109</v>
       </c>
       <c r="M31" t="n">
-        <v>1.4192</v>
+        <v>1.3439</v>
       </c>
       <c r="N31" t="n">
-        <v>295</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>loWel</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.1912</v>
+        <v>1.2706</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7082000000000001</v>
+        <v>0.7554</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0819</v>
+        <v>-0.027</v>
       </c>
       <c r="E32" t="n">
-        <v>1.1912</v>
+        <v>1.2706</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8561</v>
+        <v>1.8332</v>
       </c>
       <c r="G32" t="n">
-        <v>0.3351</v>
+        <v>-0.5626</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8561</v>
+        <v>1.8332</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8561</v>
+        <v>1.8332</v>
       </c>
       <c r="J32" t="n">
-        <v>0.3351</v>
+        <v>-0.5626</v>
       </c>
       <c r="K32" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="L32" t="n">
-        <v>54</v>
+        <v>205</v>
       </c>
       <c r="M32" t="n">
-        <v>1.1912</v>
+        <v>1.2706</v>
       </c>
       <c r="N32" t="n">
-        <v>108</v>
+        <v>248</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>loWel</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.1806</v>
+        <v>1.1394</v>
       </c>
       <c r="C33" t="n">
-        <v>0.7019</v>
+        <v>0.6774</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0868</v>
+        <v>-0.0867</v>
       </c>
       <c r="E33" t="n">
-        <v>1.1806</v>
+        <v>1.1394</v>
       </c>
       <c r="F33" t="n">
-        <v>1.8402</v>
+        <v>0.8162</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.6596</v>
+        <v>0.3232</v>
       </c>
       <c r="H33" t="n">
-        <v>1.8402</v>
+        <v>0.8162</v>
       </c>
       <c r="I33" t="n">
-        <v>1.8402</v>
+        <v>0.8162</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.6596</v>
+        <v>0.3232</v>
       </c>
       <c r="K33" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="L33" t="n">
-        <v>205</v>
+        <v>54</v>
       </c>
       <c r="M33" t="n">
-        <v>1.1806</v>
+        <v>1.1394</v>
       </c>
       <c r="N33" t="n">
-        <v>248</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34">
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.1283</v>
+        <v>1.103</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6708</v>
+        <v>0.6558</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1106</v>
+        <v>-0.1033</v>
       </c>
       <c r="E34" t="n">
-        <v>1.1283</v>
+        <v>1.103</v>
       </c>
       <c r="F34" t="n">
-        <v>1.7304</v>
+        <v>1.676</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.6021</v>
+        <v>-0.573</v>
       </c>
       <c r="H34" t="n">
-        <v>1.7304</v>
+        <v>1.676</v>
       </c>
       <c r="I34" t="n">
-        <v>1.775</v>
+        <v>1.7208</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.6021</v>
+        <v>-0.573</v>
       </c>
       <c r="K34" t="n">
         <v>120</v>
@@ -2001,7 +2001,7 @@
         <v>45</v>
       </c>
       <c r="M34" t="n">
-        <v>1.1729</v>
+        <v>1.1478</v>
       </c>
       <c r="N34" t="n">
         <v>165</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.114</v>
+        <v>1.0509</v>
       </c>
       <c r="C35" t="n">
-        <v>0.6623</v>
+        <v>0.6248</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1171</v>
+        <v>-0.1271</v>
       </c>
       <c r="E35" t="n">
-        <v>1.114</v>
+        <v>1.0509</v>
       </c>
       <c r="F35" t="n">
-        <v>1.6129</v>
+        <v>1.5202</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.4989</v>
+        <v>-0.4693</v>
       </c>
       <c r="H35" t="n">
-        <v>1.6129</v>
+        <v>1.5202</v>
       </c>
       <c r="I35" t="n">
-        <v>1.6545</v>
+        <v>1.5608</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.4989</v>
+        <v>-0.4693</v>
       </c>
       <c r="K35" t="n">
         <v>120</v>
@@ -2047,7 +2047,7 @@
         <v>45</v>
       </c>
       <c r="M35" t="n">
-        <v>1.1556</v>
+        <v>1.0915</v>
       </c>
       <c r="N35" t="n">
         <v>165</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.0851</v>
+        <v>0.9692</v>
       </c>
       <c r="C36" t="n">
-        <v>0.6452</v>
+        <v>0.5762</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1302</v>
+        <v>-0.1643</v>
       </c>
       <c r="E36" t="n">
-        <v>1.0851</v>
+        <v>0.9692</v>
       </c>
       <c r="F36" t="n">
-        <v>1.0851</v>
+        <v>0.9692</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.0851</v>
+        <v>0.9692</v>
       </c>
       <c r="I36" t="n">
-        <v>1.0851</v>
+        <v>0.9692</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.0851</v>
+        <v>0.9692</v>
       </c>
       <c r="N36" t="n">
         <v>53</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9927</v>
+        <v>0.9403</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.5591</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1723</v>
+        <v>-0.1774</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9927</v>
+        <v>0.9403</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9927</v>
+        <v>0.9403</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9927</v>
+        <v>0.9403</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9927</v>
+        <v>0.9403</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.9927</v>
+        <v>0.9403</v>
       </c>
       <c r="N37" t="n">
         <v>92</v>
@@ -2148,139 +2148,139 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SicK</t>
+          <t>pyth</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.854</v>
+        <v>0.7546</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5078</v>
+        <v>0.4487</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2354</v>
+        <v>-0.262</v>
       </c>
       <c r="E38" t="n">
-        <v>0.854</v>
+        <v>0.7546</v>
       </c>
       <c r="F38" t="n">
-        <v>0.854</v>
+        <v>1.5459</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.7913</v>
       </c>
       <c r="H38" t="n">
-        <v>0.854</v>
+        <v>1.5459</v>
       </c>
       <c r="I38" t="n">
-        <v>0.854</v>
+        <v>1.5872</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.7913</v>
       </c>
       <c r="K38" t="n">
-        <v>53</v>
+        <v>120</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M38" t="n">
-        <v>0.854</v>
+        <v>0.7958999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>53</v>
+        <v>165</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>SicK</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.762</v>
+        <v>0.7429</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4531</v>
+        <v>0.4417</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2773</v>
+        <v>-0.2674</v>
       </c>
       <c r="E39" t="n">
-        <v>0.762</v>
+        <v>0.7429</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8955</v>
+        <v>0.7429</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.1335</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8955</v>
+        <v>0.7429</v>
       </c>
       <c r="I39" t="n">
-        <v>0.9186</v>
+        <v>0.7429</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.1335</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="L39" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.7850999999999999</v>
+        <v>0.7429</v>
       </c>
       <c r="N39" t="n">
-        <v>212</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pyth</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7612</v>
+        <v>0.7032</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4526</v>
+        <v>0.4181</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2777</v>
+        <v>-0.2854</v>
       </c>
       <c r="E40" t="n">
-        <v>0.7612</v>
+        <v>0.7032</v>
       </c>
       <c r="F40" t="n">
-        <v>1.5689</v>
+        <v>0.8247</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.8077</v>
+        <v>-0.1215</v>
       </c>
       <c r="H40" t="n">
-        <v>1.5689</v>
+        <v>0.8247</v>
       </c>
       <c r="I40" t="n">
-        <v>1.6093</v>
+        <v>0.8467</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.8077</v>
+        <v>-0.1215</v>
       </c>
       <c r="K40" t="n">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="L40" t="n">
-        <v>45</v>
+        <v>124</v>
       </c>
       <c r="M40" t="n">
-        <v>0.8016</v>
+        <v>0.7252000000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>165</v>
+        <v>212</v>
       </c>
     </row>
     <row r="41">
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5034</v>
+        <v>0.4855</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2993</v>
+        <v>0.2887</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.395</v>
+        <v>-0.3846</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5034</v>
+        <v>0.4855</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5034</v>
+        <v>0.4855</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5034</v>
+        <v>0.4855</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5034</v>
+        <v>0.4855</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.5034</v>
+        <v>0.4855</v>
       </c>
       <c r="N41" t="n">
         <v>121</v>
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.467</v>
+        <v>0.4328</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2777</v>
+        <v>0.2573</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4116</v>
+        <v>-0.4086</v>
       </c>
       <c r="E42" t="n">
-        <v>0.467</v>
+        <v>0.4328</v>
       </c>
       <c r="F42" t="n">
-        <v>0.467</v>
+        <v>0.4328</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.467</v>
+        <v>0.4328</v>
       </c>
       <c r="I42" t="n">
-        <v>0.467</v>
+        <v>0.4328</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.467</v>
+        <v>0.4328</v>
       </c>
       <c r="N42" t="n">
         <v>52</v>
@@ -2378,47 +2378,47 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4663</v>
+        <v>0.397</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2772</v>
+        <v>0.236</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4119</v>
+        <v>-0.4249</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4663</v>
+        <v>0.397</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4663</v>
+        <v>0.908</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>-0.511</v>
       </c>
       <c r="H43" t="n">
-        <v>0.4663</v>
+        <v>0.908</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4663</v>
+        <v>0.9323</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>-0.511</v>
       </c>
       <c r="K43" t="n">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M43" t="n">
-        <v>0.4663</v>
+        <v>0.4213</v>
       </c>
       <c r="N43" t="n">
-        <v>134</v>
+        <v>165</v>
       </c>
     </row>
     <row r="44">
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4053</v>
+        <v>0.393</v>
       </c>
       <c r="C44" t="n">
-        <v>0.241</v>
+        <v>0.2337</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4397</v>
+        <v>-0.4268</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4053</v>
+        <v>0.393</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9449</v>
+        <v>0.904</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.5396</v>
+        <v>-0.511</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9449</v>
+        <v>0.904</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9692</v>
+        <v>0.9282</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.5396</v>
+        <v>-0.511</v>
       </c>
       <c r="K44" t="n">
         <v>120</v>
@@ -2461,7 +2461,7 @@
         <v>45</v>
       </c>
       <c r="M44" t="n">
-        <v>0.4296</v>
+        <v>0.4172</v>
       </c>
       <c r="N44" t="n">
         <v>165</v>
@@ -2470,139 +2470,139 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4023</v>
+        <v>0.3597</v>
       </c>
       <c r="C45" t="n">
-        <v>0.2392</v>
+        <v>0.2139</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4411</v>
+        <v>-0.4419</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4023</v>
+        <v>0.3597</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9419</v>
+        <v>0.3597</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.5396</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9419</v>
+        <v>0.3597</v>
       </c>
       <c r="I45" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.3597</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.5396</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="L45" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.4266</v>
+        <v>0.3597</v>
       </c>
       <c r="N45" t="n">
-        <v>165</v>
+        <v>134</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.3415</v>
+        <v>0.3278</v>
       </c>
       <c r="C46" t="n">
-        <v>0.203</v>
+        <v>0.1949</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4687</v>
+        <v>-0.4565</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3415</v>
+        <v>0.3278</v>
       </c>
       <c r="F46" t="n">
-        <v>0.3415</v>
+        <v>0.3278</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.3415</v>
+        <v>0.3278</v>
       </c>
       <c r="I46" t="n">
-        <v>0.3415</v>
+        <v>0.3278</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.3415</v>
+        <v>0.3278</v>
       </c>
       <c r="N46" t="n">
-        <v>42</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.2889</v>
+        <v>0.2882</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1718</v>
+        <v>0.1714</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4927</v>
+        <v>-0.4745</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2889</v>
+        <v>0.2882</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2889</v>
+        <v>0.2882</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2889</v>
+        <v>0.2882</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2889</v>
+        <v>0.2882</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.2889</v>
+        <v>0.2882</v>
       </c>
       <c r="N47" t="n">
-        <v>92</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48">
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.173</v>
+        <v>0.1996</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1029</v>
+        <v>0.1187</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.5455</v>
+        <v>-0.5149</v>
       </c>
       <c r="E48" t="n">
-        <v>0.173</v>
+        <v>0.1996</v>
       </c>
       <c r="F48" t="n">
-        <v>0.173</v>
+        <v>0.1996</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.173</v>
+        <v>0.1996</v>
       </c>
       <c r="I48" t="n">
-        <v>0.173</v>
+        <v>0.1996</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.173</v>
+        <v>0.1996</v>
       </c>
       <c r="N48" t="n">
         <v>93</v>
@@ -2654,93 +2654,93 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.1617</v>
+        <v>0.1914</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0961</v>
+        <v>0.1138</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.5506</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1617</v>
+        <v>0.1914</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9208</v>
+        <v>0.9042</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.7591</v>
+        <v>-0.7128</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9208</v>
+        <v>0.9042</v>
       </c>
       <c r="I49" t="n">
-        <v>0.9208</v>
+        <v>0.9284</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.7591</v>
+        <v>-0.7128</v>
       </c>
       <c r="K49" t="n">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="L49" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M49" t="n">
-        <v>0.1617</v>
+        <v>0.2156</v>
       </c>
       <c r="N49" t="n">
-        <v>119</v>
+        <v>198</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.1536</v>
+        <v>0.1293</v>
       </c>
       <c r="C50" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.0769</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5543</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1536</v>
+        <v>0.1293</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8739</v>
+        <v>0.8657</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.7203000000000001</v>
+        <v>-0.7364000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8739</v>
+        <v>0.8657</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8964</v>
+        <v>0.8657</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.7203000000000001</v>
+        <v>-0.7364000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="L50" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1760999999999999</v>
+        <v>0.1293</v>
       </c>
       <c r="N50" t="n">
-        <v>198</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51">
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.1017</v>
+        <v>0.0592</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0605</v>
+        <v>0.0352</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5779</v>
+        <v>-0.5788</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1017</v>
+        <v>0.0592</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1017</v>
+        <v>0.0592</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1017</v>
+        <v>0.0592</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1017</v>
+        <v>0.0592</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1017</v>
+        <v>0.0592</v>
       </c>
       <c r="N51" t="n">
         <v>52</v>
@@ -2796,28 +2796,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.0466</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0047</v>
+        <v>-0.0277</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.6206</v>
+        <v>-0.627</v>
       </c>
       <c r="E52" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.0466</v>
       </c>
       <c r="F52" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.0466</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.0466</v>
       </c>
       <c r="I52" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.0466</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.0466</v>
       </c>
       <c r="N52" t="n">
         <v>52</v>
@@ -2838,32 +2838,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.0901</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0428</v>
+        <v>-0.0536</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.657</v>
+        <v>-0.6468</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.0901</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.0901</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.0901</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.0901</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.0901</v>
       </c>
       <c r="N53" t="n">
         <v>134</v>
@@ -2884,93 +2884,93 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>HZ</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.1075</v>
+        <v>-0.157</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0639</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.6731</v>
+        <v>-0.6773</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.1075</v>
+        <v>-0.157</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.1075</v>
+        <v>-0.157</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.1075</v>
+        <v>-0.157</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1075</v>
+        <v>-0.157</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>134</v>
+        <v>42</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.1075</v>
+        <v>-0.157</v>
       </c>
       <c r="N54" t="n">
-        <v>134</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>HZ</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.1246</v>
+        <v>-0.1576</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0741</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6808999999999999</v>
+        <v>-0.6776</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.1246</v>
+        <v>-0.1576</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.1246</v>
+        <v>-0.1576</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.1246</v>
+        <v>-0.1576</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1246</v>
+        <v>-0.1576</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>42</v>
+        <v>134</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.1246</v>
+        <v>-0.1576</v>
       </c>
       <c r="N55" t="n">
-        <v>42</v>
+        <v>134</v>
       </c>
     </row>
     <row r="56">
@@ -2980,28 +2980,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.307</v>
+        <v>-0.2771</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1825</v>
+        <v>-0.1648</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.764</v>
+        <v>-0.732</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.307</v>
+        <v>-0.2771</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.307</v>
+        <v>-0.2771</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.307</v>
+        <v>-0.2771</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.307</v>
+        <v>-0.2771</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.307</v>
+        <v>-0.2771</v>
       </c>
       <c r="N56" t="n">
         <v>134</v>
@@ -3026,28 +3026,28 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.3263</v>
+        <v>-0.3082</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.194</v>
+        <v>-0.1832</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.7727000000000001</v>
+        <v>-0.7462</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.3263</v>
+        <v>-0.3082</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.3263</v>
+        <v>-0.3082</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.3263</v>
+        <v>-0.3082</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.3263</v>
+        <v>-0.3082</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.3263</v>
+        <v>-0.3082</v>
       </c>
       <c r="N57" t="n">
         <v>92</v>
@@ -3072,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.3282</v>
+        <v>-0.3433</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1951</v>
+        <v>-0.2041</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.7736</v>
+        <v>-0.7622</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.3282</v>
+        <v>-0.3433</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.3282</v>
+        <v>-0.3433</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.3282</v>
+        <v>-0.3433</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.3282</v>
+        <v>-0.3433</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.3282</v>
+        <v>-0.3433</v>
       </c>
       <c r="N58" t="n">
         <v>93</v>
@@ -3114,93 +3114,93 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>ANDROID</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.3617</v>
+        <v>-0.3487</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.2151</v>
+        <v>-0.2073</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.7889</v>
+        <v>-0.7645999999999999</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.3617</v>
+        <v>-0.3487</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.3617</v>
+        <v>-0.3487</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.3617</v>
+        <v>-0.3487</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3617</v>
+        <v>-0.3487</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.3617</v>
+        <v>-0.3487</v>
       </c>
       <c r="N59" t="n">
-        <v>93</v>
+        <v>41</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ANDROID</t>
+          <t>ShahZaM</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.3684</v>
+        <v>-0.3693</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.219</v>
+        <v>-0.2196</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7919</v>
+        <v>-0.774</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.3684</v>
+        <v>-0.3693</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.3684</v>
+        <v>-0.3693</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.3684</v>
+        <v>-0.3693</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3684</v>
+        <v>-0.3693</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.3684</v>
+        <v>-0.3693</v>
       </c>
       <c r="N60" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
     </row>
     <row r="61">
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.4059</v>
+        <v>-0.3732</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.2413</v>
+        <v>-0.2219</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.8090000000000001</v>
+        <v>-0.7758</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.4059</v>
+        <v>-0.3732</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.4059</v>
+        <v>-0.3732</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.4059</v>
+        <v>-0.3732</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4059</v>
+        <v>-0.3732</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.4059</v>
+        <v>-0.3732</v>
       </c>
       <c r="N61" t="n">
         <v>52</v>
@@ -3252,139 +3252,139 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ShahZaM</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.4079</v>
+        <v>-0.379</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.2425</v>
+        <v>-0.2253</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.8099</v>
+        <v>-0.7784</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.4079</v>
+        <v>-0.379</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.4079</v>
+        <v>-0.379</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.4079</v>
+        <v>-0.379</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.4079</v>
+        <v>-0.379</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.4079</v>
+        <v>-0.379</v>
       </c>
       <c r="N62" t="n">
-        <v>53</v>
+        <v>93</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.4137</v>
+        <v>-0.3989</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.246</v>
+        <v>-0.2372</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8125</v>
+        <v>-0.7875</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.4137</v>
+        <v>-0.3989</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.4137</v>
+        <v>-0.3989</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.4137</v>
+        <v>-0.3989</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.4137</v>
+        <v>-0.3989</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.4137</v>
+        <v>-0.3989</v>
       </c>
       <c r="N63" t="n">
-        <v>134</v>
+        <v>93</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.4253</v>
+        <v>-0.41</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.2529</v>
+        <v>-0.2438</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8178</v>
+        <v>-0.7926</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.4253</v>
+        <v>-0.41</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.4253</v>
+        <v>-0.41</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.4253</v>
+        <v>-0.41</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.4253</v>
+        <v>-0.41</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.4253</v>
+        <v>-0.41</v>
       </c>
       <c r="N64" t="n">
-        <v>93</v>
+        <v>134</v>
       </c>
     </row>
     <row r="65">
@@ -3394,28 +3394,28 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.5043</v>
+        <v>-0.4666</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.2998</v>
+        <v>-0.2774</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8538</v>
+        <v>-0.8183</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.5043</v>
+        <v>-0.4666</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.5043</v>
+        <v>-0.4666</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.5043</v>
+        <v>-0.4666</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5043</v>
+        <v>-0.4666</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.5043</v>
+        <v>-0.4666</v>
       </c>
       <c r="N65" t="n">
         <v>52</v>
@@ -3440,28 +3440,28 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.5053</v>
+        <v>-0.4735</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.3004</v>
+        <v>-0.2815</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8542</v>
+        <v>-0.8215</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.5053</v>
+        <v>-0.4735</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.5053</v>
+        <v>-0.4735</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.5053</v>
+        <v>-0.4735</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5053</v>
+        <v>-0.4735</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.5053</v>
+        <v>-0.4735</v>
       </c>
       <c r="N66" t="n">
         <v>41</v>
@@ -3486,28 +3486,28 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.5229</v>
+        <v>-0.5052</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.3109</v>
+        <v>-0.3004</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8622</v>
+        <v>-0.8359</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.5229</v>
+        <v>-0.5052</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.5229</v>
+        <v>-0.5052</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.5229</v>
+        <v>-0.5052</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.5229</v>
+        <v>-0.5052</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.5229</v>
+        <v>-0.5052</v>
       </c>
       <c r="N67" t="n">
         <v>53</v>
@@ -3532,28 +3532,28 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.5724</v>
+        <v>-0.541</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.3403</v>
+        <v>-0.3217</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8848</v>
+        <v>-0.8522</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.5724</v>
+        <v>-0.541</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.5724</v>
+        <v>-0.541</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.5724</v>
+        <v>-0.541</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.5724</v>
+        <v>-0.541</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.5724</v>
+        <v>-0.541</v>
       </c>
       <c r="N68" t="n">
         <v>121</v>
@@ -3578,28 +3578,28 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.5753</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.342</v>
+        <v>-0.3252</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8861</v>
+        <v>-0.8549</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.5753</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.5753</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.5753</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.5753</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.5753</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="N69" t="n">
         <v>121</v>
@@ -3624,28 +3624,28 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.6625</v>
+        <v>-0.6385</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.3939</v>
+        <v>-0.3796</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9258</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.6625</v>
+        <v>-0.6385</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.6625</v>
+        <v>-0.6385</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.6625</v>
+        <v>-0.6385</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.6625</v>
+        <v>-0.6385</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.6625</v>
+        <v>-0.6385</v>
       </c>
       <c r="N70" t="n">
         <v>41</v>
@@ -3670,28 +3670,28 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.6644</v>
+        <v>-0.6562</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.395</v>
+        <v>-0.3901</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9267</v>
+        <v>-0.9046999999999999</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.6644</v>
+        <v>-0.6562</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.6644</v>
+        <v>-0.6562</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.6644</v>
+        <v>-0.6562</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6644</v>
+        <v>-0.6562</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.6644</v>
+        <v>-0.6562</v>
       </c>
       <c r="N71" t="n">
         <v>42</v>
@@ -3716,28 +3716,28 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.6797</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.4041</v>
+        <v>-0.4091</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9336</v>
+        <v>-0.9192</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.6797</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.6797</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.6797</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.6797</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.6797</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="N72" t="n">
         <v>93</v>
@@ -3762,28 +3762,28 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.7328</v>
+        <v>-0.7094</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.4357</v>
+        <v>-0.4218</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9578</v>
+        <v>-0.929</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.7328</v>
+        <v>-0.7094</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.7328</v>
+        <v>-0.7094</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.7328</v>
+        <v>-0.7094</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.7328</v>
+        <v>-0.7094</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.7328</v>
+        <v>-0.7094</v>
       </c>
       <c r="N73" t="n">
         <v>92</v>
@@ -3808,28 +3808,28 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.7645</v>
+        <v>-0.7491</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.4545</v>
+        <v>-0.4454</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9722</v>
+        <v>-0.947</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.7645</v>
+        <v>-0.7491</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.7645</v>
+        <v>-0.7491</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.7645</v>
+        <v>-0.7491</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.7645</v>
+        <v>-0.7491</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.7645</v>
+        <v>-0.7491</v>
       </c>
       <c r="N74" t="n">
         <v>41</v>
@@ -3854,28 +3854,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.7816</v>
+        <v>-0.7684</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.4647</v>
+        <v>-0.4569</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.98</v>
+        <v>-0.9558</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.7816</v>
+        <v>-0.7684</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.7816</v>
+        <v>-0.7684</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.7816</v>
+        <v>-0.7684</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.7816</v>
+        <v>-0.7684</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.7816</v>
+        <v>-0.7684</v>
       </c>
       <c r="N75" t="n">
         <v>42</v>
@@ -3900,28 +3900,28 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.8044</v>
+        <v>-0.8146</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.4783</v>
+        <v>-0.4843</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.9903999999999999</v>
+        <v>-0.9769</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.8044</v>
+        <v>-0.8146</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.8044</v>
+        <v>-0.8146</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.8044</v>
+        <v>-0.8146</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.8044</v>
+        <v>-0.8146</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-0.8044</v>
+        <v>-0.8146</v>
       </c>
       <c r="N76" t="n">
         <v>92</v>
@@ -3946,28 +3946,28 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.9487</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.5641</v>
+        <v>-0.5649</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0561</v>
+        <v>-1.0386</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.9487</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.9487</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.9487</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.9487</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.9487</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="N77" t="n">
         <v>42</v>
@@ -3992,28 +3992,28 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.9655</v>
+        <v>-0.9695</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.574</v>
+        <v>-0.5764</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.0637</v>
+        <v>-1.0474</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.9655</v>
+        <v>-0.9695</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.9655</v>
+        <v>-0.9695</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.9655</v>
+        <v>-0.9695</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.9655</v>
+        <v>-0.9695</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-0.9655</v>
+        <v>-0.9695</v>
       </c>
       <c r="N78" t="n">
         <v>53</v>
@@ -4038,28 +4038,28 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-0.9862</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.5877</v>
+        <v>-0.5864</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.0741</v>
+        <v>-1.055</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-0.9862</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-0.9862</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-0.9862</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-0.9862</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-0.9862</v>
       </c>
       <c r="N79" t="n">
         <v>41</v>
@@ -4084,31 +4084,31 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.1994</v>
+        <v>-1.09</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.7131</v>
+        <v>-0.6481</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.1702</v>
+        <v>-1.1023</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.1994</v>
+        <v>-1.09</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.7336</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.4658</v>
+        <v>-0.4363</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.7336</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.7336</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.4658</v>
+        <v>-0.4363</v>
       </c>
       <c r="K80" t="n">
         <v>54</v>
@@ -4117,7 +4117,7 @@
         <v>54</v>
       </c>
       <c r="M80" t="n">
-        <v>-1.1994</v>
+        <v>-1.09</v>
       </c>
       <c r="N80" t="n">
         <v>108</v>
@@ -4130,31 +4130,31 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-1.5819</v>
+        <v>-1.4856</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.9405</v>
+        <v>-0.8833</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.3443</v>
+        <v>-1.2825</v>
       </c>
       <c r="E81" t="n">
-        <v>-1.5819</v>
+        <v>-1.4856</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.7789</v>
+        <v>-0.7024</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.803</v>
+        <v>-0.7832</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.7789</v>
+        <v>-0.7024</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.7789</v>
+        <v>-0.7024</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.803</v>
+        <v>-0.7832</v>
       </c>
       <c r="K81" t="n">
         <v>54</v>
@@ -4163,7 +4163,7 @@
         <v>54</v>
       </c>
       <c r="M81" t="n">
-        <v>-1.5819</v>
+        <v>-1.4856</v>
       </c>
       <c r="N81" t="n">
         <v>108</v>
@@ -4269,10 +4269,10 @@
         <v>1.05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1671</v>
+        <v>0.1579</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0104</v>
+        <v>3.7896</v>
       </c>
     </row>
     <row r="3">
@@ -4309,10 +4309,10 @@
         <v>0.88</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.146</v>
+        <v>-0.1305</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.504</v>
+        <v>-3.132</v>
       </c>
     </row>
     <row r="4">
@@ -4349,10 +4349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2207</v>
+        <v>-0.2047</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.2968</v>
+        <v>-4.9128</v>
       </c>
     </row>
     <row r="5">
@@ -4389,10 +4389,10 @@
         <v>0.68</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3411</v>
+        <v>-0.3263</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.186400000000001</v>
+        <v>-7.8312</v>
       </c>
     </row>
     <row r="6">
@@ -4429,10 +4429,10 @@
         <v>0.37</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6127</v>
+        <v>-0.6286</v>
       </c>
       <c r="J6" t="n">
-        <v>-14.7048</v>
+        <v>-15.0864</v>
       </c>
     </row>
     <row r="7">
@@ -4469,10 +4469,10 @@
         <v>1.73</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8172</v>
+        <v>0.746</v>
       </c>
       <c r="J7" t="n">
-        <v>19.6128</v>
+        <v>17.904</v>
       </c>
     </row>
     <row r="8">
@@ -4509,10 +4509,10 @@
         <v>1.64</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7337</v>
+        <v>0.6624</v>
       </c>
       <c r="J8" t="n">
-        <v>17.6088</v>
+        <v>15.8976</v>
       </c>
     </row>
     <row r="9">
@@ -4549,10 +4549,10 @@
         <v>1.49</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5906</v>
+        <v>0.5225</v>
       </c>
       <c r="J9" t="n">
-        <v>14.1744</v>
+        <v>12.54</v>
       </c>
     </row>
     <row r="10">
@@ -4589,10 +4589,10 @@
         <v>1.22</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3075</v>
+        <v>0.2575</v>
       </c>
       <c r="J10" t="n">
-        <v>7.38</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="11">
@@ -4629,10 +4629,10 @@
         <v>0.95</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1161</v>
+        <v>-0.1012</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.7864</v>
+        <v>-2.4288</v>
       </c>
     </row>
     <row r="12">
@@ -4669,10 +4669,10 @@
         <v>1.58</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2793</v>
+        <v>1.3049</v>
       </c>
       <c r="J12" t="n">
-        <v>34.5411</v>
+        <v>35.2323</v>
       </c>
     </row>
     <row r="13">
@@ -4709,10 +4709,10 @@
         <v>1.43</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0023</v>
+        <v>0.9949</v>
       </c>
       <c r="J13" t="n">
-        <v>27.0621</v>
+        <v>26.8623</v>
       </c>
     </row>
     <row r="14">
@@ -4749,10 +4749,10 @@
         <v>1.08</v>
       </c>
       <c r="I14" t="n">
-        <v>0.253</v>
+        <v>0.2224</v>
       </c>
       <c r="J14" t="n">
-        <v>6.831</v>
+        <v>6.0048</v>
       </c>
     </row>
     <row r="15">
@@ -4789,10 +4789,10 @@
         <v>1.08</v>
       </c>
       <c r="I15" t="n">
-        <v>0.253</v>
+        <v>0.2224</v>
       </c>
       <c r="J15" t="n">
-        <v>6.831</v>
+        <v>6.0048</v>
       </c>
     </row>
     <row r="16">
@@ -4829,10 +4829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2716</v>
+        <v>-0.2338</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.3332</v>
+        <v>-6.3126</v>
       </c>
     </row>
     <row r="17">
@@ -4869,10 +4869,10 @@
         <v>1.29</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6294</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>16.9938</v>
+        <v>15.6357</v>
       </c>
     </row>
     <row r="18">
@@ -4909,10 +4909,10 @@
         <v>0.98</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0304</v>
+        <v>-0.0232</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8208</v>
+        <v>-0.6264</v>
       </c>
     </row>
     <row r="19">
@@ -4949,10 +4949,10 @@
         <v>0.86</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1794</v>
+        <v>-0.1612</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.8438</v>
+        <v>-4.3524</v>
       </c>
     </row>
     <row r="20">
@@ -4989,10 +4989,10 @@
         <v>0.64</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3889</v>
+        <v>-0.3766</v>
       </c>
       <c r="J20" t="n">
-        <v>-10.5003</v>
+        <v>-10.1682</v>
       </c>
     </row>
     <row r="21">
@@ -5029,10 +5029,10 @@
         <v>0.54</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4772</v>
+        <v>-0.4741</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.8844</v>
+        <v>-12.8007</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         <v>1.36</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8925</v>
+        <v>0.8737</v>
       </c>
       <c r="J22" t="n">
-        <v>25.8825</v>
+        <v>25.3373</v>
       </c>
     </row>
     <row r="23">
@@ -5109,10 +5109,10 @@
         <v>1.35</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.8518</v>
       </c>
       <c r="J23" t="n">
-        <v>25.3025</v>
+        <v>24.7022</v>
       </c>
     </row>
     <row r="24">
@@ -5149,10 +5149,10 @@
         <v>1.15</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4426</v>
+        <v>0.4039</v>
       </c>
       <c r="J24" t="n">
-        <v>12.8354</v>
+        <v>11.7131</v>
       </c>
     </row>
     <row r="25">
@@ -5189,10 +5189,10 @@
         <v>0.88</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4182</v>
+        <v>-0.3757</v>
       </c>
       <c r="J25" t="n">
-        <v>-12.1278</v>
+        <v>-10.8953</v>
       </c>
     </row>
     <row r="26">
@@ -5229,10 +5229,10 @@
         <v>0.87</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4436</v>
+        <v>-0.4013</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.8644</v>
+        <v>-11.6377</v>
       </c>
     </row>
     <row r="27">
@@ -5269,10 +5269,10 @@
         <v>1.34</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6449</v>
+        <v>0.5857</v>
       </c>
       <c r="J27" t="n">
-        <v>18.7021</v>
+        <v>16.9853</v>
       </c>
     </row>
     <row r="28">
@@ -5309,10 +5309,10 @@
         <v>1.26</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5203</v>
+        <v>0.4608</v>
       </c>
       <c r="J28" t="n">
-        <v>15.0887</v>
+        <v>13.3632</v>
       </c>
     </row>
     <row r="29">
@@ -5349,10 +5349,10 @@
         <v>1.24</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4882</v>
+        <v>0.4292</v>
       </c>
       <c r="J29" t="n">
-        <v>14.1578</v>
+        <v>12.4468</v>
       </c>
     </row>
     <row r="30">
@@ -5389,10 +5389,10 @@
         <v>0.79</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2671</v>
+        <v>-0.2479</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.7459</v>
+        <v>-7.1891</v>
       </c>
     </row>
     <row r="31">
@@ -5429,10 +5429,10 @@
         <v>0.64</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4063</v>
+        <v>-0.3974</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.7827</v>
+        <v>-11.5246</v>
       </c>
     </row>
     <row r="32">
@@ -5469,10 +5469,10 @@
         <v>1.09</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2475</v>
+        <v>0.2012</v>
       </c>
       <c r="J32" t="n">
-        <v>7.425</v>
+        <v>6.036</v>
       </c>
     </row>
     <row r="33">
@@ -5509,10 +5509,10 @@
         <v>1.07</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2055</v>
+        <v>0.1634</v>
       </c>
       <c r="J33" t="n">
-        <v>6.165</v>
+        <v>4.902</v>
       </c>
     </row>
     <row r="34">
@@ -5549,10 +5549,10 @@
         <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>0.137</v>
+        <v>0.1038</v>
       </c>
       <c r="J34" t="n">
-        <v>4.11</v>
+        <v>3.114</v>
       </c>
     </row>
     <row r="35">
@@ -5589,10 +5589,10 @@
         <v>0.73</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3131</v>
+        <v>-0.2956</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.393000000000001</v>
+        <v>-8.868</v>
       </c>
     </row>
     <row r="36">
@@ -5629,10 +5629,10 @@
         <v>0.71</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3317</v>
+        <v>-0.3154</v>
       </c>
       <c r="J36" t="n">
-        <v>-9.951000000000001</v>
+        <v>-9.462</v>
       </c>
     </row>
     <row r="37">
@@ -5669,10 +5669,10 @@
         <v>1.63</v>
       </c>
       <c r="I37" t="n">
-        <v>1.12</v>
+        <v>1.1123</v>
       </c>
       <c r="J37" t="n">
-        <v>33.6</v>
+        <v>33.369</v>
       </c>
     </row>
     <row r="38">
@@ -5709,10 +5709,10 @@
         <v>1.57</v>
       </c>
       <c r="I38" t="n">
-        <v>1.0409</v>
+        <v>1.0297</v>
       </c>
       <c r="J38" t="n">
-        <v>31.227</v>
+        <v>30.891</v>
       </c>
     </row>
     <row r="39">
@@ -5749,10 +5749,10 @@
         <v>1.14</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4021</v>
+        <v>0.3693</v>
       </c>
       <c r="J39" t="n">
-        <v>12.063</v>
+        <v>11.079</v>
       </c>
     </row>
     <row r="40">
@@ -5789,10 +5789,10 @@
         <v>1.01</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0176</v>
+        <v>0.0076</v>
       </c>
       <c r="J40" t="n">
-        <v>0.528</v>
+        <v>0.228</v>
       </c>
     </row>
     <row r="41">
@@ -5829,10 +5829,10 @@
         <v>0.9</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3887</v>
+        <v>-0.3489</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.661</v>
+        <v>-10.467</v>
       </c>
     </row>
     <row r="42">
@@ -5869,10 +5869,10 @@
         <v>1.16</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3976</v>
+        <v>0.3443</v>
       </c>
       <c r="J42" t="n">
-        <v>9.94</v>
+        <v>8.6075</v>
       </c>
     </row>
     <row r="43">
@@ -5909,10 +5909,10 @@
         <v>0.98</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.0323</v>
+        <v>-0.0249</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.8075</v>
+        <v>-0.6225000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -5949,10 +5949,10 @@
         <v>0.84</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2007</v>
+        <v>-0.1815</v>
       </c>
       <c r="J44" t="n">
-        <v>-5.0175</v>
+        <v>-4.5375</v>
       </c>
     </row>
     <row r="45">
@@ -5989,10 +5989,10 @@
         <v>0.72</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3172</v>
+        <v>-0.3</v>
       </c>
       <c r="J45" t="n">
-        <v>-7.93</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="46">
@@ -6029,10 +6029,10 @@
         <v>0.68</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3541</v>
+        <v>-0.3392</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.852499999999999</v>
+        <v>-8.48</v>
       </c>
     </row>
     <row r="47">
@@ -6069,10 +6069,10 @@
         <v>1.47</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9073</v>
+        <v>0.8927</v>
       </c>
       <c r="J47" t="n">
-        <v>22.6825</v>
+        <v>22.3175</v>
       </c>
     </row>
     <row r="48">
@@ -6109,10 +6109,10 @@
         <v>1.46</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8935999999999999</v>
+        <v>0.8788</v>
       </c>
       <c r="J48" t="n">
-        <v>22.34</v>
+        <v>21.97</v>
       </c>
     </row>
     <row r="49">
@@ -6149,10 +6149,10 @@
         <v>1.35</v>
       </c>
       <c r="I49" t="n">
-        <v>0.7386</v>
+        <v>0.7248</v>
       </c>
       <c r="J49" t="n">
-        <v>18.465</v>
+        <v>18.12</v>
       </c>
     </row>
     <row r="50">
@@ -6189,10 +6189,10 @@
         <v>1.16</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4461</v>
+        <v>0.4177</v>
       </c>
       <c r="J50" t="n">
-        <v>11.1525</v>
+        <v>10.4425</v>
       </c>
     </row>
     <row r="51">
@@ -6229,10 +6229,10 @@
         <v>0.77</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6999</v>
+        <v>-0.6723</v>
       </c>
       <c r="J51" t="n">
-        <v>-17.4975</v>
+        <v>-16.8075</v>
       </c>
     </row>
     <row r="52">
@@ -6269,10 +6269,10 @@
         <v>1.76</v>
       </c>
       <c r="I52" t="n">
-        <v>1.233</v>
+        <v>1.2328</v>
       </c>
       <c r="J52" t="n">
-        <v>23.427</v>
+        <v>23.4232</v>
       </c>
     </row>
     <row r="53">
@@ -6309,10 +6309,10 @@
         <v>1.72</v>
       </c>
       <c r="I53" t="n">
-        <v>1.1847</v>
+        <v>1.1826</v>
       </c>
       <c r="J53" t="n">
-        <v>22.5093</v>
+        <v>22.4694</v>
       </c>
     </row>
     <row r="54">
@@ -6349,10 +6349,10 @@
         <v>1.71</v>
       </c>
       <c r="I54" t="n">
-        <v>1.1726</v>
+        <v>1.17</v>
       </c>
       <c r="J54" t="n">
-        <v>22.2794</v>
+        <v>22.23</v>
       </c>
     </row>
     <row r="55">
@@ -6389,10 +6389,10 @@
         <v>1.24</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5473</v>
+        <v>0.5461</v>
       </c>
       <c r="J55" t="n">
-        <v>10.3987</v>
+        <v>10.3759</v>
       </c>
     </row>
     <row r="56">
@@ -6429,10 +6429,10 @@
         <v>1.22</v>
       </c>
       <c r="I56" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.5115</v>
       </c>
       <c r="J56" t="n">
-        <v>9.7964</v>
+        <v>9.718500000000001</v>
       </c>
     </row>
     <row r="57">
@@ -6469,10 +6469,10 @@
         <v>0.68</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.3224</v>
+        <v>-0.3121</v>
       </c>
       <c r="J57" t="n">
-        <v>-6.1256</v>
+        <v>-5.9299</v>
       </c>
     </row>
     <row r="58">
@@ -6509,10 +6509,10 @@
         <v>0.62</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.3772</v>
+        <v>-0.3688</v>
       </c>
       <c r="J58" t="n">
-        <v>-7.1668</v>
+        <v>-7.0072</v>
       </c>
     </row>
     <row r="59">
@@ -6549,10 +6549,10 @@
         <v>0.59</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.4021</v>
+        <v>-0.3943</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.6399</v>
+        <v>-7.4917</v>
       </c>
     </row>
     <row r="60">
@@ -6589,10 +6589,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4277</v>
+        <v>-0.4207</v>
       </c>
       <c r="J60" t="n">
-        <v>-8.126300000000001</v>
+        <v>-7.9933</v>
       </c>
     </row>
     <row r="61">
@@ -6629,10 +6629,10 @@
         <v>0.55</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4363</v>
+        <v>-0.4298</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.2897</v>
+        <v>-8.1662</v>
       </c>
     </row>
     <row r="62">
@@ -6669,10 +6669,10 @@
         <v>1.02</v>
       </c>
       <c r="I62" t="n">
-        <v>0.0752</v>
+        <v>0.062</v>
       </c>
       <c r="J62" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="63">
@@ -6709,10 +6709,10 @@
         <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0158</v>
+        <v>0.0132</v>
       </c>
       <c r="J63" t="n">
-        <v>0.395</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="64">
@@ -6749,10 +6749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.08989999999999999</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="J64" t="n">
-        <v>-2.2475</v>
+        <v>-1.9075</v>
       </c>
     </row>
     <row r="65">
@@ -6789,10 +6789,10 @@
         <v>0.76</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2794</v>
+        <v>-0.2607</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.985</v>
+        <v>-6.5175</v>
       </c>
     </row>
     <row r="66">
@@ -6829,10 +6829,10 @@
         <v>0.66</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3723</v>
+        <v>-0.3587</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.307499999999999</v>
+        <v>-8.967499999999999</v>
       </c>
     </row>
     <row r="67">
@@ -6869,10 +6869,10 @@
         <v>1.56</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6198</v>
+        <v>0.5808</v>
       </c>
       <c r="J67" t="n">
-        <v>15.495</v>
+        <v>14.52</v>
       </c>
     </row>
     <row r="68">
@@ -6909,10 +6909,10 @@
         <v>1.51</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5826</v>
+        <v>0.5468</v>
       </c>
       <c r="J68" t="n">
-        <v>14.565</v>
+        <v>13.67</v>
       </c>
     </row>
     <row r="69">
@@ -6949,10 +6949,10 @@
         <v>1.2</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2986</v>
+        <v>0.2465</v>
       </c>
       <c r="J69" t="n">
-        <v>7.465</v>
+        <v>6.1625</v>
       </c>
     </row>
     <row r="70">
@@ -6989,10 +6989,10 @@
         <v>1.06</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1084</v>
+        <v>0.0819</v>
       </c>
       <c r="J70" t="n">
-        <v>2.71</v>
+        <v>2.0475</v>
       </c>
     </row>
     <row r="71">
@@ -7029,10 +7029,10 @@
         <v>0.73</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3364</v>
+        <v>-0.323</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.41</v>
+        <v>-8.074999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -7069,10 +7069,10 @@
         <v>1.87</v>
       </c>
       <c r="I72" t="n">
-        <v>1.3722</v>
+        <v>1.3796</v>
       </c>
       <c r="J72" t="n">
-        <v>27.444</v>
+        <v>27.592</v>
       </c>
     </row>
     <row r="73">
@@ -7109,10 +7109,10 @@
         <v>1.62</v>
       </c>
       <c r="I73" t="n">
-        <v>1.0681</v>
+        <v>1.0611</v>
       </c>
       <c r="J73" t="n">
-        <v>21.362</v>
+        <v>21.222</v>
       </c>
     </row>
     <row r="74">
@@ -7149,10 +7149,10 @@
         <v>1.45</v>
       </c>
       <c r="I74" t="n">
-        <v>0.853</v>
+        <v>0.845</v>
       </c>
       <c r="J74" t="n">
-        <v>17.06</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="75">
@@ -7189,10 +7189,10 @@
         <v>1.29</v>
       </c>
       <c r="I75" t="n">
-        <v>0.6291</v>
+        <v>0.6253</v>
       </c>
       <c r="J75" t="n">
-        <v>12.582</v>
+        <v>12.506</v>
       </c>
     </row>
     <row r="76">
@@ -7229,10 +7229,10 @@
         <v>1.17</v>
       </c>
       <c r="I76" t="n">
-        <v>0.4353</v>
+        <v>0.4069</v>
       </c>
       <c r="J76" t="n">
-        <v>8.706</v>
+        <v>8.138</v>
       </c>
     </row>
     <row r="77">
@@ -7269,10 +7269,10 @@
         <v>1.17</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5161</v>
+        <v>0.5228</v>
       </c>
       <c r="J77" t="n">
-        <v>10.322</v>
+        <v>10.456</v>
       </c>
     </row>
     <row r="78">
@@ -7309,10 +7309,10 @@
         <v>0.72</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.2911</v>
+        <v>-0.2789</v>
       </c>
       <c r="J78" t="n">
-        <v>-5.822</v>
+        <v>-5.578</v>
       </c>
     </row>
     <row r="79">
@@ -7349,10 +7349,10 @@
         <v>0.47</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.512</v>
+        <v>-0.5115</v>
       </c>
       <c r="J79" t="n">
-        <v>-10.24</v>
+        <v>-10.23</v>
       </c>
     </row>
     <row r="80">
@@ -7389,10 +7389,10 @@
         <v>0.45</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.5296</v>
+        <v>-0.5312</v>
       </c>
       <c r="J80" t="n">
-        <v>-10.592</v>
+        <v>-10.624</v>
       </c>
     </row>
     <row r="81">
@@ -7429,10 +7429,10 @@
         <v>0.38</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.591</v>
+        <v>-0.6014</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.82</v>
+        <v>-12.028</v>
       </c>
     </row>
     <row r="82">
@@ -7469,10 +7469,10 @@
         <v>1.29</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6872</v>
+        <v>0.6721</v>
       </c>
       <c r="J82" t="n">
-        <v>32.2984</v>
+        <v>31.5887</v>
       </c>
     </row>
     <row r="83">
@@ -7509,10 +7509,10 @@
         <v>1.15</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4532</v>
+        <v>0.4172</v>
       </c>
       <c r="J83" t="n">
-        <v>21.3004</v>
+        <v>19.6084</v>
       </c>
     </row>
     <row r="84">
@@ -7549,10 +7549,10 @@
         <v>0.93</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2664</v>
+        <v>-0.2268</v>
       </c>
       <c r="J84" t="n">
-        <v>-12.5208</v>
+        <v>-10.6596</v>
       </c>
     </row>
     <row r="85">
@@ -7589,10 +7589,10 @@
         <v>0.92</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2947</v>
+        <v>-0.2538</v>
       </c>
       <c r="J85" t="n">
-        <v>-13.8509</v>
+        <v>-11.9286</v>
       </c>
     </row>
     <row r="86">
@@ -7629,10 +7629,10 @@
         <v>0.89</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3755</v>
+        <v>-0.3326</v>
       </c>
       <c r="J86" t="n">
-        <v>-17.6485</v>
+        <v>-15.6322</v>
       </c>
     </row>
     <row r="87">
@@ -7669,10 +7669,10 @@
         <v>1.17</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3764</v>
+        <v>0.3213</v>
       </c>
       <c r="J87" t="n">
-        <v>17.6908</v>
+        <v>15.1011</v>
       </c>
     </row>
     <row r="88">
@@ -7709,10 +7709,10 @@
         <v>1.05</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1445</v>
+        <v>0.1117</v>
       </c>
       <c r="J88" t="n">
-        <v>6.7915</v>
+        <v>5.2499</v>
       </c>
     </row>
     <row r="89">
@@ -7749,10 +7749,10 @@
         <v>1.01</v>
       </c>
       <c r="I89" t="n">
-        <v>0.0413</v>
+        <v>0.0285</v>
       </c>
       <c r="J89" t="n">
-        <v>1.9411</v>
+        <v>1.3395</v>
       </c>
     </row>
     <row r="90">
@@ -7789,10 +7789,10 @@
         <v>0.98</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0445</v>
+        <v>-0.0336</v>
       </c>
       <c r="J90" t="n">
-        <v>-2.0915</v>
+        <v>-1.5792</v>
       </c>
     </row>
     <row r="91">
@@ -7829,10 +7829,10 @@
         <v>0.92</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1258</v>
+        <v>-0.107</v>
       </c>
       <c r="J91" t="n">
-        <v>-5.9126</v>
+        <v>-5.029</v>
       </c>
     </row>
     <row r="92">
@@ -7869,10 +7869,10 @@
         <v>1.63</v>
       </c>
       <c r="I92" t="n">
-        <v>1.0895</v>
+        <v>1.0816</v>
       </c>
       <c r="J92" t="n">
-        <v>25.0585</v>
+        <v>24.8768</v>
       </c>
     </row>
     <row r="93">
@@ -7909,10 +7909,10 @@
         <v>1.45</v>
       </c>
       <c r="I93" t="n">
-        <v>0.8571</v>
+        <v>0.8469</v>
       </c>
       <c r="J93" t="n">
-        <v>19.7133</v>
+        <v>19.4787</v>
       </c>
     </row>
     <row r="94">
@@ -7949,10 +7949,10 @@
         <v>1.43</v>
       </c>
       <c r="I94" t="n">
-        <v>0.8308</v>
+        <v>0.8209</v>
       </c>
       <c r="J94" t="n">
-        <v>19.1084</v>
+        <v>18.8807</v>
       </c>
     </row>
     <row r="95">
@@ -7989,10 +7989,10 @@
         <v>1.36</v>
       </c>
       <c r="I95" t="n">
-        <v>0.7368</v>
+        <v>0.7288</v>
       </c>
       <c r="J95" t="n">
-        <v>16.9464</v>
+        <v>16.7624</v>
       </c>
     </row>
     <row r="96">
@@ -8029,10 +8029,10 @@
         <v>1.2</v>
       </c>
       <c r="I96" t="n">
-        <v>0.4954</v>
+        <v>0.4861</v>
       </c>
       <c r="J96" t="n">
-        <v>11.3942</v>
+        <v>11.1803</v>
       </c>
     </row>
     <row r="97">
@@ -8069,10 +8069,10 @@
         <v>0.97</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.0054</v>
+        <v>0.0166</v>
       </c>
       <c r="J97" t="n">
-        <v>-0.1242</v>
+        <v>0.3818</v>
       </c>
     </row>
     <row r="98">
@@ -8109,10 +8109,10 @@
         <v>0.74</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.2765</v>
+        <v>-0.2633</v>
       </c>
       <c r="J98" t="n">
-        <v>-6.3595</v>
+        <v>-6.0559</v>
       </c>
     </row>
     <row r="99">
@@ -8149,10 +8149,10 @@
         <v>0.74</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2765</v>
+        <v>-0.2633</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.3595</v>
+        <v>-6.0559</v>
       </c>
     </row>
     <row r="100">
@@ -8189,10 +8189,10 @@
         <v>0.5</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4896</v>
+        <v>-0.4865</v>
       </c>
       <c r="J100" t="n">
-        <v>-11.2608</v>
+        <v>-11.1895</v>
       </c>
     </row>
     <row r="101">
@@ -8229,10 +8229,10 @@
         <v>0.38</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5945</v>
+        <v>-0.6058</v>
       </c>
       <c r="J101" t="n">
-        <v>-13.6735</v>
+        <v>-13.9334</v>
       </c>
     </row>
     <row r="102">
@@ -8269,10 +8269,10 @@
         <v>1.75</v>
       </c>
       <c r="I102" t="n">
-        <v>1.2335</v>
+        <v>1.2321</v>
       </c>
       <c r="J102" t="n">
-        <v>27.137</v>
+        <v>27.1062</v>
       </c>
     </row>
     <row r="103">
@@ -8309,10 +8309,10 @@
         <v>1.71</v>
       </c>
       <c r="I103" t="n">
-        <v>1.1844</v>
+        <v>1.1806</v>
       </c>
       <c r="J103" t="n">
-        <v>26.0568</v>
+        <v>25.9732</v>
       </c>
     </row>
     <row r="104">
@@ -8349,10 +8349,10 @@
         <v>1.49</v>
       </c>
       <c r="I104" t="n">
-        <v>0.9065</v>
+        <v>0.897</v>
       </c>
       <c r="J104" t="n">
-        <v>19.943</v>
+        <v>19.734</v>
       </c>
     </row>
     <row r="105">
@@ -8389,10 +8389,10 @@
         <v>1.18</v>
       </c>
       <c r="I105" t="n">
-        <v>0.4583</v>
+        <v>0.4357</v>
       </c>
       <c r="J105" t="n">
-        <v>10.0826</v>
+        <v>9.5854</v>
       </c>
     </row>
     <row r="106">
@@ -8429,10 +8429,10 @@
         <v>1.1</v>
       </c>
       <c r="I106" t="n">
-        <v>0.2714</v>
+        <v>0.2387</v>
       </c>
       <c r="J106" t="n">
-        <v>5.9708</v>
+        <v>5.2514</v>
       </c>
     </row>
     <row r="107">
@@ -8469,10 +8469,10 @@
         <v>0.75</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.272</v>
+        <v>-0.2578</v>
       </c>
       <c r="J107" t="n">
-        <v>-5.984</v>
+        <v>-5.6716</v>
       </c>
     </row>
     <row r="108">
@@ -8509,10 +8509,10 @@
         <v>0.73</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.2908</v>
+        <v>-0.2768</v>
       </c>
       <c r="J108" t="n">
-        <v>-6.3976</v>
+        <v>-6.0896</v>
       </c>
     </row>
     <row r="109">
@@ -8549,10 +8549,10 @@
         <v>0.7</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.3175</v>
+        <v>-0.3038</v>
       </c>
       <c r="J109" t="n">
-        <v>-6.985</v>
+        <v>-6.6836</v>
       </c>
     </row>
     <row r="110">
@@ -8589,10 +8589,10 @@
         <v>0.66</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3525</v>
+        <v>-0.3395</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.755</v>
+        <v>-7.469</v>
       </c>
     </row>
     <row r="111">
@@ -8629,10 +8629,10 @@
         <v>0.66</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3525</v>
+        <v>-0.3395</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.755</v>
+        <v>-7.469</v>
       </c>
     </row>
     <row r="112">
@@ -8669,10 +8669,10 @@
         <v>1.49</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9268999999999999</v>
+        <v>0.9132</v>
       </c>
       <c r="J112" t="n">
-        <v>21.3187</v>
+        <v>21.0036</v>
       </c>
     </row>
     <row r="113">
@@ -8709,10 +8709,10 @@
         <v>1.35</v>
       </c>
       <c r="I113" t="n">
-        <v>0.733</v>
+        <v>0.7208</v>
       </c>
       <c r="J113" t="n">
-        <v>16.859</v>
+        <v>16.5784</v>
       </c>
     </row>
     <row r="114">
@@ -8749,10 +8749,10 @@
         <v>1.32</v>
       </c>
       <c r="I114" t="n">
-        <v>0.6902</v>
+        <v>0.6793</v>
       </c>
       <c r="J114" t="n">
-        <v>15.8746</v>
+        <v>15.6239</v>
       </c>
     </row>
     <row r="115">
@@ -8789,10 +8789,10 @@
         <v>1.19</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4932</v>
+        <v>0.481</v>
       </c>
       <c r="J115" t="n">
-        <v>11.3436</v>
+        <v>11.063</v>
       </c>
     </row>
     <row r="116">
@@ -8829,10 +8829,10 @@
         <v>1.08</v>
       </c>
       <c r="I116" t="n">
-        <v>0.2424</v>
+        <v>0.2122</v>
       </c>
       <c r="J116" t="n">
-        <v>5.5752</v>
+        <v>4.8806</v>
       </c>
     </row>
     <row r="117">
@@ -8869,10 +8869,10 @@
         <v>0.84</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.1871</v>
+        <v>-0.1715</v>
       </c>
       <c r="J117" t="n">
-        <v>-4.3033</v>
+        <v>-3.9445</v>
       </c>
     </row>
     <row r="118">
@@ -8909,10 +8909,10 @@
         <v>0.84</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1871</v>
+        <v>-0.1715</v>
       </c>
       <c r="J118" t="n">
-        <v>-4.3033</v>
+        <v>-3.9445</v>
       </c>
     </row>
     <row r="119">
@@ -8949,10 +8949,10 @@
         <v>0.82</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2081</v>
+        <v>-0.1925</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.7863</v>
+        <v>-4.4275</v>
       </c>
     </row>
     <row r="120">
@@ -8989,10 +8989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3301</v>
+        <v>-0.3152</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.5923</v>
+        <v>-7.2496</v>
       </c>
     </row>
     <row r="121">
@@ -9029,10 +9029,10 @@
         <v>0.51</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4902</v>
+        <v>-0.4875</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.2746</v>
+        <v>-11.2125</v>
       </c>
     </row>
     <row r="122">
@@ -9069,10 +9069,10 @@
         <v>1.08</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2408</v>
+        <v>0.1963</v>
       </c>
       <c r="J122" t="n">
-        <v>5.7792</v>
+        <v>4.7112</v>
       </c>
     </row>
     <row r="123">
@@ -9109,10 +9109,10 @@
         <v>1.04</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1497</v>
+        <v>0.1155</v>
       </c>
       <c r="J123" t="n">
-        <v>3.5928</v>
+        <v>2.772</v>
       </c>
     </row>
     <row r="124">
@@ -9149,10 +9149,10 @@
         <v>0.92</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1145</v>
+        <v>-0.0992</v>
       </c>
       <c r="J124" t="n">
-        <v>-2.748</v>
+        <v>-2.3808</v>
       </c>
     </row>
     <row r="125">
@@ -9189,10 +9189,10 @@
         <v>0.77</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2696</v>
+        <v>-0.2507</v>
       </c>
       <c r="J125" t="n">
-        <v>-6.4704</v>
+        <v>-6.0168</v>
       </c>
     </row>
     <row r="126">
@@ -9229,10 +9229,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4609</v>
+        <v>-0.456</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.0616</v>
+        <v>-10.944</v>
       </c>
     </row>
     <row r="127">
@@ -9269,10 +9269,10 @@
         <v>1.36</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7588</v>
+        <v>0.7437</v>
       </c>
       <c r="J127" t="n">
-        <v>18.2112</v>
+        <v>17.8488</v>
       </c>
     </row>
     <row r="128">
@@ -9309,10 +9309,10 @@
         <v>1.29</v>
       </c>
       <c r="I128" t="n">
-        <v>0.6555</v>
+        <v>0.6432</v>
       </c>
       <c r="J128" t="n">
-        <v>15.732</v>
+        <v>15.4368</v>
       </c>
     </row>
     <row r="129">
@@ -9349,10 +9349,10 @@
         <v>1.24</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5794</v>
+        <v>0.5708</v>
       </c>
       <c r="J129" t="n">
-        <v>13.9056</v>
+        <v>13.6992</v>
       </c>
     </row>
     <row r="130">
@@ -9389,10 +9389,10 @@
         <v>1.08</v>
       </c>
       <c r="I130" t="n">
-        <v>0.256</v>
+        <v>0.2251</v>
       </c>
       <c r="J130" t="n">
-        <v>6.144</v>
+        <v>5.4024</v>
       </c>
     </row>
     <row r="131">
@@ -9429,10 +9429,10 @@
         <v>1.05</v>
       </c>
       <c r="I131" t="n">
-        <v>0.1688</v>
+        <v>0.1427</v>
       </c>
       <c r="J131" t="n">
-        <v>4.0512</v>
+        <v>3.4248</v>
       </c>
     </row>
     <row r="132">
@@ -9469,10 +9469,10 @@
         <v>1.64</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.8769</v>
       </c>
       <c r="J132" t="n">
-        <v>27.384</v>
+        <v>26.307</v>
       </c>
     </row>
     <row r="133">
@@ -9509,10 +9509,10 @@
         <v>1.35</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6047</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="J133" t="n">
-        <v>18.141</v>
+        <v>17.283</v>
       </c>
     </row>
     <row r="134">
@@ -9549,10 +9549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2462</v>
+        <v>-0.2263</v>
       </c>
       <c r="J134" t="n">
-        <v>-7.386</v>
+        <v>-6.789</v>
       </c>
     </row>
     <row r="135">
@@ -9589,10 +9589,10 @@
         <v>0.71</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3421</v>
+        <v>-0.3272</v>
       </c>
       <c r="J135" t="n">
-        <v>-10.263</v>
+        <v>-9.816000000000001</v>
       </c>
     </row>
     <row r="136">
@@ -9629,10 +9629,10 @@
         <v>0.7</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3513</v>
+        <v>-0.3371</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.539</v>
+        <v>-10.113</v>
       </c>
     </row>
     <row r="137">
@@ -9669,10 +9669,10 @@
         <v>1.33</v>
       </c>
       <c r="I137" t="n">
-        <v>0.7333</v>
+        <v>0.7174</v>
       </c>
       <c r="J137" t="n">
-        <v>21.999</v>
+        <v>21.522</v>
       </c>
     </row>
     <row r="138">
@@ -9709,10 +9709,10 @@
         <v>1.13</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3976</v>
+        <v>0.3586</v>
       </c>
       <c r="J138" t="n">
-        <v>11.928</v>
+        <v>10.758</v>
       </c>
     </row>
     <row r="139">
@@ -9749,10 +9749,10 @@
         <v>1.04</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1543</v>
+        <v>0.1284</v>
       </c>
       <c r="J139" t="n">
-        <v>4.629</v>
+        <v>3.852</v>
       </c>
     </row>
     <row r="140">
@@ -9789,10 +9789,10 @@
         <v>1.03</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1208</v>
+        <v>0.0985</v>
       </c>
       <c r="J140" t="n">
-        <v>3.624</v>
+        <v>2.955</v>
       </c>
     </row>
     <row r="141">
@@ -9829,10 +9829,10 @@
         <v>0.99</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.0761</v>
+        <v>-0.0558</v>
       </c>
       <c r="J141" t="n">
-        <v>-2.283</v>
+        <v>-1.674</v>
       </c>
     </row>
     <row r="142">
@@ -9869,10 +9869,10 @@
         <v>1.35</v>
       </c>
       <c r="I142" t="n">
-        <v>0.6351</v>
+        <v>0.6088</v>
       </c>
       <c r="J142" t="n">
-        <v>17.1477</v>
+        <v>16.4376</v>
       </c>
     </row>
     <row r="143">
@@ -9909,10 +9909,10 @@
         <v>1.04</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1396</v>
+        <v>0.106</v>
       </c>
       <c r="J143" t="n">
-        <v>3.7692</v>
+        <v>2.862</v>
       </c>
     </row>
     <row r="144">
@@ -9949,10 +9949,10 @@
         <v>0.85</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1939</v>
+        <v>-0.174</v>
       </c>
       <c r="J144" t="n">
-        <v>-5.2353</v>
+        <v>-4.698</v>
       </c>
     </row>
     <row r="145">
@@ -9989,10 +9989,10 @@
         <v>0.77</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2738</v>
+        <v>-0.2547</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.3926</v>
+        <v>-6.8769</v>
       </c>
     </row>
     <row r="146">
@@ -10029,10 +10029,10 @@
         <v>0.57</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4562</v>
+        <v>-0.4511</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.3174</v>
+        <v>-12.1797</v>
       </c>
     </row>
     <row r="147">
@@ -10069,10 +10069,10 @@
         <v>1.59</v>
       </c>
       <c r="I147" t="n">
-        <v>1.0683</v>
+        <v>1.0582</v>
       </c>
       <c r="J147" t="n">
-        <v>28.8441</v>
+        <v>28.5714</v>
       </c>
     </row>
     <row r="148">
@@ -10109,10 +10109,10 @@
         <v>1.35</v>
       </c>
       <c r="I148" t="n">
-        <v>0.738</v>
+        <v>0.7244</v>
       </c>
       <c r="J148" t="n">
-        <v>19.926</v>
+        <v>19.5588</v>
       </c>
     </row>
     <row r="149">
@@ -10149,10 +10149,10 @@
         <v>1.32</v>
       </c>
       <c r="I149" t="n">
-        <v>0.6945</v>
+        <v>0.6821</v>
       </c>
       <c r="J149" t="n">
-        <v>18.7515</v>
+        <v>18.4167</v>
       </c>
     </row>
     <row r="150">
@@ -10189,10 +10189,10 @@
         <v>0.99</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1014</v>
+        <v>-0.0808</v>
       </c>
       <c r="J150" t="n">
-        <v>-2.7378</v>
+        <v>-2.1816</v>
       </c>
     </row>
     <row r="151">
@@ -10229,10 +10229,10 @@
         <v>0.98</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.1428</v>
+        <v>-0.1161</v>
       </c>
       <c r="J151" t="n">
-        <v>-3.8556</v>
+        <v>-3.1347</v>
       </c>
     </row>
     <row r="152">
@@ -10269,10 +10269,10 @@
         <v>1.36</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6201</v>
+        <v>0.5908</v>
       </c>
       <c r="J152" t="n">
-        <v>26.0442</v>
+        <v>24.8136</v>
       </c>
     </row>
     <row r="153">
@@ -10309,10 +10309,10 @@
         <v>1.11</v>
       </c>
       <c r="I153" t="n">
-        <v>0.268</v>
+        <v>0.2204</v>
       </c>
       <c r="J153" t="n">
-        <v>11.256</v>
+        <v>9.2568</v>
       </c>
     </row>
     <row r="154">
@@ -10349,10 +10349,10 @@
         <v>0.97</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0598</v>
+        <v>-0.0467</v>
       </c>
       <c r="J154" t="n">
-        <v>-2.5116</v>
+        <v>-1.9614</v>
       </c>
     </row>
     <row r="155">
@@ -10389,10 +10389,10 @@
         <v>0.92</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1255</v>
+        <v>-0.1067</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.271</v>
+        <v>-4.4814</v>
       </c>
     </row>
     <row r="156">
@@ -10429,10 +10429,10 @@
         <v>0.75</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3029</v>
+        <v>-0.2853</v>
       </c>
       <c r="J156" t="n">
-        <v>-12.7218</v>
+        <v>-11.9826</v>
       </c>
     </row>
     <row r="157">
@@ -10469,10 +10469,10 @@
         <v>1.32</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7181</v>
+        <v>0.7024</v>
       </c>
       <c r="J157" t="n">
-        <v>30.1602</v>
+        <v>29.5008</v>
       </c>
     </row>
     <row r="158">
@@ -10509,10 +10509,10 @@
         <v>1.13</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3976</v>
+        <v>0.3586</v>
       </c>
       <c r="J158" t="n">
-        <v>16.6992</v>
+        <v>15.0612</v>
       </c>
     </row>
     <row r="159">
@@ -10549,10 +10549,10 @@
         <v>1.12</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3733</v>
+        <v>0.3349</v>
       </c>
       <c r="J159" t="n">
-        <v>15.6786</v>
+        <v>14.0658</v>
       </c>
     </row>
     <row r="160">
@@ -10589,10 +10589,10 @@
         <v>1.08</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2717</v>
+        <v>0.2373</v>
       </c>
       <c r="J160" t="n">
-        <v>11.4114</v>
+        <v>9.9666</v>
       </c>
     </row>
     <row r="161">
@@ -10629,10 +10629,10 @@
         <v>0.87</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4402</v>
+        <v>-0.3976</v>
       </c>
       <c r="J161" t="n">
-        <v>-18.4884</v>
+        <v>-16.6992</v>
       </c>
     </row>
     <row r="162">
@@ -10669,10 +10669,10 @@
         <v>1.53</v>
       </c>
       <c r="I162" t="n">
-        <v>1.116</v>
+        <v>1.1298</v>
       </c>
       <c r="J162" t="n">
-        <v>24.552</v>
+        <v>24.8556</v>
       </c>
     </row>
     <row r="163">
@@ -10709,10 +10709,10 @@
         <v>1.48</v>
       </c>
       <c r="I163" t="n">
-        <v>1.0489</v>
+        <v>1.0575</v>
       </c>
       <c r="J163" t="n">
-        <v>23.0758</v>
+        <v>23.265</v>
       </c>
     </row>
     <row r="164">
@@ -10749,10 +10749,10 @@
         <v>1.48</v>
       </c>
       <c r="I164" t="n">
-        <v>1.0489</v>
+        <v>1.0575</v>
       </c>
       <c r="J164" t="n">
-        <v>23.0758</v>
+        <v>23.265</v>
       </c>
     </row>
     <row r="165">
@@ -10789,10 +10789,10 @@
         <v>1.23</v>
       </c>
       <c r="I165" t="n">
-        <v>0.5888</v>
+        <v>0.5621</v>
       </c>
       <c r="J165" t="n">
-        <v>12.9536</v>
+        <v>12.3662</v>
       </c>
     </row>
     <row r="166">
@@ -10829,10 +10829,10 @@
         <v>1.08</v>
       </c>
       <c r="I166" t="n">
-        <v>0.2306</v>
+        <v>0.2</v>
       </c>
       <c r="J166" t="n">
-        <v>5.0732</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="167">
@@ -10869,10 +10869,10 @@
         <v>0.97</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.025</v>
+        <v>-0.0141</v>
       </c>
       <c r="J167" t="n">
-        <v>-0.55</v>
+        <v>-0.3102</v>
       </c>
     </row>
     <row r="168">
@@ -10909,10 +10909,10 @@
         <v>0.89</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1312</v>
+        <v>-0.1159</v>
       </c>
       <c r="J168" t="n">
-        <v>-2.8864</v>
+        <v>-2.5498</v>
       </c>
     </row>
     <row r="169">
@@ -10949,10 +10949,10 @@
         <v>0.87</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1542</v>
+        <v>-0.1387</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.3924</v>
+        <v>-3.0514</v>
       </c>
     </row>
     <row r="170">
@@ -10989,10 +10989,10 @@
         <v>0.59</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4197</v>
+        <v>-0.4099</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.2334</v>
+        <v>-9.017799999999999</v>
       </c>
     </row>
     <row r="171">
@@ -11029,10 +11029,10 @@
         <v>0.38</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6025</v>
+        <v>-0.6163</v>
       </c>
       <c r="J171" t="n">
-        <v>-13.255</v>
+        <v>-13.5586</v>
       </c>
     </row>
     <row r="172">
@@ -11069,10 +11069,10 @@
         <v>1.09</v>
       </c>
       <c r="I172" t="n">
-        <v>0.1899</v>
+        <v>0.1728</v>
       </c>
       <c r="J172" t="n">
-        <v>5.5071</v>
+        <v>5.0112</v>
       </c>
     </row>
     <row r="173">
@@ -11109,10 +11109,10 @@
         <v>1.04</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1039</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="J173" t="n">
-        <v>3.0131</v>
+        <v>2.552</v>
       </c>
     </row>
     <row r="174">
@@ -11149,10 +11149,10 @@
         <v>0.97</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0554</v>
+        <v>-0.0443</v>
       </c>
       <c r="J174" t="n">
-        <v>-1.6066</v>
+        <v>-1.2847</v>
       </c>
     </row>
     <row r="175">
@@ -11189,10 +11189,10 @@
         <v>0.88</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1649</v>
+        <v>-0.1452</v>
       </c>
       <c r="J175" t="n">
-        <v>-4.7821</v>
+        <v>-4.2108</v>
       </c>
     </row>
     <row r="176">
@@ -11229,10 +11229,10 @@
         <v>0.77</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2771</v>
+        <v>-0.258</v>
       </c>
       <c r="J176" t="n">
-        <v>-8.0359</v>
+        <v>-7.482</v>
       </c>
     </row>
     <row r="177">
@@ -11269,10 +11269,10 @@
         <v>1.31</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4367</v>
+        <v>0.3712</v>
       </c>
       <c r="J177" t="n">
-        <v>12.6643</v>
+        <v>10.7648</v>
       </c>
     </row>
     <row r="178">
@@ -11309,10 +11309,10 @@
         <v>1.2</v>
       </c>
       <c r="I178" t="n">
-        <v>0.3073</v>
+        <v>0.2517</v>
       </c>
       <c r="J178" t="n">
-        <v>8.9117</v>
+        <v>7.2993</v>
       </c>
     </row>
     <row r="179">
@@ -11349,10 +11349,10 @@
         <v>1.06</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1183</v>
+        <v>0.0891</v>
       </c>
       <c r="J179" t="n">
-        <v>3.4307</v>
+        <v>2.5839</v>
       </c>
     </row>
     <row r="180">
@@ -11389,10 +11389,10 @@
         <v>0.99</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.0327</v>
+        <v>-0.0237</v>
       </c>
       <c r="J180" t="n">
-        <v>-0.9483</v>
+        <v>-0.6873</v>
       </c>
     </row>
     <row r="181">
@@ -11429,10 +11429,10 @@
         <v>0.96</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="J181" t="n">
-        <v>-2.3403</v>
+        <v>-1.8879</v>
       </c>
     </row>
     <row r="182">
@@ -11469,10 +11469,10 @@
         <v>1.33</v>
       </c>
       <c r="I182" t="n">
-        <v>0.8088</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="J182" t="n">
-        <v>21.8376</v>
+        <v>21.2166</v>
       </c>
     </row>
     <row r="183">
@@ -11509,10 +11509,10 @@
         <v>1.26</v>
       </c>
       <c r="I183" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.6379</v>
       </c>
       <c r="J183" t="n">
-        <v>18.0306</v>
+        <v>17.2233</v>
       </c>
     </row>
     <row r="184">
@@ -11549,10 +11549,10 @@
         <v>1.26</v>
       </c>
       <c r="I184" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.6379</v>
       </c>
       <c r="J184" t="n">
-        <v>18.0306</v>
+        <v>17.2233</v>
       </c>
     </row>
     <row r="185">
@@ -11589,10 +11589,10 @@
         <v>1.2</v>
       </c>
       <c r="I185" t="n">
-        <v>0.5432</v>
+        <v>0.5102</v>
       </c>
       <c r="J185" t="n">
-        <v>14.6664</v>
+        <v>13.7754</v>
       </c>
     </row>
     <row r="186">
@@ -11629,10 +11629,10 @@
         <v>1.06</v>
       </c>
       <c r="I186" t="n">
-        <v>0.1959</v>
+        <v>0.1681</v>
       </c>
       <c r="J186" t="n">
-        <v>5.2893</v>
+        <v>4.5387</v>
       </c>
     </row>
     <row r="187">
@@ -11669,10 +11669,10 @@
         <v>1.23</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4915</v>
+        <v>0.4331</v>
       </c>
       <c r="J187" t="n">
-        <v>13.2705</v>
+        <v>11.6937</v>
       </c>
     </row>
     <row r="188">
@@ -11709,10 +11709,10 @@
         <v>1.02</v>
       </c>
       <c r="I188" t="n">
-        <v>0.077</v>
+        <v>0.0547</v>
       </c>
       <c r="J188" t="n">
-        <v>2.079</v>
+        <v>1.4769</v>
       </c>
     </row>
     <row r="189">
@@ -11749,10 +11749,10 @@
         <v>0.99</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0239</v>
+        <v>-0.0175</v>
       </c>
       <c r="J189" t="n">
-        <v>-0.6453</v>
+        <v>-0.4725</v>
       </c>
     </row>
     <row r="190">
@@ -11789,10 +11789,10 @@
         <v>0.91</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1331</v>
+        <v>-0.1144</v>
       </c>
       <c r="J190" t="n">
-        <v>-3.5937</v>
+        <v>-3.0888</v>
       </c>
     </row>
     <row r="191">
@@ -11829,10 +11829,10 @@
         <v>0.71</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3359</v>
+        <v>-0.3201</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.0693</v>
+        <v>-8.6427</v>
       </c>
     </row>
     <row r="192">
@@ -11869,10 +11869,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.2083</v>
+        <v>-0.1932</v>
       </c>
       <c r="J192" t="n">
-        <v>-3.7494</v>
+        <v>-3.4776</v>
       </c>
     </row>
     <row r="193">
@@ -11909,10 +11909,10 @@
         <v>0.78</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.2393</v>
+        <v>-0.2249</v>
       </c>
       <c r="J193" t="n">
-        <v>-4.3074</v>
+        <v>-4.0482</v>
       </c>
     </row>
     <row r="194">
@@ -11949,10 +11949,10 @@
         <v>0.71</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.3068</v>
+        <v>-0.2938</v>
       </c>
       <c r="J194" t="n">
-        <v>-5.5224</v>
+        <v>-5.2884</v>
       </c>
     </row>
     <row r="195">
@@ -11989,10 +11989,10 @@
         <v>0.7</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3159</v>
+        <v>-0.303</v>
       </c>
       <c r="J195" t="n">
-        <v>-5.6862</v>
+        <v>-5.454</v>
       </c>
     </row>
     <row r="196">
@@ -12029,10 +12029,10 @@
         <v>0.4</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5787</v>
+        <v>-0.5877</v>
       </c>
       <c r="J196" t="n">
-        <v>-10.4166</v>
+        <v>-10.5786</v>
       </c>
     </row>
     <row r="197">
@@ -12069,10 +12069,10 @@
         <v>1.92</v>
       </c>
       <c r="I197" t="n">
-        <v>0.9641999999999999</v>
+        <v>0.8996</v>
       </c>
       <c r="J197" t="n">
-        <v>17.3556</v>
+        <v>16.1928</v>
       </c>
     </row>
     <row r="198">
@@ -12109,10 +12109,10 @@
         <v>1.54</v>
       </c>
       <c r="I198" t="n">
-        <v>0.6291</v>
+        <v>0.5631</v>
       </c>
       <c r="J198" t="n">
-        <v>11.3238</v>
+        <v>10.1358</v>
       </c>
     </row>
     <row r="199">
@@ -12149,10 +12149,10 @@
         <v>1.53</v>
       </c>
       <c r="I199" t="n">
-        <v>0.6198</v>
+        <v>0.5542</v>
       </c>
       <c r="J199" t="n">
-        <v>11.1564</v>
+        <v>9.9756</v>
       </c>
     </row>
     <row r="200">
@@ -12189,10 +12189,10 @@
         <v>1.48</v>
       </c>
       <c r="I200" t="n">
-        <v>0.5724</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="J200" t="n">
-        <v>10.3032</v>
+        <v>9.1548</v>
       </c>
     </row>
     <row r="201">
@@ -12229,10 +12229,10 @@
         <v>1.33</v>
       </c>
       <c r="I201" t="n">
-        <v>0.4196</v>
+        <v>0.3629</v>
       </c>
       <c r="J201" t="n">
-        <v>7.5528</v>
+        <v>6.5322</v>
       </c>
     </row>
     <row r="202">
@@ -12269,10 +12269,10 @@
         <v>1.37</v>
       </c>
       <c r="I202" t="n">
-        <v>0.9045</v>
+        <v>0.887</v>
       </c>
       <c r="J202" t="n">
-        <v>19.899</v>
+        <v>19.514</v>
       </c>
     </row>
     <row r="203">
@@ -12309,10 +12309,10 @@
         <v>1.32</v>
       </c>
       <c r="I203" t="n">
-        <v>0.8044</v>
+        <v>0.7788</v>
       </c>
       <c r="J203" t="n">
-        <v>17.6968</v>
+        <v>17.1336</v>
       </c>
     </row>
     <row r="204">
@@ -12349,10 +12349,10 @@
         <v>1.28</v>
       </c>
       <c r="I204" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.6916</v>
       </c>
       <c r="J204" t="n">
-        <v>15.8906</v>
+        <v>15.2152</v>
       </c>
     </row>
     <row r="205">
@@ -12389,10 +12389,10 @@
         <v>1.11</v>
       </c>
       <c r="I205" t="n">
-        <v>0.3436</v>
+        <v>0.3083</v>
       </c>
       <c r="J205" t="n">
-        <v>7.5592</v>
+        <v>6.7826</v>
       </c>
     </row>
     <row r="206">
@@ -12429,10 +12429,10 @@
         <v>0.67</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.8999</v>
+        <v>-0.8884</v>
       </c>
       <c r="J206" t="n">
-        <v>-19.7978</v>
+        <v>-19.5448</v>
       </c>
     </row>
     <row r="207">
@@ -12469,10 +12469,10 @@
         <v>1.56</v>
       </c>
       <c r="I207" t="n">
-        <v>0.9922</v>
+        <v>0.9644</v>
       </c>
       <c r="J207" t="n">
-        <v>21.8284</v>
+        <v>21.2168</v>
       </c>
     </row>
     <row r="208">
@@ -12509,10 +12509,10 @@
         <v>0.9</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.1442</v>
+        <v>-0.125</v>
       </c>
       <c r="J208" t="n">
-        <v>-3.1724</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="209">
@@ -12549,10 +12549,10 @@
         <v>0.83</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2193</v>
+        <v>-0.1988</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.8246</v>
+        <v>-4.3736</v>
       </c>
     </row>
     <row r="210">
@@ -12589,10 +12589,10 @@
         <v>0.82</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2294</v>
+        <v>-0.2091</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.0468</v>
+        <v>-4.6002</v>
       </c>
     </row>
     <row r="211">
@@ -12629,10 +12629,10 @@
         <v>0.73</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3169</v>
+        <v>-0.2998</v>
       </c>
       <c r="J211" t="n">
-        <v>-6.9718</v>
+        <v>-6.5956</v>
       </c>
     </row>
     <row r="212">
@@ -12669,10 +12669,10 @@
         <v>1.24</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6466</v>
+        <v>0.6111</v>
       </c>
       <c r="J212" t="n">
-        <v>18.7514</v>
+        <v>17.7219</v>
       </c>
     </row>
     <row r="213">
@@ -12709,10 +12709,10 @@
         <v>1.2</v>
       </c>
       <c r="I213" t="n">
-        <v>0.5588</v>
+        <v>0.5205</v>
       </c>
       <c r="J213" t="n">
-        <v>16.2052</v>
+        <v>15.0945</v>
       </c>
     </row>
     <row r="214">
@@ -12749,10 +12749,10 @@
         <v>1.1</v>
       </c>
       <c r="I214" t="n">
-        <v>0.3234</v>
+        <v>0.2869</v>
       </c>
       <c r="J214" t="n">
-        <v>9.3786</v>
+        <v>8.3201</v>
       </c>
     </row>
     <row r="215">
@@ -12789,10 +12789,10 @@
         <v>1.08</v>
       </c>
       <c r="I215" t="n">
-        <v>0.2709</v>
+        <v>0.2368</v>
       </c>
       <c r="J215" t="n">
-        <v>7.8561</v>
+        <v>6.8672</v>
       </c>
     </row>
     <row r="216">
@@ -12829,10 +12829,10 @@
         <v>0.93</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2806</v>
+        <v>-0.2403</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.1374</v>
+        <v>-6.9687</v>
       </c>
     </row>
     <row r="217">
@@ -12869,10 +12869,10 @@
         <v>1.31</v>
       </c>
       <c r="I217" t="n">
-        <v>0.6155</v>
+        <v>0.5571</v>
       </c>
       <c r="J217" t="n">
-        <v>17.8495</v>
+        <v>16.1559</v>
       </c>
     </row>
     <row r="218">
@@ -12909,10 +12909,10 @@
         <v>1.19</v>
       </c>
       <c r="I218" t="n">
-        <v>0.4185</v>
+        <v>0.3614</v>
       </c>
       <c r="J218" t="n">
-        <v>12.1365</v>
+        <v>10.4806</v>
       </c>
     </row>
     <row r="219">
@@ -12949,10 +12949,10 @@
         <v>0.84</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2112</v>
+        <v>-0.1906</v>
       </c>
       <c r="J219" t="n">
-        <v>-6.1248</v>
+        <v>-5.5274</v>
       </c>
     </row>
     <row r="220">
@@ -12989,10 +12989,10 @@
         <v>0.84</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2112</v>
+        <v>-0.1906</v>
       </c>
       <c r="J220" t="n">
-        <v>-6.1248</v>
+        <v>-5.5274</v>
       </c>
     </row>
     <row r="221">
@@ -13029,10 +13029,10 @@
         <v>0.78</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2713</v>
+        <v>-0.2521</v>
       </c>
       <c r="J221" t="n">
-        <v>-7.8677</v>
+        <v>-7.3109</v>
       </c>
     </row>
     <row r="222">
@@ -13069,10 +13069,10 @@
         <v>1.22</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5088</v>
+        <v>0.4551</v>
       </c>
       <c r="J222" t="n">
-        <v>12.72</v>
+        <v>11.3775</v>
       </c>
     </row>
     <row r="223">
@@ -13109,10 +13109,10 @@
         <v>0.83</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.2099</v>
+        <v>-0.1909</v>
       </c>
       <c r="J223" t="n">
-        <v>-5.2475</v>
+        <v>-4.7725</v>
       </c>
     </row>
     <row r="224">
@@ -13149,10 +13149,10 @@
         <v>0.8</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2397</v>
+        <v>-0.2205</v>
       </c>
       <c r="J224" t="n">
-        <v>-5.9925</v>
+        <v>-5.5125</v>
       </c>
     </row>
     <row r="225">
@@ -13189,10 +13189,10 @@
         <v>0.76</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2784</v>
+        <v>-0.2598</v>
       </c>
       <c r="J225" t="n">
-        <v>-6.96</v>
+        <v>-6.495</v>
       </c>
     </row>
     <row r="226">
@@ -13229,10 +13229,10 @@
         <v>0.72</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3161</v>
+        <v>-0.299</v>
       </c>
       <c r="J226" t="n">
-        <v>-7.9025</v>
+        <v>-7.475</v>
       </c>
     </row>
     <row r="227">
@@ -13269,10 +13269,10 @@
         <v>1.59</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2318</v>
+        <v>1.2488</v>
       </c>
       <c r="J227" t="n">
-        <v>30.795</v>
+        <v>31.22</v>
       </c>
     </row>
     <row r="228">
@@ -13309,10 +13309,10 @@
         <v>1.28</v>
       </c>
       <c r="I228" t="n">
-        <v>0.7164</v>
+        <v>0.6865</v>
       </c>
       <c r="J228" t="n">
-        <v>17.91</v>
+        <v>17.1625</v>
       </c>
     </row>
     <row r="229">
@@ -13349,10 +13349,10 @@
         <v>1.23</v>
       </c>
       <c r="I229" t="n">
-        <v>0.6118</v>
+        <v>0.5778</v>
       </c>
       <c r="J229" t="n">
-        <v>15.295</v>
+        <v>14.445</v>
       </c>
     </row>
     <row r="230">
@@ -13389,10 +13389,10 @@
         <v>0.91</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3493</v>
+        <v>-0.3081</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.7325</v>
+        <v>-7.7025</v>
       </c>
     </row>
     <row r="231">
@@ -13429,10 +13429,10 @@
         <v>0.88</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4284</v>
+        <v>-0.3871</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.71</v>
+        <v>-9.6775</v>
       </c>
     </row>
     <row r="232">
@@ -13469,10 +13469,10 @@
         <v>0.78</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.2157</v>
+        <v>-0.1988</v>
       </c>
       <c r="J232" t="n">
-        <v>-3.8826</v>
+        <v>-3.5784</v>
       </c>
     </row>
     <row r="233">
@@ -13509,10 +13509,10 @@
         <v>0.78</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.2157</v>
+        <v>-0.1988</v>
       </c>
       <c r="J233" t="n">
-        <v>-3.8826</v>
+        <v>-3.5784</v>
       </c>
     </row>
     <row r="234">
@@ -13549,10 +13549,10 @@
         <v>0.72</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.2785</v>
+        <v>-0.266</v>
       </c>
       <c r="J234" t="n">
-        <v>-5.013</v>
+        <v>-4.788</v>
       </c>
     </row>
     <row r="235">
@@ -13589,10 +13589,10 @@
         <v>0.35</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.6097</v>
+        <v>-0.6223</v>
       </c>
       <c r="J235" t="n">
-        <v>-10.9746</v>
+        <v>-11.2014</v>
       </c>
     </row>
     <row r="236">
@@ -13629,10 +13629,10 @@
         <v>0.27</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.6807</v>
+        <v>-0.7065</v>
       </c>
       <c r="J236" t="n">
-        <v>-12.2526</v>
+        <v>-12.717</v>
       </c>
     </row>
     <row r="237">
@@ -13669,10 +13669,10 @@
         <v>2.22</v>
       </c>
       <c r="I237" t="n">
-        <v>1.9005</v>
+        <v>1.968</v>
       </c>
       <c r="J237" t="n">
-        <v>34.209</v>
+        <v>35.424</v>
       </c>
     </row>
     <row r="238">
@@ -13709,10 +13709,10 @@
         <v>1.51</v>
       </c>
       <c r="I238" t="n">
-        <v>1.0696</v>
+        <v>1.0885</v>
       </c>
       <c r="J238" t="n">
-        <v>19.2528</v>
+        <v>19.593</v>
       </c>
     </row>
     <row r="239">
@@ -13749,10 +13749,10 @@
         <v>1.46</v>
       </c>
       <c r="I239" t="n">
-        <v>0.9985000000000001</v>
+        <v>1.0093</v>
       </c>
       <c r="J239" t="n">
-        <v>17.973</v>
+        <v>18.1674</v>
       </c>
     </row>
     <row r="240">
@@ -13789,10 +13789,10 @@
         <v>1.4</v>
       </c>
       <c r="I240" t="n">
-        <v>0.8954</v>
+        <v>0.8934</v>
       </c>
       <c r="J240" t="n">
-        <v>16.1172</v>
+        <v>16.0812</v>
       </c>
     </row>
     <row r="241">
@@ -13829,10 +13829,10 @@
         <v>1.33</v>
       </c>
       <c r="I241" t="n">
-        <v>0.7617</v>
+        <v>0.7487</v>
       </c>
       <c r="J241" t="n">
-        <v>13.7106</v>
+        <v>13.4766</v>
       </c>
     </row>
     <row r="242">
@@ -13869,10 +13869,10 @@
         <v>2.23</v>
       </c>
       <c r="I242" t="n">
-        <v>1.9083</v>
+        <v>1.9765</v>
       </c>
       <c r="J242" t="n">
-        <v>34.3494</v>
+        <v>35.577</v>
       </c>
     </row>
     <row r="243">
@@ -13909,10 +13909,10 @@
         <v>1.79</v>
       </c>
       <c r="I243" t="n">
-        <v>1.407</v>
+        <v>1.4352</v>
       </c>
       <c r="J243" t="n">
-        <v>25.326</v>
+        <v>25.8336</v>
       </c>
     </row>
     <row r="244">
@@ -13949,10 +13949,10 @@
         <v>1.51</v>
       </c>
       <c r="I244" t="n">
-        <v>1.0683</v>
+        <v>1.0875</v>
       </c>
       <c r="J244" t="n">
-        <v>19.2294</v>
+        <v>19.575</v>
       </c>
     </row>
     <row r="245">
@@ -13989,10 +13989,10 @@
         <v>1.26</v>
       </c>
       <c r="I245" t="n">
-        <v>0.6182</v>
+        <v>0.5952</v>
       </c>
       <c r="J245" t="n">
-        <v>11.1276</v>
+        <v>10.7136</v>
       </c>
     </row>
     <row r="246">
@@ -14029,10 +14029,10 @@
         <v>1.21</v>
       </c>
       <c r="I246" t="n">
-        <v>0.5115</v>
+        <v>0.4823</v>
       </c>
       <c r="J246" t="n">
-        <v>9.207000000000001</v>
+        <v>8.6814</v>
       </c>
     </row>
     <row r="247">
@@ -14069,10 +14069,10 @@
         <v>0.78</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.2073</v>
+        <v>-0.1883</v>
       </c>
       <c r="J247" t="n">
-        <v>-3.7314</v>
+        <v>-3.3894</v>
       </c>
     </row>
     <row r="248">
@@ -14109,10 +14109,10 @@
         <v>0.6</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.3879</v>
+        <v>-0.3818</v>
       </c>
       <c r="J248" t="n">
-        <v>-6.9822</v>
+        <v>-6.8724</v>
       </c>
     </row>
     <row r="249">
@@ -14149,10 +14149,10 @@
         <v>0.58</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.4057</v>
+        <v>-0.4002</v>
       </c>
       <c r="J249" t="n">
-        <v>-7.3026</v>
+        <v>-7.2036</v>
       </c>
     </row>
     <row r="250">
@@ -14189,10 +14189,10 @@
         <v>0.41</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.5524</v>
+        <v>-0.5565</v>
       </c>
       <c r="J250" t="n">
-        <v>-9.943199999999999</v>
+        <v>-10.017</v>
       </c>
     </row>
     <row r="251">
@@ -14229,10 +14229,10 @@
         <v>0.4</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5613</v>
+        <v>-0.5665</v>
       </c>
       <c r="J251" t="n">
-        <v>-10.1034</v>
+        <v>-10.197</v>
       </c>
     </row>
     <row r="252">
@@ -14269,10 +14269,10 @@
         <v>1.65</v>
       </c>
       <c r="I252" t="n">
-        <v>1.2837</v>
+        <v>1.3022</v>
       </c>
       <c r="J252" t="n">
-        <v>29.5251</v>
+        <v>29.9506</v>
       </c>
     </row>
     <row r="253">
@@ -14309,10 +14309,10 @@
         <v>1.33</v>
       </c>
       <c r="I253" t="n">
-        <v>0.7972</v>
+        <v>0.7769</v>
       </c>
       <c r="J253" t="n">
-        <v>18.3356</v>
+        <v>17.8687</v>
       </c>
     </row>
     <row r="254">
@@ -14349,10 +14349,10 @@
         <v>1.23</v>
       </c>
       <c r="I254" t="n">
-        <v>0.5982</v>
+        <v>0.5697</v>
       </c>
       <c r="J254" t="n">
-        <v>13.7586</v>
+        <v>13.1031</v>
       </c>
     </row>
     <row r="255">
@@ -14389,10 +14389,10 @@
         <v>1.18</v>
       </c>
       <c r="I255" t="n">
-        <v>0.4888</v>
+        <v>0.4576</v>
       </c>
       <c r="J255" t="n">
-        <v>11.2424</v>
+        <v>10.5248</v>
       </c>
     </row>
     <row r="256">
@@ -14429,10 +14429,10 @@
         <v>1.08</v>
       </c>
       <c r="I256" t="n">
-        <v>0.2411</v>
+        <v>0.2109</v>
       </c>
       <c r="J256" t="n">
-        <v>5.5453</v>
+        <v>4.8507</v>
       </c>
     </row>
     <row r="257">
@@ -14469,10 +14469,10 @@
         <v>0.96</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.0549</v>
+        <v>-0.0442</v>
       </c>
       <c r="J257" t="n">
-        <v>-1.2627</v>
+        <v>-1.0166</v>
       </c>
     </row>
     <row r="258">
@@ -14509,10 +14509,10 @@
         <v>0.91</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.12</v>
+        <v>-0.1051</v>
       </c>
       <c r="J258" t="n">
-        <v>-2.76</v>
+        <v>-2.4173</v>
       </c>
     </row>
     <row r="259">
@@ -14549,10 +14549,10 @@
         <v>0.86</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.176</v>
+        <v>-0.1592</v>
       </c>
       <c r="J259" t="n">
-        <v>-4.048</v>
+        <v>-3.6616</v>
       </c>
     </row>
     <row r="260">
@@ -14589,10 +14589,10 @@
         <v>0.82</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2164</v>
+        <v>-0.1986</v>
       </c>
       <c r="J260" t="n">
-        <v>-4.9772</v>
+        <v>-4.5678</v>
       </c>
     </row>
     <row r="261">
@@ -14629,10 +14629,10 @@
         <v>0.54</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4727</v>
+        <v>-0.4686</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.8721</v>
+        <v>-10.7778</v>
       </c>
     </row>
     <row r="262">
@@ -14669,10 +14669,10 @@
         <v>1.08</v>
       </c>
       <c r="I262" t="n">
-        <v>0.2259</v>
+        <v>0.1816</v>
       </c>
       <c r="J262" t="n">
-        <v>5.8734</v>
+        <v>4.7216</v>
       </c>
     </row>
     <row r="263">
@@ -14709,10 +14709,10 @@
         <v>0.98</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.0384</v>
+        <v>-0.03</v>
       </c>
       <c r="J263" t="n">
-        <v>-0.9984</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="264">
@@ -14749,10 +14749,10 @@
         <v>0.96</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.0684</v>
+        <v>-0.056</v>
       </c>
       <c r="J264" t="n">
-        <v>-1.7784</v>
+        <v>-1.456</v>
       </c>
     </row>
     <row r="265">
@@ -14789,10 +14789,10 @@
         <v>0.95</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.0819</v>
+        <v>-0.068</v>
       </c>
       <c r="J265" t="n">
-        <v>-2.1294</v>
+        <v>-1.768</v>
       </c>
     </row>
     <row r="266">
@@ -14829,10 +14829,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3506</v>
+        <v>-0.3355</v>
       </c>
       <c r="J266" t="n">
-        <v>-9.115600000000001</v>
+        <v>-8.723000000000001</v>
       </c>
     </row>
     <row r="267">
@@ -14869,10 +14869,10 @@
         <v>1.74</v>
       </c>
       <c r="I267" t="n">
-        <v>1.4267</v>
+        <v>1.4567</v>
       </c>
       <c r="J267" t="n">
-        <v>37.0942</v>
+        <v>37.8742</v>
       </c>
     </row>
     <row r="268">
@@ -14909,10 +14909,10 @@
         <v>1.36</v>
       </c>
       <c r="I268" t="n">
-        <v>0.8752</v>
+        <v>0.8559</v>
       </c>
       <c r="J268" t="n">
-        <v>22.7552</v>
+        <v>22.2534</v>
       </c>
     </row>
     <row r="269">
@@ -14949,10 +14949,10 @@
         <v>1.02</v>
       </c>
       <c r="I269" t="n">
-        <v>0.0697</v>
+        <v>0.0535</v>
       </c>
       <c r="J269" t="n">
-        <v>1.8122</v>
+        <v>1.391</v>
       </c>
     </row>
     <row r="270">
@@ -14989,10 +14989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2656</v>
+        <v>-0.2272</v>
       </c>
       <c r="J270" t="n">
-        <v>-6.9056</v>
+        <v>-5.9072</v>
       </c>
     </row>
     <row r="271">
@@ -15029,10 +15029,10 @@
         <v>0.88</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4302</v>
+        <v>-0.3891</v>
       </c>
       <c r="J271" t="n">
-        <v>-11.1852</v>
+        <v>-10.1166</v>
       </c>
     </row>
     <row r="272">
@@ -15069,10 +15069,10 @@
         <v>1.71</v>
       </c>
       <c r="I272" t="n">
-        <v>1.3343</v>
+        <v>1.356</v>
       </c>
       <c r="J272" t="n">
-        <v>29.3546</v>
+        <v>29.832</v>
       </c>
     </row>
     <row r="273">
@@ -15109,10 +15109,10 @@
         <v>1.59</v>
       </c>
       <c r="I273" t="n">
-        <v>1.1839</v>
+        <v>1.2005</v>
       </c>
       <c r="J273" t="n">
-        <v>26.0458</v>
+        <v>26.411</v>
       </c>
     </row>
     <row r="274">
@@ -15149,10 +15149,10 @@
         <v>1.35</v>
       </c>
       <c r="I274" t="n">
-        <v>0.8209</v>
+        <v>0.8087</v>
       </c>
       <c r="J274" t="n">
-        <v>18.0598</v>
+        <v>17.7914</v>
       </c>
     </row>
     <row r="275">
@@ -15189,10 +15189,10 @@
         <v>1.32</v>
       </c>
       <c r="I275" t="n">
-        <v>0.7628</v>
+        <v>0.7469</v>
       </c>
       <c r="J275" t="n">
-        <v>16.7816</v>
+        <v>16.4318</v>
       </c>
     </row>
     <row r="276">
@@ -15229,10 +15229,10 @@
         <v>1.18</v>
       </c>
       <c r="I276" t="n">
-        <v>0.4682</v>
+        <v>0.4381</v>
       </c>
       <c r="J276" t="n">
-        <v>10.3004</v>
+        <v>9.638199999999999</v>
       </c>
     </row>
     <row r="277">
@@ -15269,10 +15269,10 @@
         <v>0.86</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.1689</v>
+        <v>-0.1532</v>
       </c>
       <c r="J277" t="n">
-        <v>-3.7158</v>
+        <v>-3.3704</v>
       </c>
     </row>
     <row r="278">
@@ -15309,10 +15309,10 @@
         <v>0.84</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.1904</v>
+        <v>-0.1745</v>
       </c>
       <c r="J278" t="n">
-        <v>-4.1888</v>
+        <v>-3.839</v>
       </c>
     </row>
     <row r="279">
@@ -15349,10 +15349,10 @@
         <v>0.82</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.2111</v>
+        <v>-0.1951</v>
       </c>
       <c r="J279" t="n">
-        <v>-4.6442</v>
+        <v>-4.2922</v>
       </c>
     </row>
     <row r="280">
@@ -15389,10 +15389,10 @@
         <v>0.65</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3687</v>
+        <v>-0.3552</v>
       </c>
       <c r="J280" t="n">
-        <v>-8.1114</v>
+        <v>-7.8144</v>
       </c>
     </row>
     <row r="281">
@@ -15429,10 +15429,10 @@
         <v>0.64</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3777</v>
+        <v>-0.3647</v>
       </c>
       <c r="J281" t="n">
-        <v>-8.3094</v>
+        <v>-8.023400000000001</v>
       </c>
     </row>
     <row r="282">
@@ -15469,10 +15469,10 @@
         <v>1.09</v>
       </c>
       <c r="I282" t="n">
-        <v>0.2706</v>
+        <v>0.2249</v>
       </c>
       <c r="J282" t="n">
-        <v>7.0356</v>
+        <v>5.8474</v>
       </c>
     </row>
     <row r="283">
@@ -15509,10 +15509,10 @@
         <v>0.9</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.135</v>
+        <v>-0.1191</v>
       </c>
       <c r="J283" t="n">
-        <v>-3.51</v>
+        <v>-3.0966</v>
       </c>
     </row>
     <row r="284">
@@ -15549,10 +15549,10 @@
         <v>0.78</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.2572</v>
+        <v>-0.2385</v>
       </c>
       <c r="J284" t="n">
-        <v>-6.6872</v>
+        <v>-6.201</v>
       </c>
     </row>
     <row r="285">
@@ -15589,10 +15589,10 @@
         <v>0.77</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2668</v>
+        <v>-0.2482</v>
       </c>
       <c r="J285" t="n">
-        <v>-6.9368</v>
+        <v>-6.4532</v>
       </c>
     </row>
     <row r="286">
@@ -15629,10 +15629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3418</v>
+        <v>-0.3261</v>
       </c>
       <c r="J286" t="n">
-        <v>-8.886799999999999</v>
+        <v>-8.4786</v>
       </c>
     </row>
     <row r="287">
@@ -15669,10 +15669,10 @@
         <v>1.82</v>
       </c>
       <c r="I287" t="n">
-        <v>1.4849</v>
+        <v>1.5156</v>
       </c>
       <c r="J287" t="n">
-        <v>38.6074</v>
+        <v>39.4056</v>
       </c>
     </row>
     <row r="288">
@@ -15709,10 +15709,10 @@
         <v>1.35</v>
       </c>
       <c r="I288" t="n">
-        <v>0.8293</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="J288" t="n">
-        <v>21.5618</v>
+        <v>21.164</v>
       </c>
     </row>
     <row r="289">
@@ -15749,10 +15749,10 @@
         <v>1.27</v>
       </c>
       <c r="I289" t="n">
-        <v>0.6734</v>
+        <v>0.65</v>
       </c>
       <c r="J289" t="n">
-        <v>17.5084</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="290">
@@ -15789,10 +15789,10 @@
         <v>1.26</v>
       </c>
       <c r="I290" t="n">
-        <v>0.6528</v>
+        <v>0.6286</v>
       </c>
       <c r="J290" t="n">
-        <v>16.9728</v>
+        <v>16.3436</v>
       </c>
     </row>
     <row r="291">
@@ -15829,10 +15829,10 @@
         <v>1.06</v>
       </c>
       <c r="I291" t="n">
-        <v>0.1747</v>
+        <v>0.1463</v>
       </c>
       <c r="J291" t="n">
-        <v>4.5422</v>
+        <v>3.8038</v>
       </c>
     </row>
     <row r="292">
@@ -15869,10 +15869,10 @@
         <v>1.51</v>
       </c>
       <c r="I292" t="n">
-        <v>1.0946</v>
+        <v>1.1068</v>
       </c>
       <c r="J292" t="n">
-        <v>27.365</v>
+        <v>27.67</v>
       </c>
     </row>
     <row r="293">
@@ -15909,10 +15909,10 @@
         <v>1.49</v>
       </c>
       <c r="I293" t="n">
-        <v>1.0677</v>
+        <v>1.0775</v>
       </c>
       <c r="J293" t="n">
-        <v>26.6925</v>
+        <v>26.9375</v>
       </c>
     </row>
     <row r="294">
@@ -15949,10 +15949,10 @@
         <v>1.38</v>
       </c>
       <c r="I294" t="n">
-        <v>0.8879</v>
+        <v>0.8749</v>
       </c>
       <c r="J294" t="n">
-        <v>22.1975</v>
+        <v>21.8725</v>
       </c>
     </row>
     <row r="295">
@@ -15989,10 +15989,10 @@
         <v>1.26</v>
       </c>
       <c r="I295" t="n">
-        <v>0.6564</v>
+        <v>0.6313</v>
       </c>
       <c r="J295" t="n">
-        <v>16.41</v>
+        <v>15.7825</v>
       </c>
     </row>
     <row r="296">
@@ -16029,10 +16029,10 @@
         <v>0.99</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.1145</v>
+        <v>-0.0953</v>
       </c>
       <c r="J296" t="n">
-        <v>-2.8625</v>
+        <v>-2.3825</v>
       </c>
     </row>
     <row r="297">
@@ -16069,10 +16069,10 @@
         <v>0.97</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.0272</v>
+        <v>-0.0167</v>
       </c>
       <c r="J297" t="n">
-        <v>-0.68</v>
+        <v>-0.4175</v>
       </c>
     </row>
     <row r="298">
@@ -16109,10 +16109,10 @@
         <v>0.86</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.167</v>
+        <v>-0.1514</v>
       </c>
       <c r="J298" t="n">
-        <v>-4.175</v>
+        <v>-3.785</v>
       </c>
     </row>
     <row r="299">
@@ -16149,10 +16149,10 @@
         <v>0.84</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1887</v>
+        <v>-0.1729</v>
       </c>
       <c r="J299" t="n">
-        <v>-4.7175</v>
+        <v>-4.3225</v>
       </c>
     </row>
     <row r="300">
@@ -16189,10 +16189,10 @@
         <v>0.68</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3402</v>
+        <v>-0.3255</v>
       </c>
       <c r="J300" t="n">
-        <v>-8.505000000000001</v>
+        <v>-8.137499999999999</v>
       </c>
     </row>
     <row r="301">
@@ -16229,10 +16229,10 @@
         <v>0.4</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5864</v>
+        <v>-0.5976</v>
       </c>
       <c r="J301" t="n">
-        <v>-14.66</v>
+        <v>-14.94</v>
       </c>
     </row>
     <row r="302">
@@ -16269,10 +16269,10 @@
         <v>1.22</v>
       </c>
       <c r="I302" t="n">
-        <v>0.5419</v>
+        <v>0.4962</v>
       </c>
       <c r="J302" t="n">
-        <v>11.9218</v>
+        <v>10.9164</v>
       </c>
     </row>
     <row r="303">
@@ -16309,10 +16309,10 @@
         <v>0.74</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.2895</v>
+        <v>-0.2724</v>
       </c>
       <c r="J303" t="n">
-        <v>-6.369</v>
+        <v>-5.9928</v>
       </c>
     </row>
     <row r="304">
@@ -16349,10 +16349,10 @@
         <v>0.72</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.308</v>
+        <v>-0.2914</v>
       </c>
       <c r="J304" t="n">
-        <v>-6.776</v>
+        <v>-6.4108</v>
       </c>
     </row>
     <row r="305">
@@ -16389,10 +16389,10 @@
         <v>0.71</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.3173</v>
+        <v>-0.3009</v>
       </c>
       <c r="J305" t="n">
-        <v>-6.9806</v>
+        <v>-6.6198</v>
       </c>
     </row>
     <row r="306">
@@ -16429,10 +16429,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4522</v>
+        <v>-0.4455</v>
       </c>
       <c r="J306" t="n">
-        <v>-9.948399999999999</v>
+        <v>-9.801</v>
       </c>
     </row>
     <row r="307">
@@ -16469,10 +16469,10 @@
         <v>1.5</v>
       </c>
       <c r="I307" t="n">
-        <v>1.087</v>
+        <v>1.0979</v>
       </c>
       <c r="J307" t="n">
-        <v>23.914</v>
+        <v>24.1538</v>
       </c>
     </row>
     <row r="308">
@@ -16509,10 +16509,10 @@
         <v>1.45</v>
       </c>
       <c r="I308" t="n">
-        <v>1.0152</v>
+        <v>1.0167</v>
       </c>
       <c r="J308" t="n">
-        <v>22.3344</v>
+        <v>22.3674</v>
       </c>
     </row>
     <row r="309">
@@ -16549,10 +16549,10 @@
         <v>1.3</v>
       </c>
       <c r="I309" t="n">
-        <v>0.7396</v>
+        <v>0.7163</v>
       </c>
       <c r="J309" t="n">
-        <v>16.2712</v>
+        <v>15.7586</v>
       </c>
     </row>
     <row r="310">
@@ -16589,10 +16589,10 @@
         <v>1.21</v>
       </c>
       <c r="I310" t="n">
-        <v>0.5558</v>
+        <v>0.5261</v>
       </c>
       <c r="J310" t="n">
-        <v>12.2276</v>
+        <v>11.5742</v>
       </c>
     </row>
     <row r="311">
@@ -16629,10 +16629,10 @@
         <v>0.99</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.1087</v>
+        <v>-0.0888</v>
       </c>
       <c r="J311" t="n">
-        <v>-2.3914</v>
+        <v>-1.9536</v>
       </c>
     </row>
     <row r="312">
@@ -16669,10 +16669,10 @@
         <v>1.09</v>
       </c>
       <c r="I312" t="n">
-        <v>0.3111</v>
+        <v>0.2722</v>
       </c>
       <c r="J312" t="n">
-        <v>6.5331</v>
+        <v>5.7162</v>
       </c>
     </row>
     <row r="313">
@@ -16709,10 +16709,10 @@
         <v>1.04</v>
       </c>
       <c r="I313" t="n">
-        <v>0.1943</v>
+        <v>0.1643</v>
       </c>
       <c r="J313" t="n">
-        <v>4.0803</v>
+        <v>3.4503</v>
       </c>
     </row>
     <row r="314">
@@ -16749,10 +16749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.3305</v>
+        <v>-0.3156</v>
       </c>
       <c r="J314" t="n">
-        <v>-6.9405</v>
+        <v>-6.6276</v>
       </c>
     </row>
     <row r="315">
@@ -16789,10 +16789,10 @@
         <v>0.47</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.5255</v>
+        <v>-0.5274</v>
       </c>
       <c r="J315" t="n">
-        <v>-11.0355</v>
+        <v>-11.0754</v>
       </c>
     </row>
     <row r="316">
@@ -16829,10 +16829,10 @@
         <v>0.43</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="J316" t="n">
-        <v>-11.76</v>
+        <v>-11.907</v>
       </c>
     </row>
     <row r="317">
@@ -16869,10 +16869,10 @@
         <v>1.87</v>
       </c>
       <c r="I317" t="n">
-        <v>1.5185</v>
+        <v>1.5513</v>
       </c>
       <c r="J317" t="n">
-        <v>31.8885</v>
+        <v>32.5773</v>
       </c>
     </row>
     <row r="318">
@@ -16909,10 +16909,10 @@
         <v>1.58</v>
       </c>
       <c r="I318" t="n">
-        <v>1.1646</v>
+        <v>1.1825</v>
       </c>
       <c r="J318" t="n">
-        <v>24.4566</v>
+        <v>24.8325</v>
       </c>
     </row>
     <row r="319">
@@ -16949,10 +16949,10 @@
         <v>1.37</v>
       </c>
       <c r="I319" t="n">
-        <v>0.8517</v>
+        <v>0.8437</v>
       </c>
       <c r="J319" t="n">
-        <v>17.8857</v>
+        <v>17.7177</v>
       </c>
     </row>
     <row r="320">
@@ -16989,10 +16989,10 @@
         <v>1.37</v>
       </c>
       <c r="I320" t="n">
-        <v>0.8517</v>
+        <v>0.8437</v>
       </c>
       <c r="J320" t="n">
-        <v>17.8857</v>
+        <v>17.7177</v>
       </c>
     </row>
     <row r="321">
@@ -17029,10 +17029,10 @@
         <v>1.24</v>
       </c>
       <c r="I321" t="n">
-        <v>0.5918</v>
+        <v>0.5671</v>
       </c>
       <c r="J321" t="n">
-        <v>12.4278</v>
+        <v>11.9091</v>
       </c>
     </row>
     <row r="322">
@@ -17069,10 +17069,10 @@
         <v>1.19</v>
       </c>
       <c r="I322" t="n">
-        <v>0.4731</v>
+        <v>0.4227</v>
       </c>
       <c r="J322" t="n">
-        <v>11.8275</v>
+        <v>10.5675</v>
       </c>
     </row>
     <row r="323">
@@ -17109,10 +17109,10 @@
         <v>1.19</v>
       </c>
       <c r="I323" t="n">
-        <v>0.4731</v>
+        <v>0.4227</v>
       </c>
       <c r="J323" t="n">
-        <v>11.8275</v>
+        <v>10.5675</v>
       </c>
     </row>
     <row r="324">
@@ -17149,10 +17149,10 @@
         <v>0.82</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.2166</v>
+        <v>-0.1987</v>
       </c>
       <c r="J324" t="n">
-        <v>-5.415</v>
+        <v>-4.9675</v>
       </c>
     </row>
     <row r="325">
@@ -17189,10 +17189,10 @@
         <v>0.55</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.4644</v>
+        <v>-0.4594</v>
       </c>
       <c r="J325" t="n">
-        <v>-11.61</v>
+        <v>-11.485</v>
       </c>
     </row>
     <row r="326">
@@ -17229,10 +17229,10 @@
         <v>0.36</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.6267</v>
+        <v>-0.6461</v>
       </c>
       <c r="J326" t="n">
-        <v>-15.6675</v>
+        <v>-16.1525</v>
       </c>
     </row>
     <row r="327">
@@ -17269,10 +17269,10 @@
         <v>1.74</v>
       </c>
       <c r="I327" t="n">
-        <v>1.4083</v>
+        <v>1.435</v>
       </c>
       <c r="J327" t="n">
-        <v>35.2075</v>
+        <v>35.875</v>
       </c>
     </row>
     <row r="328">
@@ -17309,10 +17309,10 @@
         <v>1.34</v>
       </c>
       <c r="I328" t="n">
-        <v>0.8226</v>
+        <v>0.8018</v>
       </c>
       <c r="J328" t="n">
-        <v>20.565</v>
+        <v>20.045</v>
       </c>
     </row>
     <row r="329">
@@ -17349,10 +17349,10 @@
         <v>1.12</v>
       </c>
       <c r="I329" t="n">
-        <v>0.3526</v>
+        <v>0.32</v>
       </c>
       <c r="J329" t="n">
-        <v>8.815</v>
+        <v>8</v>
       </c>
     </row>
     <row r="330">
@@ -17389,10 +17389,10 @@
         <v>1.04</v>
       </c>
       <c r="I330" t="n">
-        <v>0.1286</v>
+        <v>0.105</v>
       </c>
       <c r="J330" t="n">
-        <v>3.215</v>
+        <v>2.625</v>
       </c>
     </row>
     <row r="331">
@@ -17429,10 +17429,10 @@
         <v>1.03</v>
       </c>
       <c r="I331" t="n">
-        <v>0.0949</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="J331" t="n">
-        <v>2.3725</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="332">
@@ -17469,10 +17469,10 @@
         <v>0.98</v>
       </c>
       <c r="I332" t="n">
-        <v>-0.0075</v>
+        <v>0.003</v>
       </c>
       <c r="J332" t="n">
-        <v>-0.15</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="333">
@@ -17509,10 +17509,10 @@
         <v>0.78</v>
       </c>
       <c r="I333" t="n">
-        <v>-0.2477</v>
+        <v>-0.2323</v>
       </c>
       <c r="J333" t="n">
-        <v>-4.954</v>
+        <v>-4.646</v>
       </c>
     </row>
     <row r="334">
@@ -17549,10 +17549,10 @@
         <v>0.75</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.276</v>
+        <v>-0.2606</v>
       </c>
       <c r="J334" t="n">
-        <v>-5.52</v>
+        <v>-5.212</v>
       </c>
     </row>
     <row r="335">
@@ -17589,10 +17589,10 @@
         <v>0.72</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.3026</v>
+        <v>-0.2874</v>
       </c>
       <c r="J335" t="n">
-        <v>-6.052</v>
+        <v>-5.748</v>
       </c>
     </row>
     <row r="336">
@@ -17629,10 +17629,10 @@
         <v>0.45</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.5419</v>
+        <v>-0.546</v>
       </c>
       <c r="J336" t="n">
-        <v>-10.838</v>
+        <v>-10.92</v>
       </c>
     </row>
     <row r="337">
@@ -17669,10 +17669,10 @@
         <v>1.69</v>
       </c>
       <c r="I337" t="n">
-        <v>1.3299</v>
+        <v>1.3507</v>
       </c>
       <c r="J337" t="n">
-        <v>26.598</v>
+        <v>27.014</v>
       </c>
     </row>
     <row r="338">
@@ -17709,10 +17709,10 @@
         <v>1.28</v>
       </c>
       <c r="I338" t="n">
-        <v>0.6979</v>
+        <v>0.6742</v>
       </c>
       <c r="J338" t="n">
-        <v>13.958</v>
+        <v>13.484</v>
       </c>
     </row>
     <row r="339">
@@ -17749,10 +17749,10 @@
         <v>1.27</v>
       </c>
       <c r="I339" t="n">
-        <v>0.6778</v>
+        <v>0.6532</v>
       </c>
       <c r="J339" t="n">
-        <v>13.556</v>
+        <v>13.064</v>
       </c>
     </row>
     <row r="340">
@@ -17789,10 +17789,10 @@
         <v>1.2</v>
       </c>
       <c r="I340" t="n">
-        <v>0.5299</v>
+        <v>0.5002</v>
       </c>
       <c r="J340" t="n">
-        <v>10.598</v>
+        <v>10.004</v>
       </c>
     </row>
     <row r="341">
@@ -17829,10 +17829,10 @@
         <v>1.15</v>
       </c>
       <c r="I341" t="n">
-        <v>0.4155</v>
+        <v>0.3838</v>
       </c>
       <c r="J341" t="n">
-        <v>8.31</v>
+        <v>7.676</v>
       </c>
     </row>
     <row r="342">
@@ -17869,10 +17869,10 @@
         <v>1.22</v>
       </c>
       <c r="I342" t="n">
-        <v>0.469</v>
+        <v>0.4106</v>
       </c>
       <c r="J342" t="n">
-        <v>13.132</v>
+        <v>11.4968</v>
       </c>
     </row>
     <row r="343">
@@ -17909,10 +17909,10 @@
         <v>1.2</v>
       </c>
       <c r="I343" t="n">
-        <v>0.4351</v>
+        <v>0.3776</v>
       </c>
       <c r="J343" t="n">
-        <v>12.1828</v>
+        <v>10.5728</v>
       </c>
     </row>
     <row r="344">
@@ -17949,10 +17949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.0985</v>
+        <v>-0.0818</v>
       </c>
       <c r="J344" t="n">
-        <v>-2.758</v>
+        <v>-2.2904</v>
       </c>
     </row>
     <row r="345">
@@ -17989,10 +17989,10 @@
         <v>0.87</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.1797</v>
+        <v>-0.1592</v>
       </c>
       <c r="J345" t="n">
-        <v>-5.0316</v>
+        <v>-4.4576</v>
       </c>
     </row>
     <row r="346">
@@ -18029,10 +18029,10 @@
         <v>0.74</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.3099</v>
+        <v>-0.2925</v>
       </c>
       <c r="J346" t="n">
-        <v>-8.677199999999999</v>
+        <v>-8.19</v>
       </c>
     </row>
     <row r="347">
@@ -18069,10 +18069,10 @@
         <v>1.81</v>
       </c>
       <c r="I347" t="n">
-        <v>1.502</v>
+        <v>1.5368</v>
       </c>
       <c r="J347" t="n">
-        <v>42.056</v>
+        <v>43.0304</v>
       </c>
     </row>
     <row r="348">
@@ -18109,10 +18109,10 @@
         <v>1.32</v>
       </c>
       <c r="I348" t="n">
-        <v>0.7864</v>
+        <v>0.7627</v>
       </c>
       <c r="J348" t="n">
-        <v>22.0192</v>
+        <v>21.3556</v>
       </c>
     </row>
     <row r="349">
@@ -18149,10 +18149,10 @@
         <v>1.27</v>
       </c>
       <c r="I349" t="n">
-        <v>0.6863</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="J349" t="n">
-        <v>19.2164</v>
+        <v>18.4184</v>
       </c>
     </row>
     <row r="350">
@@ -18189,10 +18189,10 @@
         <v>0.93</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.3034</v>
+        <v>-0.2646</v>
       </c>
       <c r="J350" t="n">
-        <v>-8.495200000000001</v>
+        <v>-7.4088</v>
       </c>
     </row>
     <row r="351">
@@ -18229,10 +18229,10 @@
         <v>0.85</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.5133</v>
+        <v>-0.4752</v>
       </c>
       <c r="J351" t="n">
-        <v>-14.3724</v>
+        <v>-13.3056</v>
       </c>
     </row>
     <row r="352">
@@ -18269,10 +18269,10 @@
         <v>1.17</v>
       </c>
       <c r="I352" t="n">
-        <v>0.5087</v>
+        <v>0.467</v>
       </c>
       <c r="J352" t="n">
-        <v>15.261</v>
+        <v>14.01</v>
       </c>
     </row>
     <row r="353">
@@ -18309,10 +18309,10 @@
         <v>1.11</v>
       </c>
       <c r="I353" t="n">
-        <v>0.3612</v>
+        <v>0.3196</v>
       </c>
       <c r="J353" t="n">
-        <v>10.836</v>
+        <v>9.587999999999999</v>
       </c>
     </row>
     <row r="354">
@@ -18349,10 +18349,10 @@
         <v>1</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.0038</v>
+        <v>-0.002</v>
       </c>
       <c r="J354" t="n">
-        <v>-0.114</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="355">
@@ -18389,10 +18389,10 @@
         <v>0.98</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.1042</v>
+        <v>-0.0796</v>
       </c>
       <c r="J355" t="n">
-        <v>-3.126</v>
+        <v>-2.388</v>
       </c>
     </row>
     <row r="356">
@@ -18429,10 +18429,10 @@
         <v>0.89</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.3743</v>
+        <v>-0.3314</v>
       </c>
       <c r="J356" t="n">
-        <v>-11.229</v>
+        <v>-9.942</v>
       </c>
     </row>
     <row r="357">
@@ -18469,10 +18469,10 @@
         <v>1.22</v>
       </c>
       <c r="I357" t="n">
-        <v>0.4601</v>
+        <v>0.4017</v>
       </c>
       <c r="J357" t="n">
-        <v>13.803</v>
+        <v>12.051</v>
       </c>
     </row>
     <row r="358">
@@ -18509,10 +18509,10 @@
         <v>1.19</v>
       </c>
       <c r="I358" t="n">
-        <v>0.4097</v>
+        <v>0.353</v>
       </c>
       <c r="J358" t="n">
-        <v>12.291</v>
+        <v>10.59</v>
       </c>
     </row>
     <row r="359">
@@ -18549,10 +18549,10 @@
         <v>0.96</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.07489999999999999</v>
+        <v>-0.06</v>
       </c>
       <c r="J359" t="n">
-        <v>-2.247</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="360">
@@ -18589,10 +18589,10 @@
         <v>0.95</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.0886</v>
+        <v>-0.0723</v>
       </c>
       <c r="J360" t="n">
-        <v>-2.658</v>
+        <v>-2.169</v>
       </c>
     </row>
     <row r="361">
@@ -18629,10 +18629,10 @@
         <v>0.84</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.2148</v>
+        <v>-0.1942</v>
       </c>
       <c r="J361" t="n">
-        <v>-6.444</v>
+        <v>-5.826</v>
       </c>
     </row>
     <row r="362">
@@ -18669,10 +18669,10 @@
         <v>1.14</v>
       </c>
       <c r="I362" t="n">
-        <v>0.331</v>
+        <v>0.2782</v>
       </c>
       <c r="J362" t="n">
-        <v>9.93</v>
+        <v>8.346</v>
       </c>
     </row>
     <row r="363">
@@ -18709,10 +18709,10 @@
         <v>1.06</v>
       </c>
       <c r="I363" t="n">
-        <v>0.1724</v>
+        <v>0.1346</v>
       </c>
       <c r="J363" t="n">
-        <v>5.172</v>
+        <v>4.038</v>
       </c>
     </row>
     <row r="364">
@@ -18749,10 +18749,10 @@
         <v>1.04</v>
       </c>
       <c r="I364" t="n">
-        <v>0.1266</v>
+        <v>0.0955</v>
       </c>
       <c r="J364" t="n">
-        <v>3.798</v>
+        <v>2.865</v>
       </c>
     </row>
     <row r="365">
@@ -18789,10 +18789,10 @@
         <v>0.98</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.0419</v>
+        <v>-0.032</v>
       </c>
       <c r="J365" t="n">
-        <v>-1.257</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="366">
@@ -18829,10 +18829,10 @@
         <v>0.71</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.3372</v>
+        <v>-0.3215</v>
       </c>
       <c r="J366" t="n">
-        <v>-10.116</v>
+        <v>-9.645</v>
       </c>
     </row>
     <row r="367">
@@ -18869,10 +18869,10 @@
         <v>1.82</v>
       </c>
       <c r="I367" t="n">
-        <v>1.5366</v>
+        <v>1.5782</v>
       </c>
       <c r="J367" t="n">
-        <v>46.098</v>
+        <v>47.346</v>
       </c>
     </row>
     <row r="368">
@@ -18909,10 +18909,10 @@
         <v>1.37</v>
       </c>
       <c r="I368" t="n">
-        <v>0.9003</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="J368" t="n">
-        <v>27.009</v>
+        <v>26.478</v>
       </c>
     </row>
     <row r="369">
@@ -18949,10 +18949,10 @@
         <v>0.92</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.3195</v>
+        <v>-0.2786</v>
       </c>
       <c r="J369" t="n">
-        <v>-9.585000000000001</v>
+        <v>-8.358000000000001</v>
       </c>
     </row>
     <row r="370">
@@ -18989,10 +18989,10 @@
         <v>0.88</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.4263</v>
+        <v>-0.3846</v>
       </c>
       <c r="J370" t="n">
-        <v>-12.789</v>
+        <v>-11.538</v>
       </c>
     </row>
     <row r="371">
@@ -19029,10 +19029,10 @@
         <v>0.84</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.5255</v>
+        <v>-0.4861</v>
       </c>
       <c r="J371" t="n">
-        <v>-15.765</v>
+        <v>-14.583</v>
       </c>
     </row>
     <row r="372">
@@ -19069,10 +19069,10 @@
         <v>1.84</v>
       </c>
       <c r="I372" t="n">
-        <v>1.4838</v>
+        <v>1.5143</v>
       </c>
       <c r="J372" t="n">
-        <v>31.1598</v>
+        <v>31.8003</v>
       </c>
     </row>
     <row r="373">
@@ -19109,10 +19109,10 @@
         <v>1.65</v>
       </c>
       <c r="I373" t="n">
-        <v>1.2527</v>
+        <v>1.2723</v>
       </c>
       <c r="J373" t="n">
-        <v>26.3067</v>
+        <v>26.7183</v>
       </c>
     </row>
     <row r="374">
@@ -19149,10 +19149,10 @@
         <v>1.41</v>
       </c>
       <c r="I374" t="n">
-        <v>0.9264</v>
+        <v>0.9243</v>
       </c>
       <c r="J374" t="n">
-        <v>19.4544</v>
+        <v>19.4103</v>
       </c>
     </row>
     <row r="375">
@@ -19189,10 +19189,10 @@
         <v>1.3</v>
       </c>
       <c r="I375" t="n">
-        <v>0.7163</v>
+        <v>0.6987</v>
       </c>
       <c r="J375" t="n">
-        <v>15.0423</v>
+        <v>14.6727</v>
       </c>
     </row>
     <row r="376">
@@ -19229,10 +19229,10 @@
         <v>1.2</v>
       </c>
       <c r="I376" t="n">
-        <v>0.5059</v>
+        <v>0.4772</v>
       </c>
       <c r="J376" t="n">
-        <v>10.6239</v>
+        <v>10.0212</v>
       </c>
     </row>
     <row r="377">
@@ -19269,10 +19269,10 @@
         <v>1.02</v>
       </c>
       <c r="I377" t="n">
-        <v>0.1472</v>
+        <v>0.1259</v>
       </c>
       <c r="J377" t="n">
-        <v>3.0912</v>
+        <v>2.6439</v>
       </c>
     </row>
     <row r="378">
@@ -19309,10 +19309,10 @@
         <v>0.91</v>
       </c>
       <c r="I378" t="n">
-        <v>-0.1044</v>
+        <v>-0.0892</v>
       </c>
       <c r="J378" t="n">
-        <v>-2.1924</v>
+        <v>-1.8732</v>
       </c>
     </row>
     <row r="379">
@@ -19349,10 +19349,10 @@
         <v>0.77</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.2561</v>
+        <v>-0.241</v>
       </c>
       <c r="J379" t="n">
-        <v>-5.3781</v>
+        <v>-5.061</v>
       </c>
     </row>
     <row r="380">
@@ -19389,10 +19389,10 @@
         <v>0.57</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.4357</v>
+        <v>-0.4273</v>
       </c>
       <c r="J380" t="n">
-        <v>-9.149699999999999</v>
+        <v>-8.9733</v>
       </c>
     </row>
     <row r="381">
@@ -19429,10 +19429,10 @@
         <v>0.36</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.6182</v>
+        <v>-0.6345</v>
       </c>
       <c r="J381" t="n">
-        <v>-12.9822</v>
+        <v>-13.3245</v>
       </c>
     </row>
     <row r="382">
@@ -19469,10 +19469,10 @@
         <v>0.99</v>
       </c>
       <c r="I382" t="n">
-        <v>-0.0112</v>
+        <v>-0.0069</v>
       </c>
       <c r="J382" t="n">
-        <v>-0.2688</v>
+        <v>-0.1656</v>
       </c>
     </row>
     <row r="383">
@@ -19509,10 +19509,10 @@
         <v>0.96</v>
       </c>
       <c r="I383" t="n">
-        <v>-0.0602</v>
+        <v>-0.0493</v>
       </c>
       <c r="J383" t="n">
-        <v>-1.4448</v>
+        <v>-1.1832</v>
       </c>
     </row>
     <row r="384">
@@ -19549,10 +19549,10 @@
         <v>0.89</v>
       </c>
       <c r="I384" t="n">
-        <v>-0.1471</v>
+        <v>-0.1304</v>
       </c>
       <c r="J384" t="n">
-        <v>-3.5304</v>
+        <v>-3.1296</v>
       </c>
     </row>
     <row r="385">
@@ -19589,10 +19589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.2288</v>
+        <v>-0.2098</v>
       </c>
       <c r="J385" t="n">
-        <v>-5.4912</v>
+        <v>-5.0352</v>
       </c>
     </row>
     <row r="386">
@@ -19629,10 +19629,10 @@
         <v>0.62</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.406</v>
+        <v>-0.3951</v>
       </c>
       <c r="J386" t="n">
-        <v>-9.744</v>
+        <v>-9.4824</v>
       </c>
     </row>
     <row r="387">
@@ -19669,10 +19669,10 @@
         <v>1.67</v>
       </c>
       <c r="I387" t="n">
-        <v>1.309</v>
+        <v>1.3287</v>
       </c>
       <c r="J387" t="n">
-        <v>31.416</v>
+        <v>31.8888</v>
       </c>
     </row>
     <row r="388">
@@ -19709,10 +19709,10 @@
         <v>1.53</v>
       </c>
       <c r="I388" t="n">
-        <v>1.1262</v>
+        <v>1.139</v>
       </c>
       <c r="J388" t="n">
-        <v>27.0288</v>
+        <v>27.336</v>
       </c>
     </row>
     <row r="389">
@@ -19749,10 +19749,10 @@
         <v>1.15</v>
       </c>
       <c r="I389" t="n">
-        <v>0.4189</v>
+        <v>0.387</v>
       </c>
       <c r="J389" t="n">
-        <v>10.0536</v>
+        <v>9.288</v>
       </c>
     </row>
     <row r="390">
@@ -19789,10 +19789,10 @@
         <v>1.09</v>
       </c>
       <c r="I390" t="n">
-        <v>0.268</v>
+        <v>0.2371</v>
       </c>
       <c r="J390" t="n">
-        <v>6.432</v>
+        <v>5.6904</v>
       </c>
     </row>
     <row r="391">
@@ -19829,10 +19829,10 @@
         <v>1.04</v>
       </c>
       <c r="I391" t="n">
-        <v>0.1216</v>
+        <v>0.0978</v>
       </c>
       <c r="J391" t="n">
-        <v>2.9184</v>
+        <v>2.3472</v>
       </c>
     </row>
     <row r="392">
@@ -19869,10 +19869,10 @@
         <v>1.49</v>
       </c>
       <c r="I392" t="n">
-        <v>1.1127</v>
+        <v>1.1257</v>
       </c>
       <c r="J392" t="n">
-        <v>31.1556</v>
+        <v>31.5196</v>
       </c>
     </row>
     <row r="393">
@@ -19909,10 +19909,10 @@
         <v>1.16</v>
       </c>
       <c r="I393" t="n">
-        <v>0.4681</v>
+        <v>0.4286</v>
       </c>
       <c r="J393" t="n">
-        <v>13.1068</v>
+        <v>12.0008</v>
       </c>
     </row>
     <row r="394">
@@ -19949,10 +19949,10 @@
         <v>1</v>
       </c>
       <c r="I394" t="n">
-        <v>-0.0171</v>
+        <v>-0.0124</v>
       </c>
       <c r="J394" t="n">
-        <v>-0.4788</v>
+        <v>-0.3472</v>
       </c>
     </row>
     <row r="395">
@@ -19989,10 +19989,10 @@
         <v>0.97</v>
       </c>
       <c r="I395" t="n">
-        <v>-0.1548</v>
+        <v>-0.1235</v>
       </c>
       <c r="J395" t="n">
-        <v>-4.3344</v>
+        <v>-3.458</v>
       </c>
     </row>
     <row r="396">
@@ -20029,10 +20029,10 @@
         <v>0.92</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.3087</v>
+        <v>-0.2673</v>
       </c>
       <c r="J396" t="n">
-        <v>-8.643599999999999</v>
+        <v>-7.4844</v>
       </c>
     </row>
     <row r="397">
@@ -20069,10 +20069,10 @@
         <v>1.31</v>
       </c>
       <c r="I397" t="n">
-        <v>0.612</v>
+        <v>0.5532</v>
       </c>
       <c r="J397" t="n">
-        <v>17.136</v>
+        <v>15.4896</v>
       </c>
     </row>
     <row r="398">
@@ -20109,10 +20109,10 @@
         <v>1.17</v>
       </c>
       <c r="I398" t="n">
-        <v>0.3809</v>
+        <v>0.3254</v>
       </c>
       <c r="J398" t="n">
-        <v>10.6652</v>
+        <v>9.1112</v>
       </c>
     </row>
     <row r="399">
@@ -20149,10 +20149,10 @@
         <v>0.97</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.0585</v>
+        <v>-0.0458</v>
       </c>
       <c r="J399" t="n">
-        <v>-1.638</v>
+        <v>-1.2824</v>
       </c>
     </row>
     <row r="400">
@@ -20189,10 +20189,10 @@
         <v>0.86</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.1913</v>
+        <v>-0.1706</v>
       </c>
       <c r="J400" t="n">
-        <v>-5.3564</v>
+        <v>-4.7768</v>
       </c>
     </row>
     <row r="401">
@@ -20229,10 +20229,10 @@
         <v>0.71</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.3388</v>
+        <v>-0.3234</v>
       </c>
       <c r="J401" t="n">
-        <v>-9.4864</v>
+        <v>-9.055199999999999</v>
       </c>
     </row>
     <row r="402">
@@ -20269,10 +20269,10 @@
         <v>1.03</v>
       </c>
       <c r="I402" t="n">
-        <v>0.1262</v>
+        <v>0.0958</v>
       </c>
       <c r="J402" t="n">
-        <v>3.4074</v>
+        <v>2.5866</v>
       </c>
     </row>
     <row r="403">
@@ -20309,10 +20309,10 @@
         <v>0.96</v>
       </c>
       <c r="I403" t="n">
-        <v>-0.0617</v>
+        <v>-0.0507</v>
       </c>
       <c r="J403" t="n">
-        <v>-1.6659</v>
+        <v>-1.3689</v>
       </c>
     </row>
     <row r="404">
@@ -20349,10 +20349,10 @@
         <v>0.8</v>
       </c>
       <c r="I404" t="n">
-        <v>-0.2397</v>
+        <v>-0.2205</v>
       </c>
       <c r="J404" t="n">
-        <v>-6.4719</v>
+        <v>-5.9535</v>
       </c>
     </row>
     <row r="405">
@@ -20389,10 +20389,10 @@
         <v>0.79</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.2495</v>
+        <v>-0.2303</v>
       </c>
       <c r="J405" t="n">
-        <v>-6.7365</v>
+        <v>-6.2181</v>
       </c>
     </row>
     <row r="406">
@@ -20429,10 +20429,10 @@
         <v>0.75</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.2879</v>
+        <v>-0.2696</v>
       </c>
       <c r="J406" t="n">
-        <v>-7.7733</v>
+        <v>-7.2792</v>
       </c>
     </row>
     <row r="407">
@@ -20469,10 +20469,10 @@
         <v>1.4</v>
       </c>
       <c r="I407" t="n">
-        <v>0.9434</v>
+        <v>0.9319</v>
       </c>
       <c r="J407" t="n">
-        <v>25.4718</v>
+        <v>25.1613</v>
       </c>
     </row>
     <row r="408">
@@ -20509,10 +20509,10 @@
         <v>1.38</v>
       </c>
       <c r="I408" t="n">
-        <v>0.906</v>
+        <v>0.8902</v>
       </c>
       <c r="J408" t="n">
-        <v>24.462</v>
+        <v>24.0354</v>
       </c>
     </row>
     <row r="409">
@@ -20549,10 +20549,10 @@
         <v>1.19</v>
       </c>
       <c r="I409" t="n">
-        <v>0.5211</v>
+        <v>0.4879</v>
       </c>
       <c r="J409" t="n">
-        <v>14.0697</v>
+        <v>13.1733</v>
       </c>
     </row>
     <row r="410">
@@ -20589,10 +20589,10 @@
         <v>1.1</v>
       </c>
       <c r="I410" t="n">
-        <v>0.3063</v>
+        <v>0.2741</v>
       </c>
       <c r="J410" t="n">
-        <v>8.270099999999999</v>
+        <v>7.4007</v>
       </c>
     </row>
     <row r="411">
@@ -20629,10 +20629,10 @@
         <v>1.05</v>
       </c>
       <c r="I411" t="n">
-        <v>0.1654</v>
+        <v>0.1394</v>
       </c>
       <c r="J411" t="n">
-        <v>4.4658</v>
+        <v>3.7638</v>
       </c>
     </row>
     <row r="412">
@@ -20669,10 +20669,10 @@
         <v>1.97</v>
       </c>
       <c r="I412" t="n">
-        <v>1.6511</v>
+        <v>1.6951</v>
       </c>
       <c r="J412" t="n">
-        <v>34.6731</v>
+        <v>35.5971</v>
       </c>
     </row>
     <row r="413">
@@ -20709,10 +20709,10 @@
         <v>1.5</v>
       </c>
       <c r="I413" t="n">
-        <v>1.0695</v>
+        <v>1.0823</v>
       </c>
       <c r="J413" t="n">
-        <v>22.4595</v>
+        <v>22.7283</v>
       </c>
     </row>
     <row r="414">
@@ -20749,10 +20749,10 @@
         <v>1.35</v>
       </c>
       <c r="I414" t="n">
-        <v>0.8226</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J414" t="n">
-        <v>17.2746</v>
+        <v>17.01</v>
       </c>
     </row>
     <row r="415">
@@ -20789,10 +20789,10 @@
         <v>1.21</v>
       </c>
       <c r="I415" t="n">
-        <v>0.5373</v>
+        <v>0.5095</v>
       </c>
       <c r="J415" t="n">
-        <v>11.2833</v>
+        <v>10.6995</v>
       </c>
     </row>
     <row r="416">
@@ -20829,10 +20829,10 @@
         <v>1.05</v>
       </c>
       <c r="I416" t="n">
-        <v>0.1347</v>
+        <v>0.1068</v>
       </c>
       <c r="J416" t="n">
-        <v>2.8287</v>
+        <v>2.2428</v>
       </c>
     </row>
     <row r="417">
@@ -20869,10 +20869,10 @@
         <v>0.8</v>
       </c>
       <c r="I417" t="n">
-        <v>-0.2027</v>
+        <v>-0.1861</v>
       </c>
       <c r="J417" t="n">
-        <v>-4.2567</v>
+        <v>-3.9081</v>
       </c>
     </row>
     <row r="418">
@@ -20909,10 +20909,10 @@
         <v>0.64</v>
       </c>
       <c r="I418" t="n">
-        <v>-0.3609</v>
+        <v>-0.3517</v>
       </c>
       <c r="J418" t="n">
-        <v>-7.5789</v>
+        <v>-7.3857</v>
       </c>
     </row>
     <row r="419">
@@ -20949,10 +20949,10 @@
         <v>0.61</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.3865</v>
+        <v>-0.3779</v>
       </c>
       <c r="J419" t="n">
-        <v>-8.1165</v>
+        <v>-7.9359</v>
       </c>
     </row>
     <row r="420">
@@ -20989,10 +20989,10 @@
         <v>0.54</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.4465</v>
+        <v>-0.4402</v>
       </c>
       <c r="J420" t="n">
-        <v>-9.3765</v>
+        <v>-9.244199999999999</v>
       </c>
     </row>
     <row r="421">
